--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D53A8F-76B9-42C2-A2A1-9B6CB0B3E253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86802CD0-1F78-494F-90BC-5C846163625D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40905" yWindow="4980" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="87">
   <si>
     <t>Week:</t>
   </si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t>fixing some styles, putting first touches on Fledge Dictonary, About us write up</t>
+  </si>
+  <si>
+    <t>Added CMMC l2 controls to DB</t>
   </si>
 </sst>
 </file>
@@ -1879,10 +1882,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>5535</c:v>
+                  <c:v>5595</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3165</c:v>
+                  <c:v>3105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11885,10 +11888,18 @@
       </c>
     </row>
     <row r="61" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C61" s="24"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
+      <c r="C61" s="32">
+        <v>45977</v>
+      </c>
+      <c r="D61" s="22">
+        <v>60</v>
+      </c>
+      <c r="E61" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61" s="22" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="62" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C62" s="25"/>
@@ -17574,11 +17585,11 @@
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>5535</v>
+        <v>5595</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>3165</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86802CD0-1F78-494F-90BC-5C846163625D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6471E06-29D4-4804-8FDF-BF70E8CFA850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40905" yWindow="4980" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="88">
   <si>
     <t>Week:</t>
   </si>
@@ -302,7 +302,10 @@
     <t>fixing some styles, putting first touches on Fledge Dictonary, About us write up</t>
   </si>
   <si>
-    <t>Added CMMC l2 controls to DB</t>
+    <t>Added CMMC l2 controls to DB, Added assessments criteria to DB (both test and prod)</t>
+  </si>
+  <si>
+    <t>debugged l1 result due to improper init of values</t>
   </si>
 </sst>
 </file>
@@ -1882,10 +1885,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>5595</c:v>
+                  <c:v>5835</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3105</c:v>
+                  <c:v>2865</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11892,7 +11895,7 @@
         <v>45977</v>
       </c>
       <c r="D61" s="22">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="E61" s="22" t="s">
         <v>27</v>
@@ -11902,10 +11905,18 @@
       </c>
     </row>
     <row r="62" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C62" s="25"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
+      <c r="C62" s="33">
+        <v>45977</v>
+      </c>
+      <c r="D62" s="23">
+        <v>90</v>
+      </c>
+      <c r="E62" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62" s="23" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="63" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C63" s="24"/>
@@ -17585,11 +17596,11 @@
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>5595</v>
+        <v>5835</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>3105</v>
+        <v>2865</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6471E06-29D4-4804-8FDF-BF70E8CFA850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC51122-AEEC-49BD-8012-341AB7D3DAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="89">
   <si>
     <t>Week:</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>debugged l1 result due to improper init of values</t>
+  </si>
+  <si>
+    <t>Built out dictionary</t>
   </si>
 </sst>
 </file>
@@ -1885,10 +1888,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>5835</c:v>
+                  <c:v>5910</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2865</c:v>
+                  <c:v>2790</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10598,20 +10601,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P30"/>
-  <sheetFormatPr defaultColWidth="16.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="16.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.33203125" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="16.33203125" customWidth="1"/>
-    <col min="12" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.33203125" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="16.28515625" customWidth="1"/>
+    <col min="12" max="13" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -10646,7 +10649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
@@ -10695,7 +10698,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>4</v>
       </c>
@@ -10718,7 +10721,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="40"/>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -10733,7 +10736,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="36"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="40"/>
       <c r="B5" s="45" t="s">
         <v>4</v>
@@ -10748,7 +10751,7 @@
       <c r="J5" s="3"/>
       <c r="K5" s="36"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>13</v>
       </c>
@@ -10765,7 +10768,7 @@
       <c r="J6" s="3"/>
       <c r="K6" s="36"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="41"/>
       <c r="B7" s="3"/>
       <c r="C7" s="8"/>
@@ -10780,7 +10783,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="36"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="41"/>
       <c r="B8" s="3"/>
       <c r="C8" s="8"/>
@@ -10795,7 +10798,7 @@
       <c r="J8" s="3"/>
       <c r="K8" s="36"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="41"/>
       <c r="B9" s="3"/>
       <c r="C9" s="8"/>
@@ -10810,7 +10813,7 @@
       <c r="J9" s="3"/>
       <c r="K9" s="36"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="43" t="s">
         <v>14</v>
       </c>
@@ -10827,7 +10830,7 @@
       <c r="J10" s="3"/>
       <c r="K10" s="36"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="43"/>
       <c r="B11" s="3"/>
       <c r="C11" s="8"/>
@@ -10842,7 +10845,7 @@
       <c r="J11" s="3"/>
       <c r="K11" s="36"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="43"/>
       <c r="B12" s="3"/>
       <c r="C12" s="8"/>
@@ -10857,7 +10860,7 @@
       <c r="J12" s="3"/>
       <c r="K12" s="36"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="43"/>
       <c r="B13" s="3"/>
       <c r="C13" s="8"/>
@@ -10872,7 +10875,7 @@
       <c r="J13" s="3"/>
       <c r="K13" s="36"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="43"/>
       <c r="B14" s="3"/>
       <c r="C14" s="8"/>
@@ -10887,7 +10890,7 @@
       <c r="J14" s="3"/>
       <c r="K14" s="36"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="29"/>
       <c r="B15" s="3"/>
       <c r="C15" s="8"/>
@@ -10902,7 +10905,7 @@
       <c r="J15" s="38"/>
       <c r="K15" s="36"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="30" t="s">
         <v>15</v>
       </c>
@@ -10919,7 +10922,7 @@
       <c r="J16" s="42"/>
       <c r="K16" s="37"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="34" t="s">
         <v>36</v>
       </c>
@@ -10927,7 +10930,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="35" t="s">
         <v>29</v>
       </c>
@@ -10935,7 +10938,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
         <v>4</v>
       </c>
@@ -10943,12 +10946,12 @@
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="35" t="s">
         <v>5</v>
       </c>
@@ -10956,7 +10959,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="35" t="s">
         <v>6</v>
       </c>
@@ -10964,7 +10967,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
         <v>28</v>
       </c>
@@ -10972,7 +10975,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="35" t="s">
         <v>7</v>
       </c>
@@ -10980,7 +10983,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="35" t="s">
         <v>8</v>
       </c>
@@ -10988,7 +10991,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="35" t="s">
         <v>9</v>
       </c>
@@ -10996,7 +10999,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="35" t="s">
         <v>19</v>
       </c>
@@ -11004,7 +11007,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="35" t="s">
         <v>27</v>
       </c>
@@ -11012,7 +11015,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="35" t="s">
         <v>38</v>
       </c>
@@ -11046,15 +11049,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8154930E-2F36-41CB-8896-D63BC278B832}">
   <dimension ref="C1:F1000"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="21.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" customWidth="1"/>
-    <col min="5" max="5" width="38.5546875" customWidth="1"/>
-    <col min="6" max="6" width="114.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="38.5703125" customWidth="1"/>
+    <col min="6" max="6" width="114.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C1" s="26" t="s">
         <v>22</v>
       </c>
@@ -11068,7 +11071,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C2" s="28">
         <v>45927</v>
       </c>
@@ -11082,7 +11085,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C3" s="32">
         <v>45927</v>
       </c>
@@ -11096,7 +11099,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C4" s="33">
         <v>45928</v>
       </c>
@@ -11110,7 +11113,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C5" s="32">
         <v>45928</v>
       </c>
@@ -11124,7 +11127,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C6" s="33">
         <v>45929</v>
       </c>
@@ -11138,7 +11141,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C7" s="32">
         <v>45934</v>
       </c>
@@ -11152,7 +11155,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C8" s="33">
         <v>45934</v>
       </c>
@@ -11166,7 +11169,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C9" s="32">
         <v>45934</v>
       </c>
@@ -11180,7 +11183,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C10" s="33">
         <v>45935</v>
       </c>
@@ -11194,7 +11197,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C11" s="32">
         <v>45936</v>
       </c>
@@ -11208,7 +11211,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C12" s="33">
         <v>45940</v>
       </c>
@@ -11220,7 +11223,7 @@
       </c>
       <c r="F12" s="23"/>
     </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C13" s="32">
         <v>45941</v>
       </c>
@@ -11232,7 +11235,7 @@
       </c>
       <c r="F13" s="22"/>
     </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C14" s="33">
         <v>45942</v>
       </c>
@@ -11246,7 +11249,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C15" s="32">
         <v>45944</v>
       </c>
@@ -11260,7 +11263,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C16" s="33">
         <v>45944</v>
       </c>
@@ -11274,7 +11277,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C17" s="32">
         <v>45944</v>
       </c>
@@ -11288,7 +11291,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C18" s="33">
         <v>45944</v>
       </c>
@@ -11302,7 +11305,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C19" s="32">
         <v>45944</v>
       </c>
@@ -11316,7 +11319,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="33">
         <v>45945</v>
       </c>
@@ -11330,7 +11333,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="32">
         <v>45945</v>
       </c>
@@ -11344,7 +11347,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="33">
         <v>45945</v>
       </c>
@@ -11358,7 +11361,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C23" s="32">
         <v>45946</v>
       </c>
@@ -11372,7 +11375,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C24" s="33">
         <v>45946</v>
       </c>
@@ -11386,7 +11389,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C25" s="32">
         <v>45946</v>
       </c>
@@ -11400,7 +11403,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C26" s="33">
         <v>45946</v>
       </c>
@@ -11414,7 +11417,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C27" s="32">
         <v>45946</v>
       </c>
@@ -11428,7 +11431,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C28" s="33">
         <v>45946</v>
       </c>
@@ -11442,7 +11445,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C29" s="32">
         <v>45950</v>
       </c>
@@ -11456,7 +11459,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C30" s="33">
         <v>45950</v>
       </c>
@@ -11470,7 +11473,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C31" s="32">
         <v>45950</v>
       </c>
@@ -11484,7 +11487,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C32" s="33">
         <v>45951</v>
       </c>
@@ -11498,7 +11501,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C33" s="32">
         <v>45951</v>
       </c>
@@ -11512,7 +11515,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C34" s="33">
         <v>45955</v>
       </c>
@@ -11526,7 +11529,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C35" s="32">
         <v>45956</v>
       </c>
@@ -11540,7 +11543,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C36" s="33">
         <v>45956</v>
       </c>
@@ -11554,7 +11557,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C37" s="32">
         <v>45957</v>
       </c>
@@ -11568,7 +11571,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C38" s="33">
         <v>45958</v>
       </c>
@@ -11582,7 +11585,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="32">
         <v>45958</v>
       </c>
@@ -11596,7 +11599,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="33">
         <v>45960</v>
       </c>
@@ -11610,7 +11613,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C41" s="32">
         <v>45961</v>
       </c>
@@ -11624,7 +11627,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C42" s="33">
         <v>45962</v>
       </c>
@@ -11638,7 +11641,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C43" s="32">
         <v>45962</v>
       </c>
@@ -11652,7 +11655,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C44" s="33">
         <v>45963</v>
       </c>
@@ -11666,7 +11669,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="45" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C45" s="32">
         <v>45963</v>
       </c>
@@ -11680,7 +11683,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C46" s="33">
         <v>45964</v>
       </c>
@@ -11694,7 +11697,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C47" s="32">
         <v>45964</v>
       </c>
@@ -11708,7 +11711,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="48" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C48" s="33">
         <v>45965</v>
       </c>
@@ -11722,7 +11725,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C49" s="32">
         <v>45965</v>
       </c>
@@ -11736,7 +11739,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C50" s="33">
         <v>45969</v>
       </c>
@@ -11750,7 +11753,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="51" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C51" s="32">
         <v>45970</v>
       </c>
@@ -11764,7 +11767,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C52" s="33">
         <v>45971</v>
       </c>
@@ -11778,7 +11781,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C53" s="32">
         <v>45971</v>
       </c>
@@ -11792,7 +11795,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C54" s="33">
         <v>45972</v>
       </c>
@@ -11806,7 +11809,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C55" s="32">
         <v>45974</v>
       </c>
@@ -11820,7 +11823,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C56" s="33">
         <v>45974</v>
       </c>
@@ -11834,7 +11837,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="57" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C57" s="32">
         <v>45974</v>
       </c>
@@ -11848,7 +11851,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C58" s="33">
         <v>45975</v>
       </c>
@@ -11862,7 +11865,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C59" s="32">
         <v>45976</v>
       </c>
@@ -11876,7 +11879,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C60" s="33">
         <v>45976</v>
       </c>
@@ -11890,7 +11893,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C61" s="32">
         <v>45977</v>
       </c>
@@ -11904,7 +11907,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C62" s="33">
         <v>45977</v>
       </c>
@@ -11918,5629 +11921,5637 @@
         <v>87</v>
       </c>
     </row>
-    <row r="63" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C63" s="24"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-    </row>
-    <row r="64" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C63" s="32">
+        <v>45978</v>
+      </c>
+      <c r="D63" s="22">
+        <v>75</v>
+      </c>
+      <c r="E63" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63" s="22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="64" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C64" s="25"/>
       <c r="D64" s="23"/>
       <c r="E64" s="23"/>
       <c r="F64" s="23"/>
     </row>
-    <row r="65" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C65" s="24"/>
       <c r="D65" s="22"/>
       <c r="E65" s="22"/>
       <c r="F65" s="22"/>
     </row>
-    <row r="66" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C66" s="25"/>
       <c r="D66" s="23"/>
       <c r="E66" s="23"/>
       <c r="F66" s="23"/>
     </row>
-    <row r="67" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C67" s="24"/>
       <c r="D67" s="22"/>
       <c r="E67" s="22"/>
       <c r="F67" s="22"/>
     </row>
-    <row r="68" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C68" s="25"/>
       <c r="D68" s="23"/>
       <c r="E68" s="23"/>
       <c r="F68" s="23"/>
     </row>
-    <row r="69" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C69" s="24"/>
       <c r="D69" s="22"/>
       <c r="E69" s="22"/>
       <c r="F69" s="22"/>
     </row>
-    <row r="70" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C70" s="25"/>
       <c r="D70" s="23"/>
       <c r="E70" s="23"/>
       <c r="F70" s="23"/>
     </row>
-    <row r="71" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C71" s="24"/>
       <c r="D71" s="22"/>
       <c r="E71" s="22"/>
       <c r="F71" s="22"/>
     </row>
-    <row r="72" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C72" s="25"/>
       <c r="D72" s="23"/>
       <c r="E72" s="23"/>
       <c r="F72" s="23"/>
     </row>
-    <row r="73" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C73" s="24"/>
       <c r="D73" s="22"/>
       <c r="E73" s="22"/>
       <c r="F73" s="22"/>
     </row>
-    <row r="74" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C74" s="25"/>
       <c r="D74" s="23"/>
       <c r="E74" s="23"/>
       <c r="F74" s="23"/>
     </row>
-    <row r="75" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C75" s="24"/>
       <c r="D75" s="22"/>
       <c r="E75" s="22"/>
       <c r="F75" s="22"/>
     </row>
-    <row r="76" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C76" s="25"/>
       <c r="D76" s="23"/>
       <c r="E76" s="23"/>
       <c r="F76" s="23"/>
     </row>
-    <row r="77" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C77" s="24"/>
       <c r="D77" s="22"/>
       <c r="E77" s="22"/>
       <c r="F77" s="22"/>
     </row>
-    <row r="78" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C78" s="25"/>
       <c r="D78" s="23"/>
       <c r="E78" s="23"/>
       <c r="F78" s="23"/>
     </row>
-    <row r="79" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C79" s="24"/>
       <c r="D79" s="22"/>
       <c r="E79" s="22"/>
       <c r="F79" s="22"/>
     </row>
-    <row r="80" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C80" s="25"/>
       <c r="D80" s="23"/>
       <c r="E80" s="23"/>
       <c r="F80" s="23"/>
     </row>
-    <row r="81" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C81" s="24"/>
       <c r="D81" s="22"/>
       <c r="E81" s="22"/>
       <c r="F81" s="22"/>
     </row>
-    <row r="82" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C82" s="25"/>
       <c r="D82" s="23"/>
       <c r="E82" s="23"/>
       <c r="F82" s="23"/>
     </row>
-    <row r="83" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C83" s="24"/>
       <c r="D83" s="22"/>
       <c r="E83" s="22"/>
       <c r="F83" s="22"/>
     </row>
-    <row r="84" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C84" s="25"/>
       <c r="D84" s="23"/>
       <c r="E84" s="23"/>
       <c r="F84" s="23"/>
     </row>
-    <row r="85" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C85" s="24"/>
       <c r="D85" s="22"/>
       <c r="E85" s="22"/>
       <c r="F85" s="22"/>
     </row>
-    <row r="86" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C86" s="25"/>
       <c r="D86" s="23"/>
       <c r="E86" s="23"/>
       <c r="F86" s="23"/>
     </row>
-    <row r="87" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C87" s="24"/>
       <c r="D87" s="22"/>
       <c r="E87" s="22"/>
       <c r="F87" s="22"/>
     </row>
-    <row r="88" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C88" s="25"/>
       <c r="D88" s="23"/>
       <c r="E88" s="23"/>
       <c r="F88" s="23"/>
     </row>
-    <row r="89" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C89" s="24"/>
       <c r="D89" s="22"/>
       <c r="E89" s="22"/>
       <c r="F89" s="22"/>
     </row>
-    <row r="90" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C90" s="25"/>
       <c r="D90" s="23"/>
       <c r="E90" s="23"/>
       <c r="F90" s="23"/>
     </row>
-    <row r="91" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C91" s="24"/>
       <c r="D91" s="22"/>
       <c r="E91" s="22"/>
       <c r="F91" s="22"/>
     </row>
-    <row r="92" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C92" s="25"/>
       <c r="D92" s="23"/>
       <c r="E92" s="23"/>
       <c r="F92" s="23"/>
     </row>
-    <row r="93" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C93" s="24"/>
       <c r="D93" s="22"/>
       <c r="E93" s="22"/>
       <c r="F93" s="22"/>
     </row>
-    <row r="94" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C94" s="25"/>
       <c r="D94" s="23"/>
       <c r="E94" s="23"/>
       <c r="F94" s="23"/>
     </row>
-    <row r="95" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C95" s="24"/>
       <c r="D95" s="22"/>
       <c r="E95" s="22"/>
       <c r="F95" s="22"/>
     </row>
-    <row r="96" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C96" s="25"/>
       <c r="D96" s="23"/>
       <c r="E96" s="23"/>
       <c r="F96" s="23"/>
     </row>
-    <row r="97" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C97" s="24"/>
       <c r="D97" s="22"/>
       <c r="E97" s="22"/>
       <c r="F97" s="22"/>
     </row>
-    <row r="98" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C98" s="25"/>
       <c r="D98" s="23"/>
       <c r="E98" s="23"/>
       <c r="F98" s="23"/>
     </row>
-    <row r="99" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C99" s="24"/>
       <c r="D99" s="22"/>
       <c r="E99" s="22"/>
       <c r="F99" s="22"/>
     </row>
-    <row r="100" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C100" s="25"/>
       <c r="D100" s="23"/>
       <c r="E100" s="23"/>
       <c r="F100" s="23"/>
     </row>
-    <row r="101" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C101" s="24"/>
       <c r="D101" s="22"/>
       <c r="E101" s="22"/>
       <c r="F101" s="22"/>
     </row>
-    <row r="102" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C102" s="25"/>
       <c r="D102" s="23"/>
       <c r="E102" s="23"/>
       <c r="F102" s="23"/>
     </row>
-    <row r="103" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C103" s="24"/>
       <c r="D103" s="22"/>
       <c r="E103" s="22"/>
       <c r="F103" s="22"/>
     </row>
-    <row r="104" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C104" s="25"/>
       <c r="D104" s="23"/>
       <c r="E104" s="23"/>
       <c r="F104" s="23"/>
     </row>
-    <row r="105" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C105" s="24"/>
       <c r="D105" s="22"/>
       <c r="E105" s="22"/>
       <c r="F105" s="22"/>
     </row>
-    <row r="106" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C106" s="25"/>
       <c r="D106" s="23"/>
       <c r="E106" s="23"/>
       <c r="F106" s="23"/>
     </row>
-    <row r="107" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C107" s="24"/>
       <c r="D107" s="22"/>
       <c r="E107" s="22"/>
       <c r="F107" s="22"/>
     </row>
-    <row r="108" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C108" s="25"/>
       <c r="D108" s="23"/>
       <c r="E108" s="23"/>
       <c r="F108" s="23"/>
     </row>
-    <row r="109" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C109" s="24"/>
       <c r="D109" s="22"/>
       <c r="E109" s="22"/>
       <c r="F109" s="22"/>
     </row>
-    <row r="110" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C110" s="25"/>
       <c r="D110" s="23"/>
       <c r="E110" s="23"/>
       <c r="F110" s="23"/>
     </row>
-    <row r="111" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C111" s="24"/>
       <c r="D111" s="22"/>
       <c r="E111" s="22"/>
       <c r="F111" s="22"/>
     </row>
-    <row r="112" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C112" s="25"/>
       <c r="D112" s="23"/>
       <c r="E112" s="23"/>
       <c r="F112" s="23"/>
     </row>
-    <row r="113" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C113" s="24"/>
       <c r="D113" s="22"/>
       <c r="E113" s="22"/>
       <c r="F113" s="22"/>
     </row>
-    <row r="114" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C114" s="25"/>
       <c r="D114" s="23"/>
       <c r="E114" s="23"/>
       <c r="F114" s="23"/>
     </row>
-    <row r="115" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C115" s="24"/>
       <c r="D115" s="22"/>
       <c r="E115" s="22"/>
       <c r="F115" s="22"/>
     </row>
-    <row r="116" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C116" s="25"/>
       <c r="D116" s="23"/>
       <c r="E116" s="23"/>
       <c r="F116" s="23"/>
     </row>
-    <row r="117" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C117" s="24"/>
       <c r="D117" s="22"/>
       <c r="E117" s="22"/>
       <c r="F117" s="22"/>
     </row>
-    <row r="118" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C118" s="25"/>
       <c r="D118" s="23"/>
       <c r="E118" s="23"/>
       <c r="F118" s="23"/>
     </row>
-    <row r="119" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C119" s="24"/>
       <c r="D119" s="22"/>
       <c r="E119" s="22"/>
       <c r="F119" s="22"/>
     </row>
-    <row r="120" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C120" s="25"/>
       <c r="D120" s="23"/>
       <c r="E120" s="23"/>
       <c r="F120" s="23"/>
     </row>
-    <row r="121" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C121" s="24"/>
       <c r="D121" s="22"/>
       <c r="E121" s="22"/>
       <c r="F121" s="22"/>
     </row>
-    <row r="122" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C122" s="25"/>
       <c r="D122" s="23"/>
       <c r="E122" s="23"/>
       <c r="F122" s="23"/>
     </row>
-    <row r="123" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C123" s="24"/>
       <c r="D123" s="22"/>
       <c r="E123" s="22"/>
       <c r="F123" s="22"/>
     </row>
-    <row r="124" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C124" s="25"/>
       <c r="D124" s="23"/>
       <c r="E124" s="23"/>
       <c r="F124" s="23"/>
     </row>
-    <row r="125" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C125" s="24"/>
       <c r="D125" s="22"/>
       <c r="E125" s="22"/>
       <c r="F125" s="22"/>
     </row>
-    <row r="126" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C126" s="25"/>
       <c r="D126" s="23"/>
       <c r="E126" s="23"/>
       <c r="F126" s="23"/>
     </row>
-    <row r="127" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C127" s="24"/>
       <c r="D127" s="22"/>
       <c r="E127" s="22"/>
       <c r="F127" s="22"/>
     </row>
-    <row r="128" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C128" s="25"/>
       <c r="D128" s="23"/>
       <c r="E128" s="23"/>
       <c r="F128" s="23"/>
     </row>
-    <row r="129" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C129" s="24"/>
       <c r="D129" s="22"/>
       <c r="E129" s="22"/>
       <c r="F129" s="22"/>
     </row>
-    <row r="130" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C130" s="25"/>
       <c r="D130" s="23"/>
       <c r="E130" s="23"/>
       <c r="F130" s="23"/>
     </row>
-    <row r="131" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C131" s="24"/>
       <c r="D131" s="22"/>
       <c r="E131" s="22"/>
       <c r="F131" s="22"/>
     </row>
-    <row r="132" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C132" s="25"/>
       <c r="D132" s="23"/>
       <c r="E132" s="23"/>
       <c r="F132" s="23"/>
     </row>
-    <row r="133" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C133" s="24"/>
       <c r="D133" s="22"/>
       <c r="E133" s="22"/>
       <c r="F133" s="22"/>
     </row>
-    <row r="134" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C134" s="25"/>
       <c r="D134" s="23"/>
       <c r="E134" s="23"/>
       <c r="F134" s="23"/>
     </row>
-    <row r="135" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C135" s="24"/>
       <c r="D135" s="22"/>
       <c r="E135" s="22"/>
       <c r="F135" s="22"/>
     </row>
-    <row r="136" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C136" s="25"/>
       <c r="D136" s="23"/>
       <c r="E136" s="23"/>
       <c r="F136" s="23"/>
     </row>
-    <row r="137" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C137" s="24"/>
       <c r="D137" s="22"/>
       <c r="E137" s="22"/>
       <c r="F137" s="22"/>
     </row>
-    <row r="138" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C138" s="25"/>
       <c r="D138" s="23"/>
       <c r="E138" s="23"/>
       <c r="F138" s="23"/>
     </row>
-    <row r="139" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C139" s="24"/>
       <c r="D139" s="22"/>
       <c r="E139" s="22"/>
       <c r="F139" s="22"/>
     </row>
-    <row r="140" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C140" s="25"/>
       <c r="D140" s="23"/>
       <c r="E140" s="23"/>
       <c r="F140" s="23"/>
     </row>
-    <row r="141" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C141" s="24"/>
       <c r="D141" s="22"/>
       <c r="E141" s="22"/>
       <c r="F141" s="22"/>
     </row>
-    <row r="142" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C142" s="25"/>
       <c r="D142" s="23"/>
       <c r="E142" s="23"/>
       <c r="F142" s="23"/>
     </row>
-    <row r="143" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C143" s="24"/>
       <c r="D143" s="22"/>
       <c r="E143" s="22"/>
       <c r="F143" s="22"/>
     </row>
-    <row r="144" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C144" s="25"/>
       <c r="D144" s="23"/>
       <c r="E144" s="23"/>
       <c r="F144" s="23"/>
     </row>
-    <row r="145" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C145" s="24"/>
       <c r="D145" s="22"/>
       <c r="E145" s="22"/>
       <c r="F145" s="22"/>
     </row>
-    <row r="146" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C146" s="25"/>
       <c r="D146" s="23"/>
       <c r="E146" s="23"/>
       <c r="F146" s="23"/>
     </row>
-    <row r="147" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C147" s="24"/>
       <c r="D147" s="22"/>
       <c r="E147" s="22"/>
       <c r="F147" s="22"/>
     </row>
-    <row r="148" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C148" s="25"/>
       <c r="D148" s="23"/>
       <c r="E148" s="23"/>
       <c r="F148" s="23"/>
     </row>
-    <row r="149" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C149" s="24"/>
       <c r="D149" s="22"/>
       <c r="E149" s="22"/>
       <c r="F149" s="22"/>
     </row>
-    <row r="150" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C150" s="25"/>
       <c r="D150" s="23"/>
       <c r="E150" s="23"/>
       <c r="F150" s="23"/>
     </row>
-    <row r="151" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C151" s="24"/>
       <c r="D151" s="22"/>
       <c r="E151" s="22"/>
       <c r="F151" s="22"/>
     </row>
-    <row r="152" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C152" s="25"/>
       <c r="D152" s="23"/>
       <c r="E152" s="23"/>
       <c r="F152" s="23"/>
     </row>
-    <row r="153" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C153" s="24"/>
       <c r="D153" s="22"/>
       <c r="E153" s="22"/>
       <c r="F153" s="22"/>
     </row>
-    <row r="154" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C154" s="25"/>
       <c r="D154" s="23"/>
       <c r="E154" s="23"/>
       <c r="F154" s="23"/>
     </row>
-    <row r="155" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C155" s="24"/>
       <c r="D155" s="22"/>
       <c r="E155" s="22"/>
       <c r="F155" s="22"/>
     </row>
-    <row r="156" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C156" s="25"/>
       <c r="D156" s="23"/>
       <c r="E156" s="23"/>
       <c r="F156" s="23"/>
     </row>
-    <row r="157" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C157" s="24"/>
       <c r="D157" s="22"/>
       <c r="E157" s="22"/>
       <c r="F157" s="22"/>
     </row>
-    <row r="158" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C158" s="25"/>
       <c r="D158" s="23"/>
       <c r="E158" s="23"/>
       <c r="F158" s="23"/>
     </row>
-    <row r="159" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C159" s="24"/>
       <c r="D159" s="22"/>
       <c r="E159" s="22"/>
       <c r="F159" s="22"/>
     </row>
-    <row r="160" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C160" s="25"/>
       <c r="D160" s="23"/>
       <c r="E160" s="23"/>
       <c r="F160" s="23"/>
     </row>
-    <row r="161" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C161" s="24"/>
       <c r="D161" s="22"/>
       <c r="E161" s="22"/>
       <c r="F161" s="22"/>
     </row>
-    <row r="162" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C162" s="25"/>
       <c r="D162" s="23"/>
       <c r="E162" s="23"/>
       <c r="F162" s="23"/>
     </row>
-    <row r="163" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C163" s="24"/>
       <c r="D163" s="22"/>
       <c r="E163" s="22"/>
       <c r="F163" s="22"/>
     </row>
-    <row r="164" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C164" s="25"/>
       <c r="D164" s="23"/>
       <c r="E164" s="23"/>
       <c r="F164" s="23"/>
     </row>
-    <row r="165" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C165" s="24"/>
       <c r="D165" s="22"/>
       <c r="E165" s="22"/>
       <c r="F165" s="22"/>
     </row>
-    <row r="166" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C166" s="25"/>
       <c r="D166" s="23"/>
       <c r="E166" s="23"/>
       <c r="F166" s="23"/>
     </row>
-    <row r="167" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C167" s="24"/>
       <c r="D167" s="22"/>
       <c r="E167" s="22"/>
       <c r="F167" s="22"/>
     </row>
-    <row r="168" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C168" s="25"/>
       <c r="D168" s="23"/>
       <c r="E168" s="23"/>
       <c r="F168" s="23"/>
     </row>
-    <row r="169" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C169" s="24"/>
       <c r="D169" s="22"/>
       <c r="E169" s="22"/>
       <c r="F169" s="22"/>
     </row>
-    <row r="170" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C170" s="25"/>
       <c r="D170" s="23"/>
       <c r="E170" s="23"/>
       <c r="F170" s="23"/>
     </row>
-    <row r="171" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C171" s="24"/>
       <c r="D171" s="22"/>
       <c r="E171" s="22"/>
       <c r="F171" s="22"/>
     </row>
-    <row r="172" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C172" s="25"/>
       <c r="D172" s="23"/>
       <c r="E172" s="23"/>
       <c r="F172" s="23"/>
     </row>
-    <row r="173" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C173" s="24"/>
       <c r="D173" s="22"/>
       <c r="E173" s="22"/>
       <c r="F173" s="22"/>
     </row>
-    <row r="174" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C174" s="25"/>
       <c r="D174" s="23"/>
       <c r="E174" s="23"/>
       <c r="F174" s="23"/>
     </row>
-    <row r="175" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C175" s="24"/>
       <c r="D175" s="22"/>
       <c r="E175" s="22"/>
       <c r="F175" s="22"/>
     </row>
-    <row r="176" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C176" s="25"/>
       <c r="D176" s="23"/>
       <c r="E176" s="23"/>
       <c r="F176" s="23"/>
     </row>
-    <row r="177" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C177" s="24"/>
       <c r="D177" s="22"/>
       <c r="E177" s="22"/>
       <c r="F177" s="22"/>
     </row>
-    <row r="178" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C178" s="25"/>
       <c r="D178" s="23"/>
       <c r="E178" s="23"/>
       <c r="F178" s="23"/>
     </row>
-    <row r="179" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C179" s="24"/>
       <c r="D179" s="22"/>
       <c r="E179" s="22"/>
       <c r="F179" s="22"/>
     </row>
-    <row r="180" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C180" s="25"/>
       <c r="D180" s="23"/>
       <c r="E180" s="23"/>
       <c r="F180" s="23"/>
     </row>
-    <row r="181" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C181" s="24"/>
       <c r="D181" s="22"/>
       <c r="E181" s="22"/>
       <c r="F181" s="22"/>
     </row>
-    <row r="182" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C182" s="25"/>
       <c r="D182" s="23"/>
       <c r="E182" s="23"/>
       <c r="F182" s="23"/>
     </row>
-    <row r="183" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C183" s="24"/>
       <c r="D183" s="22"/>
       <c r="E183" s="22"/>
       <c r="F183" s="22"/>
     </row>
-    <row r="184" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C184" s="25"/>
       <c r="D184" s="23"/>
       <c r="E184" s="23"/>
       <c r="F184" s="23"/>
     </row>
-    <row r="185" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C185" s="24"/>
       <c r="D185" s="22"/>
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
     </row>
-    <row r="186" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C186" s="25"/>
       <c r="D186" s="23"/>
       <c r="E186" s="23"/>
       <c r="F186" s="23"/>
     </row>
-    <row r="187" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C187" s="24"/>
       <c r="D187" s="22"/>
       <c r="E187" s="22"/>
       <c r="F187" s="22"/>
     </row>
-    <row r="188" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C188" s="25"/>
       <c r="D188" s="23"/>
       <c r="E188" s="23"/>
       <c r="F188" s="23"/>
     </row>
-    <row r="189" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C189" s="24"/>
       <c r="D189" s="22"/>
       <c r="E189" s="22"/>
       <c r="F189" s="22"/>
     </row>
-    <row r="190" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C190" s="25"/>
       <c r="D190" s="23"/>
       <c r="E190" s="23"/>
       <c r="F190" s="23"/>
     </row>
-    <row r="191" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C191" s="24"/>
       <c r="D191" s="22"/>
       <c r="E191" s="22"/>
       <c r="F191" s="22"/>
     </row>
-    <row r="192" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C192" s="25"/>
       <c r="D192" s="23"/>
       <c r="E192" s="23"/>
       <c r="F192" s="23"/>
     </row>
-    <row r="193" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C193" s="24"/>
       <c r="D193" s="22"/>
       <c r="E193" s="22"/>
       <c r="F193" s="22"/>
     </row>
-    <row r="194" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C194" s="25"/>
       <c r="D194" s="23"/>
       <c r="E194" s="23"/>
       <c r="F194" s="23"/>
     </row>
-    <row r="195" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C195" s="24"/>
       <c r="D195" s="22"/>
       <c r="E195" s="22"/>
       <c r="F195" s="22"/>
     </row>
-    <row r="196" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C196" s="25"/>
       <c r="D196" s="23"/>
       <c r="E196" s="23"/>
       <c r="F196" s="23"/>
     </row>
-    <row r="197" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C197" s="24"/>
       <c r="D197" s="22"/>
       <c r="E197" s="22"/>
       <c r="F197" s="22"/>
     </row>
-    <row r="198" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C198" s="25"/>
       <c r="D198" s="23"/>
       <c r="E198" s="23"/>
       <c r="F198" s="23"/>
     </row>
-    <row r="199" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C199" s="24"/>
       <c r="D199" s="22"/>
       <c r="E199" s="22"/>
       <c r="F199" s="22"/>
     </row>
-    <row r="200" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C200" s="25"/>
       <c r="D200" s="23"/>
       <c r="E200" s="23"/>
       <c r="F200" s="23"/>
     </row>
-    <row r="201" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C201" s="24"/>
       <c r="D201" s="22"/>
       <c r="E201" s="22"/>
       <c r="F201" s="22"/>
     </row>
-    <row r="202" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C202" s="25"/>
       <c r="D202" s="23"/>
       <c r="E202" s="23"/>
       <c r="F202" s="23"/>
     </row>
-    <row r="203" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C203" s="24"/>
       <c r="D203" s="22"/>
       <c r="E203" s="22"/>
       <c r="F203" s="22"/>
     </row>
-    <row r="204" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C204" s="25"/>
       <c r="D204" s="23"/>
       <c r="E204" s="23"/>
       <c r="F204" s="23"/>
     </row>
-    <row r="205" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C205" s="24"/>
       <c r="D205" s="22"/>
       <c r="E205" s="22"/>
       <c r="F205" s="22"/>
     </row>
-    <row r="206" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C206" s="25"/>
       <c r="D206" s="23"/>
       <c r="E206" s="23"/>
       <c r="F206" s="23"/>
     </row>
-    <row r="207" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C207" s="24"/>
       <c r="D207" s="22"/>
       <c r="E207" s="22"/>
       <c r="F207" s="22"/>
     </row>
-    <row r="208" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C208" s="25"/>
       <c r="D208" s="23"/>
       <c r="E208" s="23"/>
       <c r="F208" s="23"/>
     </row>
-    <row r="209" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C209" s="24"/>
       <c r="D209" s="22"/>
       <c r="E209" s="22"/>
       <c r="F209" s="22"/>
     </row>
-    <row r="210" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C210" s="25"/>
       <c r="D210" s="23"/>
       <c r="E210" s="23"/>
       <c r="F210" s="23"/>
     </row>
-    <row r="211" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C211" s="24"/>
       <c r="D211" s="22"/>
       <c r="E211" s="22"/>
       <c r="F211" s="22"/>
     </row>
-    <row r="212" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C212" s="25"/>
       <c r="D212" s="23"/>
       <c r="E212" s="23"/>
       <c r="F212" s="23"/>
     </row>
-    <row r="213" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C213" s="24"/>
       <c r="D213" s="22"/>
       <c r="E213" s="22"/>
       <c r="F213" s="22"/>
     </row>
-    <row r="214" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C214" s="25"/>
       <c r="D214" s="23"/>
       <c r="E214" s="23"/>
       <c r="F214" s="23"/>
     </row>
-    <row r="215" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C215" s="24"/>
       <c r="D215" s="22"/>
       <c r="E215" s="22"/>
       <c r="F215" s="22"/>
     </row>
-    <row r="216" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C216" s="25"/>
       <c r="D216" s="23"/>
       <c r="E216" s="23"/>
       <c r="F216" s="23"/>
     </row>
-    <row r="217" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C217" s="24"/>
       <c r="D217" s="22"/>
       <c r="E217" s="22"/>
       <c r="F217" s="22"/>
     </row>
-    <row r="218" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C218" s="25"/>
       <c r="D218" s="23"/>
       <c r="E218" s="23"/>
       <c r="F218" s="23"/>
     </row>
-    <row r="219" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C219" s="24"/>
       <c r="D219" s="22"/>
       <c r="E219" s="22"/>
       <c r="F219" s="22"/>
     </row>
-    <row r="220" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C220" s="25"/>
       <c r="D220" s="23"/>
       <c r="E220" s="23"/>
       <c r="F220" s="23"/>
     </row>
-    <row r="221" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C221" s="24"/>
       <c r="D221" s="22"/>
       <c r="E221" s="22"/>
       <c r="F221" s="22"/>
     </row>
-    <row r="222" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C222" s="25"/>
       <c r="D222" s="23"/>
       <c r="E222" s="23"/>
       <c r="F222" s="23"/>
     </row>
-    <row r="223" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C223" s="24"/>
       <c r="D223" s="22"/>
       <c r="E223" s="22"/>
       <c r="F223" s="22"/>
     </row>
-    <row r="224" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C224" s="25"/>
       <c r="D224" s="23"/>
       <c r="E224" s="23"/>
       <c r="F224" s="23"/>
     </row>
-    <row r="225" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C225" s="24"/>
       <c r="D225" s="22"/>
       <c r="E225" s="22"/>
       <c r="F225" s="22"/>
     </row>
-    <row r="226" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C226" s="25"/>
       <c r="D226" s="23"/>
       <c r="E226" s="23"/>
       <c r="F226" s="23"/>
     </row>
-    <row r="227" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C227" s="24"/>
       <c r="D227" s="22"/>
       <c r="E227" s="22"/>
       <c r="F227" s="22"/>
     </row>
-    <row r="228" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C228" s="25"/>
       <c r="D228" s="23"/>
       <c r="E228" s="23"/>
       <c r="F228" s="23"/>
     </row>
-    <row r="229" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C229" s="24"/>
       <c r="D229" s="22"/>
       <c r="E229" s="22"/>
       <c r="F229" s="22"/>
     </row>
-    <row r="230" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C230" s="25"/>
       <c r="D230" s="23"/>
       <c r="E230" s="23"/>
       <c r="F230" s="23"/>
     </row>
-    <row r="231" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C231" s="24"/>
       <c r="D231" s="22"/>
       <c r="E231" s="22"/>
       <c r="F231" s="22"/>
     </row>
-    <row r="232" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C232" s="25"/>
       <c r="D232" s="23"/>
       <c r="E232" s="23"/>
       <c r="F232" s="23"/>
     </row>
-    <row r="233" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C233" s="24"/>
       <c r="D233" s="22"/>
       <c r="E233" s="22"/>
       <c r="F233" s="22"/>
     </row>
-    <row r="234" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C234" s="25"/>
       <c r="D234" s="23"/>
       <c r="E234" s="23"/>
       <c r="F234" s="23"/>
     </row>
-    <row r="235" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C235" s="24"/>
       <c r="D235" s="22"/>
       <c r="E235" s="22"/>
       <c r="F235" s="22"/>
     </row>
-    <row r="236" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C236" s="25"/>
       <c r="D236" s="23"/>
       <c r="E236" s="23"/>
       <c r="F236" s="23"/>
     </row>
-    <row r="237" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C237" s="24"/>
       <c r="D237" s="22"/>
       <c r="E237" s="22"/>
       <c r="F237" s="22"/>
     </row>
-    <row r="238" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C238" s="25"/>
       <c r="D238" s="23"/>
       <c r="E238" s="23"/>
       <c r="F238" s="23"/>
     </row>
-    <row r="239" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C239" s="24"/>
       <c r="D239" s="22"/>
       <c r="E239" s="22"/>
       <c r="F239" s="22"/>
     </row>
-    <row r="240" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C240" s="25"/>
       <c r="D240" s="23"/>
       <c r="E240" s="23"/>
       <c r="F240" s="23"/>
     </row>
-    <row r="241" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C241" s="24"/>
       <c r="D241" s="22"/>
       <c r="E241" s="22"/>
       <c r="F241" s="22"/>
     </row>
-    <row r="242" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C242" s="25"/>
       <c r="D242" s="23"/>
       <c r="E242" s="23"/>
       <c r="F242" s="23"/>
     </row>
-    <row r="243" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C243" s="24"/>
       <c r="D243" s="22"/>
       <c r="E243" s="22"/>
       <c r="F243" s="22"/>
     </row>
-    <row r="244" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C244" s="25"/>
       <c r="D244" s="23"/>
       <c r="E244" s="23"/>
       <c r="F244" s="23"/>
     </row>
-    <row r="245" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C245" s="24"/>
       <c r="D245" s="22"/>
       <c r="E245" s="22"/>
       <c r="F245" s="22"/>
     </row>
-    <row r="246" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C246" s="25"/>
       <c r="D246" s="23"/>
       <c r="E246" s="23"/>
       <c r="F246" s="23"/>
     </row>
-    <row r="247" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C247" s="24"/>
       <c r="D247" s="22"/>
       <c r="E247" s="22"/>
       <c r="F247" s="22"/>
     </row>
-    <row r="248" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C248" s="25"/>
       <c r="D248" s="23"/>
       <c r="E248" s="23"/>
       <c r="F248" s="23"/>
     </row>
-    <row r="249" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C249" s="24"/>
       <c r="D249" s="22"/>
       <c r="E249" s="22"/>
       <c r="F249" s="22"/>
     </row>
-    <row r="250" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C250" s="25"/>
       <c r="D250" s="23"/>
       <c r="E250" s="23"/>
       <c r="F250" s="23"/>
     </row>
-    <row r="251" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C251" s="24"/>
       <c r="D251" s="22"/>
       <c r="E251" s="22"/>
       <c r="F251" s="22"/>
     </row>
-    <row r="252" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C252" s="25"/>
       <c r="D252" s="23"/>
       <c r="E252" s="23"/>
       <c r="F252" s="23"/>
     </row>
-    <row r="253" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C253" s="24"/>
       <c r="D253" s="22"/>
       <c r="E253" s="22"/>
       <c r="F253" s="22"/>
     </row>
-    <row r="254" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C254" s="25"/>
       <c r="D254" s="23"/>
       <c r="E254" s="23"/>
       <c r="F254" s="23"/>
     </row>
-    <row r="255" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C255" s="24"/>
       <c r="D255" s="22"/>
       <c r="E255" s="22"/>
       <c r="F255" s="22"/>
     </row>
-    <row r="256" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C256" s="25"/>
       <c r="D256" s="23"/>
       <c r="E256" s="23"/>
       <c r="F256" s="23"/>
     </row>
-    <row r="257" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C257" s="24"/>
       <c r="D257" s="22"/>
       <c r="E257" s="22"/>
       <c r="F257" s="22"/>
     </row>
-    <row r="258" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C258" s="25"/>
       <c r="D258" s="23"/>
       <c r="E258" s="23"/>
       <c r="F258" s="23"/>
     </row>
-    <row r="259" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C259" s="24"/>
       <c r="D259" s="22"/>
       <c r="E259" s="22"/>
       <c r="F259" s="22"/>
     </row>
-    <row r="260" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C260" s="25"/>
       <c r="D260" s="23"/>
       <c r="E260" s="23"/>
       <c r="F260" s="23"/>
     </row>
-    <row r="261" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C261" s="24"/>
       <c r="D261" s="22"/>
       <c r="E261" s="22"/>
       <c r="F261" s="22"/>
     </row>
-    <row r="262" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C262" s="25"/>
       <c r="D262" s="23"/>
       <c r="E262" s="23"/>
       <c r="F262" s="23"/>
     </row>
-    <row r="263" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C263" s="24"/>
       <c r="D263" s="22"/>
       <c r="E263" s="22"/>
       <c r="F263" s="22"/>
     </row>
-    <row r="264" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C264" s="25"/>
       <c r="D264" s="23"/>
       <c r="E264" s="23"/>
       <c r="F264" s="23"/>
     </row>
-    <row r="265" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C265" s="24"/>
       <c r="D265" s="22"/>
       <c r="E265" s="22"/>
       <c r="F265" s="22"/>
     </row>
-    <row r="266" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C266" s="25"/>
       <c r="D266" s="23"/>
       <c r="E266" s="23"/>
       <c r="F266" s="23"/>
     </row>
-    <row r="267" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C267" s="24"/>
       <c r="D267" s="22"/>
       <c r="E267" s="22"/>
       <c r="F267" s="22"/>
     </row>
-    <row r="268" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C268" s="25"/>
       <c r="D268" s="23"/>
       <c r="E268" s="23"/>
       <c r="F268" s="23"/>
     </row>
-    <row r="269" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C269" s="24"/>
       <c r="D269" s="22"/>
       <c r="E269" s="22"/>
       <c r="F269" s="22"/>
     </row>
-    <row r="270" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C270" s="25"/>
       <c r="D270" s="23"/>
       <c r="E270" s="23"/>
       <c r="F270" s="23"/>
     </row>
-    <row r="271" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C271" s="24"/>
       <c r="D271" s="22"/>
       <c r="E271" s="22"/>
       <c r="F271" s="22"/>
     </row>
-    <row r="272" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C272" s="25"/>
       <c r="D272" s="23"/>
       <c r="E272" s="23"/>
       <c r="F272" s="23"/>
     </row>
-    <row r="273" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C273" s="24"/>
       <c r="D273" s="22"/>
       <c r="E273" s="22"/>
       <c r="F273" s="22"/>
     </row>
-    <row r="274" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C274" s="25"/>
       <c r="D274" s="23"/>
       <c r="E274" s="23"/>
       <c r="F274" s="23"/>
     </row>
-    <row r="275" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C275" s="24"/>
       <c r="D275" s="22"/>
       <c r="E275" s="22"/>
       <c r="F275" s="22"/>
     </row>
-    <row r="276" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C276" s="25"/>
       <c r="D276" s="23"/>
       <c r="E276" s="23"/>
       <c r="F276" s="23"/>
     </row>
-    <row r="277" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C277" s="24"/>
       <c r="D277" s="22"/>
       <c r="E277" s="22"/>
       <c r="F277" s="22"/>
     </row>
-    <row r="278" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C278" s="25"/>
       <c r="D278" s="23"/>
       <c r="E278" s="23"/>
       <c r="F278" s="23"/>
     </row>
-    <row r="279" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C279" s="24"/>
       <c r="D279" s="22"/>
       <c r="E279" s="22"/>
       <c r="F279" s="22"/>
     </row>
-    <row r="280" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C280" s="25"/>
       <c r="D280" s="23"/>
       <c r="E280" s="23"/>
       <c r="F280" s="23"/>
     </row>
-    <row r="281" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C281" s="24"/>
       <c r="D281" s="22"/>
       <c r="E281" s="22"/>
       <c r="F281" s="22"/>
     </row>
-    <row r="282" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C282" s="25"/>
       <c r="D282" s="23"/>
       <c r="E282" s="23"/>
       <c r="F282" s="23"/>
     </row>
-    <row r="283" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C283" s="24"/>
       <c r="D283" s="22"/>
       <c r="E283" s="22"/>
       <c r="F283" s="22"/>
     </row>
-    <row r="284" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C284" s="25"/>
       <c r="D284" s="23"/>
       <c r="E284" s="23"/>
       <c r="F284" s="23"/>
     </row>
-    <row r="285" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C285" s="24"/>
       <c r="D285" s="22"/>
       <c r="E285" s="22"/>
       <c r="F285" s="22"/>
     </row>
-    <row r="286" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C286" s="25"/>
       <c r="D286" s="23"/>
       <c r="E286" s="23"/>
       <c r="F286" s="23"/>
     </row>
-    <row r="287" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C287" s="24"/>
       <c r="D287" s="22"/>
       <c r="E287" s="22"/>
       <c r="F287" s="22"/>
     </row>
-    <row r="288" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C288" s="25"/>
       <c r="D288" s="23"/>
       <c r="E288" s="23"/>
       <c r="F288" s="23"/>
     </row>
-    <row r="289" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C289" s="24"/>
       <c r="D289" s="22"/>
       <c r="E289" s="22"/>
       <c r="F289" s="22"/>
     </row>
-    <row r="290" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C290" s="25"/>
       <c r="D290" s="23"/>
       <c r="E290" s="23"/>
       <c r="F290" s="23"/>
     </row>
-    <row r="291" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C291" s="24"/>
       <c r="D291" s="22"/>
       <c r="E291" s="22"/>
       <c r="F291" s="22"/>
     </row>
-    <row r="292" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C292" s="25"/>
       <c r="D292" s="23"/>
       <c r="E292" s="23"/>
       <c r="F292" s="23"/>
     </row>
-    <row r="293" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C293" s="24"/>
       <c r="D293" s="22"/>
       <c r="E293" s="22"/>
       <c r="F293" s="22"/>
     </row>
-    <row r="294" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C294" s="25"/>
       <c r="D294" s="23"/>
       <c r="E294" s="23"/>
       <c r="F294" s="23"/>
     </row>
-    <row r="295" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C295" s="24"/>
       <c r="D295" s="22"/>
       <c r="E295" s="22"/>
       <c r="F295" s="22"/>
     </row>
-    <row r="296" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C296" s="25"/>
       <c r="D296" s="23"/>
       <c r="E296" s="23"/>
       <c r="F296" s="23"/>
     </row>
-    <row r="297" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C297" s="24"/>
       <c r="D297" s="22"/>
       <c r="E297" s="22"/>
       <c r="F297" s="22"/>
     </row>
-    <row r="298" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C298" s="25"/>
       <c r="D298" s="23"/>
       <c r="E298" s="23"/>
       <c r="F298" s="23"/>
     </row>
-    <row r="299" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C299" s="24"/>
       <c r="D299" s="22"/>
       <c r="E299" s="22"/>
       <c r="F299" s="22"/>
     </row>
-    <row r="300" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C300" s="25"/>
       <c r="D300" s="23"/>
       <c r="E300" s="23"/>
       <c r="F300" s="23"/>
     </row>
-    <row r="301" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C301" s="24"/>
       <c r="D301" s="22"/>
       <c r="E301" s="22"/>
       <c r="F301" s="22"/>
     </row>
-    <row r="302" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C302" s="25"/>
       <c r="D302" s="23"/>
       <c r="E302" s="23"/>
       <c r="F302" s="23"/>
     </row>
-    <row r="303" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C303" s="24"/>
       <c r="D303" s="22"/>
       <c r="E303" s="22"/>
       <c r="F303" s="22"/>
     </row>
-    <row r="304" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C304" s="25"/>
       <c r="D304" s="23"/>
       <c r="E304" s="23"/>
       <c r="F304" s="23"/>
     </row>
-    <row r="305" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="305" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C305" s="24"/>
       <c r="D305" s="22"/>
       <c r="E305" s="22"/>
       <c r="F305" s="22"/>
     </row>
-    <row r="306" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="306" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C306" s="25"/>
       <c r="D306" s="23"/>
       <c r="E306" s="23"/>
       <c r="F306" s="23"/>
     </row>
-    <row r="307" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="307" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C307" s="24"/>
       <c r="D307" s="22"/>
       <c r="E307" s="22"/>
       <c r="F307" s="22"/>
     </row>
-    <row r="308" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="308" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C308" s="25"/>
       <c r="D308" s="23"/>
       <c r="E308" s="23"/>
       <c r="F308" s="23"/>
     </row>
-    <row r="309" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="309" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C309" s="24"/>
       <c r="D309" s="22"/>
       <c r="E309" s="22"/>
       <c r="F309" s="22"/>
     </row>
-    <row r="310" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="310" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C310" s="25"/>
       <c r="D310" s="23"/>
       <c r="E310" s="23"/>
       <c r="F310" s="23"/>
     </row>
-    <row r="311" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="311" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C311" s="24"/>
       <c r="D311" s="22"/>
       <c r="E311" s="22"/>
       <c r="F311" s="22"/>
     </row>
-    <row r="312" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="312" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C312" s="25"/>
       <c r="D312" s="23"/>
       <c r="E312" s="23"/>
       <c r="F312" s="23"/>
     </row>
-    <row r="313" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="313" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C313" s="24"/>
       <c r="D313" s="22"/>
       <c r="E313" s="22"/>
       <c r="F313" s="22"/>
     </row>
-    <row r="314" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="314" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C314" s="25"/>
       <c r="D314" s="23"/>
       <c r="E314" s="23"/>
       <c r="F314" s="23"/>
     </row>
-    <row r="315" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="315" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C315" s="24"/>
       <c r="D315" s="22"/>
       <c r="E315" s="22"/>
       <c r="F315" s="22"/>
     </row>
-    <row r="316" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="316" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C316" s="25"/>
       <c r="D316" s="23"/>
       <c r="E316" s="23"/>
       <c r="F316" s="23"/>
     </row>
-    <row r="317" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="317" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C317" s="24"/>
       <c r="D317" s="22"/>
       <c r="E317" s="22"/>
       <c r="F317" s="22"/>
     </row>
-    <row r="318" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="318" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C318" s="25"/>
       <c r="D318" s="23"/>
       <c r="E318" s="23"/>
       <c r="F318" s="23"/>
     </row>
-    <row r="319" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="319" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C319" s="24"/>
       <c r="D319" s="22"/>
       <c r="E319" s="22"/>
       <c r="F319" s="22"/>
     </row>
-    <row r="320" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="320" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C320" s="25"/>
       <c r="D320" s="23"/>
       <c r="E320" s="23"/>
       <c r="F320" s="23"/>
     </row>
-    <row r="321" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="321" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C321" s="24"/>
       <c r="D321" s="22"/>
       <c r="E321" s="22"/>
       <c r="F321" s="22"/>
     </row>
-    <row r="322" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="322" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C322" s="25"/>
       <c r="D322" s="23"/>
       <c r="E322" s="23"/>
       <c r="F322" s="23"/>
     </row>
-    <row r="323" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="323" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C323" s="24"/>
       <c r="D323" s="22"/>
       <c r="E323" s="22"/>
       <c r="F323" s="22"/>
     </row>
-    <row r="324" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="324" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C324" s="25"/>
       <c r="D324" s="23"/>
       <c r="E324" s="23"/>
       <c r="F324" s="23"/>
     </row>
-    <row r="325" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="325" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C325" s="24"/>
       <c r="D325" s="22"/>
       <c r="E325" s="22"/>
       <c r="F325" s="22"/>
     </row>
-    <row r="326" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="326" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C326" s="25"/>
       <c r="D326" s="23"/>
       <c r="E326" s="23"/>
       <c r="F326" s="23"/>
     </row>
-    <row r="327" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="327" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C327" s="24"/>
       <c r="D327" s="22"/>
       <c r="E327" s="22"/>
       <c r="F327" s="22"/>
     </row>
-    <row r="328" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="328" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C328" s="25"/>
       <c r="D328" s="23"/>
       <c r="E328" s="23"/>
       <c r="F328" s="23"/>
     </row>
-    <row r="329" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="329" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C329" s="24"/>
       <c r="D329" s="22"/>
       <c r="E329" s="22"/>
       <c r="F329" s="22"/>
     </row>
-    <row r="330" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="330" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C330" s="25"/>
       <c r="D330" s="23"/>
       <c r="E330" s="23"/>
       <c r="F330" s="23"/>
     </row>
-    <row r="331" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="331" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C331" s="24"/>
       <c r="D331" s="22"/>
       <c r="E331" s="22"/>
       <c r="F331" s="22"/>
     </row>
-    <row r="332" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="332" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C332" s="25"/>
       <c r="D332" s="23"/>
       <c r="E332" s="23"/>
       <c r="F332" s="23"/>
     </row>
-    <row r="333" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="333" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C333" s="24"/>
       <c r="D333" s="22"/>
       <c r="E333" s="22"/>
       <c r="F333" s="22"/>
     </row>
-    <row r="334" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="334" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C334" s="25"/>
       <c r="D334" s="23"/>
       <c r="E334" s="23"/>
       <c r="F334" s="23"/>
     </row>
-    <row r="335" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="335" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C335" s="24"/>
       <c r="D335" s="22"/>
       <c r="E335" s="22"/>
       <c r="F335" s="22"/>
     </row>
-    <row r="336" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="336" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C336" s="25"/>
       <c r="D336" s="23"/>
       <c r="E336" s="23"/>
       <c r="F336" s="23"/>
     </row>
-    <row r="337" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="337" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C337" s="24"/>
       <c r="D337" s="22"/>
       <c r="E337" s="22"/>
       <c r="F337" s="22"/>
     </row>
-    <row r="338" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="338" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C338" s="25"/>
       <c r="D338" s="23"/>
       <c r="E338" s="23"/>
       <c r="F338" s="23"/>
     </row>
-    <row r="339" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="339" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C339" s="24"/>
       <c r="D339" s="22"/>
       <c r="E339" s="22"/>
       <c r="F339" s="22"/>
     </row>
-    <row r="340" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="340" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C340" s="25"/>
       <c r="D340" s="23"/>
       <c r="E340" s="23"/>
       <c r="F340" s="23"/>
     </row>
-    <row r="341" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="341" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C341" s="24"/>
       <c r="D341" s="22"/>
       <c r="E341" s="22"/>
       <c r="F341" s="22"/>
     </row>
-    <row r="342" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="342" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C342" s="25"/>
       <c r="D342" s="23"/>
       <c r="E342" s="23"/>
       <c r="F342" s="23"/>
     </row>
-    <row r="343" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="343" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C343" s="24"/>
       <c r="D343" s="22"/>
       <c r="E343" s="22"/>
       <c r="F343" s="22"/>
     </row>
-    <row r="344" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="344" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C344" s="25"/>
       <c r="D344" s="23"/>
       <c r="E344" s="23"/>
       <c r="F344" s="23"/>
     </row>
-    <row r="345" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="345" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C345" s="24"/>
       <c r="D345" s="22"/>
       <c r="E345" s="22"/>
       <c r="F345" s="22"/>
     </row>
-    <row r="346" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="346" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C346" s="25"/>
       <c r="D346" s="23"/>
       <c r="E346" s="23"/>
       <c r="F346" s="23"/>
     </row>
-    <row r="347" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="347" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C347" s="24"/>
       <c r="D347" s="22"/>
       <c r="E347" s="22"/>
       <c r="F347" s="22"/>
     </row>
-    <row r="348" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="348" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C348" s="25"/>
       <c r="D348" s="23"/>
       <c r="E348" s="23"/>
       <c r="F348" s="23"/>
     </row>
-    <row r="349" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="349" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C349" s="24"/>
       <c r="D349" s="22"/>
       <c r="E349" s="22"/>
       <c r="F349" s="22"/>
     </row>
-    <row r="350" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="350" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C350" s="25"/>
       <c r="D350" s="23"/>
       <c r="E350" s="23"/>
       <c r="F350" s="23"/>
     </row>
-    <row r="351" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="351" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C351" s="24"/>
       <c r="D351" s="22"/>
       <c r="E351" s="22"/>
       <c r="F351" s="22"/>
     </row>
-    <row r="352" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="352" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C352" s="25"/>
       <c r="D352" s="23"/>
       <c r="E352" s="23"/>
       <c r="F352" s="23"/>
     </row>
-    <row r="353" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="353" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C353" s="24"/>
       <c r="D353" s="22"/>
       <c r="E353" s="22"/>
       <c r="F353" s="22"/>
     </row>
-    <row r="354" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="354" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C354" s="25"/>
       <c r="D354" s="23"/>
       <c r="E354" s="23"/>
       <c r="F354" s="23"/>
     </row>
-    <row r="355" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="355" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C355" s="24"/>
       <c r="D355" s="22"/>
       <c r="E355" s="22"/>
       <c r="F355" s="22"/>
     </row>
-    <row r="356" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="356" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C356" s="25"/>
       <c r="D356" s="23"/>
       <c r="E356" s="23"/>
       <c r="F356" s="23"/>
     </row>
-    <row r="357" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="357" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C357" s="24"/>
       <c r="D357" s="22"/>
       <c r="E357" s="22"/>
       <c r="F357" s="22"/>
     </row>
-    <row r="358" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="358" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C358" s="25"/>
       <c r="D358" s="23"/>
       <c r="E358" s="23"/>
       <c r="F358" s="23"/>
     </row>
-    <row r="359" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="359" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C359" s="24"/>
       <c r="D359" s="22"/>
       <c r="E359" s="22"/>
       <c r="F359" s="22"/>
     </row>
-    <row r="360" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="360" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C360" s="25"/>
       <c r="D360" s="23"/>
       <c r="E360" s="23"/>
       <c r="F360" s="23"/>
     </row>
-    <row r="361" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="361" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C361" s="24"/>
       <c r="D361" s="22"/>
       <c r="E361" s="22"/>
       <c r="F361" s="22"/>
     </row>
-    <row r="362" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="362" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C362" s="25"/>
       <c r="D362" s="23"/>
       <c r="E362" s="23"/>
       <c r="F362" s="23"/>
     </row>
-    <row r="363" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="363" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C363" s="24"/>
       <c r="D363" s="22"/>
       <c r="E363" s="22"/>
       <c r="F363" s="22"/>
     </row>
-    <row r="364" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="364" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C364" s="25"/>
       <c r="D364" s="23"/>
       <c r="E364" s="23"/>
       <c r="F364" s="23"/>
     </row>
-    <row r="365" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="365" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C365" s="24"/>
       <c r="D365" s="22"/>
       <c r="E365" s="22"/>
       <c r="F365" s="22"/>
     </row>
-    <row r="366" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="366" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C366" s="25"/>
       <c r="D366" s="23"/>
       <c r="E366" s="23"/>
       <c r="F366" s="23"/>
     </row>
-    <row r="367" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="367" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C367" s="24"/>
       <c r="D367" s="22"/>
       <c r="E367" s="22"/>
       <c r="F367" s="22"/>
     </row>
-    <row r="368" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="368" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C368" s="25"/>
       <c r="D368" s="23"/>
       <c r="E368" s="23"/>
       <c r="F368" s="23"/>
     </row>
-    <row r="369" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="369" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C369" s="24"/>
       <c r="D369" s="22"/>
       <c r="E369" s="22"/>
       <c r="F369" s="22"/>
     </row>
-    <row r="370" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="370" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C370" s="25"/>
       <c r="D370" s="23"/>
       <c r="E370" s="23"/>
       <c r="F370" s="23"/>
     </row>
-    <row r="371" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="371" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C371" s="24"/>
       <c r="D371" s="22"/>
       <c r="E371" s="22"/>
       <c r="F371" s="22"/>
     </row>
-    <row r="372" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="372" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C372" s="25"/>
       <c r="D372" s="23"/>
       <c r="E372" s="23"/>
       <c r="F372" s="23"/>
     </row>
-    <row r="373" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="373" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C373" s="24"/>
       <c r="D373" s="22"/>
       <c r="E373" s="22"/>
       <c r="F373" s="22"/>
     </row>
-    <row r="374" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="374" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C374" s="25"/>
       <c r="D374" s="23"/>
       <c r="E374" s="23"/>
       <c r="F374" s="23"/>
     </row>
-    <row r="375" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="375" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C375" s="24"/>
       <c r="D375" s="22"/>
       <c r="E375" s="22"/>
       <c r="F375" s="22"/>
     </row>
-    <row r="376" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="376" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C376" s="25"/>
       <c r="D376" s="23"/>
       <c r="E376" s="23"/>
       <c r="F376" s="23"/>
     </row>
-    <row r="377" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="377" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C377" s="24"/>
       <c r="D377" s="22"/>
       <c r="E377" s="22"/>
       <c r="F377" s="22"/>
     </row>
-    <row r="378" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="378" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C378" s="25"/>
       <c r="D378" s="23"/>
       <c r="E378" s="23"/>
       <c r="F378" s="23"/>
     </row>
-    <row r="379" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="379" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C379" s="24"/>
       <c r="D379" s="22"/>
       <c r="E379" s="22"/>
       <c r="F379" s="22"/>
     </row>
-    <row r="380" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="380" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C380" s="25"/>
       <c r="D380" s="23"/>
       <c r="E380" s="23"/>
       <c r="F380" s="23"/>
     </row>
-    <row r="381" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="381" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C381" s="24"/>
       <c r="D381" s="22"/>
       <c r="E381" s="22"/>
       <c r="F381" s="22"/>
     </row>
-    <row r="382" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="382" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C382" s="25"/>
       <c r="D382" s="23"/>
       <c r="E382" s="23"/>
       <c r="F382" s="23"/>
     </row>
-    <row r="383" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="383" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C383" s="24"/>
       <c r="D383" s="22"/>
       <c r="E383" s="22"/>
       <c r="F383" s="22"/>
     </row>
-    <row r="384" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="384" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C384" s="25"/>
       <c r="D384" s="23"/>
       <c r="E384" s="23"/>
       <c r="F384" s="23"/>
     </row>
-    <row r="385" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="385" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C385" s="24"/>
       <c r="D385" s="22"/>
       <c r="E385" s="22"/>
       <c r="F385" s="22"/>
     </row>
-    <row r="386" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="386" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C386" s="25"/>
       <c r="D386" s="23"/>
       <c r="E386" s="23"/>
       <c r="F386" s="23"/>
     </row>
-    <row r="387" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="387" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C387" s="24"/>
       <c r="D387" s="22"/>
       <c r="E387" s="22"/>
       <c r="F387" s="22"/>
     </row>
-    <row r="388" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="388" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C388" s="25"/>
       <c r="D388" s="23"/>
       <c r="E388" s="23"/>
       <c r="F388" s="23"/>
     </row>
-    <row r="389" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="389" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C389" s="24"/>
       <c r="D389" s="22"/>
       <c r="E389" s="22"/>
       <c r="F389" s="22"/>
     </row>
-    <row r="390" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="390" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C390" s="25"/>
       <c r="D390" s="23"/>
       <c r="E390" s="23"/>
       <c r="F390" s="23"/>
     </row>
-    <row r="391" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="391" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C391" s="24"/>
       <c r="D391" s="22"/>
       <c r="E391" s="22"/>
       <c r="F391" s="22"/>
     </row>
-    <row r="392" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="392" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C392" s="25"/>
       <c r="D392" s="23"/>
       <c r="E392" s="23"/>
       <c r="F392" s="23"/>
     </row>
-    <row r="393" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="393" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C393" s="24"/>
       <c r="D393" s="22"/>
       <c r="E393" s="22"/>
       <c r="F393" s="22"/>
     </row>
-    <row r="394" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="394" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C394" s="25"/>
       <c r="D394" s="23"/>
       <c r="E394" s="23"/>
       <c r="F394" s="23"/>
     </row>
-    <row r="395" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="395" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C395" s="24"/>
       <c r="D395" s="22"/>
       <c r="E395" s="22"/>
       <c r="F395" s="22"/>
     </row>
-    <row r="396" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="396" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C396" s="25"/>
       <c r="D396" s="23"/>
       <c r="E396" s="23"/>
       <c r="F396" s="23"/>
     </row>
-    <row r="397" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="397" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C397" s="24"/>
       <c r="D397" s="22"/>
       <c r="E397" s="22"/>
       <c r="F397" s="22"/>
     </row>
-    <row r="398" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="398" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C398" s="25"/>
       <c r="D398" s="23"/>
       <c r="E398" s="23"/>
       <c r="F398" s="23"/>
     </row>
-    <row r="399" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="399" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C399" s="24"/>
       <c r="D399" s="22"/>
       <c r="E399" s="22"/>
       <c r="F399" s="22"/>
     </row>
-    <row r="400" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="400" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C400" s="25"/>
       <c r="D400" s="23"/>
       <c r="E400" s="23"/>
       <c r="F400" s="23"/>
     </row>
-    <row r="401" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="401" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C401" s="24"/>
       <c r="D401" s="22"/>
       <c r="E401" s="22"/>
       <c r="F401" s="22"/>
     </row>
-    <row r="402" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="402" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C402" s="25"/>
       <c r="D402" s="23"/>
       <c r="E402" s="23"/>
       <c r="F402" s="23"/>
     </row>
-    <row r="403" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="403" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C403" s="24"/>
       <c r="D403" s="22"/>
       <c r="E403" s="22"/>
       <c r="F403" s="22"/>
     </row>
-    <row r="404" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="404" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C404" s="25"/>
       <c r="D404" s="23"/>
       <c r="E404" s="23"/>
       <c r="F404" s="23"/>
     </row>
-    <row r="405" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="405" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C405" s="24"/>
       <c r="D405" s="22"/>
       <c r="E405" s="22"/>
       <c r="F405" s="22"/>
     </row>
-    <row r="406" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="406" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C406" s="25"/>
       <c r="D406" s="23"/>
       <c r="E406" s="23"/>
       <c r="F406" s="23"/>
     </row>
-    <row r="407" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="407" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C407" s="24"/>
       <c r="D407" s="22"/>
       <c r="E407" s="22"/>
       <c r="F407" s="22"/>
     </row>
-    <row r="408" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="408" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C408" s="25"/>
       <c r="D408" s="23"/>
       <c r="E408" s="23"/>
       <c r="F408" s="23"/>
     </row>
-    <row r="409" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="409" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C409" s="24"/>
       <c r="D409" s="22"/>
       <c r="E409" s="22"/>
       <c r="F409" s="22"/>
     </row>
-    <row r="410" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="410" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C410" s="25"/>
       <c r="D410" s="23"/>
       <c r="E410" s="23"/>
       <c r="F410" s="23"/>
     </row>
-    <row r="411" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="411" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C411" s="24"/>
       <c r="D411" s="22"/>
       <c r="E411" s="22"/>
       <c r="F411" s="22"/>
     </row>
-    <row r="412" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="412" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C412" s="25"/>
       <c r="D412" s="23"/>
       <c r="E412" s="23"/>
       <c r="F412" s="23"/>
     </row>
-    <row r="413" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="413" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C413" s="24"/>
       <c r="D413" s="22"/>
       <c r="E413" s="22"/>
       <c r="F413" s="22"/>
     </row>
-    <row r="414" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="414" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C414" s="25"/>
       <c r="D414" s="23"/>
       <c r="E414" s="23"/>
       <c r="F414" s="23"/>
     </row>
-    <row r="415" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="415" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C415" s="24"/>
       <c r="D415" s="22"/>
       <c r="E415" s="22"/>
       <c r="F415" s="22"/>
     </row>
-    <row r="416" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="416" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C416" s="25"/>
       <c r="D416" s="23"/>
       <c r="E416" s="23"/>
       <c r="F416" s="23"/>
     </row>
-    <row r="417" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="417" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C417" s="24"/>
       <c r="D417" s="22"/>
       <c r="E417" s="22"/>
       <c r="F417" s="22"/>
     </row>
-    <row r="418" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="418" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C418" s="25"/>
       <c r="D418" s="23"/>
       <c r="E418" s="23"/>
       <c r="F418" s="23"/>
     </row>
-    <row r="419" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="419" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C419" s="24"/>
       <c r="D419" s="22"/>
       <c r="E419" s="22"/>
       <c r="F419" s="22"/>
     </row>
-    <row r="420" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="420" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C420" s="25"/>
       <c r="D420" s="23"/>
       <c r="E420" s="23"/>
       <c r="F420" s="23"/>
     </row>
-    <row r="421" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="421" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C421" s="24"/>
       <c r="D421" s="22"/>
       <c r="E421" s="22"/>
       <c r="F421" s="22"/>
     </row>
-    <row r="422" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="422" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C422" s="25"/>
       <c r="D422" s="23"/>
       <c r="E422" s="23"/>
       <c r="F422" s="23"/>
     </row>
-    <row r="423" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="423" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C423" s="24"/>
       <c r="D423" s="22"/>
       <c r="E423" s="22"/>
       <c r="F423" s="22"/>
     </row>
-    <row r="424" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="424" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C424" s="25"/>
       <c r="D424" s="23"/>
       <c r="E424" s="23"/>
       <c r="F424" s="23"/>
     </row>
-    <row r="425" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="425" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C425" s="24"/>
       <c r="D425" s="22"/>
       <c r="E425" s="22"/>
       <c r="F425" s="22"/>
     </row>
-    <row r="426" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="426" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C426" s="25"/>
       <c r="D426" s="23"/>
       <c r="E426" s="23"/>
       <c r="F426" s="23"/>
     </row>
-    <row r="427" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="427" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C427" s="24"/>
       <c r="D427" s="22"/>
       <c r="E427" s="22"/>
       <c r="F427" s="22"/>
     </row>
-    <row r="428" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="428" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C428" s="25"/>
       <c r="D428" s="23"/>
       <c r="E428" s="23"/>
       <c r="F428" s="23"/>
     </row>
-    <row r="429" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="429" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C429" s="24"/>
       <c r="D429" s="22"/>
       <c r="E429" s="22"/>
       <c r="F429" s="22"/>
     </row>
-    <row r="430" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="430" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C430" s="25"/>
       <c r="D430" s="23"/>
       <c r="E430" s="23"/>
       <c r="F430" s="23"/>
     </row>
-    <row r="431" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="431" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C431" s="24"/>
       <c r="D431" s="22"/>
       <c r="E431" s="22"/>
       <c r="F431" s="22"/>
     </row>
-    <row r="432" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="432" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C432" s="25"/>
       <c r="D432" s="23"/>
       <c r="E432" s="23"/>
       <c r="F432" s="23"/>
     </row>
-    <row r="433" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="433" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C433" s="24"/>
       <c r="D433" s="22"/>
       <c r="E433" s="22"/>
       <c r="F433" s="22"/>
     </row>
-    <row r="434" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="434" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C434" s="25"/>
       <c r="D434" s="23"/>
       <c r="E434" s="23"/>
       <c r="F434" s="23"/>
     </row>
-    <row r="435" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="435" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C435" s="24"/>
       <c r="D435" s="22"/>
       <c r="E435" s="22"/>
       <c r="F435" s="22"/>
     </row>
-    <row r="436" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="436" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C436" s="25"/>
       <c r="D436" s="23"/>
       <c r="E436" s="23"/>
       <c r="F436" s="23"/>
     </row>
-    <row r="437" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="437" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C437" s="24"/>
       <c r="D437" s="22"/>
       <c r="E437" s="22"/>
       <c r="F437" s="22"/>
     </row>
-    <row r="438" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="438" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C438" s="25"/>
       <c r="D438" s="23"/>
       <c r="E438" s="23"/>
       <c r="F438" s="23"/>
     </row>
-    <row r="439" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="439" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C439" s="24"/>
       <c r="D439" s="22"/>
       <c r="E439" s="22"/>
       <c r="F439" s="22"/>
     </row>
-    <row r="440" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="440" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C440" s="25"/>
       <c r="D440" s="23"/>
       <c r="E440" s="23"/>
       <c r="F440" s="23"/>
     </row>
-    <row r="441" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="441" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C441" s="24"/>
       <c r="D441" s="22"/>
       <c r="E441" s="22"/>
       <c r="F441" s="22"/>
     </row>
-    <row r="442" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="442" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C442" s="25"/>
       <c r="D442" s="23"/>
       <c r="E442" s="23"/>
       <c r="F442" s="23"/>
     </row>
-    <row r="443" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="443" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C443" s="24"/>
       <c r="D443" s="22"/>
       <c r="E443" s="22"/>
       <c r="F443" s="22"/>
     </row>
-    <row r="444" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="444" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C444" s="25"/>
       <c r="D444" s="23"/>
       <c r="E444" s="23"/>
       <c r="F444" s="23"/>
     </row>
-    <row r="445" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="445" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C445" s="24"/>
       <c r="D445" s="22"/>
       <c r="E445" s="22"/>
       <c r="F445" s="22"/>
     </row>
-    <row r="446" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="446" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C446" s="25"/>
       <c r="D446" s="23"/>
       <c r="E446" s="23"/>
       <c r="F446" s="23"/>
     </row>
-    <row r="447" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="447" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C447" s="24"/>
       <c r="D447" s="22"/>
       <c r="E447" s="22"/>
       <c r="F447" s="22"/>
     </row>
-    <row r="448" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="448" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C448" s="25"/>
       <c r="D448" s="23"/>
       <c r="E448" s="23"/>
       <c r="F448" s="23"/>
     </row>
-    <row r="449" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="449" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C449" s="24"/>
       <c r="D449" s="22"/>
       <c r="E449" s="22"/>
       <c r="F449" s="22"/>
     </row>
-    <row r="450" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="450" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C450" s="25"/>
       <c r="D450" s="23"/>
       <c r="E450" s="23"/>
       <c r="F450" s="23"/>
     </row>
-    <row r="451" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="451" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C451" s="24"/>
       <c r="D451" s="22"/>
       <c r="E451" s="22"/>
       <c r="F451" s="22"/>
     </row>
-    <row r="452" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="452" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C452" s="25"/>
       <c r="D452" s="23"/>
       <c r="E452" s="23"/>
       <c r="F452" s="23"/>
     </row>
-    <row r="453" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="453" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C453" s="24"/>
       <c r="D453" s="22"/>
       <c r="E453" s="22"/>
       <c r="F453" s="22"/>
     </row>
-    <row r="454" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="454" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C454" s="25"/>
       <c r="D454" s="23"/>
       <c r="E454" s="23"/>
       <c r="F454" s="23"/>
     </row>
-    <row r="455" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="455" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C455" s="24"/>
       <c r="D455" s="22"/>
       <c r="E455" s="22"/>
       <c r="F455" s="22"/>
     </row>
-    <row r="456" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="456" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C456" s="25"/>
       <c r="D456" s="23"/>
       <c r="E456" s="23"/>
       <c r="F456" s="23"/>
     </row>
-    <row r="457" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="457" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C457" s="24"/>
       <c r="D457" s="22"/>
       <c r="E457" s="22"/>
       <c r="F457" s="22"/>
     </row>
-    <row r="458" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="458" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C458" s="25"/>
       <c r="D458" s="23"/>
       <c r="E458" s="23"/>
       <c r="F458" s="23"/>
     </row>
-    <row r="459" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="459" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C459" s="24"/>
       <c r="D459" s="22"/>
       <c r="E459" s="22"/>
       <c r="F459" s="22"/>
     </row>
-    <row r="460" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="460" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C460" s="25"/>
       <c r="D460" s="23"/>
       <c r="E460" s="23"/>
       <c r="F460" s="23"/>
     </row>
-    <row r="461" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="461" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C461" s="24"/>
       <c r="D461" s="22"/>
       <c r="E461" s="22"/>
       <c r="F461" s="22"/>
     </row>
-    <row r="462" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="462" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C462" s="25"/>
       <c r="D462" s="23"/>
       <c r="E462" s="23"/>
       <c r="F462" s="23"/>
     </row>
-    <row r="463" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="463" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C463" s="24"/>
       <c r="D463" s="22"/>
       <c r="E463" s="22"/>
       <c r="F463" s="22"/>
     </row>
-    <row r="464" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="464" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C464" s="25"/>
       <c r="D464" s="23"/>
       <c r="E464" s="23"/>
       <c r="F464" s="23"/>
     </row>
-    <row r="465" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="465" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C465" s="24"/>
       <c r="D465" s="22"/>
       <c r="E465" s="22"/>
       <c r="F465" s="22"/>
     </row>
-    <row r="466" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="466" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C466" s="25"/>
       <c r="D466" s="23"/>
       <c r="E466" s="23"/>
       <c r="F466" s="23"/>
     </row>
-    <row r="467" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="467" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C467" s="24"/>
       <c r="D467" s="22"/>
       <c r="E467" s="22"/>
       <c r="F467" s="22"/>
     </row>
-    <row r="468" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="468" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C468" s="25"/>
       <c r="D468" s="23"/>
       <c r="E468" s="23"/>
       <c r="F468" s="23"/>
     </row>
-    <row r="469" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="469" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C469" s="24"/>
       <c r="D469" s="22"/>
       <c r="E469" s="22"/>
       <c r="F469" s="22"/>
     </row>
-    <row r="470" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="470" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C470" s="25"/>
       <c r="D470" s="23"/>
       <c r="E470" s="23"/>
       <c r="F470" s="23"/>
     </row>
-    <row r="471" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="471" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C471" s="24"/>
       <c r="D471" s="22"/>
       <c r="E471" s="22"/>
       <c r="F471" s="22"/>
     </row>
-    <row r="472" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="472" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C472" s="25"/>
       <c r="D472" s="23"/>
       <c r="E472" s="23"/>
       <c r="F472" s="23"/>
     </row>
-    <row r="473" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="473" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C473" s="24"/>
       <c r="D473" s="22"/>
       <c r="E473" s="22"/>
       <c r="F473" s="22"/>
     </row>
-    <row r="474" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="474" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C474" s="25"/>
       <c r="D474" s="23"/>
       <c r="E474" s="23"/>
       <c r="F474" s="23"/>
     </row>
-    <row r="475" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="475" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C475" s="24"/>
       <c r="D475" s="22"/>
       <c r="E475" s="22"/>
       <c r="F475" s="22"/>
     </row>
-    <row r="476" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="476" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C476" s="25"/>
       <c r="D476" s="23"/>
       <c r="E476" s="23"/>
       <c r="F476" s="23"/>
     </row>
-    <row r="477" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="477" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C477" s="24"/>
       <c r="D477" s="22"/>
       <c r="E477" s="22"/>
       <c r="F477" s="22"/>
     </row>
-    <row r="478" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="478" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C478" s="25"/>
       <c r="D478" s="23"/>
       <c r="E478" s="23"/>
       <c r="F478" s="23"/>
     </row>
-    <row r="479" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="479" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C479" s="24"/>
       <c r="D479" s="22"/>
       <c r="E479" s="22"/>
       <c r="F479" s="22"/>
     </row>
-    <row r="480" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="480" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C480" s="25"/>
       <c r="D480" s="23"/>
       <c r="E480" s="23"/>
       <c r="F480" s="23"/>
     </row>
-    <row r="481" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="481" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C481" s="24"/>
       <c r="D481" s="22"/>
       <c r="E481" s="22"/>
       <c r="F481" s="22"/>
     </row>
-    <row r="482" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="482" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C482" s="25"/>
       <c r="D482" s="23"/>
       <c r="E482" s="23"/>
       <c r="F482" s="23"/>
     </row>
-    <row r="483" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="483" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C483" s="24"/>
       <c r="D483" s="22"/>
       <c r="E483" s="22"/>
       <c r="F483" s="22"/>
     </row>
-    <row r="484" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="484" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C484" s="25"/>
       <c r="D484" s="23"/>
       <c r="E484" s="23"/>
       <c r="F484" s="23"/>
     </row>
-    <row r="485" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="485" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C485" s="24"/>
       <c r="D485" s="22"/>
       <c r="E485" s="22"/>
       <c r="F485" s="22"/>
     </row>
-    <row r="486" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="486" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C486" s="25"/>
       <c r="D486" s="23"/>
       <c r="E486" s="23"/>
       <c r="F486" s="23"/>
     </row>
-    <row r="487" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="487" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C487" s="24"/>
       <c r="D487" s="22"/>
       <c r="E487" s="22"/>
       <c r="F487" s="22"/>
     </row>
-    <row r="488" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="488" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C488" s="25"/>
       <c r="D488" s="23"/>
       <c r="E488" s="23"/>
       <c r="F488" s="23"/>
     </row>
-    <row r="489" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="489" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C489" s="24"/>
       <c r="D489" s="22"/>
       <c r="E489" s="22"/>
       <c r="F489" s="22"/>
     </row>
-    <row r="490" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="490" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C490" s="25"/>
       <c r="D490" s="23"/>
       <c r="E490" s="23"/>
       <c r="F490" s="23"/>
     </row>
-    <row r="491" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="491" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C491" s="24"/>
       <c r="D491" s="22"/>
       <c r="E491" s="22"/>
       <c r="F491" s="22"/>
     </row>
-    <row r="492" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="492" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C492" s="25"/>
       <c r="D492" s="23"/>
       <c r="E492" s="23"/>
       <c r="F492" s="23"/>
     </row>
-    <row r="493" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="493" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C493" s="24"/>
       <c r="D493" s="22"/>
       <c r="E493" s="22"/>
       <c r="F493" s="22"/>
     </row>
-    <row r="494" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="494" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C494" s="25"/>
       <c r="D494" s="23"/>
       <c r="E494" s="23"/>
       <c r="F494" s="23"/>
     </row>
-    <row r="495" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="495" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C495" s="24"/>
       <c r="D495" s="22"/>
       <c r="E495" s="22"/>
       <c r="F495" s="22"/>
     </row>
-    <row r="496" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="496" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C496" s="25"/>
       <c r="D496" s="23"/>
       <c r="E496" s="23"/>
       <c r="F496" s="23"/>
     </row>
-    <row r="497" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="497" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C497" s="24"/>
       <c r="D497" s="22"/>
       <c r="E497" s="22"/>
       <c r="F497" s="22"/>
     </row>
-    <row r="498" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="498" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C498" s="25"/>
       <c r="D498" s="23"/>
       <c r="E498" s="23"/>
       <c r="F498" s="23"/>
     </row>
-    <row r="499" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="499" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C499" s="24"/>
       <c r="D499" s="22"/>
       <c r="E499" s="22"/>
       <c r="F499" s="22"/>
     </row>
-    <row r="500" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="500" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C500" s="25"/>
       <c r="D500" s="23"/>
       <c r="E500" s="23"/>
       <c r="F500" s="23"/>
     </row>
-    <row r="501" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="501" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C501" s="24"/>
       <c r="D501" s="22"/>
       <c r="E501" s="22"/>
       <c r="F501" s="22"/>
     </row>
-    <row r="502" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="502" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C502" s="25"/>
       <c r="D502" s="23"/>
       <c r="E502" s="23"/>
       <c r="F502" s="23"/>
     </row>
-    <row r="503" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="503" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C503" s="24"/>
       <c r="D503" s="22"/>
       <c r="E503" s="22"/>
       <c r="F503" s="22"/>
     </row>
-    <row r="504" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="504" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C504" s="25"/>
       <c r="D504" s="23"/>
       <c r="E504" s="23"/>
       <c r="F504" s="23"/>
     </row>
-    <row r="505" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="505" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C505" s="24"/>
       <c r="D505" s="22"/>
       <c r="E505" s="22"/>
       <c r="F505" s="22"/>
     </row>
-    <row r="506" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="506" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C506" s="25"/>
       <c r="D506" s="23"/>
       <c r="E506" s="23"/>
       <c r="F506" s="23"/>
     </row>
-    <row r="507" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="507" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C507" s="24"/>
       <c r="D507" s="22"/>
       <c r="E507" s="22"/>
       <c r="F507" s="22"/>
     </row>
-    <row r="508" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="508" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C508" s="25"/>
       <c r="D508" s="23"/>
       <c r="E508" s="23"/>
       <c r="F508" s="23"/>
     </row>
-    <row r="509" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="509" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C509" s="24"/>
       <c r="D509" s="22"/>
       <c r="E509" s="22"/>
       <c r="F509" s="22"/>
     </row>
-    <row r="510" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="510" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C510" s="25"/>
       <c r="D510" s="23"/>
       <c r="E510" s="23"/>
       <c r="F510" s="23"/>
     </row>
-    <row r="511" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="511" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C511" s="24"/>
       <c r="D511" s="22"/>
       <c r="E511" s="22"/>
       <c r="F511" s="22"/>
     </row>
-    <row r="512" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="512" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C512" s="25"/>
       <c r="D512" s="23"/>
       <c r="E512" s="23"/>
       <c r="F512" s="23"/>
     </row>
-    <row r="513" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="513" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C513" s="24"/>
       <c r="D513" s="22"/>
       <c r="E513" s="22"/>
       <c r="F513" s="22"/>
     </row>
-    <row r="514" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="514" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C514" s="25"/>
       <c r="D514" s="23"/>
       <c r="E514" s="23"/>
       <c r="F514" s="23"/>
     </row>
-    <row r="515" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="515" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C515" s="24"/>
       <c r="D515" s="22"/>
       <c r="E515" s="22"/>
       <c r="F515" s="22"/>
     </row>
-    <row r="516" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="516" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C516" s="25"/>
       <c r="D516" s="23"/>
       <c r="E516" s="23"/>
       <c r="F516" s="23"/>
     </row>
-    <row r="517" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="517" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C517" s="24"/>
       <c r="D517" s="22"/>
       <c r="E517" s="22"/>
       <c r="F517" s="22"/>
     </row>
-    <row r="518" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="518" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C518" s="25"/>
       <c r="D518" s="23"/>
       <c r="E518" s="23"/>
       <c r="F518" s="23"/>
     </row>
-    <row r="519" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="519" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C519" s="24"/>
       <c r="D519" s="22"/>
       <c r="E519" s="22"/>
       <c r="F519" s="22"/>
     </row>
-    <row r="520" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="520" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C520" s="25"/>
       <c r="D520" s="23"/>
       <c r="E520" s="23"/>
       <c r="F520" s="23"/>
     </row>
-    <row r="521" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="521" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C521" s="24"/>
       <c r="D521" s="22"/>
       <c r="E521" s="22"/>
       <c r="F521" s="22"/>
     </row>
-    <row r="522" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="522" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C522" s="25"/>
       <c r="D522" s="23"/>
       <c r="E522" s="23"/>
       <c r="F522" s="23"/>
     </row>
-    <row r="523" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="523" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C523" s="24"/>
       <c r="D523" s="22"/>
       <c r="E523" s="22"/>
       <c r="F523" s="22"/>
     </row>
-    <row r="524" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="524" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C524" s="25"/>
       <c r="D524" s="23"/>
       <c r="E524" s="23"/>
       <c r="F524" s="23"/>
     </row>
-    <row r="525" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="525" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C525" s="24"/>
       <c r="D525" s="22"/>
       <c r="E525" s="22"/>
       <c r="F525" s="22"/>
     </row>
-    <row r="526" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="526" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C526" s="25"/>
       <c r="D526" s="23"/>
       <c r="E526" s="23"/>
       <c r="F526" s="23"/>
     </row>
-    <row r="527" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="527" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C527" s="24"/>
       <c r="D527" s="22"/>
       <c r="E527" s="22"/>
       <c r="F527" s="22"/>
     </row>
-    <row r="528" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="528" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C528" s="25"/>
       <c r="D528" s="23"/>
       <c r="E528" s="23"/>
       <c r="F528" s="23"/>
     </row>
-    <row r="529" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="529" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C529" s="24"/>
       <c r="D529" s="22"/>
       <c r="E529" s="22"/>
       <c r="F529" s="22"/>
     </row>
-    <row r="530" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="530" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C530" s="25"/>
       <c r="D530" s="23"/>
       <c r="E530" s="23"/>
       <c r="F530" s="23"/>
     </row>
-    <row r="531" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="531" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C531" s="24"/>
       <c r="D531" s="22"/>
       <c r="E531" s="22"/>
       <c r="F531" s="22"/>
     </row>
-    <row r="532" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="532" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C532" s="25"/>
       <c r="D532" s="23"/>
       <c r="E532" s="23"/>
       <c r="F532" s="23"/>
     </row>
-    <row r="533" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="533" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C533" s="24"/>
       <c r="D533" s="22"/>
       <c r="E533" s="22"/>
       <c r="F533" s="22"/>
     </row>
-    <row r="534" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="534" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C534" s="25"/>
       <c r="D534" s="23"/>
       <c r="E534" s="23"/>
       <c r="F534" s="23"/>
     </row>
-    <row r="535" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="535" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C535" s="24"/>
       <c r="D535" s="22"/>
       <c r="E535" s="22"/>
       <c r="F535" s="22"/>
     </row>
-    <row r="536" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="536" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C536" s="25"/>
       <c r="D536" s="23"/>
       <c r="E536" s="23"/>
       <c r="F536" s="23"/>
     </row>
-    <row r="537" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="537" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C537" s="24"/>
       <c r="D537" s="22"/>
       <c r="E537" s="22"/>
       <c r="F537" s="22"/>
     </row>
-    <row r="538" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="538" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C538" s="25"/>
       <c r="D538" s="23"/>
       <c r="E538" s="23"/>
       <c r="F538" s="23"/>
     </row>
-    <row r="539" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="539" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C539" s="24"/>
       <c r="D539" s="22"/>
       <c r="E539" s="22"/>
       <c r="F539" s="22"/>
     </row>
-    <row r="540" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="540" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C540" s="25"/>
       <c r="D540" s="23"/>
       <c r="E540" s="23"/>
       <c r="F540" s="23"/>
     </row>
-    <row r="541" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="541" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C541" s="24"/>
       <c r="D541" s="22"/>
       <c r="E541" s="22"/>
       <c r="F541" s="22"/>
     </row>
-    <row r="542" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="542" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C542" s="25"/>
       <c r="D542" s="23"/>
       <c r="E542" s="23"/>
       <c r="F542" s="23"/>
     </row>
-    <row r="543" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="543" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C543" s="24"/>
       <c r="D543" s="22"/>
       <c r="E543" s="22"/>
       <c r="F543" s="22"/>
     </row>
-    <row r="544" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="544" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C544" s="25"/>
       <c r="D544" s="23"/>
       <c r="E544" s="23"/>
       <c r="F544" s="23"/>
     </row>
-    <row r="545" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="545" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C545" s="24"/>
       <c r="D545" s="22"/>
       <c r="E545" s="22"/>
       <c r="F545" s="22"/>
     </row>
-    <row r="546" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="546" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C546" s="25"/>
       <c r="D546" s="23"/>
       <c r="E546" s="23"/>
       <c r="F546" s="23"/>
     </row>
-    <row r="547" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="547" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C547" s="24"/>
       <c r="D547" s="22"/>
       <c r="E547" s="22"/>
       <c r="F547" s="22"/>
     </row>
-    <row r="548" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="548" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C548" s="25"/>
       <c r="D548" s="23"/>
       <c r="E548" s="23"/>
       <c r="F548" s="23"/>
     </row>
-    <row r="549" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="549" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C549" s="24"/>
       <c r="D549" s="22"/>
       <c r="E549" s="22"/>
       <c r="F549" s="22"/>
     </row>
-    <row r="550" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="550" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C550" s="25"/>
       <c r="D550" s="23"/>
       <c r="E550" s="23"/>
       <c r="F550" s="23"/>
     </row>
-    <row r="551" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="551" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C551" s="24"/>
       <c r="D551" s="22"/>
       <c r="E551" s="22"/>
       <c r="F551" s="22"/>
     </row>
-    <row r="552" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="552" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C552" s="25"/>
       <c r="D552" s="23"/>
       <c r="E552" s="23"/>
       <c r="F552" s="23"/>
     </row>
-    <row r="553" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="553" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C553" s="24"/>
       <c r="D553" s="22"/>
       <c r="E553" s="22"/>
       <c r="F553" s="22"/>
     </row>
-    <row r="554" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="554" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C554" s="25"/>
       <c r="D554" s="23"/>
       <c r="E554" s="23"/>
       <c r="F554" s="23"/>
     </row>
-    <row r="555" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="555" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C555" s="24"/>
       <c r="D555" s="22"/>
       <c r="E555" s="22"/>
       <c r="F555" s="22"/>
     </row>
-    <row r="556" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="556" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C556" s="25"/>
       <c r="D556" s="23"/>
       <c r="E556" s="23"/>
       <c r="F556" s="23"/>
     </row>
-    <row r="557" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="557" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C557" s="24"/>
       <c r="D557" s="22"/>
       <c r="E557" s="22"/>
       <c r="F557" s="22"/>
     </row>
-    <row r="558" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="558" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C558" s="25"/>
       <c r="D558" s="23"/>
       <c r="E558" s="23"/>
       <c r="F558" s="23"/>
     </row>
-    <row r="559" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="559" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C559" s="24"/>
       <c r="D559" s="22"/>
       <c r="E559" s="22"/>
       <c r="F559" s="22"/>
     </row>
-    <row r="560" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="560" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C560" s="25"/>
       <c r="D560" s="23"/>
       <c r="E560" s="23"/>
       <c r="F560" s="23"/>
     </row>
-    <row r="561" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="561" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C561" s="24"/>
       <c r="D561" s="22"/>
       <c r="E561" s="22"/>
       <c r="F561" s="22"/>
     </row>
-    <row r="562" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="562" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C562" s="25"/>
       <c r="D562" s="23"/>
       <c r="E562" s="23"/>
       <c r="F562" s="23"/>
     </row>
-    <row r="563" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="563" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C563" s="24"/>
       <c r="D563" s="22"/>
       <c r="E563" s="22"/>
       <c r="F563" s="22"/>
     </row>
-    <row r="564" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="564" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C564" s="25"/>
       <c r="D564" s="23"/>
       <c r="E564" s="23"/>
       <c r="F564" s="23"/>
     </row>
-    <row r="565" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="565" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C565" s="24"/>
       <c r="D565" s="22"/>
       <c r="E565" s="22"/>
       <c r="F565" s="22"/>
     </row>
-    <row r="566" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="566" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C566" s="25"/>
       <c r="D566" s="23"/>
       <c r="E566" s="23"/>
       <c r="F566" s="23"/>
     </row>
-    <row r="567" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="567" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C567" s="24"/>
       <c r="D567" s="22"/>
       <c r="E567" s="22"/>
       <c r="F567" s="22"/>
     </row>
-    <row r="568" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="568" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C568" s="25"/>
       <c r="D568" s="23"/>
       <c r="E568" s="23"/>
       <c r="F568" s="23"/>
     </row>
-    <row r="569" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="569" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C569" s="24"/>
       <c r="D569" s="22"/>
       <c r="E569" s="22"/>
       <c r="F569" s="22"/>
     </row>
-    <row r="570" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="570" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C570" s="25"/>
       <c r="D570" s="23"/>
       <c r="E570" s="23"/>
       <c r="F570" s="23"/>
     </row>
-    <row r="571" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="571" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C571" s="24"/>
       <c r="D571" s="22"/>
       <c r="E571" s="22"/>
       <c r="F571" s="22"/>
     </row>
-    <row r="572" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="572" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C572" s="25"/>
       <c r="D572" s="23"/>
       <c r="E572" s="23"/>
       <c r="F572" s="23"/>
     </row>
-    <row r="573" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="573" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C573" s="24"/>
       <c r="D573" s="22"/>
       <c r="E573" s="22"/>
       <c r="F573" s="22"/>
     </row>
-    <row r="574" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="574" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C574" s="25"/>
       <c r="D574" s="23"/>
       <c r="E574" s="23"/>
       <c r="F574" s="23"/>
     </row>
-    <row r="575" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="575" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C575" s="24"/>
       <c r="D575" s="22"/>
       <c r="E575" s="22"/>
       <c r="F575" s="22"/>
     </row>
-    <row r="576" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="576" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C576" s="25"/>
       <c r="D576" s="23"/>
       <c r="E576" s="23"/>
       <c r="F576" s="23"/>
     </row>
-    <row r="577" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="577" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C577" s="24"/>
       <c r="D577" s="22"/>
       <c r="E577" s="22"/>
       <c r="F577" s="22"/>
     </row>
-    <row r="578" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="578" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C578" s="25"/>
       <c r="D578" s="23"/>
       <c r="E578" s="23"/>
       <c r="F578" s="23"/>
     </row>
-    <row r="579" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="579" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C579" s="24"/>
       <c r="D579" s="22"/>
       <c r="E579" s="22"/>
       <c r="F579" s="22"/>
     </row>
-    <row r="580" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="580" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C580" s="25"/>
       <c r="D580" s="23"/>
       <c r="E580" s="23"/>
       <c r="F580" s="23"/>
     </row>
-    <row r="581" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="581" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C581" s="24"/>
       <c r="D581" s="22"/>
       <c r="E581" s="22"/>
       <c r="F581" s="22"/>
     </row>
-    <row r="582" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="582" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C582" s="25"/>
       <c r="D582" s="23"/>
       <c r="E582" s="23"/>
       <c r="F582" s="23"/>
     </row>
-    <row r="583" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="583" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C583" s="24"/>
       <c r="D583" s="22"/>
       <c r="E583" s="22"/>
       <c r="F583" s="22"/>
     </row>
-    <row r="584" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="584" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C584" s="25"/>
       <c r="D584" s="23"/>
       <c r="E584" s="23"/>
       <c r="F584" s="23"/>
     </row>
-    <row r="585" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="585" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C585" s="24"/>
       <c r="D585" s="22"/>
       <c r="E585" s="22"/>
       <c r="F585" s="22"/>
     </row>
-    <row r="586" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="586" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C586" s="25"/>
       <c r="D586" s="23"/>
       <c r="E586" s="23"/>
       <c r="F586" s="23"/>
     </row>
-    <row r="587" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="587" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C587" s="24"/>
       <c r="D587" s="22"/>
       <c r="E587" s="22"/>
       <c r="F587" s="22"/>
     </row>
-    <row r="588" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="588" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C588" s="25"/>
       <c r="D588" s="23"/>
       <c r="E588" s="23"/>
       <c r="F588" s="23"/>
     </row>
-    <row r="589" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="589" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C589" s="24"/>
       <c r="D589" s="22"/>
       <c r="E589" s="22"/>
       <c r="F589" s="22"/>
     </row>
-    <row r="590" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="590" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C590" s="25"/>
       <c r="D590" s="23"/>
       <c r="E590" s="23"/>
       <c r="F590" s="23"/>
     </row>
-    <row r="591" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="591" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C591" s="24"/>
       <c r="D591" s="22"/>
       <c r="E591" s="22"/>
       <c r="F591" s="22"/>
     </row>
-    <row r="592" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="592" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C592" s="25"/>
       <c r="D592" s="23"/>
       <c r="E592" s="23"/>
       <c r="F592" s="23"/>
     </row>
-    <row r="593" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="593" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C593" s="24"/>
       <c r="D593" s="22"/>
       <c r="E593" s="22"/>
       <c r="F593" s="22"/>
     </row>
-    <row r="594" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="594" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C594" s="25"/>
       <c r="D594" s="23"/>
       <c r="E594" s="23"/>
       <c r="F594" s="23"/>
     </row>
-    <row r="595" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="595" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C595" s="24"/>
       <c r="D595" s="22"/>
       <c r="E595" s="22"/>
       <c r="F595" s="22"/>
     </row>
-    <row r="596" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="596" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C596" s="25"/>
       <c r="D596" s="23"/>
       <c r="E596" s="23"/>
       <c r="F596" s="23"/>
     </row>
-    <row r="597" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="597" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C597" s="24"/>
       <c r="D597" s="22"/>
       <c r="E597" s="22"/>
       <c r="F597" s="22"/>
     </row>
-    <row r="598" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="598" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C598" s="25"/>
       <c r="D598" s="23"/>
       <c r="E598" s="23"/>
       <c r="F598" s="23"/>
     </row>
-    <row r="599" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="599" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C599" s="24"/>
       <c r="D599" s="22"/>
       <c r="E599" s="22"/>
       <c r="F599" s="22"/>
     </row>
-    <row r="600" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="600" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C600" s="25"/>
       <c r="D600" s="23"/>
       <c r="E600" s="23"/>
       <c r="F600" s="23"/>
     </row>
-    <row r="601" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="601" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C601" s="24"/>
       <c r="D601" s="22"/>
       <c r="E601" s="22"/>
       <c r="F601" s="22"/>
     </row>
-    <row r="602" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="602" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C602" s="25"/>
       <c r="D602" s="23"/>
       <c r="E602" s="23"/>
       <c r="F602" s="23"/>
     </row>
-    <row r="603" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="603" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C603" s="24"/>
       <c r="D603" s="22"/>
       <c r="E603" s="22"/>
       <c r="F603" s="22"/>
     </row>
-    <row r="604" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="604" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C604" s="25"/>
       <c r="D604" s="23"/>
       <c r="E604" s="23"/>
       <c r="F604" s="23"/>
     </row>
-    <row r="605" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="605" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C605" s="24"/>
       <c r="D605" s="22"/>
       <c r="E605" s="22"/>
       <c r="F605" s="22"/>
     </row>
-    <row r="606" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="606" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C606" s="25"/>
       <c r="D606" s="23"/>
       <c r="E606" s="23"/>
       <c r="F606" s="23"/>
     </row>
-    <row r="607" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="607" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C607" s="24"/>
       <c r="D607" s="22"/>
       <c r="E607" s="22"/>
       <c r="F607" s="22"/>
     </row>
-    <row r="608" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="608" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C608" s="25"/>
       <c r="D608" s="23"/>
       <c r="E608" s="23"/>
       <c r="F608" s="23"/>
     </row>
-    <row r="609" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="609" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C609" s="24"/>
       <c r="D609" s="22"/>
       <c r="E609" s="22"/>
       <c r="F609" s="22"/>
     </row>
-    <row r="610" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="610" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C610" s="25"/>
       <c r="D610" s="23"/>
       <c r="E610" s="23"/>
       <c r="F610" s="23"/>
     </row>
-    <row r="611" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="611" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C611" s="24"/>
       <c r="D611" s="22"/>
       <c r="E611" s="22"/>
       <c r="F611" s="22"/>
     </row>
-    <row r="612" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="612" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C612" s="25"/>
       <c r="D612" s="23"/>
       <c r="E612" s="23"/>
       <c r="F612" s="23"/>
     </row>
-    <row r="613" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="613" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C613" s="24"/>
       <c r="D613" s="22"/>
       <c r="E613" s="22"/>
       <c r="F613" s="22"/>
     </row>
-    <row r="614" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="614" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C614" s="25"/>
       <c r="D614" s="23"/>
       <c r="E614" s="23"/>
       <c r="F614" s="23"/>
     </row>
-    <row r="615" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="615" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C615" s="24"/>
       <c r="D615" s="22"/>
       <c r="E615" s="22"/>
       <c r="F615" s="22"/>
     </row>
-    <row r="616" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="616" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C616" s="25"/>
       <c r="D616" s="23"/>
       <c r="E616" s="23"/>
       <c r="F616" s="23"/>
     </row>
-    <row r="617" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="617" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C617" s="24"/>
       <c r="D617" s="22"/>
       <c r="E617" s="22"/>
       <c r="F617" s="22"/>
     </row>
-    <row r="618" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="618" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C618" s="25"/>
       <c r="D618" s="23"/>
       <c r="E618" s="23"/>
       <c r="F618" s="23"/>
     </row>
-    <row r="619" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="619" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C619" s="24"/>
       <c r="D619" s="22"/>
       <c r="E619" s="22"/>
       <c r="F619" s="22"/>
     </row>
-    <row r="620" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="620" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C620" s="25"/>
       <c r="D620" s="23"/>
       <c r="E620" s="23"/>
       <c r="F620" s="23"/>
     </row>
-    <row r="621" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="621" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C621" s="24"/>
       <c r="D621" s="22"/>
       <c r="E621" s="22"/>
       <c r="F621" s="22"/>
     </row>
-    <row r="622" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="622" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C622" s="25"/>
       <c r="D622" s="23"/>
       <c r="E622" s="23"/>
       <c r="F622" s="23"/>
     </row>
-    <row r="623" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="623" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C623" s="24"/>
       <c r="D623" s="22"/>
       <c r="E623" s="22"/>
       <c r="F623" s="22"/>
     </row>
-    <row r="624" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="624" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C624" s="25"/>
       <c r="D624" s="23"/>
       <c r="E624" s="23"/>
       <c r="F624" s="23"/>
     </row>
-    <row r="625" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="625" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C625" s="24"/>
       <c r="D625" s="22"/>
       <c r="E625" s="22"/>
       <c r="F625" s="22"/>
     </row>
-    <row r="626" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="626" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C626" s="25"/>
       <c r="D626" s="23"/>
       <c r="E626" s="23"/>
       <c r="F626" s="23"/>
     </row>
-    <row r="627" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="627" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C627" s="24"/>
       <c r="D627" s="22"/>
       <c r="E627" s="22"/>
       <c r="F627" s="22"/>
     </row>
-    <row r="628" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="628" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C628" s="25"/>
       <c r="D628" s="23"/>
       <c r="E628" s="23"/>
       <c r="F628" s="23"/>
     </row>
-    <row r="629" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="629" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C629" s="24"/>
       <c r="D629" s="22"/>
       <c r="E629" s="22"/>
       <c r="F629" s="22"/>
     </row>
-    <row r="630" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="630" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C630" s="25"/>
       <c r="D630" s="23"/>
       <c r="E630" s="23"/>
       <c r="F630" s="23"/>
     </row>
-    <row r="631" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="631" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C631" s="24"/>
       <c r="D631" s="22"/>
       <c r="E631" s="22"/>
       <c r="F631" s="22"/>
     </row>
-    <row r="632" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="632" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C632" s="25"/>
       <c r="D632" s="23"/>
       <c r="E632" s="23"/>
       <c r="F632" s="23"/>
     </row>
-    <row r="633" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="633" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C633" s="24"/>
       <c r="D633" s="22"/>
       <c r="E633" s="22"/>
       <c r="F633" s="22"/>
     </row>
-    <row r="634" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="634" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C634" s="25"/>
       <c r="D634" s="23"/>
       <c r="E634" s="23"/>
       <c r="F634" s="23"/>
     </row>
-    <row r="635" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="635" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C635" s="24"/>
       <c r="D635" s="22"/>
       <c r="E635" s="22"/>
       <c r="F635" s="22"/>
     </row>
-    <row r="636" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="636" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C636" s="25"/>
       <c r="D636" s="23"/>
       <c r="E636" s="23"/>
       <c r="F636" s="23"/>
     </row>
-    <row r="637" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="637" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C637" s="24"/>
       <c r="D637" s="22"/>
       <c r="E637" s="22"/>
       <c r="F637" s="22"/>
     </row>
-    <row r="638" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="638" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C638" s="25"/>
       <c r="D638" s="23"/>
       <c r="E638" s="23"/>
       <c r="F638" s="23"/>
     </row>
-    <row r="639" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="639" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C639" s="24"/>
       <c r="D639" s="22"/>
       <c r="E639" s="22"/>
       <c r="F639" s="22"/>
     </row>
-    <row r="640" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="640" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C640" s="25"/>
       <c r="D640" s="23"/>
       <c r="E640" s="23"/>
       <c r="F640" s="23"/>
     </row>
-    <row r="641" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="641" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C641" s="24"/>
       <c r="D641" s="22"/>
       <c r="E641" s="22"/>
       <c r="F641" s="22"/>
     </row>
-    <row r="642" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="642" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C642" s="25"/>
       <c r="D642" s="23"/>
       <c r="E642" s="23"/>
       <c r="F642" s="23"/>
     </row>
-    <row r="643" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="643" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C643" s="24"/>
       <c r="D643" s="22"/>
       <c r="E643" s="22"/>
       <c r="F643" s="22"/>
     </row>
-    <row r="644" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="644" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C644" s="25"/>
       <c r="D644" s="23"/>
       <c r="E644" s="23"/>
       <c r="F644" s="23"/>
     </row>
-    <row r="645" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="645" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C645" s="24"/>
       <c r="D645" s="22"/>
       <c r="E645" s="22"/>
       <c r="F645" s="22"/>
     </row>
-    <row r="646" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="646" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C646" s="25"/>
       <c r="D646" s="23"/>
       <c r="E646" s="23"/>
       <c r="F646" s="23"/>
     </row>
-    <row r="647" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="647" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C647" s="24"/>
       <c r="D647" s="22"/>
       <c r="E647" s="22"/>
       <c r="F647" s="22"/>
     </row>
-    <row r="648" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="648" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C648" s="25"/>
       <c r="D648" s="23"/>
       <c r="E648" s="23"/>
       <c r="F648" s="23"/>
     </row>
-    <row r="649" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="649" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C649" s="24"/>
       <c r="D649" s="22"/>
       <c r="E649" s="22"/>
       <c r="F649" s="22"/>
     </row>
-    <row r="650" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="650" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C650" s="25"/>
       <c r="D650" s="23"/>
       <c r="E650" s="23"/>
       <c r="F650" s="23"/>
     </row>
-    <row r="651" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="651" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C651" s="24"/>
       <c r="D651" s="22"/>
       <c r="E651" s="22"/>
       <c r="F651" s="22"/>
     </row>
-    <row r="652" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="652" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C652" s="25"/>
       <c r="D652" s="23"/>
       <c r="E652" s="23"/>
       <c r="F652" s="23"/>
     </row>
-    <row r="653" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="653" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C653" s="24"/>
       <c r="D653" s="22"/>
       <c r="E653" s="22"/>
       <c r="F653" s="22"/>
     </row>
-    <row r="654" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="654" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C654" s="25"/>
       <c r="D654" s="23"/>
       <c r="E654" s="23"/>
       <c r="F654" s="23"/>
     </row>
-    <row r="655" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="655" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C655" s="24"/>
       <c r="D655" s="22"/>
       <c r="E655" s="22"/>
       <c r="F655" s="22"/>
     </row>
-    <row r="656" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="656" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C656" s="25"/>
       <c r="D656" s="23"/>
       <c r="E656" s="23"/>
       <c r="F656" s="23"/>
     </row>
-    <row r="657" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="657" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C657" s="24"/>
       <c r="D657" s="22"/>
       <c r="E657" s="22"/>
       <c r="F657" s="22"/>
     </row>
-    <row r="658" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="658" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C658" s="25"/>
       <c r="D658" s="23"/>
       <c r="E658" s="23"/>
       <c r="F658" s="23"/>
     </row>
-    <row r="659" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="659" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C659" s="24"/>
       <c r="D659" s="22"/>
       <c r="E659" s="22"/>
       <c r="F659" s="22"/>
     </row>
-    <row r="660" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="660" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C660" s="25"/>
       <c r="D660" s="23"/>
       <c r="E660" s="23"/>
       <c r="F660" s="23"/>
     </row>
-    <row r="661" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="661" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C661" s="24"/>
       <c r="D661" s="22"/>
       <c r="E661" s="22"/>
       <c r="F661" s="22"/>
     </row>
-    <row r="662" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="662" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C662" s="25"/>
       <c r="D662" s="23"/>
       <c r="E662" s="23"/>
       <c r="F662" s="23"/>
     </row>
-    <row r="663" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="663" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C663" s="24"/>
       <c r="D663" s="22"/>
       <c r="E663" s="22"/>
       <c r="F663" s="22"/>
     </row>
-    <row r="664" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="664" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C664" s="25"/>
       <c r="D664" s="23"/>
       <c r="E664" s="23"/>
       <c r="F664" s="23"/>
     </row>
-    <row r="665" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="665" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C665" s="24"/>
       <c r="D665" s="22"/>
       <c r="E665" s="22"/>
       <c r="F665" s="22"/>
     </row>
-    <row r="666" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="666" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C666" s="25"/>
       <c r="D666" s="23"/>
       <c r="E666" s="23"/>
       <c r="F666" s="23"/>
     </row>
-    <row r="667" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="667" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C667" s="24"/>
       <c r="D667" s="22"/>
       <c r="E667" s="22"/>
       <c r="F667" s="22"/>
     </row>
-    <row r="668" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="668" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C668" s="25"/>
       <c r="D668" s="23"/>
       <c r="E668" s="23"/>
       <c r="F668" s="23"/>
     </row>
-    <row r="669" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="669" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C669" s="24"/>
       <c r="D669" s="22"/>
       <c r="E669" s="22"/>
       <c r="F669" s="22"/>
     </row>
-    <row r="670" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="670" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C670" s="25"/>
       <c r="D670" s="23"/>
       <c r="E670" s="23"/>
       <c r="F670" s="23"/>
     </row>
-    <row r="671" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="671" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C671" s="24"/>
       <c r="D671" s="22"/>
       <c r="E671" s="22"/>
       <c r="F671" s="22"/>
     </row>
-    <row r="672" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="672" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C672" s="25"/>
       <c r="D672" s="23"/>
       <c r="E672" s="23"/>
       <c r="F672" s="23"/>
     </row>
-    <row r="673" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="673" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C673" s="24"/>
       <c r="D673" s="22"/>
       <c r="E673" s="22"/>
       <c r="F673" s="22"/>
     </row>
-    <row r="674" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="674" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C674" s="25"/>
       <c r="D674" s="23"/>
       <c r="E674" s="23"/>
       <c r="F674" s="23"/>
     </row>
-    <row r="675" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="675" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C675" s="24"/>
       <c r="D675" s="22"/>
       <c r="E675" s="22"/>
       <c r="F675" s="22"/>
     </row>
-    <row r="676" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="676" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C676" s="25"/>
       <c r="D676" s="23"/>
       <c r="E676" s="23"/>
       <c r="F676" s="23"/>
     </row>
-    <row r="677" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="677" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C677" s="24"/>
       <c r="D677" s="22"/>
       <c r="E677" s="22"/>
       <c r="F677" s="22"/>
     </row>
-    <row r="678" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="678" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C678" s="25"/>
       <c r="D678" s="23"/>
       <c r="E678" s="23"/>
       <c r="F678" s="23"/>
     </row>
-    <row r="679" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="679" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C679" s="24"/>
       <c r="D679" s="22"/>
       <c r="E679" s="22"/>
       <c r="F679" s="22"/>
     </row>
-    <row r="680" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="680" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C680" s="25"/>
       <c r="D680" s="23"/>
       <c r="E680" s="23"/>
       <c r="F680" s="23"/>
     </row>
-    <row r="681" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="681" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C681" s="24"/>
       <c r="D681" s="22"/>
       <c r="E681" s="22"/>
       <c r="F681" s="22"/>
     </row>
-    <row r="682" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="682" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C682" s="25"/>
       <c r="D682" s="23"/>
       <c r="E682" s="23"/>
       <c r="F682" s="23"/>
     </row>
-    <row r="683" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="683" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C683" s="24"/>
       <c r="D683" s="22"/>
       <c r="E683" s="22"/>
       <c r="F683" s="22"/>
     </row>
-    <row r="684" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="684" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C684" s="25"/>
       <c r="D684" s="23"/>
       <c r="E684" s="23"/>
       <c r="F684" s="23"/>
     </row>
-    <row r="685" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="685" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C685" s="24"/>
       <c r="D685" s="22"/>
       <c r="E685" s="22"/>
       <c r="F685" s="22"/>
     </row>
-    <row r="686" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="686" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C686" s="25"/>
       <c r="D686" s="23"/>
       <c r="E686" s="23"/>
       <c r="F686" s="23"/>
     </row>
-    <row r="687" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="687" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C687" s="24"/>
       <c r="D687" s="22"/>
       <c r="E687" s="22"/>
       <c r="F687" s="22"/>
     </row>
-    <row r="688" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="688" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C688" s="25"/>
       <c r="D688" s="23"/>
       <c r="E688" s="23"/>
       <c r="F688" s="23"/>
     </row>
-    <row r="689" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="689" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C689" s="24"/>
       <c r="D689" s="22"/>
       <c r="E689" s="22"/>
       <c r="F689" s="22"/>
     </row>
-    <row r="690" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="690" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C690" s="25"/>
       <c r="D690" s="23"/>
       <c r="E690" s="23"/>
       <c r="F690" s="23"/>
     </row>
-    <row r="691" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="691" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C691" s="24"/>
       <c r="D691" s="22"/>
       <c r="E691" s="22"/>
       <c r="F691" s="22"/>
     </row>
-    <row r="692" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="692" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C692" s="25"/>
       <c r="D692" s="23"/>
       <c r="E692" s="23"/>
       <c r="F692" s="23"/>
     </row>
-    <row r="693" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="693" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C693" s="24"/>
       <c r="D693" s="22"/>
       <c r="E693" s="22"/>
       <c r="F693" s="22"/>
     </row>
-    <row r="694" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="694" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C694" s="25"/>
       <c r="D694" s="23"/>
       <c r="E694" s="23"/>
       <c r="F694" s="23"/>
     </row>
-    <row r="695" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="695" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C695" s="24"/>
       <c r="D695" s="22"/>
       <c r="E695" s="22"/>
       <c r="F695" s="22"/>
     </row>
-    <row r="696" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="696" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C696" s="25"/>
       <c r="D696" s="23"/>
       <c r="E696" s="23"/>
       <c r="F696" s="23"/>
     </row>
-    <row r="697" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="697" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C697" s="24"/>
       <c r="D697" s="22"/>
       <c r="E697" s="22"/>
       <c r="F697" s="22"/>
     </row>
-    <row r="698" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="698" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C698" s="25"/>
       <c r="D698" s="23"/>
       <c r="E698" s="23"/>
       <c r="F698" s="23"/>
     </row>
-    <row r="699" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="699" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C699" s="24"/>
       <c r="D699" s="22"/>
       <c r="E699" s="22"/>
       <c r="F699" s="22"/>
     </row>
-    <row r="700" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="700" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C700" s="25"/>
       <c r="D700" s="23"/>
       <c r="E700" s="23"/>
       <c r="F700" s="23"/>
     </row>
-    <row r="701" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="701" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C701" s="24"/>
       <c r="D701" s="22"/>
       <c r="E701" s="22"/>
       <c r="F701" s="22"/>
     </row>
-    <row r="702" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="702" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C702" s="25"/>
       <c r="D702" s="23"/>
       <c r="E702" s="23"/>
       <c r="F702" s="23"/>
     </row>
-    <row r="703" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="703" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C703" s="24"/>
       <c r="D703" s="22"/>
       <c r="E703" s="22"/>
       <c r="F703" s="22"/>
     </row>
-    <row r="704" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="704" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C704" s="25"/>
       <c r="D704" s="23"/>
       <c r="E704" s="23"/>
       <c r="F704" s="23"/>
     </row>
-    <row r="705" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="705" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C705" s="24"/>
       <c r="D705" s="22"/>
       <c r="E705" s="22"/>
       <c r="F705" s="22"/>
     </row>
-    <row r="706" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="706" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C706" s="25"/>
       <c r="D706" s="23"/>
       <c r="E706" s="23"/>
       <c r="F706" s="23"/>
     </row>
-    <row r="707" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="707" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C707" s="24"/>
       <c r="D707" s="22"/>
       <c r="E707" s="22"/>
       <c r="F707" s="22"/>
     </row>
-    <row r="708" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="708" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C708" s="25"/>
       <c r="D708" s="23"/>
       <c r="E708" s="23"/>
       <c r="F708" s="23"/>
     </row>
-    <row r="709" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="709" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C709" s="24"/>
       <c r="D709" s="22"/>
       <c r="E709" s="22"/>
       <c r="F709" s="22"/>
     </row>
-    <row r="710" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="710" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C710" s="25"/>
       <c r="D710" s="23"/>
       <c r="E710" s="23"/>
       <c r="F710" s="23"/>
     </row>
-    <row r="711" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="711" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C711" s="24"/>
       <c r="D711" s="22"/>
       <c r="E711" s="22"/>
       <c r="F711" s="22"/>
     </row>
-    <row r="712" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="712" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C712" s="25"/>
       <c r="D712" s="23"/>
       <c r="E712" s="23"/>
       <c r="F712" s="23"/>
     </row>
-    <row r="713" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="713" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C713" s="24"/>
       <c r="D713" s="22"/>
       <c r="E713" s="22"/>
       <c r="F713" s="22"/>
     </row>
-    <row r="714" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="714" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C714" s="25"/>
       <c r="D714" s="23"/>
       <c r="E714" s="23"/>
       <c r="F714" s="23"/>
     </row>
-    <row r="715" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="715" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C715" s="24"/>
       <c r="D715" s="22"/>
       <c r="E715" s="22"/>
       <c r="F715" s="22"/>
     </row>
-    <row r="716" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="716" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C716" s="25"/>
       <c r="D716" s="23"/>
       <c r="E716" s="23"/>
       <c r="F716" s="23"/>
     </row>
-    <row r="717" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="717" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C717" s="24"/>
       <c r="D717" s="22"/>
       <c r="E717" s="22"/>
       <c r="F717" s="22"/>
     </row>
-    <row r="718" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="718" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C718" s="25"/>
       <c r="D718" s="23"/>
       <c r="E718" s="23"/>
       <c r="F718" s="23"/>
     </row>
-    <row r="719" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="719" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C719" s="24"/>
       <c r="D719" s="22"/>
       <c r="E719" s="22"/>
       <c r="F719" s="22"/>
     </row>
-    <row r="720" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="720" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C720" s="25"/>
       <c r="D720" s="23"/>
       <c r="E720" s="23"/>
       <c r="F720" s="23"/>
     </row>
-    <row r="721" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="721" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C721" s="24"/>
       <c r="D721" s="22"/>
       <c r="E721" s="22"/>
       <c r="F721" s="22"/>
     </row>
-    <row r="722" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="722" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C722" s="25"/>
       <c r="D722" s="23"/>
       <c r="E722" s="23"/>
       <c r="F722" s="23"/>
     </row>
-    <row r="723" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="723" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C723" s="24"/>
       <c r="D723" s="22"/>
       <c r="E723" s="22"/>
       <c r="F723" s="22"/>
     </row>
-    <row r="724" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="724" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C724" s="25"/>
       <c r="D724" s="23"/>
       <c r="E724" s="23"/>
       <c r="F724" s="23"/>
     </row>
-    <row r="725" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="725" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C725" s="24"/>
       <c r="D725" s="22"/>
       <c r="E725" s="22"/>
       <c r="F725" s="22"/>
     </row>
-    <row r="726" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="726" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C726" s="25"/>
       <c r="D726" s="23"/>
       <c r="E726" s="23"/>
       <c r="F726" s="23"/>
     </row>
-    <row r="727" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="727" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C727" s="24"/>
       <c r="D727" s="22"/>
       <c r="E727" s="22"/>
       <c r="F727" s="22"/>
     </row>
-    <row r="728" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="728" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C728" s="25"/>
       <c r="D728" s="23"/>
       <c r="E728" s="23"/>
       <c r="F728" s="23"/>
     </row>
-    <row r="729" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="729" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C729" s="24"/>
       <c r="D729" s="22"/>
       <c r="E729" s="22"/>
       <c r="F729" s="22"/>
     </row>
-    <row r="730" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="730" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C730" s="25"/>
       <c r="D730" s="23"/>
       <c r="E730" s="23"/>
       <c r="F730" s="23"/>
     </row>
-    <row r="731" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="731" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C731" s="24"/>
       <c r="D731" s="22"/>
       <c r="E731" s="22"/>
       <c r="F731" s="22"/>
     </row>
-    <row r="732" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="732" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C732" s="25"/>
       <c r="D732" s="23"/>
       <c r="E732" s="23"/>
       <c r="F732" s="23"/>
     </row>
-    <row r="733" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="733" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C733" s="24"/>
       <c r="D733" s="22"/>
       <c r="E733" s="22"/>
       <c r="F733" s="22"/>
     </row>
-    <row r="734" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="734" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C734" s="25"/>
       <c r="D734" s="23"/>
       <c r="E734" s="23"/>
       <c r="F734" s="23"/>
     </row>
-    <row r="735" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="735" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C735" s="24"/>
       <c r="D735" s="22"/>
       <c r="E735" s="22"/>
       <c r="F735" s="22"/>
     </row>
-    <row r="736" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="736" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C736" s="25"/>
       <c r="D736" s="23"/>
       <c r="E736" s="23"/>
       <c r="F736" s="23"/>
     </row>
-    <row r="737" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="737" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C737" s="24"/>
       <c r="D737" s="22"/>
       <c r="E737" s="22"/>
       <c r="F737" s="22"/>
     </row>
-    <row r="738" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="738" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C738" s="25"/>
       <c r="D738" s="23"/>
       <c r="E738" s="23"/>
       <c r="F738" s="23"/>
     </row>
-    <row r="739" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="739" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C739" s="24"/>
       <c r="D739" s="22"/>
       <c r="E739" s="22"/>
       <c r="F739" s="22"/>
     </row>
-    <row r="740" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="740" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C740" s="25"/>
       <c r="D740" s="23"/>
       <c r="E740" s="23"/>
       <c r="F740" s="23"/>
     </row>
-    <row r="741" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="741" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C741" s="24"/>
       <c r="D741" s="22"/>
       <c r="E741" s="22"/>
       <c r="F741" s="22"/>
     </row>
-    <row r="742" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="742" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C742" s="25"/>
       <c r="D742" s="23"/>
       <c r="E742" s="23"/>
       <c r="F742" s="23"/>
     </row>
-    <row r="743" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="743" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C743" s="24"/>
       <c r="D743" s="22"/>
       <c r="E743" s="22"/>
       <c r="F743" s="22"/>
     </row>
-    <row r="744" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="744" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C744" s="25"/>
       <c r="D744" s="23"/>
       <c r="E744" s="23"/>
       <c r="F744" s="23"/>
     </row>
-    <row r="745" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="745" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C745" s="24"/>
       <c r="D745" s="22"/>
       <c r="E745" s="22"/>
       <c r="F745" s="22"/>
     </row>
-    <row r="746" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="746" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C746" s="25"/>
       <c r="D746" s="23"/>
       <c r="E746" s="23"/>
       <c r="F746" s="23"/>
     </row>
-    <row r="747" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="747" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C747" s="24"/>
       <c r="D747" s="22"/>
       <c r="E747" s="22"/>
       <c r="F747" s="22"/>
     </row>
-    <row r="748" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="748" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C748" s="25"/>
       <c r="D748" s="23"/>
       <c r="E748" s="23"/>
       <c r="F748" s="23"/>
     </row>
-    <row r="749" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="749" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C749" s="24"/>
       <c r="D749" s="22"/>
       <c r="E749" s="22"/>
       <c r="F749" s="22"/>
     </row>
-    <row r="750" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="750" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C750" s="25"/>
       <c r="D750" s="23"/>
       <c r="E750" s="23"/>
       <c r="F750" s="23"/>
     </row>
-    <row r="751" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="751" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C751" s="24"/>
       <c r="D751" s="22"/>
       <c r="E751" s="22"/>
       <c r="F751" s="22"/>
     </row>
-    <row r="752" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="752" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C752" s="25"/>
       <c r="D752" s="23"/>
       <c r="E752" s="23"/>
       <c r="F752" s="23"/>
     </row>
-    <row r="753" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="753" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C753" s="24"/>
       <c r="D753" s="22"/>
       <c r="E753" s="22"/>
       <c r="F753" s="22"/>
     </row>
-    <row r="754" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="754" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C754" s="25"/>
       <c r="D754" s="23"/>
       <c r="E754" s="23"/>
       <c r="F754" s="23"/>
     </row>
-    <row r="755" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="755" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C755" s="24"/>
       <c r="D755" s="22"/>
       <c r="E755" s="22"/>
       <c r="F755" s="22"/>
     </row>
-    <row r="756" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="756" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C756" s="25"/>
       <c r="D756" s="23"/>
       <c r="E756" s="23"/>
       <c r="F756" s="23"/>
     </row>
-    <row r="757" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="757" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C757" s="24"/>
       <c r="D757" s="22"/>
       <c r="E757" s="22"/>
       <c r="F757" s="22"/>
     </row>
-    <row r="758" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="758" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C758" s="25"/>
       <c r="D758" s="23"/>
       <c r="E758" s="23"/>
       <c r="F758" s="23"/>
     </row>
-    <row r="759" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="759" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C759" s="24"/>
       <c r="D759" s="22"/>
       <c r="E759" s="22"/>
       <c r="F759" s="22"/>
     </row>
-    <row r="760" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="760" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C760" s="25"/>
       <c r="D760" s="23"/>
       <c r="E760" s="23"/>
       <c r="F760" s="23"/>
     </row>
-    <row r="761" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="761" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C761" s="24"/>
       <c r="D761" s="22"/>
       <c r="E761" s="22"/>
       <c r="F761" s="22"/>
     </row>
-    <row r="762" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="762" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C762" s="25"/>
       <c r="D762" s="23"/>
       <c r="E762" s="23"/>
       <c r="F762" s="23"/>
     </row>
-    <row r="763" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="763" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C763" s="24"/>
       <c r="D763" s="22"/>
       <c r="E763" s="22"/>
       <c r="F763" s="22"/>
     </row>
-    <row r="764" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="764" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C764" s="25"/>
       <c r="D764" s="23"/>
       <c r="E764" s="23"/>
       <c r="F764" s="23"/>
     </row>
-    <row r="765" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="765" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C765" s="24"/>
       <c r="D765" s="22"/>
       <c r="E765" s="22"/>
       <c r="F765" s="22"/>
     </row>
-    <row r="766" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="766" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C766" s="25"/>
       <c r="D766" s="23"/>
       <c r="E766" s="23"/>
       <c r="F766" s="23"/>
     </row>
-    <row r="767" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="767" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C767" s="24"/>
       <c r="D767" s="22"/>
       <c r="E767" s="22"/>
       <c r="F767" s="22"/>
     </row>
-    <row r="768" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="768" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C768" s="25"/>
       <c r="D768" s="23"/>
       <c r="E768" s="23"/>
       <c r="F768" s="23"/>
     </row>
-    <row r="769" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="769" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C769" s="24"/>
       <c r="D769" s="22"/>
       <c r="E769" s="22"/>
       <c r="F769" s="22"/>
     </row>
-    <row r="770" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="770" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C770" s="25"/>
       <c r="D770" s="23"/>
       <c r="E770" s="23"/>
       <c r="F770" s="23"/>
     </row>
-    <row r="771" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="771" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C771" s="24"/>
       <c r="D771" s="22"/>
       <c r="E771" s="22"/>
       <c r="F771" s="22"/>
     </row>
-    <row r="772" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="772" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C772" s="25"/>
       <c r="D772" s="23"/>
       <c r="E772" s="23"/>
       <c r="F772" s="23"/>
     </row>
-    <row r="773" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="773" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C773" s="24"/>
       <c r="D773" s="22"/>
       <c r="E773" s="22"/>
       <c r="F773" s="22"/>
     </row>
-    <row r="774" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="774" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C774" s="25"/>
       <c r="D774" s="23"/>
       <c r="E774" s="23"/>
       <c r="F774" s="23"/>
     </row>
-    <row r="775" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="775" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C775" s="24"/>
       <c r="D775" s="22"/>
       <c r="E775" s="22"/>
       <c r="F775" s="22"/>
     </row>
-    <row r="776" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="776" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C776" s="25"/>
       <c r="D776" s="23"/>
       <c r="E776" s="23"/>
       <c r="F776" s="23"/>
     </row>
-    <row r="777" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="777" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C777" s="24"/>
       <c r="D777" s="22"/>
       <c r="E777" s="22"/>
       <c r="F777" s="22"/>
     </row>
-    <row r="778" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="778" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C778" s="25"/>
       <c r="D778" s="23"/>
       <c r="E778" s="23"/>
       <c r="F778" s="23"/>
     </row>
-    <row r="779" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="779" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C779" s="24"/>
       <c r="D779" s="22"/>
       <c r="E779" s="22"/>
       <c r="F779" s="22"/>
     </row>
-    <row r="780" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="780" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C780" s="25"/>
       <c r="D780" s="23"/>
       <c r="E780" s="23"/>
       <c r="F780" s="23"/>
     </row>
-    <row r="781" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="781" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C781" s="24"/>
       <c r="D781" s="22"/>
       <c r="E781" s="22"/>
       <c r="F781" s="22"/>
     </row>
-    <row r="782" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="782" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C782" s="25"/>
       <c r="D782" s="23"/>
       <c r="E782" s="23"/>
       <c r="F782" s="23"/>
     </row>
-    <row r="783" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="783" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C783" s="24"/>
       <c r="D783" s="22"/>
       <c r="E783" s="22"/>
       <c r="F783" s="22"/>
     </row>
-    <row r="784" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="784" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C784" s="25"/>
       <c r="D784" s="23"/>
       <c r="E784" s="23"/>
       <c r="F784" s="23"/>
     </row>
-    <row r="785" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="785" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C785" s="24"/>
       <c r="D785" s="22"/>
       <c r="E785" s="22"/>
       <c r="F785" s="22"/>
     </row>
-    <row r="786" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="786" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C786" s="25"/>
       <c r="D786" s="23"/>
       <c r="E786" s="23"/>
       <c r="F786" s="23"/>
     </row>
-    <row r="787" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="787" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C787" s="24"/>
       <c r="D787" s="22"/>
       <c r="E787" s="22"/>
       <c r="F787" s="22"/>
     </row>
-    <row r="788" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="788" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C788" s="25"/>
       <c r="D788" s="23"/>
       <c r="E788" s="23"/>
       <c r="F788" s="23"/>
     </row>
-    <row r="789" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="789" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C789" s="24"/>
       <c r="D789" s="22"/>
       <c r="E789" s="22"/>
       <c r="F789" s="22"/>
     </row>
-    <row r="790" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="790" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C790" s="25"/>
       <c r="D790" s="23"/>
       <c r="E790" s="23"/>
       <c r="F790" s="23"/>
     </row>
-    <row r="791" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="791" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C791" s="24"/>
       <c r="D791" s="22"/>
       <c r="E791" s="22"/>
       <c r="F791" s="22"/>
     </row>
-    <row r="792" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="792" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C792" s="25"/>
       <c r="D792" s="23"/>
       <c r="E792" s="23"/>
       <c r="F792" s="23"/>
     </row>
-    <row r="793" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="793" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C793" s="24"/>
       <c r="D793" s="22"/>
       <c r="E793" s="22"/>
       <c r="F793" s="22"/>
     </row>
-    <row r="794" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="794" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C794" s="25"/>
       <c r="D794" s="23"/>
       <c r="E794" s="23"/>
       <c r="F794" s="23"/>
     </row>
-    <row r="795" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="795" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C795" s="24"/>
       <c r="D795" s="22"/>
       <c r="E795" s="22"/>
       <c r="F795" s="22"/>
     </row>
-    <row r="796" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="796" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C796" s="25"/>
       <c r="D796" s="23"/>
       <c r="E796" s="23"/>
       <c r="F796" s="23"/>
     </row>
-    <row r="797" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="797" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C797" s="24"/>
       <c r="D797" s="22"/>
       <c r="E797" s="22"/>
       <c r="F797" s="22"/>
     </row>
-    <row r="798" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="798" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C798" s="25"/>
       <c r="D798" s="23"/>
       <c r="E798" s="23"/>
       <c r="F798" s="23"/>
     </row>
-    <row r="799" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="799" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C799" s="24"/>
       <c r="D799" s="22"/>
       <c r="E799" s="22"/>
       <c r="F799" s="22"/>
     </row>
-    <row r="800" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="800" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C800" s="25"/>
       <c r="D800" s="23"/>
       <c r="E800" s="23"/>
       <c r="F800" s="23"/>
     </row>
-    <row r="801" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="801" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C801" s="24"/>
       <c r="D801" s="22"/>
       <c r="E801" s="22"/>
       <c r="F801" s="22"/>
     </row>
-    <row r="802" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="802" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C802" s="25"/>
       <c r="D802" s="23"/>
       <c r="E802" s="23"/>
       <c r="F802" s="23"/>
     </row>
-    <row r="803" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="803" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C803" s="24"/>
       <c r="D803" s="22"/>
       <c r="E803" s="22"/>
       <c r="F803" s="22"/>
     </row>
-    <row r="804" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="804" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C804" s="25"/>
       <c r="D804" s="23"/>
       <c r="E804" s="23"/>
       <c r="F804" s="23"/>
     </row>
-    <row r="805" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="805" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C805" s="24"/>
       <c r="D805" s="22"/>
       <c r="E805" s="22"/>
       <c r="F805" s="22"/>
     </row>
-    <row r="806" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="806" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C806" s="25"/>
       <c r="D806" s="23"/>
       <c r="E806" s="23"/>
       <c r="F806" s="23"/>
     </row>
-    <row r="807" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="807" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C807" s="24"/>
       <c r="D807" s="22"/>
       <c r="E807" s="22"/>
       <c r="F807" s="22"/>
     </row>
-    <row r="808" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="808" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C808" s="25"/>
       <c r="D808" s="23"/>
       <c r="E808" s="23"/>
       <c r="F808" s="23"/>
     </row>
-    <row r="809" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="809" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C809" s="24"/>
       <c r="D809" s="22"/>
       <c r="E809" s="22"/>
       <c r="F809" s="22"/>
     </row>
-    <row r="810" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="810" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C810" s="25"/>
       <c r="D810" s="23"/>
       <c r="E810" s="23"/>
       <c r="F810" s="23"/>
     </row>
-    <row r="811" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="811" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C811" s="24"/>
       <c r="D811" s="22"/>
       <c r="E811" s="22"/>
       <c r="F811" s="22"/>
     </row>
-    <row r="812" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="812" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C812" s="25"/>
       <c r="D812" s="23"/>
       <c r="E812" s="23"/>
       <c r="F812" s="23"/>
     </row>
-    <row r="813" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="813" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C813" s="24"/>
       <c r="D813" s="22"/>
       <c r="E813" s="22"/>
       <c r="F813" s="22"/>
     </row>
-    <row r="814" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="814" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C814" s="25"/>
       <c r="D814" s="23"/>
       <c r="E814" s="23"/>
       <c r="F814" s="23"/>
     </row>
-    <row r="815" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="815" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C815" s="24"/>
       <c r="D815" s="22"/>
       <c r="E815" s="22"/>
       <c r="F815" s="22"/>
     </row>
-    <row r="816" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="816" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C816" s="25"/>
       <c r="D816" s="23"/>
       <c r="E816" s="23"/>
       <c r="F816" s="23"/>
     </row>
-    <row r="817" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="817" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C817" s="24"/>
       <c r="D817" s="22"/>
       <c r="E817" s="22"/>
       <c r="F817" s="22"/>
     </row>
-    <row r="818" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="818" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C818" s="25"/>
       <c r="D818" s="23"/>
       <c r="E818" s="23"/>
       <c r="F818" s="23"/>
     </row>
-    <row r="819" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="819" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C819" s="24"/>
       <c r="D819" s="22"/>
       <c r="E819" s="22"/>
       <c r="F819" s="22"/>
     </row>
-    <row r="820" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="820" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C820" s="25"/>
       <c r="D820" s="23"/>
       <c r="E820" s="23"/>
       <c r="F820" s="23"/>
     </row>
-    <row r="821" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="821" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C821" s="24"/>
       <c r="D821" s="22"/>
       <c r="E821" s="22"/>
       <c r="F821" s="22"/>
     </row>
-    <row r="822" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="822" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C822" s="25"/>
       <c r="D822" s="23"/>
       <c r="E822" s="23"/>
       <c r="F822" s="23"/>
     </row>
-    <row r="823" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="823" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C823" s="24"/>
       <c r="D823" s="22"/>
       <c r="E823" s="22"/>
       <c r="F823" s="22"/>
     </row>
-    <row r="824" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="824" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C824" s="25"/>
       <c r="D824" s="23"/>
       <c r="E824" s="23"/>
       <c r="F824" s="23"/>
     </row>
-    <row r="825" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="825" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C825" s="24"/>
       <c r="D825" s="22"/>
       <c r="E825" s="22"/>
       <c r="F825" s="22"/>
     </row>
-    <row r="826" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="826" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C826" s="25"/>
       <c r="D826" s="23"/>
       <c r="E826" s="23"/>
       <c r="F826" s="23"/>
     </row>
-    <row r="827" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="827" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C827" s="24"/>
       <c r="D827" s="22"/>
       <c r="E827" s="22"/>
       <c r="F827" s="22"/>
     </row>
-    <row r="828" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="828" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C828" s="25"/>
       <c r="D828" s="23"/>
       <c r="E828" s="23"/>
       <c r="F828" s="23"/>
     </row>
-    <row r="829" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="829" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C829" s="24"/>
       <c r="D829" s="22"/>
       <c r="E829" s="22"/>
       <c r="F829" s="22"/>
     </row>
-    <row r="830" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="830" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C830" s="25"/>
       <c r="D830" s="23"/>
       <c r="E830" s="23"/>
       <c r="F830" s="23"/>
     </row>
-    <row r="831" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="831" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C831" s="24"/>
       <c r="D831" s="22"/>
       <c r="E831" s="22"/>
       <c r="F831" s="22"/>
     </row>
-    <row r="832" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="832" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C832" s="25"/>
       <c r="D832" s="23"/>
       <c r="E832" s="23"/>
       <c r="F832" s="23"/>
     </row>
-    <row r="833" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="833" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C833" s="24"/>
       <c r="D833" s="22"/>
       <c r="E833" s="22"/>
       <c r="F833" s="22"/>
     </row>
-    <row r="834" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="834" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C834" s="25"/>
       <c r="D834" s="23"/>
       <c r="E834" s="23"/>
       <c r="F834" s="23"/>
     </row>
-    <row r="835" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="835" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C835" s="24"/>
       <c r="D835" s="22"/>
       <c r="E835" s="22"/>
       <c r="F835" s="22"/>
     </row>
-    <row r="836" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="836" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C836" s="25"/>
       <c r="D836" s="23"/>
       <c r="E836" s="23"/>
       <c r="F836" s="23"/>
     </row>
-    <row r="837" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="837" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C837" s="24"/>
       <c r="D837" s="22"/>
       <c r="E837" s="22"/>
       <c r="F837" s="22"/>
     </row>
-    <row r="838" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="838" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C838" s="25"/>
       <c r="D838" s="23"/>
       <c r="E838" s="23"/>
       <c r="F838" s="23"/>
     </row>
-    <row r="839" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="839" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C839" s="24"/>
       <c r="D839" s="22"/>
       <c r="E839" s="22"/>
       <c r="F839" s="22"/>
     </row>
-    <row r="840" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="840" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C840" s="25"/>
       <c r="D840" s="23"/>
       <c r="E840" s="23"/>
       <c r="F840" s="23"/>
     </row>
-    <row r="841" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="841" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C841" s="24"/>
       <c r="D841" s="22"/>
       <c r="E841" s="22"/>
       <c r="F841" s="22"/>
     </row>
-    <row r="842" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="842" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C842" s="25"/>
       <c r="D842" s="23"/>
       <c r="E842" s="23"/>
       <c r="F842" s="23"/>
     </row>
-    <row r="843" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="843" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C843" s="24"/>
       <c r="D843" s="22"/>
       <c r="E843" s="22"/>
       <c r="F843" s="22"/>
     </row>
-    <row r="844" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="844" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C844" s="25"/>
       <c r="D844" s="23"/>
       <c r="E844" s="23"/>
       <c r="F844" s="23"/>
     </row>
-    <row r="845" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="845" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C845" s="24"/>
       <c r="D845" s="22"/>
       <c r="E845" s="22"/>
       <c r="F845" s="22"/>
     </row>
-    <row r="846" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="846" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C846" s="25"/>
       <c r="D846" s="23"/>
       <c r="E846" s="23"/>
       <c r="F846" s="23"/>
     </row>
-    <row r="847" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="847" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C847" s="24"/>
       <c r="D847" s="22"/>
       <c r="E847" s="22"/>
       <c r="F847" s="22"/>
     </row>
-    <row r="848" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="848" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C848" s="25"/>
       <c r="D848" s="23"/>
       <c r="E848" s="23"/>
       <c r="F848" s="23"/>
     </row>
-    <row r="849" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="849" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C849" s="24"/>
       <c r="D849" s="22"/>
       <c r="E849" s="22"/>
       <c r="F849" s="22"/>
     </row>
-    <row r="850" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="850" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C850" s="25"/>
       <c r="D850" s="23"/>
       <c r="E850" s="23"/>
       <c r="F850" s="23"/>
     </row>
-    <row r="851" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="851" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C851" s="24"/>
       <c r="D851" s="22"/>
       <c r="E851" s="22"/>
       <c r="F851" s="22"/>
     </row>
-    <row r="852" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="852" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C852" s="25"/>
       <c r="D852" s="23"/>
       <c r="E852" s="23"/>
       <c r="F852" s="23"/>
     </row>
-    <row r="853" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="853" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C853" s="24"/>
       <c r="D853" s="22"/>
       <c r="E853" s="22"/>
       <c r="F853" s="22"/>
     </row>
-    <row r="854" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="854" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C854" s="25"/>
       <c r="D854" s="23"/>
       <c r="E854" s="23"/>
       <c r="F854" s="23"/>
     </row>
-    <row r="855" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="855" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C855" s="24"/>
       <c r="D855" s="22"/>
       <c r="E855" s="22"/>
       <c r="F855" s="22"/>
     </row>
-    <row r="856" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="856" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C856" s="25"/>
       <c r="D856" s="23"/>
       <c r="E856" s="23"/>
       <c r="F856" s="23"/>
     </row>
-    <row r="857" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="857" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C857" s="24"/>
       <c r="D857" s="22"/>
       <c r="E857" s="22"/>
       <c r="F857" s="22"/>
     </row>
-    <row r="858" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="858" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C858" s="25"/>
       <c r="D858" s="23"/>
       <c r="E858" s="23"/>
       <c r="F858" s="23"/>
     </row>
-    <row r="859" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="859" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C859" s="24"/>
       <c r="D859" s="22"/>
       <c r="E859" s="22"/>
       <c r="F859" s="22"/>
     </row>
-    <row r="860" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="860" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C860" s="25"/>
       <c r="D860" s="23"/>
       <c r="E860" s="23"/>
       <c r="F860" s="23"/>
     </row>
-    <row r="861" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="861" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C861" s="24"/>
       <c r="D861" s="22"/>
       <c r="E861" s="22"/>
       <c r="F861" s="22"/>
     </row>
-    <row r="862" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="862" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C862" s="25"/>
       <c r="D862" s="23"/>
       <c r="E862" s="23"/>
       <c r="F862" s="23"/>
     </row>
-    <row r="863" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="863" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C863" s="24"/>
       <c r="D863" s="22"/>
       <c r="E863" s="22"/>
       <c r="F863" s="22"/>
     </row>
-    <row r="864" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="864" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C864" s="25"/>
       <c r="D864" s="23"/>
       <c r="E864" s="23"/>
       <c r="F864" s="23"/>
     </row>
-    <row r="865" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="865" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C865" s="24"/>
       <c r="D865" s="22"/>
       <c r="E865" s="22"/>
       <c r="F865" s="22"/>
     </row>
-    <row r="866" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="866" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C866" s="25"/>
       <c r="D866" s="23"/>
       <c r="E866" s="23"/>
       <c r="F866" s="23"/>
     </row>
-    <row r="867" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="867" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C867" s="24"/>
       <c r="D867" s="22"/>
       <c r="E867" s="22"/>
       <c r="F867" s="22"/>
     </row>
-    <row r="868" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="868" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C868" s="25"/>
       <c r="D868" s="23"/>
       <c r="E868" s="23"/>
       <c r="F868" s="23"/>
     </row>
-    <row r="869" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="869" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C869" s="24"/>
       <c r="D869" s="22"/>
       <c r="E869" s="22"/>
       <c r="F869" s="22"/>
     </row>
-    <row r="870" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="870" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C870" s="25"/>
       <c r="D870" s="23"/>
       <c r="E870" s="23"/>
       <c r="F870" s="23"/>
     </row>
-    <row r="871" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="871" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C871" s="24"/>
       <c r="D871" s="22"/>
       <c r="E871" s="22"/>
       <c r="F871" s="22"/>
     </row>
-    <row r="872" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="872" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C872" s="25"/>
       <c r="D872" s="23"/>
       <c r="E872" s="23"/>
       <c r="F872" s="23"/>
     </row>
-    <row r="873" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="873" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C873" s="24"/>
       <c r="D873" s="22"/>
       <c r="E873" s="22"/>
       <c r="F873" s="22"/>
     </row>
-    <row r="874" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="874" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C874" s="25"/>
       <c r="D874" s="23"/>
       <c r="E874" s="23"/>
       <c r="F874" s="23"/>
     </row>
-    <row r="875" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="875" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C875" s="24"/>
       <c r="D875" s="22"/>
       <c r="E875" s="22"/>
       <c r="F875" s="22"/>
     </row>
-    <row r="876" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="876" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C876" s="25"/>
       <c r="D876" s="23"/>
       <c r="E876" s="23"/>
       <c r="F876" s="23"/>
     </row>
-    <row r="877" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="877" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C877" s="24"/>
       <c r="D877" s="22"/>
       <c r="E877" s="22"/>
       <c r="F877" s="22"/>
     </row>
-    <row r="878" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="878" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C878" s="25"/>
       <c r="D878" s="23"/>
       <c r="E878" s="23"/>
       <c r="F878" s="23"/>
     </row>
-    <row r="879" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="879" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C879" s="24"/>
       <c r="D879" s="22"/>
       <c r="E879" s="22"/>
       <c r="F879" s="22"/>
     </row>
-    <row r="880" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="880" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C880" s="25"/>
       <c r="D880" s="23"/>
       <c r="E880" s="23"/>
       <c r="F880" s="23"/>
     </row>
-    <row r="881" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="881" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C881" s="24"/>
       <c r="D881" s="22"/>
       <c r="E881" s="22"/>
       <c r="F881" s="22"/>
     </row>
-    <row r="882" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="882" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C882" s="25"/>
       <c r="D882" s="23"/>
       <c r="E882" s="23"/>
       <c r="F882" s="23"/>
     </row>
-    <row r="883" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="883" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C883" s="24"/>
       <c r="D883" s="22"/>
       <c r="E883" s="22"/>
       <c r="F883" s="22"/>
     </row>
-    <row r="884" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="884" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C884" s="25"/>
       <c r="D884" s="23"/>
       <c r="E884" s="23"/>
       <c r="F884" s="23"/>
     </row>
-    <row r="885" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="885" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C885" s="24"/>
       <c r="D885" s="22"/>
       <c r="E885" s="22"/>
       <c r="F885" s="22"/>
     </row>
-    <row r="886" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="886" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C886" s="25"/>
       <c r="D886" s="23"/>
       <c r="E886" s="23"/>
       <c r="F886" s="23"/>
     </row>
-    <row r="887" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="887" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C887" s="24"/>
       <c r="D887" s="22"/>
       <c r="E887" s="22"/>
       <c r="F887" s="22"/>
     </row>
-    <row r="888" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="888" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C888" s="25"/>
       <c r="D888" s="23"/>
       <c r="E888" s="23"/>
       <c r="F888" s="23"/>
     </row>
-    <row r="889" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="889" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C889" s="24"/>
       <c r="D889" s="22"/>
       <c r="E889" s="22"/>
       <c r="F889" s="22"/>
     </row>
-    <row r="890" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="890" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C890" s="25"/>
       <c r="D890" s="23"/>
       <c r="E890" s="23"/>
       <c r="F890" s="23"/>
     </row>
-    <row r="891" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="891" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C891" s="24"/>
       <c r="D891" s="22"/>
       <c r="E891" s="22"/>
       <c r="F891" s="22"/>
     </row>
-    <row r="892" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="892" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C892" s="25"/>
       <c r="D892" s="23"/>
       <c r="E892" s="23"/>
       <c r="F892" s="23"/>
     </row>
-    <row r="893" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="893" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C893" s="24"/>
       <c r="D893" s="22"/>
       <c r="E893" s="22"/>
       <c r="F893" s="22"/>
     </row>
-    <row r="894" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="894" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C894" s="25"/>
       <c r="D894" s="23"/>
       <c r="E894" s="23"/>
       <c r="F894" s="23"/>
     </row>
-    <row r="895" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="895" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C895" s="24"/>
       <c r="D895" s="22"/>
       <c r="E895" s="22"/>
       <c r="F895" s="22"/>
     </row>
-    <row r="896" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="896" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C896" s="25"/>
       <c r="D896" s="23"/>
       <c r="E896" s="23"/>
       <c r="F896" s="23"/>
     </row>
-    <row r="897" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="897" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C897" s="24"/>
       <c r="D897" s="22"/>
       <c r="E897" s="22"/>
       <c r="F897" s="22"/>
     </row>
-    <row r="898" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="898" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C898" s="25"/>
       <c r="D898" s="23"/>
       <c r="E898" s="23"/>
       <c r="F898" s="23"/>
     </row>
-    <row r="899" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="899" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C899" s="24"/>
       <c r="D899" s="22"/>
       <c r="E899" s="22"/>
       <c r="F899" s="22"/>
     </row>
-    <row r="900" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="900" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C900" s="25"/>
       <c r="D900" s="23"/>
       <c r="E900" s="23"/>
       <c r="F900" s="23"/>
     </row>
-    <row r="901" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="901" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C901" s="24"/>
       <c r="D901" s="22"/>
       <c r="E901" s="22"/>
       <c r="F901" s="22"/>
     </row>
-    <row r="902" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="902" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C902" s="25"/>
       <c r="D902" s="23"/>
       <c r="E902" s="23"/>
       <c r="F902" s="23"/>
     </row>
-    <row r="903" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="903" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C903" s="24"/>
       <c r="D903" s="22"/>
       <c r="E903" s="22"/>
       <c r="F903" s="22"/>
     </row>
-    <row r="904" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="904" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C904" s="25"/>
       <c r="D904" s="23"/>
       <c r="E904" s="23"/>
       <c r="F904" s="23"/>
     </row>
-    <row r="905" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="905" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C905" s="24"/>
       <c r="D905" s="22"/>
       <c r="E905" s="22"/>
       <c r="F905" s="22"/>
     </row>
-    <row r="906" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="906" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C906" s="25"/>
       <c r="D906" s="23"/>
       <c r="E906" s="23"/>
       <c r="F906" s="23"/>
     </row>
-    <row r="907" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="907" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C907" s="24"/>
       <c r="D907" s="22"/>
       <c r="E907" s="22"/>
       <c r="F907" s="22"/>
     </row>
-    <row r="908" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="908" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C908" s="25"/>
       <c r="D908" s="23"/>
       <c r="E908" s="23"/>
       <c r="F908" s="23"/>
     </row>
-    <row r="909" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="909" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C909" s="24"/>
       <c r="D909" s="22"/>
       <c r="E909" s="22"/>
       <c r="F909" s="22"/>
     </row>
-    <row r="910" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="910" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C910" s="25"/>
       <c r="D910" s="23"/>
       <c r="E910" s="23"/>
       <c r="F910" s="23"/>
     </row>
-    <row r="911" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="911" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C911" s="24"/>
       <c r="D911" s="22"/>
       <c r="E911" s="22"/>
       <c r="F911" s="22"/>
     </row>
-    <row r="912" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="912" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C912" s="25"/>
       <c r="D912" s="23"/>
       <c r="E912" s="23"/>
       <c r="F912" s="23"/>
     </row>
-    <row r="913" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="913" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C913" s="24"/>
       <c r="D913" s="22"/>
       <c r="E913" s="22"/>
       <c r="F913" s="22"/>
     </row>
-    <row r="914" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="914" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C914" s="25"/>
       <c r="D914" s="23"/>
       <c r="E914" s="23"/>
       <c r="F914" s="23"/>
     </row>
-    <row r="915" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="915" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C915" s="24"/>
       <c r="D915" s="22"/>
       <c r="E915" s="22"/>
       <c r="F915" s="22"/>
     </row>
-    <row r="916" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="916" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C916" s="25"/>
       <c r="D916" s="23"/>
       <c r="E916" s="23"/>
       <c r="F916" s="23"/>
     </row>
-    <row r="917" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="917" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C917" s="24"/>
       <c r="D917" s="22"/>
       <c r="E917" s="22"/>
       <c r="F917" s="22"/>
     </row>
-    <row r="918" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="918" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C918" s="25"/>
       <c r="D918" s="23"/>
       <c r="E918" s="23"/>
       <c r="F918" s="23"/>
     </row>
-    <row r="919" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="919" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C919" s="24"/>
       <c r="D919" s="22"/>
       <c r="E919" s="22"/>
       <c r="F919" s="22"/>
     </row>
-    <row r="920" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="920" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C920" s="25"/>
       <c r="D920" s="23"/>
       <c r="E920" s="23"/>
       <c r="F920" s="23"/>
     </row>
-    <row r="921" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="921" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C921" s="24"/>
       <c r="D921" s="22"/>
       <c r="E921" s="22"/>
       <c r="F921" s="22"/>
     </row>
-    <row r="922" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="922" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C922" s="25"/>
       <c r="D922" s="23"/>
       <c r="E922" s="23"/>
       <c r="F922" s="23"/>
     </row>
-    <row r="923" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="923" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C923" s="24"/>
       <c r="D923" s="22"/>
       <c r="E923" s="22"/>
       <c r="F923" s="22"/>
     </row>
-    <row r="924" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="924" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C924" s="25"/>
       <c r="D924" s="23"/>
       <c r="E924" s="23"/>
       <c r="F924" s="23"/>
     </row>
-    <row r="925" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="925" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C925" s="24"/>
       <c r="D925" s="22"/>
       <c r="E925" s="22"/>
       <c r="F925" s="22"/>
     </row>
-    <row r="926" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="926" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C926" s="25"/>
       <c r="D926" s="23"/>
       <c r="E926" s="23"/>
       <c r="F926" s="23"/>
     </row>
-    <row r="927" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="927" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C927" s="24"/>
       <c r="D927" s="22"/>
       <c r="E927" s="22"/>
       <c r="F927" s="22"/>
     </row>
-    <row r="928" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="928" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C928" s="25"/>
       <c r="D928" s="23"/>
       <c r="E928" s="23"/>
       <c r="F928" s="23"/>
     </row>
-    <row r="929" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="929" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C929" s="24"/>
       <c r="D929" s="22"/>
       <c r="E929" s="22"/>
       <c r="F929" s="22"/>
     </row>
-    <row r="930" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="930" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C930" s="25"/>
       <c r="D930" s="23"/>
       <c r="E930" s="23"/>
       <c r="F930" s="23"/>
     </row>
-    <row r="931" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="931" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C931" s="24"/>
       <c r="D931" s="22"/>
       <c r="E931" s="22"/>
       <c r="F931" s="22"/>
     </row>
-    <row r="932" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="932" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C932" s="25"/>
       <c r="D932" s="23"/>
       <c r="E932" s="23"/>
       <c r="F932" s="23"/>
     </row>
-    <row r="933" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="933" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C933" s="24"/>
       <c r="D933" s="22"/>
       <c r="E933" s="22"/>
       <c r="F933" s="22"/>
     </row>
-    <row r="934" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="934" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C934" s="25"/>
       <c r="D934" s="23"/>
       <c r="E934" s="23"/>
       <c r="F934" s="23"/>
     </row>
-    <row r="935" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="935" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C935" s="24"/>
       <c r="D935" s="22"/>
       <c r="E935" s="22"/>
       <c r="F935" s="22"/>
     </row>
-    <row r="936" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="936" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C936" s="25"/>
       <c r="D936" s="23"/>
       <c r="E936" s="23"/>
       <c r="F936" s="23"/>
     </row>
-    <row r="937" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="937" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C937" s="24"/>
       <c r="D937" s="22"/>
       <c r="E937" s="22"/>
       <c r="F937" s="22"/>
     </row>
-    <row r="938" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="938" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C938" s="25"/>
       <c r="D938" s="23"/>
       <c r="E938" s="23"/>
       <c r="F938" s="23"/>
     </row>
-    <row r="939" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="939" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C939" s="24"/>
       <c r="D939" s="22"/>
       <c r="E939" s="22"/>
       <c r="F939" s="22"/>
     </row>
-    <row r="940" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="940" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C940" s="25"/>
       <c r="D940" s="23"/>
       <c r="E940" s="23"/>
       <c r="F940" s="23"/>
     </row>
-    <row r="941" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="941" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C941" s="24"/>
       <c r="D941" s="22"/>
       <c r="E941" s="22"/>
       <c r="F941" s="22"/>
     </row>
-    <row r="942" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="942" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C942" s="25"/>
       <c r="D942" s="23"/>
       <c r="E942" s="23"/>
       <c r="F942" s="23"/>
     </row>
-    <row r="943" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="943" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C943" s="24"/>
       <c r="D943" s="22"/>
       <c r="E943" s="22"/>
       <c r="F943" s="22"/>
     </row>
-    <row r="944" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="944" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C944" s="25"/>
       <c r="D944" s="23"/>
       <c r="E944" s="23"/>
       <c r="F944" s="23"/>
     </row>
-    <row r="945" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="945" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C945" s="24"/>
       <c r="D945" s="22"/>
       <c r="E945" s="22"/>
       <c r="F945" s="22"/>
     </row>
-    <row r="946" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="946" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C946" s="25"/>
       <c r="D946" s="23"/>
       <c r="E946" s="23"/>
       <c r="F946" s="23"/>
     </row>
-    <row r="947" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="947" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C947" s="24"/>
       <c r="D947" s="22"/>
       <c r="E947" s="22"/>
       <c r="F947" s="22"/>
     </row>
-    <row r="948" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="948" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C948" s="25"/>
       <c r="D948" s="23"/>
       <c r="E948" s="23"/>
       <c r="F948" s="23"/>
     </row>
-    <row r="949" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="949" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C949" s="24"/>
       <c r="D949" s="22"/>
       <c r="E949" s="22"/>
       <c r="F949" s="22"/>
     </row>
-    <row r="950" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="950" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C950" s="25"/>
       <c r="D950" s="23"/>
       <c r="E950" s="23"/>
       <c r="F950" s="23"/>
     </row>
-    <row r="951" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="951" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C951" s="24"/>
       <c r="D951" s="22"/>
       <c r="E951" s="22"/>
       <c r="F951" s="22"/>
     </row>
-    <row r="952" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="952" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C952" s="25"/>
       <c r="D952" s="23"/>
       <c r="E952" s="23"/>
       <c r="F952" s="23"/>
     </row>
-    <row r="953" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="953" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C953" s="24"/>
       <c r="D953" s="22"/>
       <c r="E953" s="22"/>
       <c r="F953" s="22"/>
     </row>
-    <row r="954" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="954" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C954" s="25"/>
       <c r="D954" s="23"/>
       <c r="E954" s="23"/>
       <c r="F954" s="23"/>
     </row>
-    <row r="955" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="955" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C955" s="24"/>
       <c r="D955" s="22"/>
       <c r="E955" s="22"/>
       <c r="F955" s="22"/>
     </row>
-    <row r="956" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="956" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C956" s="25"/>
       <c r="D956" s="23"/>
       <c r="E956" s="23"/>
       <c r="F956" s="23"/>
     </row>
-    <row r="957" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="957" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C957" s="24"/>
       <c r="D957" s="22"/>
       <c r="E957" s="22"/>
       <c r="F957" s="22"/>
     </row>
-    <row r="958" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="958" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C958" s="25"/>
       <c r="D958" s="23"/>
       <c r="E958" s="23"/>
       <c r="F958" s="23"/>
     </row>
-    <row r="959" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="959" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C959" s="24"/>
       <c r="D959" s="22"/>
       <c r="E959" s="22"/>
       <c r="F959" s="22"/>
     </row>
-    <row r="960" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="960" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C960" s="25"/>
       <c r="D960" s="23"/>
       <c r="E960" s="23"/>
       <c r="F960" s="23"/>
     </row>
-    <row r="961" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="961" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C961" s="24"/>
       <c r="D961" s="22"/>
       <c r="E961" s="22"/>
       <c r="F961" s="22"/>
     </row>
-    <row r="962" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="962" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C962" s="25"/>
       <c r="D962" s="23"/>
       <c r="E962" s="23"/>
       <c r="F962" s="23"/>
     </row>
-    <row r="963" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="963" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C963" s="24"/>
       <c r="D963" s="22"/>
       <c r="E963" s="22"/>
       <c r="F963" s="22"/>
     </row>
-    <row r="964" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="964" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C964" s="25"/>
       <c r="D964" s="23"/>
       <c r="E964" s="23"/>
       <c r="F964" s="23"/>
     </row>
-    <row r="965" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="965" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C965" s="24"/>
       <c r="D965" s="22"/>
       <c r="E965" s="22"/>
       <c r="F965" s="22"/>
     </row>
-    <row r="966" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="966" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C966" s="25"/>
       <c r="D966" s="23"/>
       <c r="E966" s="23"/>
       <c r="F966" s="23"/>
     </row>
-    <row r="967" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="967" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C967" s="24"/>
       <c r="D967" s="22"/>
       <c r="E967" s="22"/>
       <c r="F967" s="22"/>
     </row>
-    <row r="968" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="968" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C968" s="25"/>
       <c r="D968" s="23"/>
       <c r="E968" s="23"/>
       <c r="F968" s="23"/>
     </row>
-    <row r="969" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="969" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C969" s="24"/>
       <c r="D969" s="22"/>
       <c r="E969" s="22"/>
       <c r="F969" s="22"/>
     </row>
-    <row r="970" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="970" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C970" s="25"/>
       <c r="D970" s="23"/>
       <c r="E970" s="23"/>
       <c r="F970" s="23"/>
     </row>
-    <row r="971" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="971" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C971" s="24"/>
       <c r="D971" s="22"/>
       <c r="E971" s="22"/>
       <c r="F971" s="22"/>
     </row>
-    <row r="972" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="972" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C972" s="25"/>
       <c r="D972" s="23"/>
       <c r="E972" s="23"/>
       <c r="F972" s="23"/>
     </row>
-    <row r="973" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="973" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C973" s="24"/>
       <c r="D973" s="22"/>
       <c r="E973" s="22"/>
       <c r="F973" s="22"/>
     </row>
-    <row r="974" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="974" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C974" s="25"/>
       <c r="D974" s="23"/>
       <c r="E974" s="23"/>
       <c r="F974" s="23"/>
     </row>
-    <row r="975" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="975" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C975" s="24"/>
       <c r="D975" s="22"/>
       <c r="E975" s="22"/>
       <c r="F975" s="22"/>
     </row>
-    <row r="976" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="976" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C976" s="25"/>
       <c r="D976" s="23"/>
       <c r="E976" s="23"/>
       <c r="F976" s="23"/>
     </row>
-    <row r="977" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="977" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C977" s="24"/>
       <c r="D977" s="22"/>
       <c r="E977" s="22"/>
       <c r="F977" s="22"/>
     </row>
-    <row r="978" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="978" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C978" s="25"/>
       <c r="D978" s="23"/>
       <c r="E978" s="23"/>
       <c r="F978" s="23"/>
     </row>
-    <row r="979" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="979" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C979" s="24"/>
       <c r="D979" s="22"/>
       <c r="E979" s="22"/>
       <c r="F979" s="22"/>
     </row>
-    <row r="980" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="980" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C980" s="25"/>
       <c r="D980" s="23"/>
       <c r="E980" s="23"/>
       <c r="F980" s="23"/>
     </row>
-    <row r="981" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="981" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C981" s="24"/>
       <c r="D981" s="22"/>
       <c r="E981" s="22"/>
       <c r="F981" s="22"/>
     </row>
-    <row r="982" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="982" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C982" s="25"/>
       <c r="D982" s="23"/>
       <c r="E982" s="23"/>
       <c r="F982" s="23"/>
     </row>
-    <row r="983" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="983" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C983" s="24"/>
       <c r="D983" s="22"/>
       <c r="E983" s="22"/>
       <c r="F983" s="22"/>
     </row>
-    <row r="984" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="984" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C984" s="25"/>
       <c r="D984" s="23"/>
       <c r="E984" s="23"/>
       <c r="F984" s="23"/>
     </row>
-    <row r="985" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="985" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C985" s="24"/>
       <c r="D985" s="22"/>
       <c r="E985" s="22"/>
       <c r="F985" s="22"/>
     </row>
-    <row r="986" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="986" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C986" s="25"/>
       <c r="D986" s="23"/>
       <c r="E986" s="23"/>
       <c r="F986" s="23"/>
     </row>
-    <row r="987" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="987" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C987" s="24"/>
       <c r="D987" s="22"/>
       <c r="E987" s="22"/>
       <c r="F987" s="22"/>
     </row>
-    <row r="988" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="988" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C988" s="25"/>
       <c r="D988" s="23"/>
       <c r="E988" s="23"/>
       <c r="F988" s="23"/>
     </row>
-    <row r="989" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="989" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C989" s="24"/>
       <c r="D989" s="22"/>
       <c r="E989" s="22"/>
       <c r="F989" s="22"/>
     </row>
-    <row r="990" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="990" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C990" s="25"/>
       <c r="D990" s="23"/>
       <c r="E990" s="23"/>
       <c r="F990" s="23"/>
     </row>
-    <row r="991" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="991" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C991" s="24"/>
       <c r="D991" s="22"/>
       <c r="E991" s="22"/>
       <c r="F991" s="22"/>
     </row>
-    <row r="992" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="992" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C992" s="25"/>
       <c r="D992" s="23"/>
       <c r="E992" s="23"/>
       <c r="F992" s="23"/>
     </row>
-    <row r="993" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="993" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C993" s="24"/>
       <c r="D993" s="22"/>
       <c r="E993" s="22"/>
       <c r="F993" s="22"/>
     </row>
-    <row r="994" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="994" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C994" s="25"/>
       <c r="D994" s="23"/>
       <c r="E994" s="23"/>
       <c r="F994" s="23"/>
     </row>
-    <row r="995" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="995" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C995" s="24"/>
       <c r="D995" s="22"/>
       <c r="E995" s="22"/>
       <c r="F995" s="22"/>
     </row>
-    <row r="996" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="996" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C996" s="25"/>
       <c r="D996" s="23"/>
       <c r="E996" s="23"/>
       <c r="F996" s="23"/>
     </row>
-    <row r="997" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="997" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C997" s="24"/>
       <c r="D997" s="22"/>
       <c r="E997" s="22"/>
       <c r="F997" s="22"/>
     </row>
-    <row r="998" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="998" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C998" s="25"/>
       <c r="D998" s="23"/>
       <c r="E998" s="23"/>
       <c r="F998" s="23"/>
     </row>
-    <row r="999" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="999" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C999" s="24"/>
       <c r="D999" s="22"/>
       <c r="E999" s="22"/>
       <c r="F999" s="22"/>
     </row>
-    <row r="1000" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="1000" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C1000" s="25"/>
       <c r="D1000" s="23"/>
       <c r="E1000" s="23"/>
@@ -17572,14 +17583,14 @@
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="B1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="41.6640625" customWidth="1"/>
+    <col min="2" max="2" width="41.7109375" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1" s="31" t="s">
         <v>26</v>
       </c>
@@ -17590,80 +17601,80 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>5835</v>
+        <v>5910</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>2865</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -17676,7 +17687,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BDDE723-6D9A-4C8A-97FE-709060F4DF0D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,19 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC51122-AEEC-49BD-8012-341AB7D3DAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC833DE-A913-4772-A4BC-596EEBC530D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
+    <workbookView xWindow="40290" yWindow="3735" windowWidth="23040" windowHeight="12120" activeTab="2" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Time_Log" sheetId="2" r:id="rId2"/>
     <sheet name="BACKGROUND_LOGIC" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1888,10 +1887,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>5910</c:v>
+                  <c:v>6855</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2790</c:v>
+                  <c:v>1845</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3115,16 +3114,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>264795</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>154305</xdr:rowOff>
+      <xdr:rowOff>173355</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>264795</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1905</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3139,8 +3138,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9599295" y="335280"/>
-          <a:ext cx="0" cy="2541270"/>
+          <a:off x="10732770" y="354330"/>
+          <a:ext cx="0" cy="2543175"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -10601,20 +10600,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P30"/>
-  <sheetFormatPr defaultColWidth="16.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="16.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="16.28515625" customWidth="1"/>
-    <col min="12" max="13" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.28515625" customWidth="1"/>
+    <col min="3" max="4" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="16.33203125" customWidth="1"/>
+    <col min="12" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -10649,7 +10648,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
@@ -10698,7 +10697,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="39" t="s">
         <v>4</v>
       </c>
@@ -10721,7 +10720,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="40"/>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -10736,7 +10735,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="36"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="40"/>
       <c r="B5" s="45" t="s">
         <v>4</v>
@@ -10751,7 +10750,7 @@
       <c r="J5" s="3"/>
       <c r="K5" s="36"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
         <v>13</v>
       </c>
@@ -10768,7 +10767,7 @@
       <c r="J6" s="3"/>
       <c r="K6" s="36"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="41"/>
       <c r="B7" s="3"/>
       <c r="C7" s="8"/>
@@ -10783,7 +10782,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="36"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="41"/>
       <c r="B8" s="3"/>
       <c r="C8" s="8"/>
@@ -10798,7 +10797,7 @@
       <c r="J8" s="3"/>
       <c r="K8" s="36"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="41"/>
       <c r="B9" s="3"/>
       <c r="C9" s="8"/>
@@ -10813,7 +10812,7 @@
       <c r="J9" s="3"/>
       <c r="K9" s="36"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="43" t="s">
         <v>14</v>
       </c>
@@ -10830,7 +10829,7 @@
       <c r="J10" s="3"/>
       <c r="K10" s="36"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="43"/>
       <c r="B11" s="3"/>
       <c r="C11" s="8"/>
@@ -10845,7 +10844,7 @@
       <c r="J11" s="3"/>
       <c r="K11" s="36"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="43"/>
       <c r="B12" s="3"/>
       <c r="C12" s="8"/>
@@ -10860,7 +10859,7 @@
       <c r="J12" s="3"/>
       <c r="K12" s="36"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="43"/>
       <c r="B13" s="3"/>
       <c r="C13" s="8"/>
@@ -10875,7 +10874,7 @@
       <c r="J13" s="3"/>
       <c r="K13" s="36"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="43"/>
       <c r="B14" s="3"/>
       <c r="C14" s="8"/>
@@ -10890,7 +10889,7 @@
       <c r="J14" s="3"/>
       <c r="K14" s="36"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="29"/>
       <c r="B15" s="3"/>
       <c r="C15" s="8"/>
@@ -10905,7 +10904,7 @@
       <c r="J15" s="38"/>
       <c r="K15" s="36"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="30" t="s">
         <v>15</v>
       </c>
@@ -10922,7 +10921,7 @@
       <c r="J16" s="42"/>
       <c r="K16" s="37"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="34" t="s">
         <v>36</v>
       </c>
@@ -10930,7 +10929,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="35" t="s">
         <v>29</v>
       </c>
@@ -10938,7 +10937,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="35" t="s">
         <v>4</v>
       </c>
@@ -10946,12 +10945,12 @@
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="35" t="s">
         <v>5</v>
       </c>
@@ -10959,7 +10958,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="35" t="s">
         <v>6</v>
       </c>
@@ -10967,7 +10966,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="35" t="s">
         <v>28</v>
       </c>
@@ -10975,7 +10974,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="35" t="s">
         <v>7</v>
       </c>
@@ -10983,7 +10982,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="35" t="s">
         <v>8</v>
       </c>
@@ -10991,7 +10990,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="35" t="s">
         <v>9</v>
       </c>
@@ -10999,7 +10998,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="35" t="s">
         <v>19</v>
       </c>
@@ -11007,7 +11006,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="35" t="s">
         <v>27</v>
       </c>
@@ -11015,7 +11014,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="35" t="s">
         <v>38</v>
       </c>
@@ -11049,15 +11048,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8154930E-2F36-41CB-8896-D63BC278B832}">
   <dimension ref="C1:F1000"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="21.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
-    <col min="5" max="5" width="38.5703125" customWidth="1"/>
-    <col min="6" max="6" width="114.7109375" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" customWidth="1"/>
+    <col min="5" max="5" width="38.5546875" customWidth="1"/>
+    <col min="6" max="6" width="114.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C1" s="26" t="s">
         <v>22</v>
       </c>
@@ -11071,7 +11070,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C2" s="28">
         <v>45927</v>
       </c>
@@ -11085,7 +11084,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C3" s="32">
         <v>45927</v>
       </c>
@@ -11099,7 +11098,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C4" s="33">
         <v>45928</v>
       </c>
@@ -11113,7 +11112,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C5" s="32">
         <v>45928</v>
       </c>
@@ -11127,7 +11126,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C6" s="33">
         <v>45929</v>
       </c>
@@ -11141,7 +11140,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C7" s="32">
         <v>45934</v>
       </c>
@@ -11155,7 +11154,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C8" s="33">
         <v>45934</v>
       </c>
@@ -11169,7 +11168,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C9" s="32">
         <v>45934</v>
       </c>
@@ -11183,7 +11182,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C10" s="33">
         <v>45935</v>
       </c>
@@ -11197,7 +11196,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C11" s="32">
         <v>45936</v>
       </c>
@@ -11211,7 +11210,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C12" s="33">
         <v>45940</v>
       </c>
@@ -11223,7 +11222,7 @@
       </c>
       <c r="F12" s="23"/>
     </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C13" s="32">
         <v>45941</v>
       </c>
@@ -11235,7 +11234,7 @@
       </c>
       <c r="F13" s="22"/>
     </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C14" s="33">
         <v>45942</v>
       </c>
@@ -11249,7 +11248,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C15" s="32">
         <v>45944</v>
       </c>
@@ -11263,7 +11262,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C16" s="33">
         <v>45944</v>
       </c>
@@ -11277,7 +11276,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C17" s="32">
         <v>45944</v>
       </c>
@@ -11291,7 +11290,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C18" s="33">
         <v>45944</v>
       </c>
@@ -11305,7 +11304,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C19" s="32">
         <v>45944</v>
       </c>
@@ -11319,7 +11318,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C20" s="33">
         <v>45945</v>
       </c>
@@ -11333,7 +11332,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C21" s="32">
         <v>45945</v>
       </c>
@@ -11347,7 +11346,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C22" s="33">
         <v>45945</v>
       </c>
@@ -11361,7 +11360,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C23" s="32">
         <v>45946</v>
       </c>
@@ -11375,7 +11374,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C24" s="33">
         <v>45946</v>
       </c>
@@ -11389,7 +11388,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C25" s="32">
         <v>45946</v>
       </c>
@@ -11403,7 +11402,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C26" s="33">
         <v>45946</v>
       </c>
@@ -11417,7 +11416,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C27" s="32">
         <v>45946</v>
       </c>
@@ -11431,7 +11430,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C28" s="33">
         <v>45946</v>
       </c>
@@ -11445,7 +11444,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C29" s="32">
         <v>45950</v>
       </c>
@@ -11459,7 +11458,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C30" s="33">
         <v>45950</v>
       </c>
@@ -11473,7 +11472,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C31" s="32">
         <v>45950</v>
       </c>
@@ -11487,7 +11486,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C32" s="33">
         <v>45951</v>
       </c>
@@ -11501,7 +11500,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C33" s="32">
         <v>45951</v>
       </c>
@@ -11515,7 +11514,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C34" s="33">
         <v>45955</v>
       </c>
@@ -11529,7 +11528,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C35" s="32">
         <v>45956</v>
       </c>
@@ -11543,7 +11542,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C36" s="33">
         <v>45956</v>
       </c>
@@ -11557,7 +11556,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C37" s="32">
         <v>45957</v>
       </c>
@@ -11571,7 +11570,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C38" s="33">
         <v>45958</v>
       </c>
@@ -11585,7 +11584,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C39" s="32">
         <v>45958</v>
       </c>
@@ -11599,7 +11598,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C40" s="33">
         <v>45960</v>
       </c>
@@ -11613,7 +11612,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C41" s="32">
         <v>45961</v>
       </c>
@@ -11627,7 +11626,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C42" s="33">
         <v>45962</v>
       </c>
@@ -11641,7 +11640,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C43" s="32">
         <v>45962</v>
       </c>
@@ -11655,7 +11654,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C44" s="33">
         <v>45963</v>
       </c>
@@ -11669,7 +11668,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="45" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C45" s="32">
         <v>45963</v>
       </c>
@@ -11683,7 +11682,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C46" s="33">
         <v>45964</v>
       </c>
@@ -11697,7 +11696,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C47" s="32">
         <v>45964</v>
       </c>
@@ -11711,7 +11710,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="48" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C48" s="33">
         <v>45965</v>
       </c>
@@ -11725,7 +11724,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C49" s="32">
         <v>45965</v>
       </c>
@@ -11739,7 +11738,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C50" s="33">
         <v>45969</v>
       </c>
@@ -11753,7 +11752,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="51" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C51" s="32">
         <v>45970</v>
       </c>
@@ -11767,7 +11766,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C52" s="33">
         <v>45971</v>
       </c>
@@ -11781,7 +11780,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C53" s="32">
         <v>45971</v>
       </c>
@@ -11795,7 +11794,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C54" s="33">
         <v>45972</v>
       </c>
@@ -11809,7 +11808,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C55" s="32">
         <v>45974</v>
       </c>
@@ -11823,7 +11822,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C56" s="33">
         <v>45974</v>
       </c>
@@ -11837,7 +11836,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="57" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C57" s="32">
         <v>45974</v>
       </c>
@@ -11851,7 +11850,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C58" s="33">
         <v>45975</v>
       </c>
@@ -11865,7 +11864,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C59" s="32">
         <v>45976</v>
       </c>
@@ -11879,7 +11878,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C60" s="33">
         <v>45976</v>
       </c>
@@ -11893,7 +11892,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C61" s="32">
         <v>45977</v>
       </c>
@@ -11907,7 +11906,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C62" s="33">
         <v>45977</v>
       </c>
@@ -11921,7 +11920,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="63" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C63" s="32">
         <v>45978</v>
       </c>
@@ -11935,5623 +11934,5626 @@
         <v>88</v>
       </c>
     </row>
-    <row r="64" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C64" s="25"/>
-      <c r="D64" s="23"/>
+      <c r="D64" s="23">
+        <f>SUM(D54:D63)</f>
+        <v>945</v>
+      </c>
       <c r="E64" s="23"/>
       <c r="F64" s="23"/>
     </row>
-    <row r="65" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C65" s="24"/>
       <c r="D65" s="22"/>
       <c r="E65" s="22"/>
       <c r="F65" s="22"/>
     </row>
-    <row r="66" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C66" s="25"/>
       <c r="D66" s="23"/>
       <c r="E66" s="23"/>
       <c r="F66" s="23"/>
     </row>
-    <row r="67" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C67" s="24"/>
       <c r="D67" s="22"/>
       <c r="E67" s="22"/>
       <c r="F67" s="22"/>
     </row>
-    <row r="68" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C68" s="25"/>
       <c r="D68" s="23"/>
       <c r="E68" s="23"/>
       <c r="F68" s="23"/>
     </row>
-    <row r="69" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C69" s="24"/>
       <c r="D69" s="22"/>
       <c r="E69" s="22"/>
       <c r="F69" s="22"/>
     </row>
-    <row r="70" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C70" s="25"/>
       <c r="D70" s="23"/>
       <c r="E70" s="23"/>
       <c r="F70" s="23"/>
     </row>
-    <row r="71" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C71" s="24"/>
       <c r="D71" s="22"/>
       <c r="E71" s="22"/>
       <c r="F71" s="22"/>
     </row>
-    <row r="72" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C72" s="25"/>
       <c r="D72" s="23"/>
       <c r="E72" s="23"/>
       <c r="F72" s="23"/>
     </row>
-    <row r="73" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C73" s="24"/>
       <c r="D73" s="22"/>
       <c r="E73" s="22"/>
       <c r="F73" s="22"/>
     </row>
-    <row r="74" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C74" s="25"/>
       <c r="D74" s="23"/>
       <c r="E74" s="23"/>
       <c r="F74" s="23"/>
     </row>
-    <row r="75" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C75" s="24"/>
       <c r="D75" s="22"/>
       <c r="E75" s="22"/>
       <c r="F75" s="22"/>
     </row>
-    <row r="76" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C76" s="25"/>
       <c r="D76" s="23"/>
       <c r="E76" s="23"/>
       <c r="F76" s="23"/>
     </row>
-    <row r="77" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C77" s="24"/>
       <c r="D77" s="22"/>
       <c r="E77" s="22"/>
       <c r="F77" s="22"/>
     </row>
-    <row r="78" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C78" s="25"/>
       <c r="D78" s="23"/>
       <c r="E78" s="23"/>
       <c r="F78" s="23"/>
     </row>
-    <row r="79" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C79" s="24"/>
       <c r="D79" s="22"/>
       <c r="E79" s="22"/>
       <c r="F79" s="22"/>
     </row>
-    <row r="80" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C80" s="25"/>
       <c r="D80" s="23"/>
       <c r="E80" s="23"/>
       <c r="F80" s="23"/>
     </row>
-    <row r="81" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C81" s="24"/>
       <c r="D81" s="22"/>
       <c r="E81" s="22"/>
       <c r="F81" s="22"/>
     </row>
-    <row r="82" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C82" s="25"/>
       <c r="D82" s="23"/>
       <c r="E82" s="23"/>
       <c r="F82" s="23"/>
     </row>
-    <row r="83" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C83" s="24"/>
       <c r="D83" s="22"/>
       <c r="E83" s="22"/>
       <c r="F83" s="22"/>
     </row>
-    <row r="84" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C84" s="25"/>
       <c r="D84" s="23"/>
       <c r="E84" s="23"/>
       <c r="F84" s="23"/>
     </row>
-    <row r="85" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C85" s="24"/>
       <c r="D85" s="22"/>
       <c r="E85" s="22"/>
       <c r="F85" s="22"/>
     </row>
-    <row r="86" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C86" s="25"/>
       <c r="D86" s="23"/>
       <c r="E86" s="23"/>
       <c r="F86" s="23"/>
     </row>
-    <row r="87" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C87" s="24"/>
       <c r="D87" s="22"/>
       <c r="E87" s="22"/>
       <c r="F87" s="22"/>
     </row>
-    <row r="88" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C88" s="25"/>
       <c r="D88" s="23"/>
       <c r="E88" s="23"/>
       <c r="F88" s="23"/>
     </row>
-    <row r="89" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C89" s="24"/>
       <c r="D89" s="22"/>
       <c r="E89" s="22"/>
       <c r="F89" s="22"/>
     </row>
-    <row r="90" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C90" s="25"/>
       <c r="D90" s="23"/>
       <c r="E90" s="23"/>
       <c r="F90" s="23"/>
     </row>
-    <row r="91" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C91" s="24"/>
       <c r="D91" s="22"/>
       <c r="E91" s="22"/>
       <c r="F91" s="22"/>
     </row>
-    <row r="92" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C92" s="25"/>
       <c r="D92" s="23"/>
       <c r="E92" s="23"/>
       <c r="F92" s="23"/>
     </row>
-    <row r="93" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C93" s="24"/>
       <c r="D93" s="22"/>
       <c r="E93" s="22"/>
       <c r="F93" s="22"/>
     </row>
-    <row r="94" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C94" s="25"/>
       <c r="D94" s="23"/>
       <c r="E94" s="23"/>
       <c r="F94" s="23"/>
     </row>
-    <row r="95" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C95" s="24"/>
       <c r="D95" s="22"/>
       <c r="E95" s="22"/>
       <c r="F95" s="22"/>
     </row>
-    <row r="96" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C96" s="25"/>
       <c r="D96" s="23"/>
       <c r="E96" s="23"/>
       <c r="F96" s="23"/>
     </row>
-    <row r="97" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C97" s="24"/>
       <c r="D97" s="22"/>
       <c r="E97" s="22"/>
       <c r="F97" s="22"/>
     </row>
-    <row r="98" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C98" s="25"/>
       <c r="D98" s="23"/>
       <c r="E98" s="23"/>
       <c r="F98" s="23"/>
     </row>
-    <row r="99" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C99" s="24"/>
       <c r="D99" s="22"/>
       <c r="E99" s="22"/>
       <c r="F99" s="22"/>
     </row>
-    <row r="100" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C100" s="25"/>
       <c r="D100" s="23"/>
       <c r="E100" s="23"/>
       <c r="F100" s="23"/>
     </row>
-    <row r="101" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C101" s="24"/>
       <c r="D101" s="22"/>
       <c r="E101" s="22"/>
       <c r="F101" s="22"/>
     </row>
-    <row r="102" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C102" s="25"/>
       <c r="D102" s="23"/>
       <c r="E102" s="23"/>
       <c r="F102" s="23"/>
     </row>
-    <row r="103" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C103" s="24"/>
       <c r="D103" s="22"/>
       <c r="E103" s="22"/>
       <c r="F103" s="22"/>
     </row>
-    <row r="104" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C104" s="25"/>
       <c r="D104" s="23"/>
       <c r="E104" s="23"/>
       <c r="F104" s="23"/>
     </row>
-    <row r="105" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C105" s="24"/>
       <c r="D105" s="22"/>
       <c r="E105" s="22"/>
       <c r="F105" s="22"/>
     </row>
-    <row r="106" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C106" s="25"/>
       <c r="D106" s="23"/>
       <c r="E106" s="23"/>
       <c r="F106" s="23"/>
     </row>
-    <row r="107" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C107" s="24"/>
       <c r="D107" s="22"/>
       <c r="E107" s="22"/>
       <c r="F107" s="22"/>
     </row>
-    <row r="108" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C108" s="25"/>
       <c r="D108" s="23"/>
       <c r="E108" s="23"/>
       <c r="F108" s="23"/>
     </row>
-    <row r="109" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C109" s="24"/>
       <c r="D109" s="22"/>
       <c r="E109" s="22"/>
       <c r="F109" s="22"/>
     </row>
-    <row r="110" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C110" s="25"/>
       <c r="D110" s="23"/>
       <c r="E110" s="23"/>
       <c r="F110" s="23"/>
     </row>
-    <row r="111" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C111" s="24"/>
       <c r="D111" s="22"/>
       <c r="E111" s="22"/>
       <c r="F111" s="22"/>
     </row>
-    <row r="112" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C112" s="25"/>
       <c r="D112" s="23"/>
       <c r="E112" s="23"/>
       <c r="F112" s="23"/>
     </row>
-    <row r="113" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C113" s="24"/>
       <c r="D113" s="22"/>
       <c r="E113" s="22"/>
       <c r="F113" s="22"/>
     </row>
-    <row r="114" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C114" s="25"/>
       <c r="D114" s="23"/>
       <c r="E114" s="23"/>
       <c r="F114" s="23"/>
     </row>
-    <row r="115" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C115" s="24"/>
       <c r="D115" s="22"/>
       <c r="E115" s="22"/>
       <c r="F115" s="22"/>
     </row>
-    <row r="116" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C116" s="25"/>
       <c r="D116" s="23"/>
       <c r="E116" s="23"/>
       <c r="F116" s="23"/>
     </row>
-    <row r="117" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C117" s="24"/>
       <c r="D117" s="22"/>
       <c r="E117" s="22"/>
       <c r="F117" s="22"/>
     </row>
-    <row r="118" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C118" s="25"/>
       <c r="D118" s="23"/>
       <c r="E118" s="23"/>
       <c r="F118" s="23"/>
     </row>
-    <row r="119" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C119" s="24"/>
       <c r="D119" s="22"/>
       <c r="E119" s="22"/>
       <c r="F119" s="22"/>
     </row>
-    <row r="120" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C120" s="25"/>
       <c r="D120" s="23"/>
       <c r="E120" s="23"/>
       <c r="F120" s="23"/>
     </row>
-    <row r="121" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C121" s="24"/>
       <c r="D121" s="22"/>
       <c r="E121" s="22"/>
       <c r="F121" s="22"/>
     </row>
-    <row r="122" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C122" s="25"/>
       <c r="D122" s="23"/>
       <c r="E122" s="23"/>
       <c r="F122" s="23"/>
     </row>
-    <row r="123" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C123" s="24"/>
       <c r="D123" s="22"/>
       <c r="E123" s="22"/>
       <c r="F123" s="22"/>
     </row>
-    <row r="124" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C124" s="25"/>
       <c r="D124" s="23"/>
       <c r="E124" s="23"/>
       <c r="F124" s="23"/>
     </row>
-    <row r="125" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C125" s="24"/>
       <c r="D125" s="22"/>
       <c r="E125" s="22"/>
       <c r="F125" s="22"/>
     </row>
-    <row r="126" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C126" s="25"/>
       <c r="D126" s="23"/>
       <c r="E126" s="23"/>
       <c r="F126" s="23"/>
     </row>
-    <row r="127" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C127" s="24"/>
       <c r="D127" s="22"/>
       <c r="E127" s="22"/>
       <c r="F127" s="22"/>
     </row>
-    <row r="128" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C128" s="25"/>
       <c r="D128" s="23"/>
       <c r="E128" s="23"/>
       <c r="F128" s="23"/>
     </row>
-    <row r="129" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C129" s="24"/>
       <c r="D129" s="22"/>
       <c r="E129" s="22"/>
       <c r="F129" s="22"/>
     </row>
-    <row r="130" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C130" s="25"/>
       <c r="D130" s="23"/>
       <c r="E130" s="23"/>
       <c r="F130" s="23"/>
     </row>
-    <row r="131" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C131" s="24"/>
       <c r="D131" s="22"/>
       <c r="E131" s="22"/>
       <c r="F131" s="22"/>
     </row>
-    <row r="132" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C132" s="25"/>
       <c r="D132" s="23"/>
       <c r="E132" s="23"/>
       <c r="F132" s="23"/>
     </row>
-    <row r="133" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C133" s="24"/>
       <c r="D133" s="22"/>
       <c r="E133" s="22"/>
       <c r="F133" s="22"/>
     </row>
-    <row r="134" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C134" s="25"/>
       <c r="D134" s="23"/>
       <c r="E134" s="23"/>
       <c r="F134" s="23"/>
     </row>
-    <row r="135" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C135" s="24"/>
       <c r="D135" s="22"/>
       <c r="E135" s="22"/>
       <c r="F135" s="22"/>
     </row>
-    <row r="136" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C136" s="25"/>
       <c r="D136" s="23"/>
       <c r="E136" s="23"/>
       <c r="F136" s="23"/>
     </row>
-    <row r="137" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C137" s="24"/>
       <c r="D137" s="22"/>
       <c r="E137" s="22"/>
       <c r="F137" s="22"/>
     </row>
-    <row r="138" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C138" s="25"/>
       <c r="D138" s="23"/>
       <c r="E138" s="23"/>
       <c r="F138" s="23"/>
     </row>
-    <row r="139" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C139" s="24"/>
       <c r="D139" s="22"/>
       <c r="E139" s="22"/>
       <c r="F139" s="22"/>
     </row>
-    <row r="140" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C140" s="25"/>
       <c r="D140" s="23"/>
       <c r="E140" s="23"/>
       <c r="F140" s="23"/>
     </row>
-    <row r="141" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C141" s="24"/>
       <c r="D141" s="22"/>
       <c r="E141" s="22"/>
       <c r="F141" s="22"/>
     </row>
-    <row r="142" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C142" s="25"/>
       <c r="D142" s="23"/>
       <c r="E142" s="23"/>
       <c r="F142" s="23"/>
     </row>
-    <row r="143" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C143" s="24"/>
       <c r="D143" s="22"/>
       <c r="E143" s="22"/>
       <c r="F143" s="22"/>
     </row>
-    <row r="144" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C144" s="25"/>
       <c r="D144" s="23"/>
       <c r="E144" s="23"/>
       <c r="F144" s="23"/>
     </row>
-    <row r="145" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C145" s="24"/>
       <c r="D145" s="22"/>
       <c r="E145" s="22"/>
       <c r="F145" s="22"/>
     </row>
-    <row r="146" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C146" s="25"/>
       <c r="D146" s="23"/>
       <c r="E146" s="23"/>
       <c r="F146" s="23"/>
     </row>
-    <row r="147" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C147" s="24"/>
       <c r="D147" s="22"/>
       <c r="E147" s="22"/>
       <c r="F147" s="22"/>
     </row>
-    <row r="148" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C148" s="25"/>
       <c r="D148" s="23"/>
       <c r="E148" s="23"/>
       <c r="F148" s="23"/>
     </row>
-    <row r="149" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C149" s="24"/>
       <c r="D149" s="22"/>
       <c r="E149" s="22"/>
       <c r="F149" s="22"/>
     </row>
-    <row r="150" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C150" s="25"/>
       <c r="D150" s="23"/>
       <c r="E150" s="23"/>
       <c r="F150" s="23"/>
     </row>
-    <row r="151" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C151" s="24"/>
       <c r="D151" s="22"/>
       <c r="E151" s="22"/>
       <c r="F151" s="22"/>
     </row>
-    <row r="152" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C152" s="25"/>
       <c r="D152" s="23"/>
       <c r="E152" s="23"/>
       <c r="F152" s="23"/>
     </row>
-    <row r="153" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C153" s="24"/>
       <c r="D153" s="22"/>
       <c r="E153" s="22"/>
       <c r="F153" s="22"/>
     </row>
-    <row r="154" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C154" s="25"/>
       <c r="D154" s="23"/>
       <c r="E154" s="23"/>
       <c r="F154" s="23"/>
     </row>
-    <row r="155" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C155" s="24"/>
       <c r="D155" s="22"/>
       <c r="E155" s="22"/>
       <c r="F155" s="22"/>
     </row>
-    <row r="156" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C156" s="25"/>
       <c r="D156" s="23"/>
       <c r="E156" s="23"/>
       <c r="F156" s="23"/>
     </row>
-    <row r="157" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C157" s="24"/>
       <c r="D157" s="22"/>
       <c r="E157" s="22"/>
       <c r="F157" s="22"/>
     </row>
-    <row r="158" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C158" s="25"/>
       <c r="D158" s="23"/>
       <c r="E158" s="23"/>
       <c r="F158" s="23"/>
     </row>
-    <row r="159" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C159" s="24"/>
       <c r="D159" s="22"/>
       <c r="E159" s="22"/>
       <c r="F159" s="22"/>
     </row>
-    <row r="160" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C160" s="25"/>
       <c r="D160" s="23"/>
       <c r="E160" s="23"/>
       <c r="F160" s="23"/>
     </row>
-    <row r="161" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C161" s="24"/>
       <c r="D161" s="22"/>
       <c r="E161" s="22"/>
       <c r="F161" s="22"/>
     </row>
-    <row r="162" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C162" s="25"/>
       <c r="D162" s="23"/>
       <c r="E162" s="23"/>
       <c r="F162" s="23"/>
     </row>
-    <row r="163" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C163" s="24"/>
       <c r="D163" s="22"/>
       <c r="E163" s="22"/>
       <c r="F163" s="22"/>
     </row>
-    <row r="164" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C164" s="25"/>
       <c r="D164" s="23"/>
       <c r="E164" s="23"/>
       <c r="F164" s="23"/>
     </row>
-    <row r="165" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C165" s="24"/>
       <c r="D165" s="22"/>
       <c r="E165" s="22"/>
       <c r="F165" s="22"/>
     </row>
-    <row r="166" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C166" s="25"/>
       <c r="D166" s="23"/>
       <c r="E166" s="23"/>
       <c r="F166" s="23"/>
     </row>
-    <row r="167" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C167" s="24"/>
       <c r="D167" s="22"/>
       <c r="E167" s="22"/>
       <c r="F167" s="22"/>
     </row>
-    <row r="168" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C168" s="25"/>
       <c r="D168" s="23"/>
       <c r="E168" s="23"/>
       <c r="F168" s="23"/>
     </row>
-    <row r="169" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C169" s="24"/>
       <c r="D169" s="22"/>
       <c r="E169" s="22"/>
       <c r="F169" s="22"/>
     </row>
-    <row r="170" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C170" s="25"/>
       <c r="D170" s="23"/>
       <c r="E170" s="23"/>
       <c r="F170" s="23"/>
     </row>
-    <row r="171" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C171" s="24"/>
       <c r="D171" s="22"/>
       <c r="E171" s="22"/>
       <c r="F171" s="22"/>
     </row>
-    <row r="172" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C172" s="25"/>
       <c r="D172" s="23"/>
       <c r="E172" s="23"/>
       <c r="F172" s="23"/>
     </row>
-    <row r="173" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C173" s="24"/>
       <c r="D173" s="22"/>
       <c r="E173" s="22"/>
       <c r="F173" s="22"/>
     </row>
-    <row r="174" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C174" s="25"/>
       <c r="D174" s="23"/>
       <c r="E174" s="23"/>
       <c r="F174" s="23"/>
     </row>
-    <row r="175" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C175" s="24"/>
       <c r="D175" s="22"/>
       <c r="E175" s="22"/>
       <c r="F175" s="22"/>
     </row>
-    <row r="176" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C176" s="25"/>
       <c r="D176" s="23"/>
       <c r="E176" s="23"/>
       <c r="F176" s="23"/>
     </row>
-    <row r="177" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C177" s="24"/>
       <c r="D177" s="22"/>
       <c r="E177" s="22"/>
       <c r="F177" s="22"/>
     </row>
-    <row r="178" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C178" s="25"/>
       <c r="D178" s="23"/>
       <c r="E178" s="23"/>
       <c r="F178" s="23"/>
     </row>
-    <row r="179" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C179" s="24"/>
       <c r="D179" s="22"/>
       <c r="E179" s="22"/>
       <c r="F179" s="22"/>
     </row>
-    <row r="180" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C180" s="25"/>
       <c r="D180" s="23"/>
       <c r="E180" s="23"/>
       <c r="F180" s="23"/>
     </row>
-    <row r="181" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C181" s="24"/>
       <c r="D181" s="22"/>
       <c r="E181" s="22"/>
       <c r="F181" s="22"/>
     </row>
-    <row r="182" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C182" s="25"/>
       <c r="D182" s="23"/>
       <c r="E182" s="23"/>
       <c r="F182" s="23"/>
     </row>
-    <row r="183" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C183" s="24"/>
       <c r="D183" s="22"/>
       <c r="E183" s="22"/>
       <c r="F183" s="22"/>
     </row>
-    <row r="184" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C184" s="25"/>
       <c r="D184" s="23"/>
       <c r="E184" s="23"/>
       <c r="F184" s="23"/>
     </row>
-    <row r="185" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C185" s="24"/>
       <c r="D185" s="22"/>
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
     </row>
-    <row r="186" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C186" s="25"/>
       <c r="D186" s="23"/>
       <c r="E186" s="23"/>
       <c r="F186" s="23"/>
     </row>
-    <row r="187" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C187" s="24"/>
       <c r="D187" s="22"/>
       <c r="E187" s="22"/>
       <c r="F187" s="22"/>
     </row>
-    <row r="188" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C188" s="25"/>
       <c r="D188" s="23"/>
       <c r="E188" s="23"/>
       <c r="F188" s="23"/>
     </row>
-    <row r="189" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C189" s="24"/>
       <c r="D189" s="22"/>
       <c r="E189" s="22"/>
       <c r="F189" s="22"/>
     </row>
-    <row r="190" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C190" s="25"/>
       <c r="D190" s="23"/>
       <c r="E190" s="23"/>
       <c r="F190" s="23"/>
     </row>
-    <row r="191" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C191" s="24"/>
       <c r="D191" s="22"/>
       <c r="E191" s="22"/>
       <c r="F191" s="22"/>
     </row>
-    <row r="192" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C192" s="25"/>
       <c r="D192" s="23"/>
       <c r="E192" s="23"/>
       <c r="F192" s="23"/>
     </row>
-    <row r="193" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C193" s="24"/>
       <c r="D193" s="22"/>
       <c r="E193" s="22"/>
       <c r="F193" s="22"/>
     </row>
-    <row r="194" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C194" s="25"/>
       <c r="D194" s="23"/>
       <c r="E194" s="23"/>
       <c r="F194" s="23"/>
     </row>
-    <row r="195" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C195" s="24"/>
       <c r="D195" s="22"/>
       <c r="E195" s="22"/>
       <c r="F195" s="22"/>
     </row>
-    <row r="196" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C196" s="25"/>
       <c r="D196" s="23"/>
       <c r="E196" s="23"/>
       <c r="F196" s="23"/>
     </row>
-    <row r="197" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C197" s="24"/>
       <c r="D197" s="22"/>
       <c r="E197" s="22"/>
       <c r="F197" s="22"/>
     </row>
-    <row r="198" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C198" s="25"/>
       <c r="D198" s="23"/>
       <c r="E198" s="23"/>
       <c r="F198" s="23"/>
     </row>
-    <row r="199" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C199" s="24"/>
       <c r="D199" s="22"/>
       <c r="E199" s="22"/>
       <c r="F199" s="22"/>
     </row>
-    <row r="200" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C200" s="25"/>
       <c r="D200" s="23"/>
       <c r="E200" s="23"/>
       <c r="F200" s="23"/>
     </row>
-    <row r="201" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C201" s="24"/>
       <c r="D201" s="22"/>
       <c r="E201" s="22"/>
       <c r="F201" s="22"/>
     </row>
-    <row r="202" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C202" s="25"/>
       <c r="D202" s="23"/>
       <c r="E202" s="23"/>
       <c r="F202" s="23"/>
     </row>
-    <row r="203" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C203" s="24"/>
       <c r="D203" s="22"/>
       <c r="E203" s="22"/>
       <c r="F203" s="22"/>
     </row>
-    <row r="204" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C204" s="25"/>
       <c r="D204" s="23"/>
       <c r="E204" s="23"/>
       <c r="F204" s="23"/>
     </row>
-    <row r="205" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C205" s="24"/>
       <c r="D205" s="22"/>
       <c r="E205" s="22"/>
       <c r="F205" s="22"/>
     </row>
-    <row r="206" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C206" s="25"/>
       <c r="D206" s="23"/>
       <c r="E206" s="23"/>
       <c r="F206" s="23"/>
     </row>
-    <row r="207" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C207" s="24"/>
       <c r="D207" s="22"/>
       <c r="E207" s="22"/>
       <c r="F207" s="22"/>
     </row>
-    <row r="208" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C208" s="25"/>
       <c r="D208" s="23"/>
       <c r="E208" s="23"/>
       <c r="F208" s="23"/>
     </row>
-    <row r="209" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C209" s="24"/>
       <c r="D209" s="22"/>
       <c r="E209" s="22"/>
       <c r="F209" s="22"/>
     </row>
-    <row r="210" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C210" s="25"/>
       <c r="D210" s="23"/>
       <c r="E210" s="23"/>
       <c r="F210" s="23"/>
     </row>
-    <row r="211" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C211" s="24"/>
       <c r="D211" s="22"/>
       <c r="E211" s="22"/>
       <c r="F211" s="22"/>
     </row>
-    <row r="212" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C212" s="25"/>
       <c r="D212" s="23"/>
       <c r="E212" s="23"/>
       <c r="F212" s="23"/>
     </row>
-    <row r="213" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C213" s="24"/>
       <c r="D213" s="22"/>
       <c r="E213" s="22"/>
       <c r="F213" s="22"/>
     </row>
-    <row r="214" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C214" s="25"/>
       <c r="D214" s="23"/>
       <c r="E214" s="23"/>
       <c r="F214" s="23"/>
     </row>
-    <row r="215" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C215" s="24"/>
       <c r="D215" s="22"/>
       <c r="E215" s="22"/>
       <c r="F215" s="22"/>
     </row>
-    <row r="216" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C216" s="25"/>
       <c r="D216" s="23"/>
       <c r="E216" s="23"/>
       <c r="F216" s="23"/>
     </row>
-    <row r="217" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C217" s="24"/>
       <c r="D217" s="22"/>
       <c r="E217" s="22"/>
       <c r="F217" s="22"/>
     </row>
-    <row r="218" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C218" s="25"/>
       <c r="D218" s="23"/>
       <c r="E218" s="23"/>
       <c r="F218" s="23"/>
     </row>
-    <row r="219" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C219" s="24"/>
       <c r="D219" s="22"/>
       <c r="E219" s="22"/>
       <c r="F219" s="22"/>
     </row>
-    <row r="220" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C220" s="25"/>
       <c r="D220" s="23"/>
       <c r="E220" s="23"/>
       <c r="F220" s="23"/>
     </row>
-    <row r="221" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C221" s="24"/>
       <c r="D221" s="22"/>
       <c r="E221" s="22"/>
       <c r="F221" s="22"/>
     </row>
-    <row r="222" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C222" s="25"/>
       <c r="D222" s="23"/>
       <c r="E222" s="23"/>
       <c r="F222" s="23"/>
     </row>
-    <row r="223" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C223" s="24"/>
       <c r="D223" s="22"/>
       <c r="E223" s="22"/>
       <c r="F223" s="22"/>
     </row>
-    <row r="224" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C224" s="25"/>
       <c r="D224" s="23"/>
       <c r="E224" s="23"/>
       <c r="F224" s="23"/>
     </row>
-    <row r="225" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C225" s="24"/>
       <c r="D225" s="22"/>
       <c r="E225" s="22"/>
       <c r="F225" s="22"/>
     </row>
-    <row r="226" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C226" s="25"/>
       <c r="D226" s="23"/>
       <c r="E226" s="23"/>
       <c r="F226" s="23"/>
     </row>
-    <row r="227" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C227" s="24"/>
       <c r="D227" s="22"/>
       <c r="E227" s="22"/>
       <c r="F227" s="22"/>
     </row>
-    <row r="228" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C228" s="25"/>
       <c r="D228" s="23"/>
       <c r="E228" s="23"/>
       <c r="F228" s="23"/>
     </row>
-    <row r="229" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C229" s="24"/>
       <c r="D229" s="22"/>
       <c r="E229" s="22"/>
       <c r="F229" s="22"/>
     </row>
-    <row r="230" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C230" s="25"/>
       <c r="D230" s="23"/>
       <c r="E230" s="23"/>
       <c r="F230" s="23"/>
     </row>
-    <row r="231" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C231" s="24"/>
       <c r="D231" s="22"/>
       <c r="E231" s="22"/>
       <c r="F231" s="22"/>
     </row>
-    <row r="232" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C232" s="25"/>
       <c r="D232" s="23"/>
       <c r="E232" s="23"/>
       <c r="F232" s="23"/>
     </row>
-    <row r="233" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C233" s="24"/>
       <c r="D233" s="22"/>
       <c r="E233" s="22"/>
       <c r="F233" s="22"/>
     </row>
-    <row r="234" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C234" s="25"/>
       <c r="D234" s="23"/>
       <c r="E234" s="23"/>
       <c r="F234" s="23"/>
     </row>
-    <row r="235" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C235" s="24"/>
       <c r="D235" s="22"/>
       <c r="E235" s="22"/>
       <c r="F235" s="22"/>
     </row>
-    <row r="236" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C236" s="25"/>
       <c r="D236" s="23"/>
       <c r="E236" s="23"/>
       <c r="F236" s="23"/>
     </row>
-    <row r="237" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C237" s="24"/>
       <c r="D237" s="22"/>
       <c r="E237" s="22"/>
       <c r="F237" s="22"/>
     </row>
-    <row r="238" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C238" s="25"/>
       <c r="D238" s="23"/>
       <c r="E238" s="23"/>
       <c r="F238" s="23"/>
     </row>
-    <row r="239" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C239" s="24"/>
       <c r="D239" s="22"/>
       <c r="E239" s="22"/>
       <c r="F239" s="22"/>
     </row>
-    <row r="240" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C240" s="25"/>
       <c r="D240" s="23"/>
       <c r="E240" s="23"/>
       <c r="F240" s="23"/>
     </row>
-    <row r="241" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C241" s="24"/>
       <c r="D241" s="22"/>
       <c r="E241" s="22"/>
       <c r="F241" s="22"/>
     </row>
-    <row r="242" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C242" s="25"/>
       <c r="D242" s="23"/>
       <c r="E242" s="23"/>
       <c r="F242" s="23"/>
     </row>
-    <row r="243" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C243" s="24"/>
       <c r="D243" s="22"/>
       <c r="E243" s="22"/>
       <c r="F243" s="22"/>
     </row>
-    <row r="244" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C244" s="25"/>
       <c r="D244" s="23"/>
       <c r="E244" s="23"/>
       <c r="F244" s="23"/>
     </row>
-    <row r="245" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C245" s="24"/>
       <c r="D245" s="22"/>
       <c r="E245" s="22"/>
       <c r="F245" s="22"/>
     </row>
-    <row r="246" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C246" s="25"/>
       <c r="D246" s="23"/>
       <c r="E246" s="23"/>
       <c r="F246" s="23"/>
     </row>
-    <row r="247" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C247" s="24"/>
       <c r="D247" s="22"/>
       <c r="E247" s="22"/>
       <c r="F247" s="22"/>
     </row>
-    <row r="248" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C248" s="25"/>
       <c r="D248" s="23"/>
       <c r="E248" s="23"/>
       <c r="F248" s="23"/>
     </row>
-    <row r="249" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C249" s="24"/>
       <c r="D249" s="22"/>
       <c r="E249" s="22"/>
       <c r="F249" s="22"/>
     </row>
-    <row r="250" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C250" s="25"/>
       <c r="D250" s="23"/>
       <c r="E250" s="23"/>
       <c r="F250" s="23"/>
     </row>
-    <row r="251" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C251" s="24"/>
       <c r="D251" s="22"/>
       <c r="E251" s="22"/>
       <c r="F251" s="22"/>
     </row>
-    <row r="252" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C252" s="25"/>
       <c r="D252" s="23"/>
       <c r="E252" s="23"/>
       <c r="F252" s="23"/>
     </row>
-    <row r="253" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C253" s="24"/>
       <c r="D253" s="22"/>
       <c r="E253" s="22"/>
       <c r="F253" s="22"/>
     </row>
-    <row r="254" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C254" s="25"/>
       <c r="D254" s="23"/>
       <c r="E254" s="23"/>
       <c r="F254" s="23"/>
     </row>
-    <row r="255" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C255" s="24"/>
       <c r="D255" s="22"/>
       <c r="E255" s="22"/>
       <c r="F255" s="22"/>
     </row>
-    <row r="256" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C256" s="25"/>
       <c r="D256" s="23"/>
       <c r="E256" s="23"/>
       <c r="F256" s="23"/>
     </row>
-    <row r="257" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C257" s="24"/>
       <c r="D257" s="22"/>
       <c r="E257" s="22"/>
       <c r="F257" s="22"/>
     </row>
-    <row r="258" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C258" s="25"/>
       <c r="D258" s="23"/>
       <c r="E258" s="23"/>
       <c r="F258" s="23"/>
     </row>
-    <row r="259" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C259" s="24"/>
       <c r="D259" s="22"/>
       <c r="E259" s="22"/>
       <c r="F259" s="22"/>
     </row>
-    <row r="260" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C260" s="25"/>
       <c r="D260" s="23"/>
       <c r="E260" s="23"/>
       <c r="F260" s="23"/>
     </row>
-    <row r="261" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C261" s="24"/>
       <c r="D261" s="22"/>
       <c r="E261" s="22"/>
       <c r="F261" s="22"/>
     </row>
-    <row r="262" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C262" s="25"/>
       <c r="D262" s="23"/>
       <c r="E262" s="23"/>
       <c r="F262" s="23"/>
     </row>
-    <row r="263" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C263" s="24"/>
       <c r="D263" s="22"/>
       <c r="E263" s="22"/>
       <c r="F263" s="22"/>
     </row>
-    <row r="264" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C264" s="25"/>
       <c r="D264" s="23"/>
       <c r="E264" s="23"/>
       <c r="F264" s="23"/>
     </row>
-    <row r="265" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C265" s="24"/>
       <c r="D265" s="22"/>
       <c r="E265" s="22"/>
       <c r="F265" s="22"/>
     </row>
-    <row r="266" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C266" s="25"/>
       <c r="D266" s="23"/>
       <c r="E266" s="23"/>
       <c r="F266" s="23"/>
     </row>
-    <row r="267" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C267" s="24"/>
       <c r="D267" s="22"/>
       <c r="E267" s="22"/>
       <c r="F267" s="22"/>
     </row>
-    <row r="268" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C268" s="25"/>
       <c r="D268" s="23"/>
       <c r="E268" s="23"/>
       <c r="F268" s="23"/>
     </row>
-    <row r="269" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C269" s="24"/>
       <c r="D269" s="22"/>
       <c r="E269" s="22"/>
       <c r="F269" s="22"/>
     </row>
-    <row r="270" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C270" s="25"/>
       <c r="D270" s="23"/>
       <c r="E270" s="23"/>
       <c r="F270" s="23"/>
     </row>
-    <row r="271" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C271" s="24"/>
       <c r="D271" s="22"/>
       <c r="E271" s="22"/>
       <c r="F271" s="22"/>
     </row>
-    <row r="272" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C272" s="25"/>
       <c r="D272" s="23"/>
       <c r="E272" s="23"/>
       <c r="F272" s="23"/>
     </row>
-    <row r="273" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C273" s="24"/>
       <c r="D273" s="22"/>
       <c r="E273" s="22"/>
       <c r="F273" s="22"/>
     </row>
-    <row r="274" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C274" s="25"/>
       <c r="D274" s="23"/>
       <c r="E274" s="23"/>
       <c r="F274" s="23"/>
     </row>
-    <row r="275" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C275" s="24"/>
       <c r="D275" s="22"/>
       <c r="E275" s="22"/>
       <c r="F275" s="22"/>
     </row>
-    <row r="276" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C276" s="25"/>
       <c r="D276" s="23"/>
       <c r="E276" s="23"/>
       <c r="F276" s="23"/>
     </row>
-    <row r="277" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C277" s="24"/>
       <c r="D277" s="22"/>
       <c r="E277" s="22"/>
       <c r="F277" s="22"/>
     </row>
-    <row r="278" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C278" s="25"/>
       <c r="D278" s="23"/>
       <c r="E278" s="23"/>
       <c r="F278" s="23"/>
     </row>
-    <row r="279" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C279" s="24"/>
       <c r="D279" s="22"/>
       <c r="E279" s="22"/>
       <c r="F279" s="22"/>
     </row>
-    <row r="280" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C280" s="25"/>
       <c r="D280" s="23"/>
       <c r="E280" s="23"/>
       <c r="F280" s="23"/>
     </row>
-    <row r="281" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C281" s="24"/>
       <c r="D281" s="22"/>
       <c r="E281" s="22"/>
       <c r="F281" s="22"/>
     </row>
-    <row r="282" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C282" s="25"/>
       <c r="D282" s="23"/>
       <c r="E282" s="23"/>
       <c r="F282" s="23"/>
     </row>
-    <row r="283" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C283" s="24"/>
       <c r="D283" s="22"/>
       <c r="E283" s="22"/>
       <c r="F283" s="22"/>
     </row>
-    <row r="284" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C284" s="25"/>
       <c r="D284" s="23"/>
       <c r="E284" s="23"/>
       <c r="F284" s="23"/>
     </row>
-    <row r="285" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C285" s="24"/>
       <c r="D285" s="22"/>
       <c r="E285" s="22"/>
       <c r="F285" s="22"/>
     </row>
-    <row r="286" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C286" s="25"/>
       <c r="D286" s="23"/>
       <c r="E286" s="23"/>
       <c r="F286" s="23"/>
     </row>
-    <row r="287" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C287" s="24"/>
       <c r="D287" s="22"/>
       <c r="E287" s="22"/>
       <c r="F287" s="22"/>
     </row>
-    <row r="288" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C288" s="25"/>
       <c r="D288" s="23"/>
       <c r="E288" s="23"/>
       <c r="F288" s="23"/>
     </row>
-    <row r="289" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C289" s="24"/>
       <c r="D289" s="22"/>
       <c r="E289" s="22"/>
       <c r="F289" s="22"/>
     </row>
-    <row r="290" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C290" s="25"/>
       <c r="D290" s="23"/>
       <c r="E290" s="23"/>
       <c r="F290" s="23"/>
     </row>
-    <row r="291" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C291" s="24"/>
       <c r="D291" s="22"/>
       <c r="E291" s="22"/>
       <c r="F291" s="22"/>
     </row>
-    <row r="292" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C292" s="25"/>
       <c r="D292" s="23"/>
       <c r="E292" s="23"/>
       <c r="F292" s="23"/>
     </row>
-    <row r="293" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C293" s="24"/>
       <c r="D293" s="22"/>
       <c r="E293" s="22"/>
       <c r="F293" s="22"/>
     </row>
-    <row r="294" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C294" s="25"/>
       <c r="D294" s="23"/>
       <c r="E294" s="23"/>
       <c r="F294" s="23"/>
     </row>
-    <row r="295" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C295" s="24"/>
       <c r="D295" s="22"/>
       <c r="E295" s="22"/>
       <c r="F295" s="22"/>
     </row>
-    <row r="296" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C296" s="25"/>
       <c r="D296" s="23"/>
       <c r="E296" s="23"/>
       <c r="F296" s="23"/>
     </row>
-    <row r="297" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C297" s="24"/>
       <c r="D297" s="22"/>
       <c r="E297" s="22"/>
       <c r="F297" s="22"/>
     </row>
-    <row r="298" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C298" s="25"/>
       <c r="D298" s="23"/>
       <c r="E298" s="23"/>
       <c r="F298" s="23"/>
     </row>
-    <row r="299" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C299" s="24"/>
       <c r="D299" s="22"/>
       <c r="E299" s="22"/>
       <c r="F299" s="22"/>
     </row>
-    <row r="300" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C300" s="25"/>
       <c r="D300" s="23"/>
       <c r="E300" s="23"/>
       <c r="F300" s="23"/>
     </row>
-    <row r="301" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C301" s="24"/>
       <c r="D301" s="22"/>
       <c r="E301" s="22"/>
       <c r="F301" s="22"/>
     </row>
-    <row r="302" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C302" s="25"/>
       <c r="D302" s="23"/>
       <c r="E302" s="23"/>
       <c r="F302" s="23"/>
     </row>
-    <row r="303" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C303" s="24"/>
       <c r="D303" s="22"/>
       <c r="E303" s="22"/>
       <c r="F303" s="22"/>
     </row>
-    <row r="304" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C304" s="25"/>
       <c r="D304" s="23"/>
       <c r="E304" s="23"/>
       <c r="F304" s="23"/>
     </row>
-    <row r="305" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C305" s="24"/>
       <c r="D305" s="22"/>
       <c r="E305" s="22"/>
       <c r="F305" s="22"/>
     </row>
-    <row r="306" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C306" s="25"/>
       <c r="D306" s="23"/>
       <c r="E306" s="23"/>
       <c r="F306" s="23"/>
     </row>
-    <row r="307" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C307" s="24"/>
       <c r="D307" s="22"/>
       <c r="E307" s="22"/>
       <c r="F307" s="22"/>
     </row>
-    <row r="308" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C308" s="25"/>
       <c r="D308" s="23"/>
       <c r="E308" s="23"/>
       <c r="F308" s="23"/>
     </row>
-    <row r="309" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C309" s="24"/>
       <c r="D309" s="22"/>
       <c r="E309" s="22"/>
       <c r="F309" s="22"/>
     </row>
-    <row r="310" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C310" s="25"/>
       <c r="D310" s="23"/>
       <c r="E310" s="23"/>
       <c r="F310" s="23"/>
     </row>
-    <row r="311" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C311" s="24"/>
       <c r="D311" s="22"/>
       <c r="E311" s="22"/>
       <c r="F311" s="22"/>
     </row>
-    <row r="312" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C312" s="25"/>
       <c r="D312" s="23"/>
       <c r="E312" s="23"/>
       <c r="F312" s="23"/>
     </row>
-    <row r="313" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C313" s="24"/>
       <c r="D313" s="22"/>
       <c r="E313" s="22"/>
       <c r="F313" s="22"/>
     </row>
-    <row r="314" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C314" s="25"/>
       <c r="D314" s="23"/>
       <c r="E314" s="23"/>
       <c r="F314" s="23"/>
     </row>
-    <row r="315" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C315" s="24"/>
       <c r="D315" s="22"/>
       <c r="E315" s="22"/>
       <c r="F315" s="22"/>
     </row>
-    <row r="316" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C316" s="25"/>
       <c r="D316" s="23"/>
       <c r="E316" s="23"/>
       <c r="F316" s="23"/>
     </row>
-    <row r="317" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C317" s="24"/>
       <c r="D317" s="22"/>
       <c r="E317" s="22"/>
       <c r="F317" s="22"/>
     </row>
-    <row r="318" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C318" s="25"/>
       <c r="D318" s="23"/>
       <c r="E318" s="23"/>
       <c r="F318" s="23"/>
     </row>
-    <row r="319" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C319" s="24"/>
       <c r="D319" s="22"/>
       <c r="E319" s="22"/>
       <c r="F319" s="22"/>
     </row>
-    <row r="320" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C320" s="25"/>
       <c r="D320" s="23"/>
       <c r="E320" s="23"/>
       <c r="F320" s="23"/>
     </row>
-    <row r="321" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C321" s="24"/>
       <c r="D321" s="22"/>
       <c r="E321" s="22"/>
       <c r="F321" s="22"/>
     </row>
-    <row r="322" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C322" s="25"/>
       <c r="D322" s="23"/>
       <c r="E322" s="23"/>
       <c r="F322" s="23"/>
     </row>
-    <row r="323" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C323" s="24"/>
       <c r="D323" s="22"/>
       <c r="E323" s="22"/>
       <c r="F323" s="22"/>
     </row>
-    <row r="324" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C324" s="25"/>
       <c r="D324" s="23"/>
       <c r="E324" s="23"/>
       <c r="F324" s="23"/>
     </row>
-    <row r="325" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C325" s="24"/>
       <c r="D325" s="22"/>
       <c r="E325" s="22"/>
       <c r="F325" s="22"/>
     </row>
-    <row r="326" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C326" s="25"/>
       <c r="D326" s="23"/>
       <c r="E326" s="23"/>
       <c r="F326" s="23"/>
     </row>
-    <row r="327" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C327" s="24"/>
       <c r="D327" s="22"/>
       <c r="E327" s="22"/>
       <c r="F327" s="22"/>
     </row>
-    <row r="328" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C328" s="25"/>
       <c r="D328" s="23"/>
       <c r="E328" s="23"/>
       <c r="F328" s="23"/>
     </row>
-    <row r="329" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C329" s="24"/>
       <c r="D329" s="22"/>
       <c r="E329" s="22"/>
       <c r="F329" s="22"/>
     </row>
-    <row r="330" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C330" s="25"/>
       <c r="D330" s="23"/>
       <c r="E330" s="23"/>
       <c r="F330" s="23"/>
     </row>
-    <row r="331" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C331" s="24"/>
       <c r="D331" s="22"/>
       <c r="E331" s="22"/>
       <c r="F331" s="22"/>
     </row>
-    <row r="332" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C332" s="25"/>
       <c r="D332" s="23"/>
       <c r="E332" s="23"/>
       <c r="F332" s="23"/>
     </row>
-    <row r="333" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C333" s="24"/>
       <c r="D333" s="22"/>
       <c r="E333" s="22"/>
       <c r="F333" s="22"/>
     </row>
-    <row r="334" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C334" s="25"/>
       <c r="D334" s="23"/>
       <c r="E334" s="23"/>
       <c r="F334" s="23"/>
     </row>
-    <row r="335" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C335" s="24"/>
       <c r="D335" s="22"/>
       <c r="E335" s="22"/>
       <c r="F335" s="22"/>
     </row>
-    <row r="336" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C336" s="25"/>
       <c r="D336" s="23"/>
       <c r="E336" s="23"/>
       <c r="F336" s="23"/>
     </row>
-    <row r="337" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C337" s="24"/>
       <c r="D337" s="22"/>
       <c r="E337" s="22"/>
       <c r="F337" s="22"/>
     </row>
-    <row r="338" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C338" s="25"/>
       <c r="D338" s="23"/>
       <c r="E338" s="23"/>
       <c r="F338" s="23"/>
     </row>
-    <row r="339" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C339" s="24"/>
       <c r="D339" s="22"/>
       <c r="E339" s="22"/>
       <c r="F339" s="22"/>
     </row>
-    <row r="340" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C340" s="25"/>
       <c r="D340" s="23"/>
       <c r="E340" s="23"/>
       <c r="F340" s="23"/>
     </row>
-    <row r="341" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C341" s="24"/>
       <c r="D341" s="22"/>
       <c r="E341" s="22"/>
       <c r="F341" s="22"/>
     </row>
-    <row r="342" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C342" s="25"/>
       <c r="D342" s="23"/>
       <c r="E342" s="23"/>
       <c r="F342" s="23"/>
     </row>
-    <row r="343" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C343" s="24"/>
       <c r="D343" s="22"/>
       <c r="E343" s="22"/>
       <c r="F343" s="22"/>
     </row>
-    <row r="344" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C344" s="25"/>
       <c r="D344" s="23"/>
       <c r="E344" s="23"/>
       <c r="F344" s="23"/>
     </row>
-    <row r="345" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C345" s="24"/>
       <c r="D345" s="22"/>
       <c r="E345" s="22"/>
       <c r="F345" s="22"/>
     </row>
-    <row r="346" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C346" s="25"/>
       <c r="D346" s="23"/>
       <c r="E346" s="23"/>
       <c r="F346" s="23"/>
     </row>
-    <row r="347" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C347" s="24"/>
       <c r="D347" s="22"/>
       <c r="E347" s="22"/>
       <c r="F347" s="22"/>
     </row>
-    <row r="348" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C348" s="25"/>
       <c r="D348" s="23"/>
       <c r="E348" s="23"/>
       <c r="F348" s="23"/>
     </row>
-    <row r="349" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C349" s="24"/>
       <c r="D349" s="22"/>
       <c r="E349" s="22"/>
       <c r="F349" s="22"/>
     </row>
-    <row r="350" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C350" s="25"/>
       <c r="D350" s="23"/>
       <c r="E350" s="23"/>
       <c r="F350" s="23"/>
     </row>
-    <row r="351" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C351" s="24"/>
       <c r="D351" s="22"/>
       <c r="E351" s="22"/>
       <c r="F351" s="22"/>
     </row>
-    <row r="352" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C352" s="25"/>
       <c r="D352" s="23"/>
       <c r="E352" s="23"/>
       <c r="F352" s="23"/>
     </row>
-    <row r="353" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C353" s="24"/>
       <c r="D353" s="22"/>
       <c r="E353" s="22"/>
       <c r="F353" s="22"/>
     </row>
-    <row r="354" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C354" s="25"/>
       <c r="D354" s="23"/>
       <c r="E354" s="23"/>
       <c r="F354" s="23"/>
     </row>
-    <row r="355" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C355" s="24"/>
       <c r="D355" s="22"/>
       <c r="E355" s="22"/>
       <c r="F355" s="22"/>
     </row>
-    <row r="356" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C356" s="25"/>
       <c r="D356" s="23"/>
       <c r="E356" s="23"/>
       <c r="F356" s="23"/>
     </row>
-    <row r="357" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C357" s="24"/>
       <c r="D357" s="22"/>
       <c r="E357" s="22"/>
       <c r="F357" s="22"/>
     </row>
-    <row r="358" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C358" s="25"/>
       <c r="D358" s="23"/>
       <c r="E358" s="23"/>
       <c r="F358" s="23"/>
     </row>
-    <row r="359" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C359" s="24"/>
       <c r="D359" s="22"/>
       <c r="E359" s="22"/>
       <c r="F359" s="22"/>
     </row>
-    <row r="360" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C360" s="25"/>
       <c r="D360" s="23"/>
       <c r="E360" s="23"/>
       <c r="F360" s="23"/>
     </row>
-    <row r="361" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C361" s="24"/>
       <c r="D361" s="22"/>
       <c r="E361" s="22"/>
       <c r="F361" s="22"/>
     </row>
-    <row r="362" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C362" s="25"/>
       <c r="D362" s="23"/>
       <c r="E362" s="23"/>
       <c r="F362" s="23"/>
     </row>
-    <row r="363" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C363" s="24"/>
       <c r="D363" s="22"/>
       <c r="E363" s="22"/>
       <c r="F363" s="22"/>
     </row>
-    <row r="364" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C364" s="25"/>
       <c r="D364" s="23"/>
       <c r="E364" s="23"/>
       <c r="F364" s="23"/>
     </row>
-    <row r="365" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C365" s="24"/>
       <c r="D365" s="22"/>
       <c r="E365" s="22"/>
       <c r="F365" s="22"/>
     </row>
-    <row r="366" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C366" s="25"/>
       <c r="D366" s="23"/>
       <c r="E366" s="23"/>
       <c r="F366" s="23"/>
     </row>
-    <row r="367" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C367" s="24"/>
       <c r="D367" s="22"/>
       <c r="E367" s="22"/>
       <c r="F367" s="22"/>
     </row>
-    <row r="368" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C368" s="25"/>
       <c r="D368" s="23"/>
       <c r="E368" s="23"/>
       <c r="F368" s="23"/>
     </row>
-    <row r="369" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C369" s="24"/>
       <c r="D369" s="22"/>
       <c r="E369" s="22"/>
       <c r="F369" s="22"/>
     </row>
-    <row r="370" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C370" s="25"/>
       <c r="D370" s="23"/>
       <c r="E370" s="23"/>
       <c r="F370" s="23"/>
     </row>
-    <row r="371" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C371" s="24"/>
       <c r="D371" s="22"/>
       <c r="E371" s="22"/>
       <c r="F371" s="22"/>
     </row>
-    <row r="372" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C372" s="25"/>
       <c r="D372" s="23"/>
       <c r="E372" s="23"/>
       <c r="F372" s="23"/>
     </row>
-    <row r="373" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C373" s="24"/>
       <c r="D373" s="22"/>
       <c r="E373" s="22"/>
       <c r="F373" s="22"/>
     </row>
-    <row r="374" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C374" s="25"/>
       <c r="D374" s="23"/>
       <c r="E374" s="23"/>
       <c r="F374" s="23"/>
     </row>
-    <row r="375" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C375" s="24"/>
       <c r="D375" s="22"/>
       <c r="E375" s="22"/>
       <c r="F375" s="22"/>
     </row>
-    <row r="376" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C376" s="25"/>
       <c r="D376" s="23"/>
       <c r="E376" s="23"/>
       <c r="F376" s="23"/>
     </row>
-    <row r="377" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C377" s="24"/>
       <c r="D377" s="22"/>
       <c r="E377" s="22"/>
       <c r="F377" s="22"/>
     </row>
-    <row r="378" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C378" s="25"/>
       <c r="D378" s="23"/>
       <c r="E378" s="23"/>
       <c r="F378" s="23"/>
     </row>
-    <row r="379" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C379" s="24"/>
       <c r="D379" s="22"/>
       <c r="E379" s="22"/>
       <c r="F379" s="22"/>
     </row>
-    <row r="380" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C380" s="25"/>
       <c r="D380" s="23"/>
       <c r="E380" s="23"/>
       <c r="F380" s="23"/>
     </row>
-    <row r="381" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C381" s="24"/>
       <c r="D381" s="22"/>
       <c r="E381" s="22"/>
       <c r="F381" s="22"/>
     </row>
-    <row r="382" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C382" s="25"/>
       <c r="D382" s="23"/>
       <c r="E382" s="23"/>
       <c r="F382" s="23"/>
     </row>
-    <row r="383" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C383" s="24"/>
       <c r="D383" s="22"/>
       <c r="E383" s="22"/>
       <c r="F383" s="22"/>
     </row>
-    <row r="384" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C384" s="25"/>
       <c r="D384" s="23"/>
       <c r="E384" s="23"/>
       <c r="F384" s="23"/>
     </row>
-    <row r="385" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C385" s="24"/>
       <c r="D385" s="22"/>
       <c r="E385" s="22"/>
       <c r="F385" s="22"/>
     </row>
-    <row r="386" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C386" s="25"/>
       <c r="D386" s="23"/>
       <c r="E386" s="23"/>
       <c r="F386" s="23"/>
     </row>
-    <row r="387" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C387" s="24"/>
       <c r="D387" s="22"/>
       <c r="E387" s="22"/>
       <c r="F387" s="22"/>
     </row>
-    <row r="388" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C388" s="25"/>
       <c r="D388" s="23"/>
       <c r="E388" s="23"/>
       <c r="F388" s="23"/>
     </row>
-    <row r="389" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C389" s="24"/>
       <c r="D389" s="22"/>
       <c r="E389" s="22"/>
       <c r="F389" s="22"/>
     </row>
-    <row r="390" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C390" s="25"/>
       <c r="D390" s="23"/>
       <c r="E390" s="23"/>
       <c r="F390" s="23"/>
     </row>
-    <row r="391" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C391" s="24"/>
       <c r="D391" s="22"/>
       <c r="E391" s="22"/>
       <c r="F391" s="22"/>
     </row>
-    <row r="392" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C392" s="25"/>
       <c r="D392" s="23"/>
       <c r="E392" s="23"/>
       <c r="F392" s="23"/>
     </row>
-    <row r="393" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C393" s="24"/>
       <c r="D393" s="22"/>
       <c r="E393" s="22"/>
       <c r="F393" s="22"/>
     </row>
-    <row r="394" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C394" s="25"/>
       <c r="D394" s="23"/>
       <c r="E394" s="23"/>
       <c r="F394" s="23"/>
     </row>
-    <row r="395" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C395" s="24"/>
       <c r="D395" s="22"/>
       <c r="E395" s="22"/>
       <c r="F395" s="22"/>
     </row>
-    <row r="396" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C396" s="25"/>
       <c r="D396" s="23"/>
       <c r="E396" s="23"/>
       <c r="F396" s="23"/>
     </row>
-    <row r="397" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C397" s="24"/>
       <c r="D397" s="22"/>
       <c r="E397" s="22"/>
       <c r="F397" s="22"/>
     </row>
-    <row r="398" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C398" s="25"/>
       <c r="D398" s="23"/>
       <c r="E398" s="23"/>
       <c r="F398" s="23"/>
     </row>
-    <row r="399" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C399" s="24"/>
       <c r="D399" s="22"/>
       <c r="E399" s="22"/>
       <c r="F399" s="22"/>
     </row>
-    <row r="400" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C400" s="25"/>
       <c r="D400" s="23"/>
       <c r="E400" s="23"/>
       <c r="F400" s="23"/>
     </row>
-    <row r="401" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C401" s="24"/>
       <c r="D401" s="22"/>
       <c r="E401" s="22"/>
       <c r="F401" s="22"/>
     </row>
-    <row r="402" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C402" s="25"/>
       <c r="D402" s="23"/>
       <c r="E402" s="23"/>
       <c r="F402" s="23"/>
     </row>
-    <row r="403" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C403" s="24"/>
       <c r="D403" s="22"/>
       <c r="E403" s="22"/>
       <c r="F403" s="22"/>
     </row>
-    <row r="404" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C404" s="25"/>
       <c r="D404" s="23"/>
       <c r="E404" s="23"/>
       <c r="F404" s="23"/>
     </row>
-    <row r="405" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C405" s="24"/>
       <c r="D405" s="22"/>
       <c r="E405" s="22"/>
       <c r="F405" s="22"/>
     </row>
-    <row r="406" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C406" s="25"/>
       <c r="D406" s="23"/>
       <c r="E406" s="23"/>
       <c r="F406" s="23"/>
     </row>
-    <row r="407" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C407" s="24"/>
       <c r="D407" s="22"/>
       <c r="E407" s="22"/>
       <c r="F407" s="22"/>
     </row>
-    <row r="408" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C408" s="25"/>
       <c r="D408" s="23"/>
       <c r="E408" s="23"/>
       <c r="F408" s="23"/>
     </row>
-    <row r="409" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C409" s="24"/>
       <c r="D409" s="22"/>
       <c r="E409" s="22"/>
       <c r="F409" s="22"/>
     </row>
-    <row r="410" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C410" s="25"/>
       <c r="D410" s="23"/>
       <c r="E410" s="23"/>
       <c r="F410" s="23"/>
     </row>
-    <row r="411" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C411" s="24"/>
       <c r="D411" s="22"/>
       <c r="E411" s="22"/>
       <c r="F411" s="22"/>
     </row>
-    <row r="412" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C412" s="25"/>
       <c r="D412" s="23"/>
       <c r="E412" s="23"/>
       <c r="F412" s="23"/>
     </row>
-    <row r="413" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C413" s="24"/>
       <c r="D413" s="22"/>
       <c r="E413" s="22"/>
       <c r="F413" s="22"/>
     </row>
-    <row r="414" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C414" s="25"/>
       <c r="D414" s="23"/>
       <c r="E414" s="23"/>
       <c r="F414" s="23"/>
     </row>
-    <row r="415" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C415" s="24"/>
       <c r="D415" s="22"/>
       <c r="E415" s="22"/>
       <c r="F415" s="22"/>
     </row>
-    <row r="416" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C416" s="25"/>
       <c r="D416" s="23"/>
       <c r="E416" s="23"/>
       <c r="F416" s="23"/>
     </row>
-    <row r="417" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C417" s="24"/>
       <c r="D417" s="22"/>
       <c r="E417" s="22"/>
       <c r="F417" s="22"/>
     </row>
-    <row r="418" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C418" s="25"/>
       <c r="D418" s="23"/>
       <c r="E418" s="23"/>
       <c r="F418" s="23"/>
     </row>
-    <row r="419" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C419" s="24"/>
       <c r="D419" s="22"/>
       <c r="E419" s="22"/>
       <c r="F419" s="22"/>
     </row>
-    <row r="420" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C420" s="25"/>
       <c r="D420" s="23"/>
       <c r="E420" s="23"/>
       <c r="F420" s="23"/>
     </row>
-    <row r="421" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C421" s="24"/>
       <c r="D421" s="22"/>
       <c r="E421" s="22"/>
       <c r="F421" s="22"/>
     </row>
-    <row r="422" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C422" s="25"/>
       <c r="D422" s="23"/>
       <c r="E422" s="23"/>
       <c r="F422" s="23"/>
     </row>
-    <row r="423" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C423" s="24"/>
       <c r="D423" s="22"/>
       <c r="E423" s="22"/>
       <c r="F423" s="22"/>
     </row>
-    <row r="424" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C424" s="25"/>
       <c r="D424" s="23"/>
       <c r="E424" s="23"/>
       <c r="F424" s="23"/>
     </row>
-    <row r="425" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C425" s="24"/>
       <c r="D425" s="22"/>
       <c r="E425" s="22"/>
       <c r="F425" s="22"/>
     </row>
-    <row r="426" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C426" s="25"/>
       <c r="D426" s="23"/>
       <c r="E426" s="23"/>
       <c r="F426" s="23"/>
     </row>
-    <row r="427" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C427" s="24"/>
       <c r="D427" s="22"/>
       <c r="E427" s="22"/>
       <c r="F427" s="22"/>
     </row>
-    <row r="428" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C428" s="25"/>
       <c r="D428" s="23"/>
       <c r="E428" s="23"/>
       <c r="F428" s="23"/>
     </row>
-    <row r="429" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C429" s="24"/>
       <c r="D429" s="22"/>
       <c r="E429" s="22"/>
       <c r="F429" s="22"/>
     </row>
-    <row r="430" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C430" s="25"/>
       <c r="D430" s="23"/>
       <c r="E430" s="23"/>
       <c r="F430" s="23"/>
     </row>
-    <row r="431" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C431" s="24"/>
       <c r="D431" s="22"/>
       <c r="E431" s="22"/>
       <c r="F431" s="22"/>
     </row>
-    <row r="432" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C432" s="25"/>
       <c r="D432" s="23"/>
       <c r="E432" s="23"/>
       <c r="F432" s="23"/>
     </row>
-    <row r="433" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C433" s="24"/>
       <c r="D433" s="22"/>
       <c r="E433" s="22"/>
       <c r="F433" s="22"/>
     </row>
-    <row r="434" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C434" s="25"/>
       <c r="D434" s="23"/>
       <c r="E434" s="23"/>
       <c r="F434" s="23"/>
     </row>
-    <row r="435" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C435" s="24"/>
       <c r="D435" s="22"/>
       <c r="E435" s="22"/>
       <c r="F435" s="22"/>
     </row>
-    <row r="436" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C436" s="25"/>
       <c r="D436" s="23"/>
       <c r="E436" s="23"/>
       <c r="F436" s="23"/>
     </row>
-    <row r="437" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C437" s="24"/>
       <c r="D437" s="22"/>
       <c r="E437" s="22"/>
       <c r="F437" s="22"/>
     </row>
-    <row r="438" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C438" s="25"/>
       <c r="D438" s="23"/>
       <c r="E438" s="23"/>
       <c r="F438" s="23"/>
     </row>
-    <row r="439" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C439" s="24"/>
       <c r="D439" s="22"/>
       <c r="E439" s="22"/>
       <c r="F439" s="22"/>
     </row>
-    <row r="440" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C440" s="25"/>
       <c r="D440" s="23"/>
       <c r="E440" s="23"/>
       <c r="F440" s="23"/>
     </row>
-    <row r="441" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C441" s="24"/>
       <c r="D441" s="22"/>
       <c r="E441" s="22"/>
       <c r="F441" s="22"/>
     </row>
-    <row r="442" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C442" s="25"/>
       <c r="D442" s="23"/>
       <c r="E442" s="23"/>
       <c r="F442" s="23"/>
     </row>
-    <row r="443" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C443" s="24"/>
       <c r="D443" s="22"/>
       <c r="E443" s="22"/>
       <c r="F443" s="22"/>
     </row>
-    <row r="444" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C444" s="25"/>
       <c r="D444" s="23"/>
       <c r="E444" s="23"/>
       <c r="F444" s="23"/>
     </row>
-    <row r="445" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C445" s="24"/>
       <c r="D445" s="22"/>
       <c r="E445" s="22"/>
       <c r="F445" s="22"/>
     </row>
-    <row r="446" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C446" s="25"/>
       <c r="D446" s="23"/>
       <c r="E446" s="23"/>
       <c r="F446" s="23"/>
     </row>
-    <row r="447" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C447" s="24"/>
       <c r="D447" s="22"/>
       <c r="E447" s="22"/>
       <c r="F447" s="22"/>
     </row>
-    <row r="448" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C448" s="25"/>
       <c r="D448" s="23"/>
       <c r="E448" s="23"/>
       <c r="F448" s="23"/>
     </row>
-    <row r="449" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C449" s="24"/>
       <c r="D449" s="22"/>
       <c r="E449" s="22"/>
       <c r="F449" s="22"/>
     </row>
-    <row r="450" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C450" s="25"/>
       <c r="D450" s="23"/>
       <c r="E450" s="23"/>
       <c r="F450" s="23"/>
     </row>
-    <row r="451" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C451" s="24"/>
       <c r="D451" s="22"/>
       <c r="E451" s="22"/>
       <c r="F451" s="22"/>
     </row>
-    <row r="452" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C452" s="25"/>
       <c r="D452" s="23"/>
       <c r="E452" s="23"/>
       <c r="F452" s="23"/>
     </row>
-    <row r="453" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C453" s="24"/>
       <c r="D453" s="22"/>
       <c r="E453" s="22"/>
       <c r="F453" s="22"/>
     </row>
-    <row r="454" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C454" s="25"/>
       <c r="D454" s="23"/>
       <c r="E454" s="23"/>
       <c r="F454" s="23"/>
     </row>
-    <row r="455" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C455" s="24"/>
       <c r="D455" s="22"/>
       <c r="E455" s="22"/>
       <c r="F455" s="22"/>
     </row>
-    <row r="456" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C456" s="25"/>
       <c r="D456" s="23"/>
       <c r="E456" s="23"/>
       <c r="F456" s="23"/>
     </row>
-    <row r="457" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C457" s="24"/>
       <c r="D457" s="22"/>
       <c r="E457" s="22"/>
       <c r="F457" s="22"/>
     </row>
-    <row r="458" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C458" s="25"/>
       <c r="D458" s="23"/>
       <c r="E458" s="23"/>
       <c r="F458" s="23"/>
     </row>
-    <row r="459" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C459" s="24"/>
       <c r="D459" s="22"/>
       <c r="E459" s="22"/>
       <c r="F459" s="22"/>
     </row>
-    <row r="460" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C460" s="25"/>
       <c r="D460" s="23"/>
       <c r="E460" s="23"/>
       <c r="F460" s="23"/>
     </row>
-    <row r="461" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C461" s="24"/>
       <c r="D461" s="22"/>
       <c r="E461" s="22"/>
       <c r="F461" s="22"/>
     </row>
-    <row r="462" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C462" s="25"/>
       <c r="D462" s="23"/>
       <c r="E462" s="23"/>
       <c r="F462" s="23"/>
     </row>
-    <row r="463" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C463" s="24"/>
       <c r="D463" s="22"/>
       <c r="E463" s="22"/>
       <c r="F463" s="22"/>
     </row>
-    <row r="464" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C464" s="25"/>
       <c r="D464" s="23"/>
       <c r="E464" s="23"/>
       <c r="F464" s="23"/>
     </row>
-    <row r="465" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C465" s="24"/>
       <c r="D465" s="22"/>
       <c r="E465" s="22"/>
       <c r="F465" s="22"/>
     </row>
-    <row r="466" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C466" s="25"/>
       <c r="D466" s="23"/>
       <c r="E466" s="23"/>
       <c r="F466" s="23"/>
     </row>
-    <row r="467" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C467" s="24"/>
       <c r="D467" s="22"/>
       <c r="E467" s="22"/>
       <c r="F467" s="22"/>
     </row>
-    <row r="468" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C468" s="25"/>
       <c r="D468" s="23"/>
       <c r="E468" s="23"/>
       <c r="F468" s="23"/>
     </row>
-    <row r="469" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C469" s="24"/>
       <c r="D469" s="22"/>
       <c r="E469" s="22"/>
       <c r="F469" s="22"/>
     </row>
-    <row r="470" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C470" s="25"/>
       <c r="D470" s="23"/>
       <c r="E470" s="23"/>
       <c r="F470" s="23"/>
     </row>
-    <row r="471" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C471" s="24"/>
       <c r="D471" s="22"/>
       <c r="E471" s="22"/>
       <c r="F471" s="22"/>
     </row>
-    <row r="472" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C472" s="25"/>
       <c r="D472" s="23"/>
       <c r="E472" s="23"/>
       <c r="F472" s="23"/>
     </row>
-    <row r="473" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C473" s="24"/>
       <c r="D473" s="22"/>
       <c r="E473" s="22"/>
       <c r="F473" s="22"/>
     </row>
-    <row r="474" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C474" s="25"/>
       <c r="D474" s="23"/>
       <c r="E474" s="23"/>
       <c r="F474" s="23"/>
     </row>
-    <row r="475" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C475" s="24"/>
       <c r="D475" s="22"/>
       <c r="E475" s="22"/>
       <c r="F475" s="22"/>
     </row>
-    <row r="476" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C476" s="25"/>
       <c r="D476" s="23"/>
       <c r="E476" s="23"/>
       <c r="F476" s="23"/>
     </row>
-    <row r="477" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C477" s="24"/>
       <c r="D477" s="22"/>
       <c r="E477" s="22"/>
       <c r="F477" s="22"/>
     </row>
-    <row r="478" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C478" s="25"/>
       <c r="D478" s="23"/>
       <c r="E478" s="23"/>
       <c r="F478" s="23"/>
     </row>
-    <row r="479" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C479" s="24"/>
       <c r="D479" s="22"/>
       <c r="E479" s="22"/>
       <c r="F479" s="22"/>
     </row>
-    <row r="480" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C480" s="25"/>
       <c r="D480" s="23"/>
       <c r="E480" s="23"/>
       <c r="F480" s="23"/>
     </row>
-    <row r="481" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C481" s="24"/>
       <c r="D481" s="22"/>
       <c r="E481" s="22"/>
       <c r="F481" s="22"/>
     </row>
-    <row r="482" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C482" s="25"/>
       <c r="D482" s="23"/>
       <c r="E482" s="23"/>
       <c r="F482" s="23"/>
     </row>
-    <row r="483" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C483" s="24"/>
       <c r="D483" s="22"/>
       <c r="E483" s="22"/>
       <c r="F483" s="22"/>
     </row>
-    <row r="484" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="484" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C484" s="25"/>
       <c r="D484" s="23"/>
       <c r="E484" s="23"/>
       <c r="F484" s="23"/>
     </row>
-    <row r="485" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C485" s="24"/>
       <c r="D485" s="22"/>
       <c r="E485" s="22"/>
       <c r="F485" s="22"/>
     </row>
-    <row r="486" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="486" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C486" s="25"/>
       <c r="D486" s="23"/>
       <c r="E486" s="23"/>
       <c r="F486" s="23"/>
     </row>
-    <row r="487" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="487" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C487" s="24"/>
       <c r="D487" s="22"/>
       <c r="E487" s="22"/>
       <c r="F487" s="22"/>
     </row>
-    <row r="488" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C488" s="25"/>
       <c r="D488" s="23"/>
       <c r="E488" s="23"/>
       <c r="F488" s="23"/>
     </row>
-    <row r="489" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C489" s="24"/>
       <c r="D489" s="22"/>
       <c r="E489" s="22"/>
       <c r="F489" s="22"/>
     </row>
-    <row r="490" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="490" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C490" s="25"/>
       <c r="D490" s="23"/>
       <c r="E490" s="23"/>
       <c r="F490" s="23"/>
     </row>
-    <row r="491" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C491" s="24"/>
       <c r="D491" s="22"/>
       <c r="E491" s="22"/>
       <c r="F491" s="22"/>
     </row>
-    <row r="492" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="492" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C492" s="25"/>
       <c r="D492" s="23"/>
       <c r="E492" s="23"/>
       <c r="F492" s="23"/>
     </row>
-    <row r="493" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="493" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C493" s="24"/>
       <c r="D493" s="22"/>
       <c r="E493" s="22"/>
       <c r="F493" s="22"/>
     </row>
-    <row r="494" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C494" s="25"/>
       <c r="D494" s="23"/>
       <c r="E494" s="23"/>
       <c r="F494" s="23"/>
     </row>
-    <row r="495" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="495" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C495" s="24"/>
       <c r="D495" s="22"/>
       <c r="E495" s="22"/>
       <c r="F495" s="22"/>
     </row>
-    <row r="496" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="496" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C496" s="25"/>
       <c r="D496" s="23"/>
       <c r="E496" s="23"/>
       <c r="F496" s="23"/>
     </row>
-    <row r="497" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="497" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C497" s="24"/>
       <c r="D497" s="22"/>
       <c r="E497" s="22"/>
       <c r="F497" s="22"/>
     </row>
-    <row r="498" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="498" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C498" s="25"/>
       <c r="D498" s="23"/>
       <c r="E498" s="23"/>
       <c r="F498" s="23"/>
     </row>
-    <row r="499" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="499" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C499" s="24"/>
       <c r="D499" s="22"/>
       <c r="E499" s="22"/>
       <c r="F499" s="22"/>
     </row>
-    <row r="500" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="500" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C500" s="25"/>
       <c r="D500" s="23"/>
       <c r="E500" s="23"/>
       <c r="F500" s="23"/>
     </row>
-    <row r="501" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="501" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C501" s="24"/>
       <c r="D501" s="22"/>
       <c r="E501" s="22"/>
       <c r="F501" s="22"/>
     </row>
-    <row r="502" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="502" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C502" s="25"/>
       <c r="D502" s="23"/>
       <c r="E502" s="23"/>
       <c r="F502" s="23"/>
     </row>
-    <row r="503" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="503" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C503" s="24"/>
       <c r="D503" s="22"/>
       <c r="E503" s="22"/>
       <c r="F503" s="22"/>
     </row>
-    <row r="504" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="504" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C504" s="25"/>
       <c r="D504" s="23"/>
       <c r="E504" s="23"/>
       <c r="F504" s="23"/>
     </row>
-    <row r="505" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="505" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C505" s="24"/>
       <c r="D505" s="22"/>
       <c r="E505" s="22"/>
       <c r="F505" s="22"/>
     </row>
-    <row r="506" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="506" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C506" s="25"/>
       <c r="D506" s="23"/>
       <c r="E506" s="23"/>
       <c r="F506" s="23"/>
     </row>
-    <row r="507" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="507" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C507" s="24"/>
       <c r="D507" s="22"/>
       <c r="E507" s="22"/>
       <c r="F507" s="22"/>
     </row>
-    <row r="508" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="508" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C508" s="25"/>
       <c r="D508" s="23"/>
       <c r="E508" s="23"/>
       <c r="F508" s="23"/>
     </row>
-    <row r="509" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C509" s="24"/>
       <c r="D509" s="22"/>
       <c r="E509" s="22"/>
       <c r="F509" s="22"/>
     </row>
-    <row r="510" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="510" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C510" s="25"/>
       <c r="D510" s="23"/>
       <c r="E510" s="23"/>
       <c r="F510" s="23"/>
     </row>
-    <row r="511" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="511" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C511" s="24"/>
       <c r="D511" s="22"/>
       <c r="E511" s="22"/>
       <c r="F511" s="22"/>
     </row>
-    <row r="512" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="512" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C512" s="25"/>
       <c r="D512" s="23"/>
       <c r="E512" s="23"/>
       <c r="F512" s="23"/>
     </row>
-    <row r="513" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="513" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C513" s="24"/>
       <c r="D513" s="22"/>
       <c r="E513" s="22"/>
       <c r="F513" s="22"/>
     </row>
-    <row r="514" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="514" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C514" s="25"/>
       <c r="D514" s="23"/>
       <c r="E514" s="23"/>
       <c r="F514" s="23"/>
     </row>
-    <row r="515" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C515" s="24"/>
       <c r="D515" s="22"/>
       <c r="E515" s="22"/>
       <c r="F515" s="22"/>
     </row>
-    <row r="516" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C516" s="25"/>
       <c r="D516" s="23"/>
       <c r="E516" s="23"/>
       <c r="F516" s="23"/>
     </row>
-    <row r="517" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C517" s="24"/>
       <c r="D517" s="22"/>
       <c r="E517" s="22"/>
       <c r="F517" s="22"/>
     </row>
-    <row r="518" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C518" s="25"/>
       <c r="D518" s="23"/>
       <c r="E518" s="23"/>
       <c r="F518" s="23"/>
     </row>
-    <row r="519" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C519" s="24"/>
       <c r="D519" s="22"/>
       <c r="E519" s="22"/>
       <c r="F519" s="22"/>
     </row>
-    <row r="520" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="520" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C520" s="25"/>
       <c r="D520" s="23"/>
       <c r="E520" s="23"/>
       <c r="F520" s="23"/>
     </row>
-    <row r="521" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C521" s="24"/>
       <c r="D521" s="22"/>
       <c r="E521" s="22"/>
       <c r="F521" s="22"/>
     </row>
-    <row r="522" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C522" s="25"/>
       <c r="D522" s="23"/>
       <c r="E522" s="23"/>
       <c r="F522" s="23"/>
     </row>
-    <row r="523" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="523" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C523" s="24"/>
       <c r="D523" s="22"/>
       <c r="E523" s="22"/>
       <c r="F523" s="22"/>
     </row>
-    <row r="524" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C524" s="25"/>
       <c r="D524" s="23"/>
       <c r="E524" s="23"/>
       <c r="F524" s="23"/>
     </row>
-    <row r="525" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C525" s="24"/>
       <c r="D525" s="22"/>
       <c r="E525" s="22"/>
       <c r="F525" s="22"/>
     </row>
-    <row r="526" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="526" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C526" s="25"/>
       <c r="D526" s="23"/>
       <c r="E526" s="23"/>
       <c r="F526" s="23"/>
     </row>
-    <row r="527" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="527" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C527" s="24"/>
       <c r="D527" s="22"/>
       <c r="E527" s="22"/>
       <c r="F527" s="22"/>
     </row>
-    <row r="528" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="528" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C528" s="25"/>
       <c r="D528" s="23"/>
       <c r="E528" s="23"/>
       <c r="F528" s="23"/>
     </row>
-    <row r="529" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="529" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C529" s="24"/>
       <c r="D529" s="22"/>
       <c r="E529" s="22"/>
       <c r="F529" s="22"/>
     </row>
-    <row r="530" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C530" s="25"/>
       <c r="D530" s="23"/>
       <c r="E530" s="23"/>
       <c r="F530" s="23"/>
     </row>
-    <row r="531" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C531" s="24"/>
       <c r="D531" s="22"/>
       <c r="E531" s="22"/>
       <c r="F531" s="22"/>
     </row>
-    <row r="532" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="532" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C532" s="25"/>
       <c r="D532" s="23"/>
       <c r="E532" s="23"/>
       <c r="F532" s="23"/>
     </row>
-    <row r="533" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C533" s="24"/>
       <c r="D533" s="22"/>
       <c r="E533" s="22"/>
       <c r="F533" s="22"/>
     </row>
-    <row r="534" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C534" s="25"/>
       <c r="D534" s="23"/>
       <c r="E534" s="23"/>
       <c r="F534" s="23"/>
     </row>
-    <row r="535" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C535" s="24"/>
       <c r="D535" s="22"/>
       <c r="E535" s="22"/>
       <c r="F535" s="22"/>
     </row>
-    <row r="536" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C536" s="25"/>
       <c r="D536" s="23"/>
       <c r="E536" s="23"/>
       <c r="F536" s="23"/>
     </row>
-    <row r="537" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C537" s="24"/>
       <c r="D537" s="22"/>
       <c r="E537" s="22"/>
       <c r="F537" s="22"/>
     </row>
-    <row r="538" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C538" s="25"/>
       <c r="D538" s="23"/>
       <c r="E538" s="23"/>
       <c r="F538" s="23"/>
     </row>
-    <row r="539" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C539" s="24"/>
       <c r="D539" s="22"/>
       <c r="E539" s="22"/>
       <c r="F539" s="22"/>
     </row>
-    <row r="540" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C540" s="25"/>
       <c r="D540" s="23"/>
       <c r="E540" s="23"/>
       <c r="F540" s="23"/>
     </row>
-    <row r="541" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C541" s="24"/>
       <c r="D541" s="22"/>
       <c r="E541" s="22"/>
       <c r="F541" s="22"/>
     </row>
-    <row r="542" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C542" s="25"/>
       <c r="D542" s="23"/>
       <c r="E542" s="23"/>
       <c r="F542" s="23"/>
     </row>
-    <row r="543" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C543" s="24"/>
       <c r="D543" s="22"/>
       <c r="E543" s="22"/>
       <c r="F543" s="22"/>
     </row>
-    <row r="544" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="544" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C544" s="25"/>
       <c r="D544" s="23"/>
       <c r="E544" s="23"/>
       <c r="F544" s="23"/>
     </row>
-    <row r="545" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C545" s="24"/>
       <c r="D545" s="22"/>
       <c r="E545" s="22"/>
       <c r="F545" s="22"/>
     </row>
-    <row r="546" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C546" s="25"/>
       <c r="D546" s="23"/>
       <c r="E546" s="23"/>
       <c r="F546" s="23"/>
     </row>
-    <row r="547" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="547" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C547" s="24"/>
       <c r="D547" s="22"/>
       <c r="E547" s="22"/>
       <c r="F547" s="22"/>
     </row>
-    <row r="548" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C548" s="25"/>
       <c r="D548" s="23"/>
       <c r="E548" s="23"/>
       <c r="F548" s="23"/>
     </row>
-    <row r="549" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C549" s="24"/>
       <c r="D549" s="22"/>
       <c r="E549" s="22"/>
       <c r="F549" s="22"/>
     </row>
-    <row r="550" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C550" s="25"/>
       <c r="D550" s="23"/>
       <c r="E550" s="23"/>
       <c r="F550" s="23"/>
     </row>
-    <row r="551" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C551" s="24"/>
       <c r="D551" s="22"/>
       <c r="E551" s="22"/>
       <c r="F551" s="22"/>
     </row>
-    <row r="552" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C552" s="25"/>
       <c r="D552" s="23"/>
       <c r="E552" s="23"/>
       <c r="F552" s="23"/>
     </row>
-    <row r="553" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="553" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C553" s="24"/>
       <c r="D553" s="22"/>
       <c r="E553" s="22"/>
       <c r="F553" s="22"/>
     </row>
-    <row r="554" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C554" s="25"/>
       <c r="D554" s="23"/>
       <c r="E554" s="23"/>
       <c r="F554" s="23"/>
     </row>
-    <row r="555" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C555" s="24"/>
       <c r="D555" s="22"/>
       <c r="E555" s="22"/>
       <c r="F555" s="22"/>
     </row>
-    <row r="556" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="556" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C556" s="25"/>
       <c r="D556" s="23"/>
       <c r="E556" s="23"/>
       <c r="F556" s="23"/>
     </row>
-    <row r="557" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C557" s="24"/>
       <c r="D557" s="22"/>
       <c r="E557" s="22"/>
       <c r="F557" s="22"/>
     </row>
-    <row r="558" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C558" s="25"/>
       <c r="D558" s="23"/>
       <c r="E558" s="23"/>
       <c r="F558" s="23"/>
     </row>
-    <row r="559" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="559" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C559" s="24"/>
       <c r="D559" s="22"/>
       <c r="E559" s="22"/>
       <c r="F559" s="22"/>
     </row>
-    <row r="560" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C560" s="25"/>
       <c r="D560" s="23"/>
       <c r="E560" s="23"/>
       <c r="F560" s="23"/>
     </row>
-    <row r="561" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C561" s="24"/>
       <c r="D561" s="22"/>
       <c r="E561" s="22"/>
       <c r="F561" s="22"/>
     </row>
-    <row r="562" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C562" s="25"/>
       <c r="D562" s="23"/>
       <c r="E562" s="23"/>
       <c r="F562" s="23"/>
     </row>
-    <row r="563" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C563" s="24"/>
       <c r="D563" s="22"/>
       <c r="E563" s="22"/>
       <c r="F563" s="22"/>
     </row>
-    <row r="564" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C564" s="25"/>
       <c r="D564" s="23"/>
       <c r="E564" s="23"/>
       <c r="F564" s="23"/>
     </row>
-    <row r="565" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C565" s="24"/>
       <c r="D565" s="22"/>
       <c r="E565" s="22"/>
       <c r="F565" s="22"/>
     </row>
-    <row r="566" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C566" s="25"/>
       <c r="D566" s="23"/>
       <c r="E566" s="23"/>
       <c r="F566" s="23"/>
     </row>
-    <row r="567" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C567" s="24"/>
       <c r="D567" s="22"/>
       <c r="E567" s="22"/>
       <c r="F567" s="22"/>
     </row>
-    <row r="568" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C568" s="25"/>
       <c r="D568" s="23"/>
       <c r="E568" s="23"/>
       <c r="F568" s="23"/>
     </row>
-    <row r="569" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C569" s="24"/>
       <c r="D569" s="22"/>
       <c r="E569" s="22"/>
       <c r="F569" s="22"/>
     </row>
-    <row r="570" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C570" s="25"/>
       <c r="D570" s="23"/>
       <c r="E570" s="23"/>
       <c r="F570" s="23"/>
     </row>
-    <row r="571" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="571" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C571" s="24"/>
       <c r="D571" s="22"/>
       <c r="E571" s="22"/>
       <c r="F571" s="22"/>
     </row>
-    <row r="572" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C572" s="25"/>
       <c r="D572" s="23"/>
       <c r="E572" s="23"/>
       <c r="F572" s="23"/>
     </row>
-    <row r="573" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C573" s="24"/>
       <c r="D573" s="22"/>
       <c r="E573" s="22"/>
       <c r="F573" s="22"/>
     </row>
-    <row r="574" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="574" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C574" s="25"/>
       <c r="D574" s="23"/>
       <c r="E574" s="23"/>
       <c r="F574" s="23"/>
     </row>
-    <row r="575" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C575" s="24"/>
       <c r="D575" s="22"/>
       <c r="E575" s="22"/>
       <c r="F575" s="22"/>
     </row>
-    <row r="576" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C576" s="25"/>
       <c r="D576" s="23"/>
       <c r="E576" s="23"/>
       <c r="F576" s="23"/>
     </row>
-    <row r="577" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="577" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C577" s="24"/>
       <c r="D577" s="22"/>
       <c r="E577" s="22"/>
       <c r="F577" s="22"/>
     </row>
-    <row r="578" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C578" s="25"/>
       <c r="D578" s="23"/>
       <c r="E578" s="23"/>
       <c r="F578" s="23"/>
     </row>
-    <row r="579" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C579" s="24"/>
       <c r="D579" s="22"/>
       <c r="E579" s="22"/>
       <c r="F579" s="22"/>
     </row>
-    <row r="580" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="580" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C580" s="25"/>
       <c r="D580" s="23"/>
       <c r="E580" s="23"/>
       <c r="F580" s="23"/>
     </row>
-    <row r="581" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C581" s="24"/>
       <c r="D581" s="22"/>
       <c r="E581" s="22"/>
       <c r="F581" s="22"/>
     </row>
-    <row r="582" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C582" s="25"/>
       <c r="D582" s="23"/>
       <c r="E582" s="23"/>
       <c r="F582" s="23"/>
     </row>
-    <row r="583" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C583" s="24"/>
       <c r="D583" s="22"/>
       <c r="E583" s="22"/>
       <c r="F583" s="22"/>
     </row>
-    <row r="584" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C584" s="25"/>
       <c r="D584" s="23"/>
       <c r="E584" s="23"/>
       <c r="F584" s="23"/>
     </row>
-    <row r="585" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C585" s="24"/>
       <c r="D585" s="22"/>
       <c r="E585" s="22"/>
       <c r="F585" s="22"/>
     </row>
-    <row r="586" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="586" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C586" s="25"/>
       <c r="D586" s="23"/>
       <c r="E586" s="23"/>
       <c r="F586" s="23"/>
     </row>
-    <row r="587" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C587" s="24"/>
       <c r="D587" s="22"/>
       <c r="E587" s="22"/>
       <c r="F587" s="22"/>
     </row>
-    <row r="588" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C588" s="25"/>
       <c r="D588" s="23"/>
       <c r="E588" s="23"/>
       <c r="F588" s="23"/>
     </row>
-    <row r="589" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C589" s="24"/>
       <c r="D589" s="22"/>
       <c r="E589" s="22"/>
       <c r="F589" s="22"/>
     </row>
-    <row r="590" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C590" s="25"/>
       <c r="D590" s="23"/>
       <c r="E590" s="23"/>
       <c r="F590" s="23"/>
     </row>
-    <row r="591" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C591" s="24"/>
       <c r="D591" s="22"/>
       <c r="E591" s="22"/>
       <c r="F591" s="22"/>
     </row>
-    <row r="592" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="592" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C592" s="25"/>
       <c r="D592" s="23"/>
       <c r="E592" s="23"/>
       <c r="F592" s="23"/>
     </row>
-    <row r="593" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C593" s="24"/>
       <c r="D593" s="22"/>
       <c r="E593" s="22"/>
       <c r="F593" s="22"/>
     </row>
-    <row r="594" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C594" s="25"/>
       <c r="D594" s="23"/>
       <c r="E594" s="23"/>
       <c r="F594" s="23"/>
     </row>
-    <row r="595" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="595" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C595" s="24"/>
       <c r="D595" s="22"/>
       <c r="E595" s="22"/>
       <c r="F595" s="22"/>
     </row>
-    <row r="596" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C596" s="25"/>
       <c r="D596" s="23"/>
       <c r="E596" s="23"/>
       <c r="F596" s="23"/>
     </row>
-    <row r="597" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C597" s="24"/>
       <c r="D597" s="22"/>
       <c r="E597" s="22"/>
       <c r="F597" s="22"/>
     </row>
-    <row r="598" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="598" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C598" s="25"/>
       <c r="D598" s="23"/>
       <c r="E598" s="23"/>
       <c r="F598" s="23"/>
     </row>
-    <row r="599" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C599" s="24"/>
       <c r="D599" s="22"/>
       <c r="E599" s="22"/>
       <c r="F599" s="22"/>
     </row>
-    <row r="600" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="600" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C600" s="25"/>
       <c r="D600" s="23"/>
       <c r="E600" s="23"/>
       <c r="F600" s="23"/>
     </row>
-    <row r="601" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="601" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C601" s="24"/>
       <c r="D601" s="22"/>
       <c r="E601" s="22"/>
       <c r="F601" s="22"/>
     </row>
-    <row r="602" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C602" s="25"/>
       <c r="D602" s="23"/>
       <c r="E602" s="23"/>
       <c r="F602" s="23"/>
     </row>
-    <row r="603" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C603" s="24"/>
       <c r="D603" s="22"/>
       <c r="E603" s="22"/>
       <c r="F603" s="22"/>
     </row>
-    <row r="604" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="604" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C604" s="25"/>
       <c r="D604" s="23"/>
       <c r="E604" s="23"/>
       <c r="F604" s="23"/>
     </row>
-    <row r="605" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C605" s="24"/>
       <c r="D605" s="22"/>
       <c r="E605" s="22"/>
       <c r="F605" s="22"/>
     </row>
-    <row r="606" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C606" s="25"/>
       <c r="D606" s="23"/>
       <c r="E606" s="23"/>
       <c r="F606" s="23"/>
     </row>
-    <row r="607" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="607" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C607" s="24"/>
       <c r="D607" s="22"/>
       <c r="E607" s="22"/>
       <c r="F607" s="22"/>
     </row>
-    <row r="608" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C608" s="25"/>
       <c r="D608" s="23"/>
       <c r="E608" s="23"/>
       <c r="F608" s="23"/>
     </row>
-    <row r="609" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C609" s="24"/>
       <c r="D609" s="22"/>
       <c r="E609" s="22"/>
       <c r="F609" s="22"/>
     </row>
-    <row r="610" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="610" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C610" s="25"/>
       <c r="D610" s="23"/>
       <c r="E610" s="23"/>
       <c r="F610" s="23"/>
     </row>
-    <row r="611" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C611" s="24"/>
       <c r="D611" s="22"/>
       <c r="E611" s="22"/>
       <c r="F611" s="22"/>
     </row>
-    <row r="612" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C612" s="25"/>
       <c r="D612" s="23"/>
       <c r="E612" s="23"/>
       <c r="F612" s="23"/>
     </row>
-    <row r="613" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="613" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C613" s="24"/>
       <c r="D613" s="22"/>
       <c r="E613" s="22"/>
       <c r="F613" s="22"/>
     </row>
-    <row r="614" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C614" s="25"/>
       <c r="D614" s="23"/>
       <c r="E614" s="23"/>
       <c r="F614" s="23"/>
     </row>
-    <row r="615" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C615" s="24"/>
       <c r="D615" s="22"/>
       <c r="E615" s="22"/>
       <c r="F615" s="22"/>
     </row>
-    <row r="616" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C616" s="25"/>
       <c r="D616" s="23"/>
       <c r="E616" s="23"/>
       <c r="F616" s="23"/>
     </row>
-    <row r="617" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C617" s="24"/>
       <c r="D617" s="22"/>
       <c r="E617" s="22"/>
       <c r="F617" s="22"/>
     </row>
-    <row r="618" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C618" s="25"/>
       <c r="D618" s="23"/>
       <c r="E618" s="23"/>
       <c r="F618" s="23"/>
     </row>
-    <row r="619" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C619" s="24"/>
       <c r="D619" s="22"/>
       <c r="E619" s="22"/>
       <c r="F619" s="22"/>
     </row>
-    <row r="620" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C620" s="25"/>
       <c r="D620" s="23"/>
       <c r="E620" s="23"/>
       <c r="F620" s="23"/>
     </row>
-    <row r="621" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C621" s="24"/>
       <c r="D621" s="22"/>
       <c r="E621" s="22"/>
       <c r="F621" s="22"/>
     </row>
-    <row r="622" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C622" s="25"/>
       <c r="D622" s="23"/>
       <c r="E622" s="23"/>
       <c r="F622" s="23"/>
     </row>
-    <row r="623" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C623" s="24"/>
       <c r="D623" s="22"/>
       <c r="E623" s="22"/>
       <c r="F623" s="22"/>
     </row>
-    <row r="624" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C624" s="25"/>
       <c r="D624" s="23"/>
       <c r="E624" s="23"/>
       <c r="F624" s="23"/>
     </row>
-    <row r="625" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C625" s="24"/>
       <c r="D625" s="22"/>
       <c r="E625" s="22"/>
       <c r="F625" s="22"/>
     </row>
-    <row r="626" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C626" s="25"/>
       <c r="D626" s="23"/>
       <c r="E626" s="23"/>
       <c r="F626" s="23"/>
     </row>
-    <row r="627" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C627" s="24"/>
       <c r="D627" s="22"/>
       <c r="E627" s="22"/>
       <c r="F627" s="22"/>
     </row>
-    <row r="628" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="628" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C628" s="25"/>
       <c r="D628" s="23"/>
       <c r="E628" s="23"/>
       <c r="F628" s="23"/>
     </row>
-    <row r="629" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="629" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C629" s="24"/>
       <c r="D629" s="22"/>
       <c r="E629" s="22"/>
       <c r="F629" s="22"/>
     </row>
-    <row r="630" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="630" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C630" s="25"/>
       <c r="D630" s="23"/>
       <c r="E630" s="23"/>
       <c r="F630" s="23"/>
     </row>
-    <row r="631" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="631" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C631" s="24"/>
       <c r="D631" s="22"/>
       <c r="E631" s="22"/>
       <c r="F631" s="22"/>
     </row>
-    <row r="632" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="632" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C632" s="25"/>
       <c r="D632" s="23"/>
       <c r="E632" s="23"/>
       <c r="F632" s="23"/>
     </row>
-    <row r="633" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="633" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C633" s="24"/>
       <c r="D633" s="22"/>
       <c r="E633" s="22"/>
       <c r="F633" s="22"/>
     </row>
-    <row r="634" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="634" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C634" s="25"/>
       <c r="D634" s="23"/>
       <c r="E634" s="23"/>
       <c r="F634" s="23"/>
     </row>
-    <row r="635" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C635" s="24"/>
       <c r="D635" s="22"/>
       <c r="E635" s="22"/>
       <c r="F635" s="22"/>
     </row>
-    <row r="636" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C636" s="25"/>
       <c r="D636" s="23"/>
       <c r="E636" s="23"/>
       <c r="F636" s="23"/>
     </row>
-    <row r="637" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="637" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C637" s="24"/>
       <c r="D637" s="22"/>
       <c r="E637" s="22"/>
       <c r="F637" s="22"/>
     </row>
-    <row r="638" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="638" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C638" s="25"/>
       <c r="D638" s="23"/>
       <c r="E638" s="23"/>
       <c r="F638" s="23"/>
     </row>
-    <row r="639" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="639" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C639" s="24"/>
       <c r="D639" s="22"/>
       <c r="E639" s="22"/>
       <c r="F639" s="22"/>
     </row>
-    <row r="640" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="640" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C640" s="25"/>
       <c r="D640" s="23"/>
       <c r="E640" s="23"/>
       <c r="F640" s="23"/>
     </row>
-    <row r="641" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C641" s="24"/>
       <c r="D641" s="22"/>
       <c r="E641" s="22"/>
       <c r="F641" s="22"/>
     </row>
-    <row r="642" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C642" s="25"/>
       <c r="D642" s="23"/>
       <c r="E642" s="23"/>
       <c r="F642" s="23"/>
     </row>
-    <row r="643" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C643" s="24"/>
       <c r="D643" s="22"/>
       <c r="E643" s="22"/>
       <c r="F643" s="22"/>
     </row>
-    <row r="644" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C644" s="25"/>
       <c r="D644" s="23"/>
       <c r="E644" s="23"/>
       <c r="F644" s="23"/>
     </row>
-    <row r="645" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C645" s="24"/>
       <c r="D645" s="22"/>
       <c r="E645" s="22"/>
       <c r="F645" s="22"/>
     </row>
-    <row r="646" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="646" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C646" s="25"/>
       <c r="D646" s="23"/>
       <c r="E646" s="23"/>
       <c r="F646" s="23"/>
     </row>
-    <row r="647" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="647" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C647" s="24"/>
       <c r="D647" s="22"/>
       <c r="E647" s="22"/>
       <c r="F647" s="22"/>
     </row>
-    <row r="648" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="648" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C648" s="25"/>
       <c r="D648" s="23"/>
       <c r="E648" s="23"/>
       <c r="F648" s="23"/>
     </row>
-    <row r="649" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="649" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C649" s="24"/>
       <c r="D649" s="22"/>
       <c r="E649" s="22"/>
       <c r="F649" s="22"/>
     </row>
-    <row r="650" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="650" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C650" s="25"/>
       <c r="D650" s="23"/>
       <c r="E650" s="23"/>
       <c r="F650" s="23"/>
     </row>
-    <row r="651" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="651" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C651" s="24"/>
       <c r="D651" s="22"/>
       <c r="E651" s="22"/>
       <c r="F651" s="22"/>
     </row>
-    <row r="652" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="652" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C652" s="25"/>
       <c r="D652" s="23"/>
       <c r="E652" s="23"/>
       <c r="F652" s="23"/>
     </row>
-    <row r="653" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="653" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C653" s="24"/>
       <c r="D653" s="22"/>
       <c r="E653" s="22"/>
       <c r="F653" s="22"/>
     </row>
-    <row r="654" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="654" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C654" s="25"/>
       <c r="D654" s="23"/>
       <c r="E654" s="23"/>
       <c r="F654" s="23"/>
     </row>
-    <row r="655" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="655" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C655" s="24"/>
       <c r="D655" s="22"/>
       <c r="E655" s="22"/>
       <c r="F655" s="22"/>
     </row>
-    <row r="656" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="656" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C656" s="25"/>
       <c r="D656" s="23"/>
       <c r="E656" s="23"/>
       <c r="F656" s="23"/>
     </row>
-    <row r="657" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C657" s="24"/>
       <c r="D657" s="22"/>
       <c r="E657" s="22"/>
       <c r="F657" s="22"/>
     </row>
-    <row r="658" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="658" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C658" s="25"/>
       <c r="D658" s="23"/>
       <c r="E658" s="23"/>
       <c r="F658" s="23"/>
     </row>
-    <row r="659" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="659" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C659" s="24"/>
       <c r="D659" s="22"/>
       <c r="E659" s="22"/>
       <c r="F659" s="22"/>
     </row>
-    <row r="660" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="660" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C660" s="25"/>
       <c r="D660" s="23"/>
       <c r="E660" s="23"/>
       <c r="F660" s="23"/>
     </row>
-    <row r="661" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="661" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C661" s="24"/>
       <c r="D661" s="22"/>
       <c r="E661" s="22"/>
       <c r="F661" s="22"/>
     </row>
-    <row r="662" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="662" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C662" s="25"/>
       <c r="D662" s="23"/>
       <c r="E662" s="23"/>
       <c r="F662" s="23"/>
     </row>
-    <row r="663" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="663" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C663" s="24"/>
       <c r="D663" s="22"/>
       <c r="E663" s="22"/>
       <c r="F663" s="22"/>
     </row>
-    <row r="664" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="664" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C664" s="25"/>
       <c r="D664" s="23"/>
       <c r="E664" s="23"/>
       <c r="F664" s="23"/>
     </row>
-    <row r="665" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="665" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C665" s="24"/>
       <c r="D665" s="22"/>
       <c r="E665" s="22"/>
       <c r="F665" s="22"/>
     </row>
-    <row r="666" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="666" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C666" s="25"/>
       <c r="D666" s="23"/>
       <c r="E666" s="23"/>
       <c r="F666" s="23"/>
     </row>
-    <row r="667" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="667" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C667" s="24"/>
       <c r="D667" s="22"/>
       <c r="E667" s="22"/>
       <c r="F667" s="22"/>
     </row>
-    <row r="668" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="668" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C668" s="25"/>
       <c r="D668" s="23"/>
       <c r="E668" s="23"/>
       <c r="F668" s="23"/>
     </row>
-    <row r="669" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="669" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C669" s="24"/>
       <c r="D669" s="22"/>
       <c r="E669" s="22"/>
       <c r="F669" s="22"/>
     </row>
-    <row r="670" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="670" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C670" s="25"/>
       <c r="D670" s="23"/>
       <c r="E670" s="23"/>
       <c r="F670" s="23"/>
     </row>
-    <row r="671" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="671" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C671" s="24"/>
       <c r="D671" s="22"/>
       <c r="E671" s="22"/>
       <c r="F671" s="22"/>
     </row>
-    <row r="672" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="672" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C672" s="25"/>
       <c r="D672" s="23"/>
       <c r="E672" s="23"/>
       <c r="F672" s="23"/>
     </row>
-    <row r="673" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="673" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C673" s="24"/>
       <c r="D673" s="22"/>
       <c r="E673" s="22"/>
       <c r="F673" s="22"/>
     </row>
-    <row r="674" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="674" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C674" s="25"/>
       <c r="D674" s="23"/>
       <c r="E674" s="23"/>
       <c r="F674" s="23"/>
     </row>
-    <row r="675" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="675" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C675" s="24"/>
       <c r="D675" s="22"/>
       <c r="E675" s="22"/>
       <c r="F675" s="22"/>
     </row>
-    <row r="676" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="676" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C676" s="25"/>
       <c r="D676" s="23"/>
       <c r="E676" s="23"/>
       <c r="F676" s="23"/>
     </row>
-    <row r="677" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="677" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C677" s="24"/>
       <c r="D677" s="22"/>
       <c r="E677" s="22"/>
       <c r="F677" s="22"/>
     </row>
-    <row r="678" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="678" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C678" s="25"/>
       <c r="D678" s="23"/>
       <c r="E678" s="23"/>
       <c r="F678" s="23"/>
     </row>
-    <row r="679" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="679" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C679" s="24"/>
       <c r="D679" s="22"/>
       <c r="E679" s="22"/>
       <c r="F679" s="22"/>
     </row>
-    <row r="680" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="680" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C680" s="25"/>
       <c r="D680" s="23"/>
       <c r="E680" s="23"/>
       <c r="F680" s="23"/>
     </row>
-    <row r="681" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="681" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C681" s="24"/>
       <c r="D681" s="22"/>
       <c r="E681" s="22"/>
       <c r="F681" s="22"/>
     </row>
-    <row r="682" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="682" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C682" s="25"/>
       <c r="D682" s="23"/>
       <c r="E682" s="23"/>
       <c r="F682" s="23"/>
     </row>
-    <row r="683" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="683" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C683" s="24"/>
       <c r="D683" s="22"/>
       <c r="E683" s="22"/>
       <c r="F683" s="22"/>
     </row>
-    <row r="684" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="684" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C684" s="25"/>
       <c r="D684" s="23"/>
       <c r="E684" s="23"/>
       <c r="F684" s="23"/>
     </row>
-    <row r="685" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="685" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C685" s="24"/>
       <c r="D685" s="22"/>
       <c r="E685" s="22"/>
       <c r="F685" s="22"/>
     </row>
-    <row r="686" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="686" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C686" s="25"/>
       <c r="D686" s="23"/>
       <c r="E686" s="23"/>
       <c r="F686" s="23"/>
     </row>
-    <row r="687" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="687" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C687" s="24"/>
       <c r="D687" s="22"/>
       <c r="E687" s="22"/>
       <c r="F687" s="22"/>
     </row>
-    <row r="688" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="688" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C688" s="25"/>
       <c r="D688" s="23"/>
       <c r="E688" s="23"/>
       <c r="F688" s="23"/>
     </row>
-    <row r="689" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="689" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C689" s="24"/>
       <c r="D689" s="22"/>
       <c r="E689" s="22"/>
       <c r="F689" s="22"/>
     </row>
-    <row r="690" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="690" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C690" s="25"/>
       <c r="D690" s="23"/>
       <c r="E690" s="23"/>
       <c r="F690" s="23"/>
     </row>
-    <row r="691" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="691" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C691" s="24"/>
       <c r="D691" s="22"/>
       <c r="E691" s="22"/>
       <c r="F691" s="22"/>
     </row>
-    <row r="692" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="692" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C692" s="25"/>
       <c r="D692" s="23"/>
       <c r="E692" s="23"/>
       <c r="F692" s="23"/>
     </row>
-    <row r="693" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="693" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C693" s="24"/>
       <c r="D693" s="22"/>
       <c r="E693" s="22"/>
       <c r="F693" s="22"/>
     </row>
-    <row r="694" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="694" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C694" s="25"/>
       <c r="D694" s="23"/>
       <c r="E694" s="23"/>
       <c r="F694" s="23"/>
     </row>
-    <row r="695" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="695" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C695" s="24"/>
       <c r="D695" s="22"/>
       <c r="E695" s="22"/>
       <c r="F695" s="22"/>
     </row>
-    <row r="696" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="696" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C696" s="25"/>
       <c r="D696" s="23"/>
       <c r="E696" s="23"/>
       <c r="F696" s="23"/>
     </row>
-    <row r="697" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="697" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C697" s="24"/>
       <c r="D697" s="22"/>
       <c r="E697" s="22"/>
       <c r="F697" s="22"/>
     </row>
-    <row r="698" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="698" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C698" s="25"/>
       <c r="D698" s="23"/>
       <c r="E698" s="23"/>
       <c r="F698" s="23"/>
     </row>
-    <row r="699" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="699" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C699" s="24"/>
       <c r="D699" s="22"/>
       <c r="E699" s="22"/>
       <c r="F699" s="22"/>
     </row>
-    <row r="700" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="700" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C700" s="25"/>
       <c r="D700" s="23"/>
       <c r="E700" s="23"/>
       <c r="F700" s="23"/>
     </row>
-    <row r="701" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="701" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C701" s="24"/>
       <c r="D701" s="22"/>
       <c r="E701" s="22"/>
       <c r="F701" s="22"/>
     </row>
-    <row r="702" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="702" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C702" s="25"/>
       <c r="D702" s="23"/>
       <c r="E702" s="23"/>
       <c r="F702" s="23"/>
     </row>
-    <row r="703" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="703" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C703" s="24"/>
       <c r="D703" s="22"/>
       <c r="E703" s="22"/>
       <c r="F703" s="22"/>
     </row>
-    <row r="704" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="704" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C704" s="25"/>
       <c r="D704" s="23"/>
       <c r="E704" s="23"/>
       <c r="F704" s="23"/>
     </row>
-    <row r="705" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="705" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C705" s="24"/>
       <c r="D705" s="22"/>
       <c r="E705" s="22"/>
       <c r="F705" s="22"/>
     </row>
-    <row r="706" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="706" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C706" s="25"/>
       <c r="D706" s="23"/>
       <c r="E706" s="23"/>
       <c r="F706" s="23"/>
     </row>
-    <row r="707" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="707" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C707" s="24"/>
       <c r="D707" s="22"/>
       <c r="E707" s="22"/>
       <c r="F707" s="22"/>
     </row>
-    <row r="708" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="708" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C708" s="25"/>
       <c r="D708" s="23"/>
       <c r="E708" s="23"/>
       <c r="F708" s="23"/>
     </row>
-    <row r="709" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="709" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C709" s="24"/>
       <c r="D709" s="22"/>
       <c r="E709" s="22"/>
       <c r="F709" s="22"/>
     </row>
-    <row r="710" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="710" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C710" s="25"/>
       <c r="D710" s="23"/>
       <c r="E710" s="23"/>
       <c r="F710" s="23"/>
     </row>
-    <row r="711" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="711" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C711" s="24"/>
       <c r="D711" s="22"/>
       <c r="E711" s="22"/>
       <c r="F711" s="22"/>
     </row>
-    <row r="712" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="712" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C712" s="25"/>
       <c r="D712" s="23"/>
       <c r="E712" s="23"/>
       <c r="F712" s="23"/>
     </row>
-    <row r="713" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="713" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C713" s="24"/>
       <c r="D713" s="22"/>
       <c r="E713" s="22"/>
       <c r="F713" s="22"/>
     </row>
-    <row r="714" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="714" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C714" s="25"/>
       <c r="D714" s="23"/>
       <c r="E714" s="23"/>
       <c r="F714" s="23"/>
     </row>
-    <row r="715" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="715" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C715" s="24"/>
       <c r="D715" s="22"/>
       <c r="E715" s="22"/>
       <c r="F715" s="22"/>
     </row>
-    <row r="716" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="716" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C716" s="25"/>
       <c r="D716" s="23"/>
       <c r="E716" s="23"/>
       <c r="F716" s="23"/>
     </row>
-    <row r="717" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="717" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C717" s="24"/>
       <c r="D717" s="22"/>
       <c r="E717" s="22"/>
       <c r="F717" s="22"/>
     </row>
-    <row r="718" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="718" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C718" s="25"/>
       <c r="D718" s="23"/>
       <c r="E718" s="23"/>
       <c r="F718" s="23"/>
     </row>
-    <row r="719" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="719" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C719" s="24"/>
       <c r="D719" s="22"/>
       <c r="E719" s="22"/>
       <c r="F719" s="22"/>
     </row>
-    <row r="720" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="720" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C720" s="25"/>
       <c r="D720" s="23"/>
       <c r="E720" s="23"/>
       <c r="F720" s="23"/>
     </row>
-    <row r="721" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="721" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C721" s="24"/>
       <c r="D721" s="22"/>
       <c r="E721" s="22"/>
       <c r="F721" s="22"/>
     </row>
-    <row r="722" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="722" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C722" s="25"/>
       <c r="D722" s="23"/>
       <c r="E722" s="23"/>
       <c r="F722" s="23"/>
     </row>
-    <row r="723" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="723" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C723" s="24"/>
       <c r="D723" s="22"/>
       <c r="E723" s="22"/>
       <c r="F723" s="22"/>
     </row>
-    <row r="724" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="724" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C724" s="25"/>
       <c r="D724" s="23"/>
       <c r="E724" s="23"/>
       <c r="F724" s="23"/>
     </row>
-    <row r="725" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="725" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C725" s="24"/>
       <c r="D725" s="22"/>
       <c r="E725" s="22"/>
       <c r="F725" s="22"/>
     </row>
-    <row r="726" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="726" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C726" s="25"/>
       <c r="D726" s="23"/>
       <c r="E726" s="23"/>
       <c r="F726" s="23"/>
     </row>
-    <row r="727" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="727" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C727" s="24"/>
       <c r="D727" s="22"/>
       <c r="E727" s="22"/>
       <c r="F727" s="22"/>
     </row>
-    <row r="728" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="728" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C728" s="25"/>
       <c r="D728" s="23"/>
       <c r="E728" s="23"/>
       <c r="F728" s="23"/>
     </row>
-    <row r="729" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="729" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C729" s="24"/>
       <c r="D729" s="22"/>
       <c r="E729" s="22"/>
       <c r="F729" s="22"/>
     </row>
-    <row r="730" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="730" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C730" s="25"/>
       <c r="D730" s="23"/>
       <c r="E730" s="23"/>
       <c r="F730" s="23"/>
     </row>
-    <row r="731" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="731" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C731" s="24"/>
       <c r="D731" s="22"/>
       <c r="E731" s="22"/>
       <c r="F731" s="22"/>
     </row>
-    <row r="732" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="732" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C732" s="25"/>
       <c r="D732" s="23"/>
       <c r="E732" s="23"/>
       <c r="F732" s="23"/>
     </row>
-    <row r="733" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="733" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C733" s="24"/>
       <c r="D733" s="22"/>
       <c r="E733" s="22"/>
       <c r="F733" s="22"/>
     </row>
-    <row r="734" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="734" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C734" s="25"/>
       <c r="D734" s="23"/>
       <c r="E734" s="23"/>
       <c r="F734" s="23"/>
     </row>
-    <row r="735" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="735" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C735" s="24"/>
       <c r="D735" s="22"/>
       <c r="E735" s="22"/>
       <c r="F735" s="22"/>
     </row>
-    <row r="736" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="736" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C736" s="25"/>
       <c r="D736" s="23"/>
       <c r="E736" s="23"/>
       <c r="F736" s="23"/>
     </row>
-    <row r="737" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="737" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C737" s="24"/>
       <c r="D737" s="22"/>
       <c r="E737" s="22"/>
       <c r="F737" s="22"/>
     </row>
-    <row r="738" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="738" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C738" s="25"/>
       <c r="D738" s="23"/>
       <c r="E738" s="23"/>
       <c r="F738" s="23"/>
     </row>
-    <row r="739" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="739" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C739" s="24"/>
       <c r="D739" s="22"/>
       <c r="E739" s="22"/>
       <c r="F739" s="22"/>
     </row>
-    <row r="740" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="740" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C740" s="25"/>
       <c r="D740" s="23"/>
       <c r="E740" s="23"/>
       <c r="F740" s="23"/>
     </row>
-    <row r="741" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="741" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C741" s="24"/>
       <c r="D741" s="22"/>
       <c r="E741" s="22"/>
       <c r="F741" s="22"/>
     </row>
-    <row r="742" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="742" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C742" s="25"/>
       <c r="D742" s="23"/>
       <c r="E742" s="23"/>
       <c r="F742" s="23"/>
     </row>
-    <row r="743" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="743" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C743" s="24"/>
       <c r="D743" s="22"/>
       <c r="E743" s="22"/>
       <c r="F743" s="22"/>
     </row>
-    <row r="744" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="744" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C744" s="25"/>
       <c r="D744" s="23"/>
       <c r="E744" s="23"/>
       <c r="F744" s="23"/>
     </row>
-    <row r="745" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="745" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C745" s="24"/>
       <c r="D745" s="22"/>
       <c r="E745" s="22"/>
       <c r="F745" s="22"/>
     </row>
-    <row r="746" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="746" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C746" s="25"/>
       <c r="D746" s="23"/>
       <c r="E746" s="23"/>
       <c r="F746" s="23"/>
     </row>
-    <row r="747" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="747" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C747" s="24"/>
       <c r="D747" s="22"/>
       <c r="E747" s="22"/>
       <c r="F747" s="22"/>
     </row>
-    <row r="748" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="748" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C748" s="25"/>
       <c r="D748" s="23"/>
       <c r="E748" s="23"/>
       <c r="F748" s="23"/>
     </row>
-    <row r="749" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="749" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C749" s="24"/>
       <c r="D749" s="22"/>
       <c r="E749" s="22"/>
       <c r="F749" s="22"/>
     </row>
-    <row r="750" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="750" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C750" s="25"/>
       <c r="D750" s="23"/>
       <c r="E750" s="23"/>
       <c r="F750" s="23"/>
     </row>
-    <row r="751" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="751" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C751" s="24"/>
       <c r="D751" s="22"/>
       <c r="E751" s="22"/>
       <c r="F751" s="22"/>
     </row>
-    <row r="752" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="752" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C752" s="25"/>
       <c r="D752" s="23"/>
       <c r="E752" s="23"/>
       <c r="F752" s="23"/>
     </row>
-    <row r="753" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="753" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C753" s="24"/>
       <c r="D753" s="22"/>
       <c r="E753" s="22"/>
       <c r="F753" s="22"/>
     </row>
-    <row r="754" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="754" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C754" s="25"/>
       <c r="D754" s="23"/>
       <c r="E754" s="23"/>
       <c r="F754" s="23"/>
     </row>
-    <row r="755" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="755" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C755" s="24"/>
       <c r="D755" s="22"/>
       <c r="E755" s="22"/>
       <c r="F755" s="22"/>
     </row>
-    <row r="756" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="756" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C756" s="25"/>
       <c r="D756" s="23"/>
       <c r="E756" s="23"/>
       <c r="F756" s="23"/>
     </row>
-    <row r="757" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="757" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C757" s="24"/>
       <c r="D757" s="22"/>
       <c r="E757" s="22"/>
       <c r="F757" s="22"/>
     </row>
-    <row r="758" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="758" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C758" s="25"/>
       <c r="D758" s="23"/>
       <c r="E758" s="23"/>
       <c r="F758" s="23"/>
     </row>
-    <row r="759" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="759" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C759" s="24"/>
       <c r="D759" s="22"/>
       <c r="E759" s="22"/>
       <c r="F759" s="22"/>
     </row>
-    <row r="760" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="760" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C760" s="25"/>
       <c r="D760" s="23"/>
       <c r="E760" s="23"/>
       <c r="F760" s="23"/>
     </row>
-    <row r="761" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="761" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C761" s="24"/>
       <c r="D761" s="22"/>
       <c r="E761" s="22"/>
       <c r="F761" s="22"/>
     </row>
-    <row r="762" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="762" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C762" s="25"/>
       <c r="D762" s="23"/>
       <c r="E762" s="23"/>
       <c r="F762" s="23"/>
     </row>
-    <row r="763" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="763" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C763" s="24"/>
       <c r="D763" s="22"/>
       <c r="E763" s="22"/>
       <c r="F763" s="22"/>
     </row>
-    <row r="764" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="764" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C764" s="25"/>
       <c r="D764" s="23"/>
       <c r="E764" s="23"/>
       <c r="F764" s="23"/>
     </row>
-    <row r="765" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="765" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C765" s="24"/>
       <c r="D765" s="22"/>
       <c r="E765" s="22"/>
       <c r="F765" s="22"/>
     </row>
-    <row r="766" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="766" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C766" s="25"/>
       <c r="D766" s="23"/>
       <c r="E766" s="23"/>
       <c r="F766" s="23"/>
     </row>
-    <row r="767" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="767" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C767" s="24"/>
       <c r="D767" s="22"/>
       <c r="E767" s="22"/>
       <c r="F767" s="22"/>
     </row>
-    <row r="768" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="768" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C768" s="25"/>
       <c r="D768" s="23"/>
       <c r="E768" s="23"/>
       <c r="F768" s="23"/>
     </row>
-    <row r="769" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="769" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C769" s="24"/>
       <c r="D769" s="22"/>
       <c r="E769" s="22"/>
       <c r="F769" s="22"/>
     </row>
-    <row r="770" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="770" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C770" s="25"/>
       <c r="D770" s="23"/>
       <c r="E770" s="23"/>
       <c r="F770" s="23"/>
     </row>
-    <row r="771" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="771" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C771" s="24"/>
       <c r="D771" s="22"/>
       <c r="E771" s="22"/>
       <c r="F771" s="22"/>
     </row>
-    <row r="772" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="772" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C772" s="25"/>
       <c r="D772" s="23"/>
       <c r="E772" s="23"/>
       <c r="F772" s="23"/>
     </row>
-    <row r="773" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="773" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C773" s="24"/>
       <c r="D773" s="22"/>
       <c r="E773" s="22"/>
       <c r="F773" s="22"/>
     </row>
-    <row r="774" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="774" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C774" s="25"/>
       <c r="D774" s="23"/>
       <c r="E774" s="23"/>
       <c r="F774" s="23"/>
     </row>
-    <row r="775" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="775" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C775" s="24"/>
       <c r="D775" s="22"/>
       <c r="E775" s="22"/>
       <c r="F775" s="22"/>
     </row>
-    <row r="776" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="776" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C776" s="25"/>
       <c r="D776" s="23"/>
       <c r="E776" s="23"/>
       <c r="F776" s="23"/>
     </row>
-    <row r="777" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="777" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C777" s="24"/>
       <c r="D777" s="22"/>
       <c r="E777" s="22"/>
       <c r="F777" s="22"/>
     </row>
-    <row r="778" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="778" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C778" s="25"/>
       <c r="D778" s="23"/>
       <c r="E778" s="23"/>
       <c r="F778" s="23"/>
     </row>
-    <row r="779" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="779" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C779" s="24"/>
       <c r="D779" s="22"/>
       <c r="E779" s="22"/>
       <c r="F779" s="22"/>
     </row>
-    <row r="780" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="780" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C780" s="25"/>
       <c r="D780" s="23"/>
       <c r="E780" s="23"/>
       <c r="F780" s="23"/>
     </row>
-    <row r="781" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="781" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C781" s="24"/>
       <c r="D781" s="22"/>
       <c r="E781" s="22"/>
       <c r="F781" s="22"/>
     </row>
-    <row r="782" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="782" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C782" s="25"/>
       <c r="D782" s="23"/>
       <c r="E782" s="23"/>
       <c r="F782" s="23"/>
     </row>
-    <row r="783" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="783" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C783" s="24"/>
       <c r="D783" s="22"/>
       <c r="E783" s="22"/>
       <c r="F783" s="22"/>
     </row>
-    <row r="784" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="784" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C784" s="25"/>
       <c r="D784" s="23"/>
       <c r="E784" s="23"/>
       <c r="F784" s="23"/>
     </row>
-    <row r="785" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="785" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C785" s="24"/>
       <c r="D785" s="22"/>
       <c r="E785" s="22"/>
       <c r="F785" s="22"/>
     </row>
-    <row r="786" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="786" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C786" s="25"/>
       <c r="D786" s="23"/>
       <c r="E786" s="23"/>
       <c r="F786" s="23"/>
     </row>
-    <row r="787" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="787" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C787" s="24"/>
       <c r="D787" s="22"/>
       <c r="E787" s="22"/>
       <c r="F787" s="22"/>
     </row>
-    <row r="788" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="788" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C788" s="25"/>
       <c r="D788" s="23"/>
       <c r="E788" s="23"/>
       <c r="F788" s="23"/>
     </row>
-    <row r="789" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="789" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C789" s="24"/>
       <c r="D789" s="22"/>
       <c r="E789" s="22"/>
       <c r="F789" s="22"/>
     </row>
-    <row r="790" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="790" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C790" s="25"/>
       <c r="D790" s="23"/>
       <c r="E790" s="23"/>
       <c r="F790" s="23"/>
     </row>
-    <row r="791" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="791" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C791" s="24"/>
       <c r="D791" s="22"/>
       <c r="E791" s="22"/>
       <c r="F791" s="22"/>
     </row>
-    <row r="792" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="792" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C792" s="25"/>
       <c r="D792" s="23"/>
       <c r="E792" s="23"/>
       <c r="F792" s="23"/>
     </row>
-    <row r="793" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="793" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C793" s="24"/>
       <c r="D793" s="22"/>
       <c r="E793" s="22"/>
       <c r="F793" s="22"/>
     </row>
-    <row r="794" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="794" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C794" s="25"/>
       <c r="D794" s="23"/>
       <c r="E794" s="23"/>
       <c r="F794" s="23"/>
     </row>
-    <row r="795" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="795" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C795" s="24"/>
       <c r="D795" s="22"/>
       <c r="E795" s="22"/>
       <c r="F795" s="22"/>
     </row>
-    <row r="796" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="796" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C796" s="25"/>
       <c r="D796" s="23"/>
       <c r="E796" s="23"/>
       <c r="F796" s="23"/>
     </row>
-    <row r="797" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="797" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C797" s="24"/>
       <c r="D797" s="22"/>
       <c r="E797" s="22"/>
       <c r="F797" s="22"/>
     </row>
-    <row r="798" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="798" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C798" s="25"/>
       <c r="D798" s="23"/>
       <c r="E798" s="23"/>
       <c r="F798" s="23"/>
     </row>
-    <row r="799" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="799" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C799" s="24"/>
       <c r="D799" s="22"/>
       <c r="E799" s="22"/>
       <c r="F799" s="22"/>
     </row>
-    <row r="800" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="800" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C800" s="25"/>
       <c r="D800" s="23"/>
       <c r="E800" s="23"/>
       <c r="F800" s="23"/>
     </row>
-    <row r="801" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="801" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C801" s="24"/>
       <c r="D801" s="22"/>
       <c r="E801" s="22"/>
       <c r="F801" s="22"/>
     </row>
-    <row r="802" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="802" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C802" s="25"/>
       <c r="D802" s="23"/>
       <c r="E802" s="23"/>
       <c r="F802" s="23"/>
     </row>
-    <row r="803" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="803" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C803" s="24"/>
       <c r="D803" s="22"/>
       <c r="E803" s="22"/>
       <c r="F803" s="22"/>
     </row>
-    <row r="804" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="804" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C804" s="25"/>
       <c r="D804" s="23"/>
       <c r="E804" s="23"/>
       <c r="F804" s="23"/>
     </row>
-    <row r="805" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="805" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C805" s="24"/>
       <c r="D805" s="22"/>
       <c r="E805" s="22"/>
       <c r="F805" s="22"/>
     </row>
-    <row r="806" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="806" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C806" s="25"/>
       <c r="D806" s="23"/>
       <c r="E806" s="23"/>
       <c r="F806" s="23"/>
     </row>
-    <row r="807" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="807" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C807" s="24"/>
       <c r="D807" s="22"/>
       <c r="E807" s="22"/>
       <c r="F807" s="22"/>
     </row>
-    <row r="808" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="808" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C808" s="25"/>
       <c r="D808" s="23"/>
       <c r="E808" s="23"/>
       <c r="F808" s="23"/>
     </row>
-    <row r="809" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="809" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C809" s="24"/>
       <c r="D809" s="22"/>
       <c r="E809" s="22"/>
       <c r="F809" s="22"/>
     </row>
-    <row r="810" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="810" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C810" s="25"/>
       <c r="D810" s="23"/>
       <c r="E810" s="23"/>
       <c r="F810" s="23"/>
     </row>
-    <row r="811" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="811" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C811" s="24"/>
       <c r="D811" s="22"/>
       <c r="E811" s="22"/>
       <c r="F811" s="22"/>
     </row>
-    <row r="812" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="812" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C812" s="25"/>
       <c r="D812" s="23"/>
       <c r="E812" s="23"/>
       <c r="F812" s="23"/>
     </row>
-    <row r="813" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="813" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C813" s="24"/>
       <c r="D813" s="22"/>
       <c r="E813" s="22"/>
       <c r="F813" s="22"/>
     </row>
-    <row r="814" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="814" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C814" s="25"/>
       <c r="D814" s="23"/>
       <c r="E814" s="23"/>
       <c r="F814" s="23"/>
     </row>
-    <row r="815" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="815" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C815" s="24"/>
       <c r="D815" s="22"/>
       <c r="E815" s="22"/>
       <c r="F815" s="22"/>
     </row>
-    <row r="816" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="816" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C816" s="25"/>
       <c r="D816" s="23"/>
       <c r="E816" s="23"/>
       <c r="F816" s="23"/>
     </row>
-    <row r="817" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="817" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C817" s="24"/>
       <c r="D817" s="22"/>
       <c r="E817" s="22"/>
       <c r="F817" s="22"/>
     </row>
-    <row r="818" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="818" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C818" s="25"/>
       <c r="D818" s="23"/>
       <c r="E818" s="23"/>
       <c r="F818" s="23"/>
     </row>
-    <row r="819" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="819" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C819" s="24"/>
       <c r="D819" s="22"/>
       <c r="E819" s="22"/>
       <c r="F819" s="22"/>
     </row>
-    <row r="820" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="820" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C820" s="25"/>
       <c r="D820" s="23"/>
       <c r="E820" s="23"/>
       <c r="F820" s="23"/>
     </row>
-    <row r="821" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="821" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C821" s="24"/>
       <c r="D821" s="22"/>
       <c r="E821" s="22"/>
       <c r="F821" s="22"/>
     </row>
-    <row r="822" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="822" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C822" s="25"/>
       <c r="D822" s="23"/>
       <c r="E822" s="23"/>
       <c r="F822" s="23"/>
     </row>
-    <row r="823" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="823" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C823" s="24"/>
       <c r="D823" s="22"/>
       <c r="E823" s="22"/>
       <c r="F823" s="22"/>
     </row>
-    <row r="824" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="824" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C824" s="25"/>
       <c r="D824" s="23"/>
       <c r="E824" s="23"/>
       <c r="F824" s="23"/>
     </row>
-    <row r="825" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="825" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C825" s="24"/>
       <c r="D825" s="22"/>
       <c r="E825" s="22"/>
       <c r="F825" s="22"/>
     </row>
-    <row r="826" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="826" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C826" s="25"/>
       <c r="D826" s="23"/>
       <c r="E826" s="23"/>
       <c r="F826" s="23"/>
     </row>
-    <row r="827" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="827" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C827" s="24"/>
       <c r="D827" s="22"/>
       <c r="E827" s="22"/>
       <c r="F827" s="22"/>
     </row>
-    <row r="828" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="828" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C828" s="25"/>
       <c r="D828" s="23"/>
       <c r="E828" s="23"/>
       <c r="F828" s="23"/>
     </row>
-    <row r="829" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="829" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C829" s="24"/>
       <c r="D829" s="22"/>
       <c r="E829" s="22"/>
       <c r="F829" s="22"/>
     </row>
-    <row r="830" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="830" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C830" s="25"/>
       <c r="D830" s="23"/>
       <c r="E830" s="23"/>
       <c r="F830" s="23"/>
     </row>
-    <row r="831" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="831" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C831" s="24"/>
       <c r="D831" s="22"/>
       <c r="E831" s="22"/>
       <c r="F831" s="22"/>
     </row>
-    <row r="832" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="832" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C832" s="25"/>
       <c r="D832" s="23"/>
       <c r="E832" s="23"/>
       <c r="F832" s="23"/>
     </row>
-    <row r="833" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="833" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C833" s="24"/>
       <c r="D833" s="22"/>
       <c r="E833" s="22"/>
       <c r="F833" s="22"/>
     </row>
-    <row r="834" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="834" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C834" s="25"/>
       <c r="D834" s="23"/>
       <c r="E834" s="23"/>
       <c r="F834" s="23"/>
     </row>
-    <row r="835" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="835" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C835" s="24"/>
       <c r="D835" s="22"/>
       <c r="E835" s="22"/>
       <c r="F835" s="22"/>
     </row>
-    <row r="836" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="836" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C836" s="25"/>
       <c r="D836" s="23"/>
       <c r="E836" s="23"/>
       <c r="F836" s="23"/>
     </row>
-    <row r="837" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="837" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C837" s="24"/>
       <c r="D837" s="22"/>
       <c r="E837" s="22"/>
       <c r="F837" s="22"/>
     </row>
-    <row r="838" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="838" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C838" s="25"/>
       <c r="D838" s="23"/>
       <c r="E838" s="23"/>
       <c r="F838" s="23"/>
     </row>
-    <row r="839" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="839" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C839" s="24"/>
       <c r="D839" s="22"/>
       <c r="E839" s="22"/>
       <c r="F839" s="22"/>
     </row>
-    <row r="840" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="840" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C840" s="25"/>
       <c r="D840" s="23"/>
       <c r="E840" s="23"/>
       <c r="F840" s="23"/>
     </row>
-    <row r="841" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="841" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C841" s="24"/>
       <c r="D841" s="22"/>
       <c r="E841" s="22"/>
       <c r="F841" s="22"/>
     </row>
-    <row r="842" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="842" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C842" s="25"/>
       <c r="D842" s="23"/>
       <c r="E842" s="23"/>
       <c r="F842" s="23"/>
     </row>
-    <row r="843" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="843" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C843" s="24"/>
       <c r="D843" s="22"/>
       <c r="E843" s="22"/>
       <c r="F843" s="22"/>
     </row>
-    <row r="844" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="844" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C844" s="25"/>
       <c r="D844" s="23"/>
       <c r="E844" s="23"/>
       <c r="F844" s="23"/>
     </row>
-    <row r="845" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="845" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C845" s="24"/>
       <c r="D845" s="22"/>
       <c r="E845" s="22"/>
       <c r="F845" s="22"/>
     </row>
-    <row r="846" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="846" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C846" s="25"/>
       <c r="D846" s="23"/>
       <c r="E846" s="23"/>
       <c r="F846" s="23"/>
     </row>
-    <row r="847" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="847" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C847" s="24"/>
       <c r="D847" s="22"/>
       <c r="E847" s="22"/>
       <c r="F847" s="22"/>
     </row>
-    <row r="848" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="848" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C848" s="25"/>
       <c r="D848" s="23"/>
       <c r="E848" s="23"/>
       <c r="F848" s="23"/>
     </row>
-    <row r="849" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="849" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C849" s="24"/>
       <c r="D849" s="22"/>
       <c r="E849" s="22"/>
       <c r="F849" s="22"/>
     </row>
-    <row r="850" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="850" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C850" s="25"/>
       <c r="D850" s="23"/>
       <c r="E850" s="23"/>
       <c r="F850" s="23"/>
     </row>
-    <row r="851" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="851" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C851" s="24"/>
       <c r="D851" s="22"/>
       <c r="E851" s="22"/>
       <c r="F851" s="22"/>
     </row>
-    <row r="852" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="852" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C852" s="25"/>
       <c r="D852" s="23"/>
       <c r="E852" s="23"/>
       <c r="F852" s="23"/>
     </row>
-    <row r="853" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="853" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C853" s="24"/>
       <c r="D853" s="22"/>
       <c r="E853" s="22"/>
       <c r="F853" s="22"/>
     </row>
-    <row r="854" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="854" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C854" s="25"/>
       <c r="D854" s="23"/>
       <c r="E854" s="23"/>
       <c r="F854" s="23"/>
     </row>
-    <row r="855" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="855" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C855" s="24"/>
       <c r="D855" s="22"/>
       <c r="E855" s="22"/>
       <c r="F855" s="22"/>
     </row>
-    <row r="856" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="856" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C856" s="25"/>
       <c r="D856" s="23"/>
       <c r="E856" s="23"/>
       <c r="F856" s="23"/>
     </row>
-    <row r="857" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="857" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C857" s="24"/>
       <c r="D857" s="22"/>
       <c r="E857" s="22"/>
       <c r="F857" s="22"/>
     </row>
-    <row r="858" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="858" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C858" s="25"/>
       <c r="D858" s="23"/>
       <c r="E858" s="23"/>
       <c r="F858" s="23"/>
     </row>
-    <row r="859" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="859" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C859" s="24"/>
       <c r="D859" s="22"/>
       <c r="E859" s="22"/>
       <c r="F859" s="22"/>
     </row>
-    <row r="860" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="860" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C860" s="25"/>
       <c r="D860" s="23"/>
       <c r="E860" s="23"/>
       <c r="F860" s="23"/>
     </row>
-    <row r="861" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="861" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C861" s="24"/>
       <c r="D861" s="22"/>
       <c r="E861" s="22"/>
       <c r="F861" s="22"/>
     </row>
-    <row r="862" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="862" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C862" s="25"/>
       <c r="D862" s="23"/>
       <c r="E862" s="23"/>
       <c r="F862" s="23"/>
     </row>
-    <row r="863" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="863" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C863" s="24"/>
       <c r="D863" s="22"/>
       <c r="E863" s="22"/>
       <c r="F863" s="22"/>
     </row>
-    <row r="864" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="864" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C864" s="25"/>
       <c r="D864" s="23"/>
       <c r="E864" s="23"/>
       <c r="F864" s="23"/>
     </row>
-    <row r="865" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="865" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C865" s="24"/>
       <c r="D865" s="22"/>
       <c r="E865" s="22"/>
       <c r="F865" s="22"/>
     </row>
-    <row r="866" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="866" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C866" s="25"/>
       <c r="D866" s="23"/>
       <c r="E866" s="23"/>
       <c r="F866" s="23"/>
     </row>
-    <row r="867" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="867" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C867" s="24"/>
       <c r="D867" s="22"/>
       <c r="E867" s="22"/>
       <c r="F867" s="22"/>
     </row>
-    <row r="868" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="868" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C868" s="25"/>
       <c r="D868" s="23"/>
       <c r="E868" s="23"/>
       <c r="F868" s="23"/>
     </row>
-    <row r="869" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="869" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C869" s="24"/>
       <c r="D869" s="22"/>
       <c r="E869" s="22"/>
       <c r="F869" s="22"/>
     </row>
-    <row r="870" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="870" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C870" s="25"/>
       <c r="D870" s="23"/>
       <c r="E870" s="23"/>
       <c r="F870" s="23"/>
     </row>
-    <row r="871" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="871" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C871" s="24"/>
       <c r="D871" s="22"/>
       <c r="E871" s="22"/>
       <c r="F871" s="22"/>
     </row>
-    <row r="872" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="872" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C872" s="25"/>
       <c r="D872" s="23"/>
       <c r="E872" s="23"/>
       <c r="F872" s="23"/>
     </row>
-    <row r="873" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="873" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C873" s="24"/>
       <c r="D873" s="22"/>
       <c r="E873" s="22"/>
       <c r="F873" s="22"/>
     </row>
-    <row r="874" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="874" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C874" s="25"/>
       <c r="D874" s="23"/>
       <c r="E874" s="23"/>
       <c r="F874" s="23"/>
     </row>
-    <row r="875" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="875" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C875" s="24"/>
       <c r="D875" s="22"/>
       <c r="E875" s="22"/>
       <c r="F875" s="22"/>
     </row>
-    <row r="876" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="876" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C876" s="25"/>
       <c r="D876" s="23"/>
       <c r="E876" s="23"/>
       <c r="F876" s="23"/>
     </row>
-    <row r="877" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="877" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C877" s="24"/>
       <c r="D877" s="22"/>
       <c r="E877" s="22"/>
       <c r="F877" s="22"/>
     </row>
-    <row r="878" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="878" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C878" s="25"/>
       <c r="D878" s="23"/>
       <c r="E878" s="23"/>
       <c r="F878" s="23"/>
     </row>
-    <row r="879" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="879" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C879" s="24"/>
       <c r="D879" s="22"/>
       <c r="E879" s="22"/>
       <c r="F879" s="22"/>
     </row>
-    <row r="880" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="880" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C880" s="25"/>
       <c r="D880" s="23"/>
       <c r="E880" s="23"/>
       <c r="F880" s="23"/>
     </row>
-    <row r="881" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="881" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C881" s="24"/>
       <c r="D881" s="22"/>
       <c r="E881" s="22"/>
       <c r="F881" s="22"/>
     </row>
-    <row r="882" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="882" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C882" s="25"/>
       <c r="D882" s="23"/>
       <c r="E882" s="23"/>
       <c r="F882" s="23"/>
     </row>
-    <row r="883" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="883" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C883" s="24"/>
       <c r="D883" s="22"/>
       <c r="E883" s="22"/>
       <c r="F883" s="22"/>
     </row>
-    <row r="884" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="884" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C884" s="25"/>
       <c r="D884" s="23"/>
       <c r="E884" s="23"/>
       <c r="F884" s="23"/>
     </row>
-    <row r="885" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="885" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C885" s="24"/>
       <c r="D885" s="22"/>
       <c r="E885" s="22"/>
       <c r="F885" s="22"/>
     </row>
-    <row r="886" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="886" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C886" s="25"/>
       <c r="D886" s="23"/>
       <c r="E886" s="23"/>
       <c r="F886" s="23"/>
     </row>
-    <row r="887" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="887" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C887" s="24"/>
       <c r="D887" s="22"/>
       <c r="E887" s="22"/>
       <c r="F887" s="22"/>
     </row>
-    <row r="888" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="888" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C888" s="25"/>
       <c r="D888" s="23"/>
       <c r="E888" s="23"/>
       <c r="F888" s="23"/>
     </row>
-    <row r="889" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="889" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C889" s="24"/>
       <c r="D889" s="22"/>
       <c r="E889" s="22"/>
       <c r="F889" s="22"/>
     </row>
-    <row r="890" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="890" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C890" s="25"/>
       <c r="D890" s="23"/>
       <c r="E890" s="23"/>
       <c r="F890" s="23"/>
     </row>
-    <row r="891" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="891" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C891" s="24"/>
       <c r="D891" s="22"/>
       <c r="E891" s="22"/>
       <c r="F891" s="22"/>
     </row>
-    <row r="892" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="892" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C892" s="25"/>
       <c r="D892" s="23"/>
       <c r="E892" s="23"/>
       <c r="F892" s="23"/>
     </row>
-    <row r="893" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="893" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C893" s="24"/>
       <c r="D893" s="22"/>
       <c r="E893" s="22"/>
       <c r="F893" s="22"/>
     </row>
-    <row r="894" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="894" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C894" s="25"/>
       <c r="D894" s="23"/>
       <c r="E894" s="23"/>
       <c r="F894" s="23"/>
     </row>
-    <row r="895" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="895" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C895" s="24"/>
       <c r="D895" s="22"/>
       <c r="E895" s="22"/>
       <c r="F895" s="22"/>
     </row>
-    <row r="896" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="896" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C896" s="25"/>
       <c r="D896" s="23"/>
       <c r="E896" s="23"/>
       <c r="F896" s="23"/>
     </row>
-    <row r="897" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="897" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C897" s="24"/>
       <c r="D897" s="22"/>
       <c r="E897" s="22"/>
       <c r="F897" s="22"/>
     </row>
-    <row r="898" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="898" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C898" s="25"/>
       <c r="D898" s="23"/>
       <c r="E898" s="23"/>
       <c r="F898" s="23"/>
     </row>
-    <row r="899" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="899" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C899" s="24"/>
       <c r="D899" s="22"/>
       <c r="E899" s="22"/>
       <c r="F899" s="22"/>
     </row>
-    <row r="900" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="900" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C900" s="25"/>
       <c r="D900" s="23"/>
       <c r="E900" s="23"/>
       <c r="F900" s="23"/>
     </row>
-    <row r="901" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="901" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C901" s="24"/>
       <c r="D901" s="22"/>
       <c r="E901" s="22"/>
       <c r="F901" s="22"/>
     </row>
-    <row r="902" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="902" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C902" s="25"/>
       <c r="D902" s="23"/>
       <c r="E902" s="23"/>
       <c r="F902" s="23"/>
     </row>
-    <row r="903" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="903" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C903" s="24"/>
       <c r="D903" s="22"/>
       <c r="E903" s="22"/>
       <c r="F903" s="22"/>
     </row>
-    <row r="904" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="904" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C904" s="25"/>
       <c r="D904" s="23"/>
       <c r="E904" s="23"/>
       <c r="F904" s="23"/>
     </row>
-    <row r="905" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="905" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C905" s="24"/>
       <c r="D905" s="22"/>
       <c r="E905" s="22"/>
       <c r="F905" s="22"/>
     </row>
-    <row r="906" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="906" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C906" s="25"/>
       <c r="D906" s="23"/>
       <c r="E906" s="23"/>
       <c r="F906" s="23"/>
     </row>
-    <row r="907" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="907" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C907" s="24"/>
       <c r="D907" s="22"/>
       <c r="E907" s="22"/>
       <c r="F907" s="22"/>
     </row>
-    <row r="908" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="908" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C908" s="25"/>
       <c r="D908" s="23"/>
       <c r="E908" s="23"/>
       <c r="F908" s="23"/>
     </row>
-    <row r="909" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="909" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C909" s="24"/>
       <c r="D909" s="22"/>
       <c r="E909" s="22"/>
       <c r="F909" s="22"/>
     </row>
-    <row r="910" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="910" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C910" s="25"/>
       <c r="D910" s="23"/>
       <c r="E910" s="23"/>
       <c r="F910" s="23"/>
     </row>
-    <row r="911" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="911" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C911" s="24"/>
       <c r="D911" s="22"/>
       <c r="E911" s="22"/>
       <c r="F911" s="22"/>
     </row>
-    <row r="912" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="912" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C912" s="25"/>
       <c r="D912" s="23"/>
       <c r="E912" s="23"/>
       <c r="F912" s="23"/>
     </row>
-    <row r="913" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="913" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C913" s="24"/>
       <c r="D913" s="22"/>
       <c r="E913" s="22"/>
       <c r="F913" s="22"/>
     </row>
-    <row r="914" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="914" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C914" s="25"/>
       <c r="D914" s="23"/>
       <c r="E914" s="23"/>
       <c r="F914" s="23"/>
     </row>
-    <row r="915" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="915" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C915" s="24"/>
       <c r="D915" s="22"/>
       <c r="E915" s="22"/>
       <c r="F915" s="22"/>
     </row>
-    <row r="916" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="916" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C916" s="25"/>
       <c r="D916" s="23"/>
       <c r="E916" s="23"/>
       <c r="F916" s="23"/>
     </row>
-    <row r="917" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="917" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C917" s="24"/>
       <c r="D917" s="22"/>
       <c r="E917" s="22"/>
       <c r="F917" s="22"/>
     </row>
-    <row r="918" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="918" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C918" s="25"/>
       <c r="D918" s="23"/>
       <c r="E918" s="23"/>
       <c r="F918" s="23"/>
     </row>
-    <row r="919" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="919" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C919" s="24"/>
       <c r="D919" s="22"/>
       <c r="E919" s="22"/>
       <c r="F919" s="22"/>
     </row>
-    <row r="920" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="920" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C920" s="25"/>
       <c r="D920" s="23"/>
       <c r="E920" s="23"/>
       <c r="F920" s="23"/>
     </row>
-    <row r="921" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="921" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C921" s="24"/>
       <c r="D921" s="22"/>
       <c r="E921" s="22"/>
       <c r="F921" s="22"/>
     </row>
-    <row r="922" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="922" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C922" s="25"/>
       <c r="D922" s="23"/>
       <c r="E922" s="23"/>
       <c r="F922" s="23"/>
     </row>
-    <row r="923" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="923" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C923" s="24"/>
       <c r="D923" s="22"/>
       <c r="E923" s="22"/>
       <c r="F923" s="22"/>
     </row>
-    <row r="924" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="924" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C924" s="25"/>
       <c r="D924" s="23"/>
       <c r="E924" s="23"/>
       <c r="F924" s="23"/>
     </row>
-    <row r="925" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="925" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C925" s="24"/>
       <c r="D925" s="22"/>
       <c r="E925" s="22"/>
       <c r="F925" s="22"/>
     </row>
-    <row r="926" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="926" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C926" s="25"/>
       <c r="D926" s="23"/>
       <c r="E926" s="23"/>
       <c r="F926" s="23"/>
     </row>
-    <row r="927" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="927" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C927" s="24"/>
       <c r="D927" s="22"/>
       <c r="E927" s="22"/>
       <c r="F927" s="22"/>
     </row>
-    <row r="928" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="928" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C928" s="25"/>
       <c r="D928" s="23"/>
       <c r="E928" s="23"/>
       <c r="F928" s="23"/>
     </row>
-    <row r="929" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="929" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C929" s="24"/>
       <c r="D929" s="22"/>
       <c r="E929" s="22"/>
       <c r="F929" s="22"/>
     </row>
-    <row r="930" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="930" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C930" s="25"/>
       <c r="D930" s="23"/>
       <c r="E930" s="23"/>
       <c r="F930" s="23"/>
     </row>
-    <row r="931" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="931" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C931" s="24"/>
       <c r="D931" s="22"/>
       <c r="E931" s="22"/>
       <c r="F931" s="22"/>
     </row>
-    <row r="932" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="932" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C932" s="25"/>
       <c r="D932" s="23"/>
       <c r="E932" s="23"/>
       <c r="F932" s="23"/>
     </row>
-    <row r="933" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="933" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C933" s="24"/>
       <c r="D933" s="22"/>
       <c r="E933" s="22"/>
       <c r="F933" s="22"/>
     </row>
-    <row r="934" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="934" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C934" s="25"/>
       <c r="D934" s="23"/>
       <c r="E934" s="23"/>
       <c r="F934" s="23"/>
     </row>
-    <row r="935" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="935" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C935" s="24"/>
       <c r="D935" s="22"/>
       <c r="E935" s="22"/>
       <c r="F935" s="22"/>
     </row>
-    <row r="936" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="936" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C936" s="25"/>
       <c r="D936" s="23"/>
       <c r="E936" s="23"/>
       <c r="F936" s="23"/>
     </row>
-    <row r="937" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="937" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C937" s="24"/>
       <c r="D937" s="22"/>
       <c r="E937" s="22"/>
       <c r="F937" s="22"/>
     </row>
-    <row r="938" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="938" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C938" s="25"/>
       <c r="D938" s="23"/>
       <c r="E938" s="23"/>
       <c r="F938" s="23"/>
     </row>
-    <row r="939" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="939" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C939" s="24"/>
       <c r="D939" s="22"/>
       <c r="E939" s="22"/>
       <c r="F939" s="22"/>
     </row>
-    <row r="940" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="940" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C940" s="25"/>
       <c r="D940" s="23"/>
       <c r="E940" s="23"/>
       <c r="F940" s="23"/>
     </row>
-    <row r="941" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="941" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C941" s="24"/>
       <c r="D941" s="22"/>
       <c r="E941" s="22"/>
       <c r="F941" s="22"/>
     </row>
-    <row r="942" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="942" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C942" s="25"/>
       <c r="D942" s="23"/>
       <c r="E942" s="23"/>
       <c r="F942" s="23"/>
     </row>
-    <row r="943" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="943" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C943" s="24"/>
       <c r="D943" s="22"/>
       <c r="E943" s="22"/>
       <c r="F943" s="22"/>
     </row>
-    <row r="944" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="944" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C944" s="25"/>
       <c r="D944" s="23"/>
       <c r="E944" s="23"/>
       <c r="F944" s="23"/>
     </row>
-    <row r="945" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="945" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C945" s="24"/>
       <c r="D945" s="22"/>
       <c r="E945" s="22"/>
       <c r="F945" s="22"/>
     </row>
-    <row r="946" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="946" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C946" s="25"/>
       <c r="D946" s="23"/>
       <c r="E946" s="23"/>
       <c r="F946" s="23"/>
     </row>
-    <row r="947" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="947" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C947" s="24"/>
       <c r="D947" s="22"/>
       <c r="E947" s="22"/>
       <c r="F947" s="22"/>
     </row>
-    <row r="948" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="948" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C948" s="25"/>
       <c r="D948" s="23"/>
       <c r="E948" s="23"/>
       <c r="F948" s="23"/>
     </row>
-    <row r="949" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="949" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C949" s="24"/>
       <c r="D949" s="22"/>
       <c r="E949" s="22"/>
       <c r="F949" s="22"/>
     </row>
-    <row r="950" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="950" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C950" s="25"/>
       <c r="D950" s="23"/>
       <c r="E950" s="23"/>
       <c r="F950" s="23"/>
     </row>
-    <row r="951" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="951" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C951" s="24"/>
       <c r="D951" s="22"/>
       <c r="E951" s="22"/>
       <c r="F951" s="22"/>
     </row>
-    <row r="952" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="952" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C952" s="25"/>
       <c r="D952" s="23"/>
       <c r="E952" s="23"/>
       <c r="F952" s="23"/>
     </row>
-    <row r="953" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="953" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C953" s="24"/>
       <c r="D953" s="22"/>
       <c r="E953" s="22"/>
       <c r="F953" s="22"/>
     </row>
-    <row r="954" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="954" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C954" s="25"/>
       <c r="D954" s="23"/>
       <c r="E954" s="23"/>
       <c r="F954" s="23"/>
     </row>
-    <row r="955" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="955" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C955" s="24"/>
       <c r="D955" s="22"/>
       <c r="E955" s="22"/>
       <c r="F955" s="22"/>
     </row>
-    <row r="956" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="956" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C956" s="25"/>
       <c r="D956" s="23"/>
       <c r="E956" s="23"/>
       <c r="F956" s="23"/>
     </row>
-    <row r="957" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="957" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C957" s="24"/>
       <c r="D957" s="22"/>
       <c r="E957" s="22"/>
       <c r="F957" s="22"/>
     </row>
-    <row r="958" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="958" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C958" s="25"/>
       <c r="D958" s="23"/>
       <c r="E958" s="23"/>
       <c r="F958" s="23"/>
     </row>
-    <row r="959" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="959" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C959" s="24"/>
       <c r="D959" s="22"/>
       <c r="E959" s="22"/>
       <c r="F959" s="22"/>
     </row>
-    <row r="960" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="960" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C960" s="25"/>
       <c r="D960" s="23"/>
       <c r="E960" s="23"/>
       <c r="F960" s="23"/>
     </row>
-    <row r="961" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="961" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C961" s="24"/>
       <c r="D961" s="22"/>
       <c r="E961" s="22"/>
       <c r="F961" s="22"/>
     </row>
-    <row r="962" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="962" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C962" s="25"/>
       <c r="D962" s="23"/>
       <c r="E962" s="23"/>
       <c r="F962" s="23"/>
     </row>
-    <row r="963" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="963" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C963" s="24"/>
       <c r="D963" s="22"/>
       <c r="E963" s="22"/>
       <c r="F963" s="22"/>
     </row>
-    <row r="964" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="964" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C964" s="25"/>
       <c r="D964" s="23"/>
       <c r="E964" s="23"/>
       <c r="F964" s="23"/>
     </row>
-    <row r="965" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="965" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C965" s="24"/>
       <c r="D965" s="22"/>
       <c r="E965" s="22"/>
       <c r="F965" s="22"/>
     </row>
-    <row r="966" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="966" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C966" s="25"/>
       <c r="D966" s="23"/>
       <c r="E966" s="23"/>
       <c r="F966" s="23"/>
     </row>
-    <row r="967" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="967" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C967" s="24"/>
       <c r="D967" s="22"/>
       <c r="E967" s="22"/>
       <c r="F967" s="22"/>
     </row>
-    <row r="968" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="968" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C968" s="25"/>
       <c r="D968" s="23"/>
       <c r="E968" s="23"/>
       <c r="F968" s="23"/>
     </row>
-    <row r="969" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="969" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C969" s="24"/>
       <c r="D969" s="22"/>
       <c r="E969" s="22"/>
       <c r="F969" s="22"/>
     </row>
-    <row r="970" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="970" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C970" s="25"/>
       <c r="D970" s="23"/>
       <c r="E970" s="23"/>
       <c r="F970" s="23"/>
     </row>
-    <row r="971" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="971" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C971" s="24"/>
       <c r="D971" s="22"/>
       <c r="E971" s="22"/>
       <c r="F971" s="22"/>
     </row>
-    <row r="972" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="972" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C972" s="25"/>
       <c r="D972" s="23"/>
       <c r="E972" s="23"/>
       <c r="F972" s="23"/>
     </row>
-    <row r="973" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="973" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C973" s="24"/>
       <c r="D973" s="22"/>
       <c r="E973" s="22"/>
       <c r="F973" s="22"/>
     </row>
-    <row r="974" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="974" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C974" s="25"/>
       <c r="D974" s="23"/>
       <c r="E974" s="23"/>
       <c r="F974" s="23"/>
     </row>
-    <row r="975" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="975" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C975" s="24"/>
       <c r="D975" s="22"/>
       <c r="E975" s="22"/>
       <c r="F975" s="22"/>
     </row>
-    <row r="976" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="976" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C976" s="25"/>
       <c r="D976" s="23"/>
       <c r="E976" s="23"/>
       <c r="F976" s="23"/>
     </row>
-    <row r="977" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="977" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C977" s="24"/>
       <c r="D977" s="22"/>
       <c r="E977" s="22"/>
       <c r="F977" s="22"/>
     </row>
-    <row r="978" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="978" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C978" s="25"/>
       <c r="D978" s="23"/>
       <c r="E978" s="23"/>
       <c r="F978" s="23"/>
     </row>
-    <row r="979" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="979" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C979" s="24"/>
       <c r="D979" s="22"/>
       <c r="E979" s="22"/>
       <c r="F979" s="22"/>
     </row>
-    <row r="980" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="980" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C980" s="25"/>
       <c r="D980" s="23"/>
       <c r="E980" s="23"/>
       <c r="F980" s="23"/>
     </row>
-    <row r="981" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="981" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C981" s="24"/>
       <c r="D981" s="22"/>
       <c r="E981" s="22"/>
       <c r="F981" s="22"/>
     </row>
-    <row r="982" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="982" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C982" s="25"/>
       <c r="D982" s="23"/>
       <c r="E982" s="23"/>
       <c r="F982" s="23"/>
     </row>
-    <row r="983" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="983" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C983" s="24"/>
       <c r="D983" s="22"/>
       <c r="E983" s="22"/>
       <c r="F983" s="22"/>
     </row>
-    <row r="984" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="984" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C984" s="25"/>
       <c r="D984" s="23"/>
       <c r="E984" s="23"/>
       <c r="F984" s="23"/>
     </row>
-    <row r="985" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="985" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C985" s="24"/>
       <c r="D985" s="22"/>
       <c r="E985" s="22"/>
       <c r="F985" s="22"/>
     </row>
-    <row r="986" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="986" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C986" s="25"/>
       <c r="D986" s="23"/>
       <c r="E986" s="23"/>
       <c r="F986" s="23"/>
     </row>
-    <row r="987" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="987" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C987" s="24"/>
       <c r="D987" s="22"/>
       <c r="E987" s="22"/>
       <c r="F987" s="22"/>
     </row>
-    <row r="988" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="988" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C988" s="25"/>
       <c r="D988" s="23"/>
       <c r="E988" s="23"/>
       <c r="F988" s="23"/>
     </row>
-    <row r="989" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="989" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C989" s="24"/>
       <c r="D989" s="22"/>
       <c r="E989" s="22"/>
       <c r="F989" s="22"/>
     </row>
-    <row r="990" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="990" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C990" s="25"/>
       <c r="D990" s="23"/>
       <c r="E990" s="23"/>
       <c r="F990" s="23"/>
     </row>
-    <row r="991" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="991" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C991" s="24"/>
       <c r="D991" s="22"/>
       <c r="E991" s="22"/>
       <c r="F991" s="22"/>
     </row>
-    <row r="992" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="992" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C992" s="25"/>
       <c r="D992" s="23"/>
       <c r="E992" s="23"/>
       <c r="F992" s="23"/>
     </row>
-    <row r="993" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="993" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C993" s="24"/>
       <c r="D993" s="22"/>
       <c r="E993" s="22"/>
       <c r="F993" s="22"/>
     </row>
-    <row r="994" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="994" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C994" s="25"/>
       <c r="D994" s="23"/>
       <c r="E994" s="23"/>
       <c r="F994" s="23"/>
     </row>
-    <row r="995" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="995" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C995" s="24"/>
       <c r="D995" s="22"/>
       <c r="E995" s="22"/>
       <c r="F995" s="22"/>
     </row>
-    <row r="996" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="996" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C996" s="25"/>
       <c r="D996" s="23"/>
       <c r="E996" s="23"/>
       <c r="F996" s="23"/>
     </row>
-    <row r="997" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="997" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C997" s="24"/>
       <c r="D997" s="22"/>
       <c r="E997" s="22"/>
       <c r="F997" s="22"/>
     </row>
-    <row r="998" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="998" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C998" s="25"/>
       <c r="D998" s="23"/>
       <c r="E998" s="23"/>
       <c r="F998" s="23"/>
     </row>
-    <row r="999" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="999" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C999" s="24"/>
       <c r="D999" s="22"/>
       <c r="E999" s="22"/>
       <c r="F999" s="22"/>
     </row>
-    <row r="1000" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="1000" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C1000" s="25"/>
       <c r="D1000" s="23"/>
       <c r="E1000" s="23"/>
@@ -17583,14 +17585,14 @@
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="B1:E15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="41.7109375" customWidth="1"/>
+    <col min="2" max="2" width="41.6640625" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B1" s="31" t="s">
         <v>26</v>
       </c>
@@ -17601,80 +17603,80 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>5910</v>
+        <v>6855</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>2790</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -17682,13 +17684,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BDDE723-6D9A-4C8A-97FE-709060F4DF0D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC833DE-A913-4772-A4BC-596EEBC530D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91622F2E-6951-4B19-A271-7A4917CE2419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40290" yWindow="3735" windowWidth="23040" windowHeight="12120" activeTab="2" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
+    <workbookView xWindow="40290" yWindow="3735" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="90">
   <si>
     <t>Week:</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>Built out dictionary</t>
+  </si>
+  <si>
+    <t>Building out L2 assessment outline</t>
   </si>
 </sst>
 </file>
@@ -1887,10 +1890,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6855</c:v>
+                  <c:v>6015</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1845</c:v>
+                  <c:v>2685</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11935,19 +11938,32 @@
       </c>
     </row>
     <row r="64" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C64" s="25"/>
+      <c r="C64" s="33">
+        <v>45980</v>
+      </c>
       <c r="D64" s="23">
-        <f>SUM(D54:D63)</f>
-        <v>945</v>
-      </c>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
+        <v>45</v>
+      </c>
+      <c r="E64" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64" s="23" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="65" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C65" s="24"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
+      <c r="C65" s="32">
+        <v>45981</v>
+      </c>
+      <c r="D65" s="22">
+        <v>60</v>
+      </c>
+      <c r="E65" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65" s="22" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="66" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C66" s="25"/>
@@ -17609,11 +17625,11 @@
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>6855</v>
+        <v>6015</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>1845</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91622F2E-6951-4B19-A271-7A4917CE2419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D8BBBA-B9F6-4848-B56F-09D32F9DF043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40290" yWindow="3735" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
+    <workbookView xWindow="38280" yWindow="2325" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="91">
   <si>
     <t>Week:</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>Building out L2 assessment outline</t>
+  </si>
+  <si>
+    <t>Building out L2 assessment</t>
   </si>
 </sst>
 </file>
@@ -1890,10 +1893,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6015</c:v>
+                  <c:v>6285</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2685</c:v>
+                  <c:v>2415</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11966,22 +11969,46 @@
       </c>
     </row>
     <row r="66" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C66" s="25"/>
-      <c r="D66" s="23"/>
-      <c r="E66" s="23"/>
-      <c r="F66" s="23"/>
+      <c r="C66" s="33">
+        <v>45981</v>
+      </c>
+      <c r="D66" s="23">
+        <v>45</v>
+      </c>
+      <c r="E66" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F66" s="23" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="67" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C67" s="24"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
+      <c r="C67" s="32">
+        <v>45982</v>
+      </c>
+      <c r="D67" s="22">
+        <v>75</v>
+      </c>
+      <c r="E67" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F67" s="22" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="68" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C68" s="25"/>
-      <c r="D68" s="23"/>
-      <c r="E68" s="23"/>
-      <c r="F68" s="23"/>
+      <c r="C68" s="33">
+        <v>45679</v>
+      </c>
+      <c r="D68" s="23">
+        <v>150</v>
+      </c>
+      <c r="E68" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" s="23" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="69" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C69" s="24"/>
@@ -17625,11 +17652,11 @@
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>6015</v>
+        <v>6285</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>2685</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D8BBBA-B9F6-4848-B56F-09D32F9DF043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8844F5B6-4448-42CD-8426-8342A009F146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="2325" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
   <si>
     <t>Week:</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>Building out L2 assessment</t>
+  </si>
+  <si>
+    <t>Outside stakeholder discussion</t>
   </si>
 </sst>
 </file>
@@ -1893,10 +1896,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6285</c:v>
+                  <c:v>6375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2415</c:v>
+                  <c:v>2325</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11998,10 +12001,10 @@
     </row>
     <row r="68" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C68" s="33">
-        <v>45679</v>
+        <v>45983</v>
       </c>
       <c r="D68" s="23">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="E68" s="23" t="s">
         <v>27</v>
@@ -12011,10 +12014,18 @@
       </c>
     </row>
     <row r="69" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C69" s="24"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
+      <c r="C69" s="32">
+        <v>45983</v>
+      </c>
+      <c r="D69" s="22">
+        <v>30</v>
+      </c>
+      <c r="E69" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F69" s="22" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="70" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C70" s="25"/>
@@ -17652,11 +17663,11 @@
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>6285</v>
+        <v>6375</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>2415</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8844F5B6-4448-42CD-8426-8342A009F146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC41099-2EF0-4BA1-B77F-D3EFE7A478AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="2325" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="93">
   <si>
     <t>Week:</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>Outside stakeholder discussion</t>
+  </si>
+  <si>
+    <t>Building out L2 assessment, AC/AT</t>
   </si>
 </sst>
 </file>
@@ -1896,10 +1899,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6375</c:v>
+                  <c:v>6495</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2325</c:v>
+                  <c:v>2205</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12004,13 +12007,13 @@
         <v>45983</v>
       </c>
       <c r="D68" s="23">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="E68" s="23" t="s">
         <v>27</v>
       </c>
       <c r="F68" s="23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="69" spans="3:6" x14ac:dyDescent="0.3">
@@ -17663,11 +17666,11 @@
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>6375</v>
+        <v>6495</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>2325</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC41099-2EF0-4BA1-B77F-D3EFE7A478AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6B8888-0C64-440B-83B0-A365D872802D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="2325" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="94">
   <si>
     <t>Week:</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>Building out L2 assessment, AC/AT</t>
+  </si>
+  <si>
+    <t>Changed start page, drafted progress bar</t>
   </si>
 </sst>
 </file>
@@ -1899,10 +1902,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6495</c:v>
+                  <c:v>6525</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2205</c:v>
+                  <c:v>2175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12031,10 +12034,18 @@
       </c>
     </row>
     <row r="70" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C70" s="25"/>
-      <c r="D70" s="23"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="23"/>
+      <c r="C70" s="33">
+        <v>45984</v>
+      </c>
+      <c r="D70" s="23">
+        <v>30</v>
+      </c>
+      <c r="E70" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70" s="23" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="71" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C71" s="24"/>
@@ -17666,11 +17677,11 @@
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>6495</v>
+        <v>6525</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>2205</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6B8888-0C64-440B-83B0-A365D872802D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8712732-C7BF-401E-A0D1-DF62C5862937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="2325" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="95">
   <si>
     <t>Week:</t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>Changed start page, drafted progress bar</t>
+  </si>
+  <si>
+    <t>Fixed CUI cat pages due to N/A vars after user test</t>
   </si>
 </sst>
 </file>
@@ -1902,10 +1905,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6525</c:v>
+                  <c:v>6555</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2175</c:v>
+                  <c:v>2145</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12048,10 +12051,18 @@
       </c>
     </row>
     <row r="71" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C71" s="24"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
+      <c r="C71" s="32">
+        <v>45984</v>
+      </c>
+      <c r="D71" s="22">
+        <v>30</v>
+      </c>
+      <c r="E71" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F71" s="22" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="72" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C72" s="25"/>
@@ -17677,11 +17688,11 @@
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>6525</v>
+        <v>6555</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>2175</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8712732-C7BF-401E-A0D1-DF62C5862937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D7AA5C-1C51-4D2A-ACAC-DA00B995180E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="2325" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="96">
   <si>
     <t>Week:</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>Fixed CUI cat pages due to N/A vars after user test</t>
+  </si>
+  <si>
+    <t>Building out L2 assessment, AU</t>
   </si>
 </sst>
 </file>
@@ -1905,10 +1908,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6555</c:v>
+                  <c:v>6630</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2145</c:v>
+                  <c:v>2070</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12065,10 +12068,18 @@
       </c>
     </row>
     <row r="72" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C72" s="25"/>
-      <c r="D72" s="23"/>
-      <c r="E72" s="23"/>
-      <c r="F72" s="23"/>
+      <c r="C72" s="33">
+        <v>45984</v>
+      </c>
+      <c r="D72" s="23">
+        <v>75</v>
+      </c>
+      <c r="E72" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F72" s="23" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="73" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C73" s="24"/>
@@ -17688,11 +17699,11 @@
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>6555</v>
+        <v>6630</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>2145</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D7AA5C-1C51-4D2A-ACAC-DA00B995180E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337AEC10-71EC-47DC-AE3C-83D7D06AADF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2325" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
+    <workbookView xWindow="39840" yWindow="3885" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="97">
   <si>
     <t>Week:</t>
   </si>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t>Building out L2 assessment, AU</t>
+  </si>
+  <si>
+    <t>Fixed L1 Formatting</t>
   </si>
 </sst>
 </file>
@@ -1908,10 +1911,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6630</c:v>
+                  <c:v>6645</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2070</c:v>
+                  <c:v>2055</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12082,10 +12085,18 @@
       </c>
     </row>
     <row r="73" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C73" s="24"/>
-      <c r="D73" s="22"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
+      <c r="C73" s="32">
+        <v>45984</v>
+      </c>
+      <c r="D73" s="22">
+        <v>15</v>
+      </c>
+      <c r="E73" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" s="22" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="74" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C74" s="25"/>
@@ -17699,11 +17710,11 @@
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>6630</v>
+        <v>6645</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>2070</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337AEC10-71EC-47DC-AE3C-83D7D06AADF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1C7B6A-7C5F-4BD9-A7FD-76D674885FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="39840" yWindow="3885" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="98">
   <si>
     <t>Week:</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>Fixed L1 Formatting</t>
+  </si>
+  <si>
+    <t>Favicon Added</t>
   </si>
 </sst>
 </file>
@@ -1911,10 +1914,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6645</c:v>
+                  <c:v>6675</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2055</c:v>
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12099,10 +12102,18 @@
       </c>
     </row>
     <row r="74" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C74" s="25"/>
-      <c r="D74" s="23"/>
-      <c r="E74" s="23"/>
-      <c r="F74" s="23"/>
+      <c r="C74" s="33">
+        <v>45984</v>
+      </c>
+      <c r="D74" s="23">
+        <v>30</v>
+      </c>
+      <c r="E74" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F74" s="23" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="75" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C75" s="24"/>
@@ -17710,11 +17721,11 @@
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>6645</v>
+        <v>6675</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>2055</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1C7B6A-7C5F-4BD9-A7FD-76D674885FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45EB74C-FF32-48B6-9C04-C2DAA7149C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39840" yWindow="3885" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="99">
   <si>
     <t>Week:</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>Favicon Added</t>
+  </si>
+  <si>
+    <t>Preparing for Final Deliverables</t>
   </si>
 </sst>
 </file>
@@ -1914,10 +1917,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6675</c:v>
+                  <c:v>6720</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2025</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10627,20 +10630,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P30"/>
-  <sheetFormatPr defaultColWidth="16.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="16.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.33203125" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="16.33203125" customWidth="1"/>
-    <col min="12" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.33203125" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="16.28515625" customWidth="1"/>
+    <col min="12" max="13" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -10675,7 +10678,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
@@ -10724,7 +10727,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>4</v>
       </c>
@@ -10747,7 +10750,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="40"/>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -10762,7 +10765,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="36"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="40"/>
       <c r="B5" s="45" t="s">
         <v>4</v>
@@ -10777,7 +10780,7 @@
       <c r="J5" s="3"/>
       <c r="K5" s="36"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>13</v>
       </c>
@@ -10794,7 +10797,7 @@
       <c r="J6" s="3"/>
       <c r="K6" s="36"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="41"/>
       <c r="B7" s="3"/>
       <c r="C7" s="8"/>
@@ -10809,7 +10812,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="36"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="41"/>
       <c r="B8" s="3"/>
       <c r="C8" s="8"/>
@@ -10824,7 +10827,7 @@
       <c r="J8" s="3"/>
       <c r="K8" s="36"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="41"/>
       <c r="B9" s="3"/>
       <c r="C9" s="8"/>
@@ -10839,7 +10842,7 @@
       <c r="J9" s="3"/>
       <c r="K9" s="36"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="43" t="s">
         <v>14</v>
       </c>
@@ -10856,7 +10859,7 @@
       <c r="J10" s="3"/>
       <c r="K10" s="36"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="43"/>
       <c r="B11" s="3"/>
       <c r="C11" s="8"/>
@@ -10871,7 +10874,7 @@
       <c r="J11" s="3"/>
       <c r="K11" s="36"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="43"/>
       <c r="B12" s="3"/>
       <c r="C12" s="8"/>
@@ -10886,7 +10889,7 @@
       <c r="J12" s="3"/>
       <c r="K12" s="36"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="43"/>
       <c r="B13" s="3"/>
       <c r="C13" s="8"/>
@@ -10901,7 +10904,7 @@
       <c r="J13" s="3"/>
       <c r="K13" s="36"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="43"/>
       <c r="B14" s="3"/>
       <c r="C14" s="8"/>
@@ -10916,7 +10919,7 @@
       <c r="J14" s="3"/>
       <c r="K14" s="36"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="29"/>
       <c r="B15" s="3"/>
       <c r="C15" s="8"/>
@@ -10931,7 +10934,7 @@
       <c r="J15" s="38"/>
       <c r="K15" s="36"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="30" t="s">
         <v>15</v>
       </c>
@@ -10948,7 +10951,7 @@
       <c r="J16" s="42"/>
       <c r="K16" s="37"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="34" t="s">
         <v>36</v>
       </c>
@@ -10956,7 +10959,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="35" t="s">
         <v>29</v>
       </c>
@@ -10964,7 +10967,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
         <v>4</v>
       </c>
@@ -10972,12 +10975,12 @@
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="35" t="s">
         <v>5</v>
       </c>
@@ -10985,7 +10988,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="35" t="s">
         <v>6</v>
       </c>
@@ -10993,7 +10996,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
         <v>28</v>
       </c>
@@ -11001,7 +11004,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="35" t="s">
         <v>7</v>
       </c>
@@ -11009,7 +11012,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="35" t="s">
         <v>8</v>
       </c>
@@ -11017,7 +11020,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="35" t="s">
         <v>9</v>
       </c>
@@ -11025,7 +11028,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="35" t="s">
         <v>19</v>
       </c>
@@ -11033,7 +11036,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="35" t="s">
         <v>27</v>
       </c>
@@ -11041,7 +11044,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="35" t="s">
         <v>38</v>
       </c>
@@ -11075,15 +11078,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8154930E-2F36-41CB-8896-D63BC278B832}">
   <dimension ref="C1:F1000"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="21.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" customWidth="1"/>
-    <col min="5" max="5" width="38.5546875" customWidth="1"/>
-    <col min="6" max="6" width="114.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="38.5703125" customWidth="1"/>
+    <col min="6" max="6" width="114.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C1" s="26" t="s">
         <v>22</v>
       </c>
@@ -11097,7 +11100,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C2" s="28">
         <v>45927</v>
       </c>
@@ -11111,7 +11114,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C3" s="32">
         <v>45927</v>
       </c>
@@ -11125,7 +11128,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C4" s="33">
         <v>45928</v>
       </c>
@@ -11139,7 +11142,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C5" s="32">
         <v>45928</v>
       </c>
@@ -11153,7 +11156,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C6" s="33">
         <v>45929</v>
       </c>
@@ -11167,7 +11170,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C7" s="32">
         <v>45934</v>
       </c>
@@ -11181,7 +11184,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C8" s="33">
         <v>45934</v>
       </c>
@@ -11195,7 +11198,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C9" s="32">
         <v>45934</v>
       </c>
@@ -11209,7 +11212,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C10" s="33">
         <v>45935</v>
       </c>
@@ -11223,7 +11226,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C11" s="32">
         <v>45936</v>
       </c>
@@ -11237,7 +11240,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C12" s="33">
         <v>45940</v>
       </c>
@@ -11249,7 +11252,7 @@
       </c>
       <c r="F12" s="23"/>
     </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C13" s="32">
         <v>45941</v>
       </c>
@@ -11261,7 +11264,7 @@
       </c>
       <c r="F13" s="22"/>
     </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C14" s="33">
         <v>45942</v>
       </c>
@@ -11275,7 +11278,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C15" s="32">
         <v>45944</v>
       </c>
@@ -11289,7 +11292,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C16" s="33">
         <v>45944</v>
       </c>
@@ -11303,7 +11306,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C17" s="32">
         <v>45944</v>
       </c>
@@ -11317,7 +11320,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C18" s="33">
         <v>45944</v>
       </c>
@@ -11331,7 +11334,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C19" s="32">
         <v>45944</v>
       </c>
@@ -11345,7 +11348,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="33">
         <v>45945</v>
       </c>
@@ -11359,7 +11362,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="32">
         <v>45945</v>
       </c>
@@ -11373,7 +11376,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="33">
         <v>45945</v>
       </c>
@@ -11387,7 +11390,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C23" s="32">
         <v>45946</v>
       </c>
@@ -11401,7 +11404,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C24" s="33">
         <v>45946</v>
       </c>
@@ -11415,7 +11418,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C25" s="32">
         <v>45946</v>
       </c>
@@ -11429,7 +11432,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C26" s="33">
         <v>45946</v>
       </c>
@@ -11443,7 +11446,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C27" s="32">
         <v>45946</v>
       </c>
@@ -11457,7 +11460,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C28" s="33">
         <v>45946</v>
       </c>
@@ -11471,7 +11474,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C29" s="32">
         <v>45950</v>
       </c>
@@ -11485,7 +11488,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C30" s="33">
         <v>45950</v>
       </c>
@@ -11499,7 +11502,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C31" s="32">
         <v>45950</v>
       </c>
@@ -11513,7 +11516,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C32" s="33">
         <v>45951</v>
       </c>
@@ -11527,7 +11530,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C33" s="32">
         <v>45951</v>
       </c>
@@ -11541,7 +11544,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C34" s="33">
         <v>45955</v>
       </c>
@@ -11555,7 +11558,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C35" s="32">
         <v>45956</v>
       </c>
@@ -11569,7 +11572,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C36" s="33">
         <v>45956</v>
       </c>
@@ -11583,7 +11586,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C37" s="32">
         <v>45957</v>
       </c>
@@ -11597,7 +11600,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C38" s="33">
         <v>45958</v>
       </c>
@@ -11611,7 +11614,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="32">
         <v>45958</v>
       </c>
@@ -11625,7 +11628,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="33">
         <v>45960</v>
       </c>
@@ -11639,7 +11642,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C41" s="32">
         <v>45961</v>
       </c>
@@ -11653,7 +11656,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C42" s="33">
         <v>45962</v>
       </c>
@@ -11667,7 +11670,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C43" s="32">
         <v>45962</v>
       </c>
@@ -11681,7 +11684,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C44" s="33">
         <v>45963</v>
       </c>
@@ -11695,7 +11698,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="45" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C45" s="32">
         <v>45963</v>
       </c>
@@ -11709,7 +11712,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C46" s="33">
         <v>45964</v>
       </c>
@@ -11723,7 +11726,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C47" s="32">
         <v>45964</v>
       </c>
@@ -11737,7 +11740,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="48" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C48" s="33">
         <v>45965</v>
       </c>
@@ -11751,7 +11754,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C49" s="32">
         <v>45965</v>
       </c>
@@ -11765,7 +11768,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C50" s="33">
         <v>45969</v>
       </c>
@@ -11779,7 +11782,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="51" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C51" s="32">
         <v>45970</v>
       </c>
@@ -11793,7 +11796,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C52" s="33">
         <v>45971</v>
       </c>
@@ -11807,7 +11810,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C53" s="32">
         <v>45971</v>
       </c>
@@ -11821,7 +11824,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C54" s="33">
         <v>45972</v>
       </c>
@@ -11835,7 +11838,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C55" s="32">
         <v>45974</v>
       </c>
@@ -11849,7 +11852,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C56" s="33">
         <v>45974</v>
       </c>
@@ -11863,7 +11866,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="57" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C57" s="32">
         <v>45974</v>
       </c>
@@ -11877,7 +11880,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C58" s="33">
         <v>45975</v>
       </c>
@@ -11891,7 +11894,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C59" s="32">
         <v>45976</v>
       </c>
@@ -11905,7 +11908,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C60" s="33">
         <v>45976</v>
       </c>
@@ -11919,7 +11922,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C61" s="32">
         <v>45977</v>
       </c>
@@ -11933,7 +11936,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C62" s="33">
         <v>45977</v>
       </c>
@@ -11947,7 +11950,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="63" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C63" s="32">
         <v>45978</v>
       </c>
@@ -11961,7 +11964,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="64" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C64" s="33">
         <v>45980</v>
       </c>
@@ -11975,7 +11978,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="65" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C65" s="32">
         <v>45981</v>
       </c>
@@ -11989,7 +11992,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="66" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C66" s="33">
         <v>45981</v>
       </c>
@@ -12003,7 +12006,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="67" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C67" s="32">
         <v>45982</v>
       </c>
@@ -12017,7 +12020,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C68" s="33">
         <v>45983</v>
       </c>
@@ -12031,7 +12034,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="69" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C69" s="32">
         <v>45983</v>
       </c>
@@ -12045,7 +12048,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="70" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C70" s="33">
         <v>45984</v>
       </c>
@@ -12059,7 +12062,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="71" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C71" s="32">
         <v>45984</v>
       </c>
@@ -12073,7 +12076,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="72" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C72" s="33">
         <v>45984</v>
       </c>
@@ -12087,7 +12090,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="73" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C73" s="32">
         <v>45984</v>
       </c>
@@ -12101,7 +12104,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="74" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C74" s="33">
         <v>45984</v>
       </c>
@@ -12115,5557 +12118,5565 @@
         <v>97</v>
       </c>
     </row>
-    <row r="75" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C75" s="24"/>
-      <c r="D75" s="22"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-    </row>
-    <row r="76" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C75" s="32">
+        <v>45985</v>
+      </c>
+      <c r="D75" s="22">
+        <v>45</v>
+      </c>
+      <c r="E75" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F75" s="22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="76" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C76" s="25"/>
       <c r="D76" s="23"/>
       <c r="E76" s="23"/>
       <c r="F76" s="23"/>
     </row>
-    <row r="77" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C77" s="24"/>
       <c r="D77" s="22"/>
       <c r="E77" s="22"/>
       <c r="F77" s="22"/>
     </row>
-    <row r="78" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C78" s="25"/>
       <c r="D78" s="23"/>
       <c r="E78" s="23"/>
       <c r="F78" s="23"/>
     </row>
-    <row r="79" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C79" s="24"/>
       <c r="D79" s="22"/>
       <c r="E79" s="22"/>
       <c r="F79" s="22"/>
     </row>
-    <row r="80" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C80" s="25"/>
       <c r="D80" s="23"/>
       <c r="E80" s="23"/>
       <c r="F80" s="23"/>
     </row>
-    <row r="81" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C81" s="24"/>
       <c r="D81" s="22"/>
       <c r="E81" s="22"/>
       <c r="F81" s="22"/>
     </row>
-    <row r="82" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C82" s="25"/>
       <c r="D82" s="23"/>
       <c r="E82" s="23"/>
       <c r="F82" s="23"/>
     </row>
-    <row r="83" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C83" s="24"/>
       <c r="D83" s="22"/>
       <c r="E83" s="22"/>
       <c r="F83" s="22"/>
     </row>
-    <row r="84" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C84" s="25"/>
       <c r="D84" s="23"/>
       <c r="E84" s="23"/>
       <c r="F84" s="23"/>
     </row>
-    <row r="85" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C85" s="24"/>
       <c r="D85" s="22"/>
       <c r="E85" s="22"/>
       <c r="F85" s="22"/>
     </row>
-    <row r="86" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C86" s="25"/>
       <c r="D86" s="23"/>
       <c r="E86" s="23"/>
       <c r="F86" s="23"/>
     </row>
-    <row r="87" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C87" s="24"/>
       <c r="D87" s="22"/>
       <c r="E87" s="22"/>
       <c r="F87" s="22"/>
     </row>
-    <row r="88" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C88" s="25"/>
       <c r="D88" s="23"/>
       <c r="E88" s="23"/>
       <c r="F88" s="23"/>
     </row>
-    <row r="89" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C89" s="24"/>
       <c r="D89" s="22"/>
       <c r="E89" s="22"/>
       <c r="F89" s="22"/>
     </row>
-    <row r="90" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C90" s="25"/>
       <c r="D90" s="23"/>
       <c r="E90" s="23"/>
       <c r="F90" s="23"/>
     </row>
-    <row r="91" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C91" s="24"/>
       <c r="D91" s="22"/>
       <c r="E91" s="22"/>
       <c r="F91" s="22"/>
     </row>
-    <row r="92" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C92" s="25"/>
       <c r="D92" s="23"/>
       <c r="E92" s="23"/>
       <c r="F92" s="23"/>
     </row>
-    <row r="93" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C93" s="24"/>
       <c r="D93" s="22"/>
       <c r="E93" s="22"/>
       <c r="F93" s="22"/>
     </row>
-    <row r="94" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C94" s="25"/>
       <c r="D94" s="23"/>
       <c r="E94" s="23"/>
       <c r="F94" s="23"/>
     </row>
-    <row r="95" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C95" s="24"/>
       <c r="D95" s="22"/>
       <c r="E95" s="22"/>
       <c r="F95" s="22"/>
     </row>
-    <row r="96" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C96" s="25"/>
       <c r="D96" s="23"/>
       <c r="E96" s="23"/>
       <c r="F96" s="23"/>
     </row>
-    <row r="97" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C97" s="24"/>
       <c r="D97" s="22"/>
       <c r="E97" s="22"/>
       <c r="F97" s="22"/>
     </row>
-    <row r="98" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C98" s="25"/>
       <c r="D98" s="23"/>
       <c r="E98" s="23"/>
       <c r="F98" s="23"/>
     </row>
-    <row r="99" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C99" s="24"/>
       <c r="D99" s="22"/>
       <c r="E99" s="22"/>
       <c r="F99" s="22"/>
     </row>
-    <row r="100" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C100" s="25"/>
       <c r="D100" s="23"/>
       <c r="E100" s="23"/>
       <c r="F100" s="23"/>
     </row>
-    <row r="101" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C101" s="24"/>
       <c r="D101" s="22"/>
       <c r="E101" s="22"/>
       <c r="F101" s="22"/>
     </row>
-    <row r="102" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C102" s="25"/>
       <c r="D102" s="23"/>
       <c r="E102" s="23"/>
       <c r="F102" s="23"/>
     </row>
-    <row r="103" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C103" s="24"/>
       <c r="D103" s="22"/>
       <c r="E103" s="22"/>
       <c r="F103" s="22"/>
     </row>
-    <row r="104" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C104" s="25"/>
       <c r="D104" s="23"/>
       <c r="E104" s="23"/>
       <c r="F104" s="23"/>
     </row>
-    <row r="105" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C105" s="24"/>
       <c r="D105" s="22"/>
       <c r="E105" s="22"/>
       <c r="F105" s="22"/>
     </row>
-    <row r="106" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C106" s="25"/>
       <c r="D106" s="23"/>
       <c r="E106" s="23"/>
       <c r="F106" s="23"/>
     </row>
-    <row r="107" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C107" s="24"/>
       <c r="D107" s="22"/>
       <c r="E107" s="22"/>
       <c r="F107" s="22"/>
     </row>
-    <row r="108" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C108" s="25"/>
       <c r="D108" s="23"/>
       <c r="E108" s="23"/>
       <c r="F108" s="23"/>
     </row>
-    <row r="109" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C109" s="24"/>
       <c r="D109" s="22"/>
       <c r="E109" s="22"/>
       <c r="F109" s="22"/>
     </row>
-    <row r="110" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C110" s="25"/>
       <c r="D110" s="23"/>
       <c r="E110" s="23"/>
       <c r="F110" s="23"/>
     </row>
-    <row r="111" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C111" s="24"/>
       <c r="D111" s="22"/>
       <c r="E111" s="22"/>
       <c r="F111" s="22"/>
     </row>
-    <row r="112" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C112" s="25"/>
       <c r="D112" s="23"/>
       <c r="E112" s="23"/>
       <c r="F112" s="23"/>
     </row>
-    <row r="113" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C113" s="24"/>
       <c r="D113" s="22"/>
       <c r="E113" s="22"/>
       <c r="F113" s="22"/>
     </row>
-    <row r="114" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C114" s="25"/>
       <c r="D114" s="23"/>
       <c r="E114" s="23"/>
       <c r="F114" s="23"/>
     </row>
-    <row r="115" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C115" s="24"/>
       <c r="D115" s="22"/>
       <c r="E115" s="22"/>
       <c r="F115" s="22"/>
     </row>
-    <row r="116" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C116" s="25"/>
       <c r="D116" s="23"/>
       <c r="E116" s="23"/>
       <c r="F116" s="23"/>
     </row>
-    <row r="117" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C117" s="24"/>
       <c r="D117" s="22"/>
       <c r="E117" s="22"/>
       <c r="F117" s="22"/>
     </row>
-    <row r="118" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C118" s="25"/>
       <c r="D118" s="23"/>
       <c r="E118" s="23"/>
       <c r="F118" s="23"/>
     </row>
-    <row r="119" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C119" s="24"/>
       <c r="D119" s="22"/>
       <c r="E119" s="22"/>
       <c r="F119" s="22"/>
     </row>
-    <row r="120" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C120" s="25"/>
       <c r="D120" s="23"/>
       <c r="E120" s="23"/>
       <c r="F120" s="23"/>
     </row>
-    <row r="121" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C121" s="24"/>
       <c r="D121" s="22"/>
       <c r="E121" s="22"/>
       <c r="F121" s="22"/>
     </row>
-    <row r="122" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C122" s="25"/>
       <c r="D122" s="23"/>
       <c r="E122" s="23"/>
       <c r="F122" s="23"/>
     </row>
-    <row r="123" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C123" s="24"/>
       <c r="D123" s="22"/>
       <c r="E123" s="22"/>
       <c r="F123" s="22"/>
     </row>
-    <row r="124" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C124" s="25"/>
       <c r="D124" s="23"/>
       <c r="E124" s="23"/>
       <c r="F124" s="23"/>
     </row>
-    <row r="125" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C125" s="24"/>
       <c r="D125" s="22"/>
       <c r="E125" s="22"/>
       <c r="F125" s="22"/>
     </row>
-    <row r="126" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C126" s="25"/>
       <c r="D126" s="23"/>
       <c r="E126" s="23"/>
       <c r="F126" s="23"/>
     </row>
-    <row r="127" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C127" s="24"/>
       <c r="D127" s="22"/>
       <c r="E127" s="22"/>
       <c r="F127" s="22"/>
     </row>
-    <row r="128" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C128" s="25"/>
       <c r="D128" s="23"/>
       <c r="E128" s="23"/>
       <c r="F128" s="23"/>
     </row>
-    <row r="129" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C129" s="24"/>
       <c r="D129" s="22"/>
       <c r="E129" s="22"/>
       <c r="F129" s="22"/>
     </row>
-    <row r="130" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C130" s="25"/>
       <c r="D130" s="23"/>
       <c r="E130" s="23"/>
       <c r="F130" s="23"/>
     </row>
-    <row r="131" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C131" s="24"/>
       <c r="D131" s="22"/>
       <c r="E131" s="22"/>
       <c r="F131" s="22"/>
     </row>
-    <row r="132" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C132" s="25"/>
       <c r="D132" s="23"/>
       <c r="E132" s="23"/>
       <c r="F132" s="23"/>
     </row>
-    <row r="133" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C133" s="24"/>
       <c r="D133" s="22"/>
       <c r="E133" s="22"/>
       <c r="F133" s="22"/>
     </row>
-    <row r="134" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C134" s="25"/>
       <c r="D134" s="23"/>
       <c r="E134" s="23"/>
       <c r="F134" s="23"/>
     </row>
-    <row r="135" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C135" s="24"/>
       <c r="D135" s="22"/>
       <c r="E135" s="22"/>
       <c r="F135" s="22"/>
     </row>
-    <row r="136" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C136" s="25"/>
       <c r="D136" s="23"/>
       <c r="E136" s="23"/>
       <c r="F136" s="23"/>
     </row>
-    <row r="137" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C137" s="24"/>
       <c r="D137" s="22"/>
       <c r="E137" s="22"/>
       <c r="F137" s="22"/>
     </row>
-    <row r="138" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C138" s="25"/>
       <c r="D138" s="23"/>
       <c r="E138" s="23"/>
       <c r="F138" s="23"/>
     </row>
-    <row r="139" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C139" s="24"/>
       <c r="D139" s="22"/>
       <c r="E139" s="22"/>
       <c r="F139" s="22"/>
     </row>
-    <row r="140" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C140" s="25"/>
       <c r="D140" s="23"/>
       <c r="E140" s="23"/>
       <c r="F140" s="23"/>
     </row>
-    <row r="141" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C141" s="24"/>
       <c r="D141" s="22"/>
       <c r="E141" s="22"/>
       <c r="F141" s="22"/>
     </row>
-    <row r="142" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C142" s="25"/>
       <c r="D142" s="23"/>
       <c r="E142" s="23"/>
       <c r="F142" s="23"/>
     </row>
-    <row r="143" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C143" s="24"/>
       <c r="D143" s="22"/>
       <c r="E143" s="22"/>
       <c r="F143" s="22"/>
     </row>
-    <row r="144" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C144" s="25"/>
       <c r="D144" s="23"/>
       <c r="E144" s="23"/>
       <c r="F144" s="23"/>
     </row>
-    <row r="145" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C145" s="24"/>
       <c r="D145" s="22"/>
       <c r="E145" s="22"/>
       <c r="F145" s="22"/>
     </row>
-    <row r="146" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C146" s="25"/>
       <c r="D146" s="23"/>
       <c r="E146" s="23"/>
       <c r="F146" s="23"/>
     </row>
-    <row r="147" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C147" s="24"/>
       <c r="D147" s="22"/>
       <c r="E147" s="22"/>
       <c r="F147" s="22"/>
     </row>
-    <row r="148" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C148" s="25"/>
       <c r="D148" s="23"/>
       <c r="E148" s="23"/>
       <c r="F148" s="23"/>
     </row>
-    <row r="149" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C149" s="24"/>
       <c r="D149" s="22"/>
       <c r="E149" s="22"/>
       <c r="F149" s="22"/>
     </row>
-    <row r="150" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C150" s="25"/>
       <c r="D150" s="23"/>
       <c r="E150" s="23"/>
       <c r="F150" s="23"/>
     </row>
-    <row r="151" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C151" s="24"/>
       <c r="D151" s="22"/>
       <c r="E151" s="22"/>
       <c r="F151" s="22"/>
     </row>
-    <row r="152" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C152" s="25"/>
       <c r="D152" s="23"/>
       <c r="E152" s="23"/>
       <c r="F152" s="23"/>
     </row>
-    <row r="153" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C153" s="24"/>
       <c r="D153" s="22"/>
       <c r="E153" s="22"/>
       <c r="F153" s="22"/>
     </row>
-    <row r="154" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C154" s="25"/>
       <c r="D154" s="23"/>
       <c r="E154" s="23"/>
       <c r="F154" s="23"/>
     </row>
-    <row r="155" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C155" s="24"/>
       <c r="D155" s="22"/>
       <c r="E155" s="22"/>
       <c r="F155" s="22"/>
     </row>
-    <row r="156" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C156" s="25"/>
       <c r="D156" s="23"/>
       <c r="E156" s="23"/>
       <c r="F156" s="23"/>
     </row>
-    <row r="157" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C157" s="24"/>
       <c r="D157" s="22"/>
       <c r="E157" s="22"/>
       <c r="F157" s="22"/>
     </row>
-    <row r="158" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C158" s="25"/>
       <c r="D158" s="23"/>
       <c r="E158" s="23"/>
       <c r="F158" s="23"/>
     </row>
-    <row r="159" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C159" s="24"/>
       <c r="D159" s="22"/>
       <c r="E159" s="22"/>
       <c r="F159" s="22"/>
     </row>
-    <row r="160" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C160" s="25"/>
       <c r="D160" s="23"/>
       <c r="E160" s="23"/>
       <c r="F160" s="23"/>
     </row>
-    <row r="161" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C161" s="24"/>
       <c r="D161" s="22"/>
       <c r="E161" s="22"/>
       <c r="F161" s="22"/>
     </row>
-    <row r="162" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C162" s="25"/>
       <c r="D162" s="23"/>
       <c r="E162" s="23"/>
       <c r="F162" s="23"/>
     </row>
-    <row r="163" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C163" s="24"/>
       <c r="D163" s="22"/>
       <c r="E163" s="22"/>
       <c r="F163" s="22"/>
     </row>
-    <row r="164" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C164" s="25"/>
       <c r="D164" s="23"/>
       <c r="E164" s="23"/>
       <c r="F164" s="23"/>
     </row>
-    <row r="165" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C165" s="24"/>
       <c r="D165" s="22"/>
       <c r="E165" s="22"/>
       <c r="F165" s="22"/>
     </row>
-    <row r="166" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C166" s="25"/>
       <c r="D166" s="23"/>
       <c r="E166" s="23"/>
       <c r="F166" s="23"/>
     </row>
-    <row r="167" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C167" s="24"/>
       <c r="D167" s="22"/>
       <c r="E167" s="22"/>
       <c r="F167" s="22"/>
     </row>
-    <row r="168" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C168" s="25"/>
       <c r="D168" s="23"/>
       <c r="E168" s="23"/>
       <c r="F168" s="23"/>
     </row>
-    <row r="169" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C169" s="24"/>
       <c r="D169" s="22"/>
       <c r="E169" s="22"/>
       <c r="F169" s="22"/>
     </row>
-    <row r="170" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C170" s="25"/>
       <c r="D170" s="23"/>
       <c r="E170" s="23"/>
       <c r="F170" s="23"/>
     </row>
-    <row r="171" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C171" s="24"/>
       <c r="D171" s="22"/>
       <c r="E171" s="22"/>
       <c r="F171" s="22"/>
     </row>
-    <row r="172" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C172" s="25"/>
       <c r="D172" s="23"/>
       <c r="E172" s="23"/>
       <c r="F172" s="23"/>
     </row>
-    <row r="173" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C173" s="24"/>
       <c r="D173" s="22"/>
       <c r="E173" s="22"/>
       <c r="F173" s="22"/>
     </row>
-    <row r="174" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C174" s="25"/>
       <c r="D174" s="23"/>
       <c r="E174" s="23"/>
       <c r="F174" s="23"/>
     </row>
-    <row r="175" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C175" s="24"/>
       <c r="D175" s="22"/>
       <c r="E175" s="22"/>
       <c r="F175" s="22"/>
     </row>
-    <row r="176" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C176" s="25"/>
       <c r="D176" s="23"/>
       <c r="E176" s="23"/>
       <c r="F176" s="23"/>
     </row>
-    <row r="177" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C177" s="24"/>
       <c r="D177" s="22"/>
       <c r="E177" s="22"/>
       <c r="F177" s="22"/>
     </row>
-    <row r="178" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C178" s="25"/>
       <c r="D178" s="23"/>
       <c r="E178" s="23"/>
       <c r="F178" s="23"/>
     </row>
-    <row r="179" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C179" s="24"/>
       <c r="D179" s="22"/>
       <c r="E179" s="22"/>
       <c r="F179" s="22"/>
     </row>
-    <row r="180" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C180" s="25"/>
       <c r="D180" s="23"/>
       <c r="E180" s="23"/>
       <c r="F180" s="23"/>
     </row>
-    <row r="181" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C181" s="24"/>
       <c r="D181" s="22"/>
       <c r="E181" s="22"/>
       <c r="F181" s="22"/>
     </row>
-    <row r="182" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C182" s="25"/>
       <c r="D182" s="23"/>
       <c r="E182" s="23"/>
       <c r="F182" s="23"/>
     </row>
-    <row r="183" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C183" s="24"/>
       <c r="D183" s="22"/>
       <c r="E183" s="22"/>
       <c r="F183" s="22"/>
     </row>
-    <row r="184" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C184" s="25"/>
       <c r="D184" s="23"/>
       <c r="E184" s="23"/>
       <c r="F184" s="23"/>
     </row>
-    <row r="185" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C185" s="24"/>
       <c r="D185" s="22"/>
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
     </row>
-    <row r="186" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C186" s="25"/>
       <c r="D186" s="23"/>
       <c r="E186" s="23"/>
       <c r="F186" s="23"/>
     </row>
-    <row r="187" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C187" s="24"/>
       <c r="D187" s="22"/>
       <c r="E187" s="22"/>
       <c r="F187" s="22"/>
     </row>
-    <row r="188" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C188" s="25"/>
       <c r="D188" s="23"/>
       <c r="E188" s="23"/>
       <c r="F188" s="23"/>
     </row>
-    <row r="189" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C189" s="24"/>
       <c r="D189" s="22"/>
       <c r="E189" s="22"/>
       <c r="F189" s="22"/>
     </row>
-    <row r="190" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C190" s="25"/>
       <c r="D190" s="23"/>
       <c r="E190" s="23"/>
       <c r="F190" s="23"/>
     </row>
-    <row r="191" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C191" s="24"/>
       <c r="D191" s="22"/>
       <c r="E191" s="22"/>
       <c r="F191" s="22"/>
     </row>
-    <row r="192" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C192" s="25"/>
       <c r="D192" s="23"/>
       <c r="E192" s="23"/>
       <c r="F192" s="23"/>
     </row>
-    <row r="193" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C193" s="24"/>
       <c r="D193" s="22"/>
       <c r="E193" s="22"/>
       <c r="F193" s="22"/>
     </row>
-    <row r="194" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C194" s="25"/>
       <c r="D194" s="23"/>
       <c r="E194" s="23"/>
       <c r="F194" s="23"/>
     </row>
-    <row r="195" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C195" s="24"/>
       <c r="D195" s="22"/>
       <c r="E195" s="22"/>
       <c r="F195" s="22"/>
     </row>
-    <row r="196" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C196" s="25"/>
       <c r="D196" s="23"/>
       <c r="E196" s="23"/>
       <c r="F196" s="23"/>
     </row>
-    <row r="197" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C197" s="24"/>
       <c r="D197" s="22"/>
       <c r="E197" s="22"/>
       <c r="F197" s="22"/>
     </row>
-    <row r="198" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C198" s="25"/>
       <c r="D198" s="23"/>
       <c r="E198" s="23"/>
       <c r="F198" s="23"/>
     </row>
-    <row r="199" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C199" s="24"/>
       <c r="D199" s="22"/>
       <c r="E199" s="22"/>
       <c r="F199" s="22"/>
     </row>
-    <row r="200" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C200" s="25"/>
       <c r="D200" s="23"/>
       <c r="E200" s="23"/>
       <c r="F200" s="23"/>
     </row>
-    <row r="201" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C201" s="24"/>
       <c r="D201" s="22"/>
       <c r="E201" s="22"/>
       <c r="F201" s="22"/>
     </row>
-    <row r="202" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C202" s="25"/>
       <c r="D202" s="23"/>
       <c r="E202" s="23"/>
       <c r="F202" s="23"/>
     </row>
-    <row r="203" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C203" s="24"/>
       <c r="D203" s="22"/>
       <c r="E203" s="22"/>
       <c r="F203" s="22"/>
     </row>
-    <row r="204" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C204" s="25"/>
       <c r="D204" s="23"/>
       <c r="E204" s="23"/>
       <c r="F204" s="23"/>
     </row>
-    <row r="205" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C205" s="24"/>
       <c r="D205" s="22"/>
       <c r="E205" s="22"/>
       <c r="F205" s="22"/>
     </row>
-    <row r="206" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C206" s="25"/>
       <c r="D206" s="23"/>
       <c r="E206" s="23"/>
       <c r="F206" s="23"/>
     </row>
-    <row r="207" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C207" s="24"/>
       <c r="D207" s="22"/>
       <c r="E207" s="22"/>
       <c r="F207" s="22"/>
     </row>
-    <row r="208" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C208" s="25"/>
       <c r="D208" s="23"/>
       <c r="E208" s="23"/>
       <c r="F208" s="23"/>
     </row>
-    <row r="209" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C209" s="24"/>
       <c r="D209" s="22"/>
       <c r="E209" s="22"/>
       <c r="F209" s="22"/>
     </row>
-    <row r="210" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C210" s="25"/>
       <c r="D210" s="23"/>
       <c r="E210" s="23"/>
       <c r="F210" s="23"/>
     </row>
-    <row r="211" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C211" s="24"/>
       <c r="D211" s="22"/>
       <c r="E211" s="22"/>
       <c r="F211" s="22"/>
     </row>
-    <row r="212" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C212" s="25"/>
       <c r="D212" s="23"/>
       <c r="E212" s="23"/>
       <c r="F212" s="23"/>
     </row>
-    <row r="213" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C213" s="24"/>
       <c r="D213" s="22"/>
       <c r="E213" s="22"/>
       <c r="F213" s="22"/>
     </row>
-    <row r="214" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C214" s="25"/>
       <c r="D214" s="23"/>
       <c r="E214" s="23"/>
       <c r="F214" s="23"/>
     </row>
-    <row r="215" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C215" s="24"/>
       <c r="D215" s="22"/>
       <c r="E215" s="22"/>
       <c r="F215" s="22"/>
     </row>
-    <row r="216" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C216" s="25"/>
       <c r="D216" s="23"/>
       <c r="E216" s="23"/>
       <c r="F216" s="23"/>
     </row>
-    <row r="217" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C217" s="24"/>
       <c r="D217" s="22"/>
       <c r="E217" s="22"/>
       <c r="F217" s="22"/>
     </row>
-    <row r="218" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C218" s="25"/>
       <c r="D218" s="23"/>
       <c r="E218" s="23"/>
       <c r="F218" s="23"/>
     </row>
-    <row r="219" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C219" s="24"/>
       <c r="D219" s="22"/>
       <c r="E219" s="22"/>
       <c r="F219" s="22"/>
     </row>
-    <row r="220" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C220" s="25"/>
       <c r="D220" s="23"/>
       <c r="E220" s="23"/>
       <c r="F220" s="23"/>
     </row>
-    <row r="221" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C221" s="24"/>
       <c r="D221" s="22"/>
       <c r="E221" s="22"/>
       <c r="F221" s="22"/>
     </row>
-    <row r="222" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C222" s="25"/>
       <c r="D222" s="23"/>
       <c r="E222" s="23"/>
       <c r="F222" s="23"/>
     </row>
-    <row r="223" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C223" s="24"/>
       <c r="D223" s="22"/>
       <c r="E223" s="22"/>
       <c r="F223" s="22"/>
     </row>
-    <row r="224" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C224" s="25"/>
       <c r="D224" s="23"/>
       <c r="E224" s="23"/>
       <c r="F224" s="23"/>
     </row>
-    <row r="225" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C225" s="24"/>
       <c r="D225" s="22"/>
       <c r="E225" s="22"/>
       <c r="F225" s="22"/>
     </row>
-    <row r="226" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C226" s="25"/>
       <c r="D226" s="23"/>
       <c r="E226" s="23"/>
       <c r="F226" s="23"/>
     </row>
-    <row r="227" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C227" s="24"/>
       <c r="D227" s="22"/>
       <c r="E227" s="22"/>
       <c r="F227" s="22"/>
     </row>
-    <row r="228" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C228" s="25"/>
       <c r="D228" s="23"/>
       <c r="E228" s="23"/>
       <c r="F228" s="23"/>
     </row>
-    <row r="229" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C229" s="24"/>
       <c r="D229" s="22"/>
       <c r="E229" s="22"/>
       <c r="F229" s="22"/>
     </row>
-    <row r="230" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C230" s="25"/>
       <c r="D230" s="23"/>
       <c r="E230" s="23"/>
       <c r="F230" s="23"/>
     </row>
-    <row r="231" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C231" s="24"/>
       <c r="D231" s="22"/>
       <c r="E231" s="22"/>
       <c r="F231" s="22"/>
     </row>
-    <row r="232" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C232" s="25"/>
       <c r="D232" s="23"/>
       <c r="E232" s="23"/>
       <c r="F232" s="23"/>
     </row>
-    <row r="233" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C233" s="24"/>
       <c r="D233" s="22"/>
       <c r="E233" s="22"/>
       <c r="F233" s="22"/>
     </row>
-    <row r="234" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C234" s="25"/>
       <c r="D234" s="23"/>
       <c r="E234" s="23"/>
       <c r="F234" s="23"/>
     </row>
-    <row r="235" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C235" s="24"/>
       <c r="D235" s="22"/>
       <c r="E235" s="22"/>
       <c r="F235" s="22"/>
     </row>
-    <row r="236" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C236" s="25"/>
       <c r="D236" s="23"/>
       <c r="E236" s="23"/>
       <c r="F236" s="23"/>
     </row>
-    <row r="237" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C237" s="24"/>
       <c r="D237" s="22"/>
       <c r="E237" s="22"/>
       <c r="F237" s="22"/>
     </row>
-    <row r="238" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C238" s="25"/>
       <c r="D238" s="23"/>
       <c r="E238" s="23"/>
       <c r="F238" s="23"/>
     </row>
-    <row r="239" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C239" s="24"/>
       <c r="D239" s="22"/>
       <c r="E239" s="22"/>
       <c r="F239" s="22"/>
     </row>
-    <row r="240" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C240" s="25"/>
       <c r="D240" s="23"/>
       <c r="E240" s="23"/>
       <c r="F240" s="23"/>
     </row>
-    <row r="241" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C241" s="24"/>
       <c r="D241" s="22"/>
       <c r="E241" s="22"/>
       <c r="F241" s="22"/>
     </row>
-    <row r="242" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C242" s="25"/>
       <c r="D242" s="23"/>
       <c r="E242" s="23"/>
       <c r="F242" s="23"/>
     </row>
-    <row r="243" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C243" s="24"/>
       <c r="D243" s="22"/>
       <c r="E243" s="22"/>
       <c r="F243" s="22"/>
     </row>
-    <row r="244" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C244" s="25"/>
       <c r="D244" s="23"/>
       <c r="E244" s="23"/>
       <c r="F244" s="23"/>
     </row>
-    <row r="245" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C245" s="24"/>
       <c r="D245" s="22"/>
       <c r="E245" s="22"/>
       <c r="F245" s="22"/>
     </row>
-    <row r="246" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C246" s="25"/>
       <c r="D246" s="23"/>
       <c r="E246" s="23"/>
       <c r="F246" s="23"/>
     </row>
-    <row r="247" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C247" s="24"/>
       <c r="D247" s="22"/>
       <c r="E247" s="22"/>
       <c r="F247" s="22"/>
     </row>
-    <row r="248" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C248" s="25"/>
       <c r="D248" s="23"/>
       <c r="E248" s="23"/>
       <c r="F248" s="23"/>
     </row>
-    <row r="249" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C249" s="24"/>
       <c r="D249" s="22"/>
       <c r="E249" s="22"/>
       <c r="F249" s="22"/>
     </row>
-    <row r="250" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C250" s="25"/>
       <c r="D250" s="23"/>
       <c r="E250" s="23"/>
       <c r="F250" s="23"/>
     </row>
-    <row r="251" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C251" s="24"/>
       <c r="D251" s="22"/>
       <c r="E251" s="22"/>
       <c r="F251" s="22"/>
     </row>
-    <row r="252" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C252" s="25"/>
       <c r="D252" s="23"/>
       <c r="E252" s="23"/>
       <c r="F252" s="23"/>
     </row>
-    <row r="253" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C253" s="24"/>
       <c r="D253" s="22"/>
       <c r="E253" s="22"/>
       <c r="F253" s="22"/>
     </row>
-    <row r="254" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C254" s="25"/>
       <c r="D254" s="23"/>
       <c r="E254" s="23"/>
       <c r="F254" s="23"/>
     </row>
-    <row r="255" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C255" s="24"/>
       <c r="D255" s="22"/>
       <c r="E255" s="22"/>
       <c r="F255" s="22"/>
     </row>
-    <row r="256" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C256" s="25"/>
       <c r="D256" s="23"/>
       <c r="E256" s="23"/>
       <c r="F256" s="23"/>
     </row>
-    <row r="257" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C257" s="24"/>
       <c r="D257" s="22"/>
       <c r="E257" s="22"/>
       <c r="F257" s="22"/>
     </row>
-    <row r="258" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C258" s="25"/>
       <c r="D258" s="23"/>
       <c r="E258" s="23"/>
       <c r="F258" s="23"/>
     </row>
-    <row r="259" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C259" s="24"/>
       <c r="D259" s="22"/>
       <c r="E259" s="22"/>
       <c r="F259" s="22"/>
     </row>
-    <row r="260" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C260" s="25"/>
       <c r="D260" s="23"/>
       <c r="E260" s="23"/>
       <c r="F260" s="23"/>
     </row>
-    <row r="261" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C261" s="24"/>
       <c r="D261" s="22"/>
       <c r="E261" s="22"/>
       <c r="F261" s="22"/>
     </row>
-    <row r="262" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C262" s="25"/>
       <c r="D262" s="23"/>
       <c r="E262" s="23"/>
       <c r="F262" s="23"/>
     </row>
-    <row r="263" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C263" s="24"/>
       <c r="D263" s="22"/>
       <c r="E263" s="22"/>
       <c r="F263" s="22"/>
     </row>
-    <row r="264" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C264" s="25"/>
       <c r="D264" s="23"/>
       <c r="E264" s="23"/>
       <c r="F264" s="23"/>
     </row>
-    <row r="265" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C265" s="24"/>
       <c r="D265" s="22"/>
       <c r="E265" s="22"/>
       <c r="F265" s="22"/>
     </row>
-    <row r="266" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C266" s="25"/>
       <c r="D266" s="23"/>
       <c r="E266" s="23"/>
       <c r="F266" s="23"/>
     </row>
-    <row r="267" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C267" s="24"/>
       <c r="D267" s="22"/>
       <c r="E267" s="22"/>
       <c r="F267" s="22"/>
     </row>
-    <row r="268" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C268" s="25"/>
       <c r="D268" s="23"/>
       <c r="E268" s="23"/>
       <c r="F268" s="23"/>
     </row>
-    <row r="269" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C269" s="24"/>
       <c r="D269" s="22"/>
       <c r="E269" s="22"/>
       <c r="F269" s="22"/>
     </row>
-    <row r="270" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C270" s="25"/>
       <c r="D270" s="23"/>
       <c r="E270" s="23"/>
       <c r="F270" s="23"/>
     </row>
-    <row r="271" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C271" s="24"/>
       <c r="D271" s="22"/>
       <c r="E271" s="22"/>
       <c r="F271" s="22"/>
     </row>
-    <row r="272" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C272" s="25"/>
       <c r="D272" s="23"/>
       <c r="E272" s="23"/>
       <c r="F272" s="23"/>
     </row>
-    <row r="273" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C273" s="24"/>
       <c r="D273" s="22"/>
       <c r="E273" s="22"/>
       <c r="F273" s="22"/>
     </row>
-    <row r="274" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C274" s="25"/>
       <c r="D274" s="23"/>
       <c r="E274" s="23"/>
       <c r="F274" s="23"/>
     </row>
-    <row r="275" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C275" s="24"/>
       <c r="D275" s="22"/>
       <c r="E275" s="22"/>
       <c r="F275" s="22"/>
     </row>
-    <row r="276" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C276" s="25"/>
       <c r="D276" s="23"/>
       <c r="E276" s="23"/>
       <c r="F276" s="23"/>
     </row>
-    <row r="277" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C277" s="24"/>
       <c r="D277" s="22"/>
       <c r="E277" s="22"/>
       <c r="F277" s="22"/>
     </row>
-    <row r="278" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C278" s="25"/>
       <c r="D278" s="23"/>
       <c r="E278" s="23"/>
       <c r="F278" s="23"/>
     </row>
-    <row r="279" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C279" s="24"/>
       <c r="D279" s="22"/>
       <c r="E279" s="22"/>
       <c r="F279" s="22"/>
     </row>
-    <row r="280" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C280" s="25"/>
       <c r="D280" s="23"/>
       <c r="E280" s="23"/>
       <c r="F280" s="23"/>
     </row>
-    <row r="281" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C281" s="24"/>
       <c r="D281" s="22"/>
       <c r="E281" s="22"/>
       <c r="F281" s="22"/>
     </row>
-    <row r="282" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C282" s="25"/>
       <c r="D282" s="23"/>
       <c r="E282" s="23"/>
       <c r="F282" s="23"/>
     </row>
-    <row r="283" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C283" s="24"/>
       <c r="D283" s="22"/>
       <c r="E283" s="22"/>
       <c r="F283" s="22"/>
     </row>
-    <row r="284" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C284" s="25"/>
       <c r="D284" s="23"/>
       <c r="E284" s="23"/>
       <c r="F284" s="23"/>
     </row>
-    <row r="285" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C285" s="24"/>
       <c r="D285" s="22"/>
       <c r="E285" s="22"/>
       <c r="F285" s="22"/>
     </row>
-    <row r="286" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C286" s="25"/>
       <c r="D286" s="23"/>
       <c r="E286" s="23"/>
       <c r="F286" s="23"/>
     </row>
-    <row r="287" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C287" s="24"/>
       <c r="D287" s="22"/>
       <c r="E287" s="22"/>
       <c r="F287" s="22"/>
     </row>
-    <row r="288" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C288" s="25"/>
       <c r="D288" s="23"/>
       <c r="E288" s="23"/>
       <c r="F288" s="23"/>
     </row>
-    <row r="289" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C289" s="24"/>
       <c r="D289" s="22"/>
       <c r="E289" s="22"/>
       <c r="F289" s="22"/>
     </row>
-    <row r="290" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C290" s="25"/>
       <c r="D290" s="23"/>
       <c r="E290" s="23"/>
       <c r="F290" s="23"/>
     </row>
-    <row r="291" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C291" s="24"/>
       <c r="D291" s="22"/>
       <c r="E291" s="22"/>
       <c r="F291" s="22"/>
     </row>
-    <row r="292" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C292" s="25"/>
       <c r="D292" s="23"/>
       <c r="E292" s="23"/>
       <c r="F292" s="23"/>
     </row>
-    <row r="293" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C293" s="24"/>
       <c r="D293" s="22"/>
       <c r="E293" s="22"/>
       <c r="F293" s="22"/>
     </row>
-    <row r="294" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C294" s="25"/>
       <c r="D294" s="23"/>
       <c r="E294" s="23"/>
       <c r="F294" s="23"/>
     </row>
-    <row r="295" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C295" s="24"/>
       <c r="D295" s="22"/>
       <c r="E295" s="22"/>
       <c r="F295" s="22"/>
     </row>
-    <row r="296" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C296" s="25"/>
       <c r="D296" s="23"/>
       <c r="E296" s="23"/>
       <c r="F296" s="23"/>
     </row>
-    <row r="297" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C297" s="24"/>
       <c r="D297" s="22"/>
       <c r="E297" s="22"/>
       <c r="F297" s="22"/>
     </row>
-    <row r="298" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C298" s="25"/>
       <c r="D298" s="23"/>
       <c r="E298" s="23"/>
       <c r="F298" s="23"/>
     </row>
-    <row r="299" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C299" s="24"/>
       <c r="D299" s="22"/>
       <c r="E299" s="22"/>
       <c r="F299" s="22"/>
     </row>
-    <row r="300" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C300" s="25"/>
       <c r="D300" s="23"/>
       <c r="E300" s="23"/>
       <c r="F300" s="23"/>
     </row>
-    <row r="301" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C301" s="24"/>
       <c r="D301" s="22"/>
       <c r="E301" s="22"/>
       <c r="F301" s="22"/>
     </row>
-    <row r="302" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C302" s="25"/>
       <c r="D302" s="23"/>
       <c r="E302" s="23"/>
       <c r="F302" s="23"/>
     </row>
-    <row r="303" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C303" s="24"/>
       <c r="D303" s="22"/>
       <c r="E303" s="22"/>
       <c r="F303" s="22"/>
     </row>
-    <row r="304" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C304" s="25"/>
       <c r="D304" s="23"/>
       <c r="E304" s="23"/>
       <c r="F304" s="23"/>
     </row>
-    <row r="305" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="305" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C305" s="24"/>
       <c r="D305" s="22"/>
       <c r="E305" s="22"/>
       <c r="F305" s="22"/>
     </row>
-    <row r="306" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="306" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C306" s="25"/>
       <c r="D306" s="23"/>
       <c r="E306" s="23"/>
       <c r="F306" s="23"/>
     </row>
-    <row r="307" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="307" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C307" s="24"/>
       <c r="D307" s="22"/>
       <c r="E307" s="22"/>
       <c r="F307" s="22"/>
     </row>
-    <row r="308" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="308" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C308" s="25"/>
       <c r="D308" s="23"/>
       <c r="E308" s="23"/>
       <c r="F308" s="23"/>
     </row>
-    <row r="309" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="309" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C309" s="24"/>
       <c r="D309" s="22"/>
       <c r="E309" s="22"/>
       <c r="F309" s="22"/>
     </row>
-    <row r="310" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="310" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C310" s="25"/>
       <c r="D310" s="23"/>
       <c r="E310" s="23"/>
       <c r="F310" s="23"/>
     </row>
-    <row r="311" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="311" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C311" s="24"/>
       <c r="D311" s="22"/>
       <c r="E311" s="22"/>
       <c r="F311" s="22"/>
     </row>
-    <row r="312" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="312" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C312" s="25"/>
       <c r="D312" s="23"/>
       <c r="E312" s="23"/>
       <c r="F312" s="23"/>
     </row>
-    <row r="313" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="313" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C313" s="24"/>
       <c r="D313" s="22"/>
       <c r="E313" s="22"/>
       <c r="F313" s="22"/>
     </row>
-    <row r="314" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="314" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C314" s="25"/>
       <c r="D314" s="23"/>
       <c r="E314" s="23"/>
       <c r="F314" s="23"/>
     </row>
-    <row r="315" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="315" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C315" s="24"/>
       <c r="D315" s="22"/>
       <c r="E315" s="22"/>
       <c r="F315" s="22"/>
     </row>
-    <row r="316" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="316" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C316" s="25"/>
       <c r="D316" s="23"/>
       <c r="E316" s="23"/>
       <c r="F316" s="23"/>
     </row>
-    <row r="317" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="317" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C317" s="24"/>
       <c r="D317" s="22"/>
       <c r="E317" s="22"/>
       <c r="F317" s="22"/>
     </row>
-    <row r="318" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="318" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C318" s="25"/>
       <c r="D318" s="23"/>
       <c r="E318" s="23"/>
       <c r="F318" s="23"/>
     </row>
-    <row r="319" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="319" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C319" s="24"/>
       <c r="D319" s="22"/>
       <c r="E319" s="22"/>
       <c r="F319" s="22"/>
     </row>
-    <row r="320" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="320" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C320" s="25"/>
       <c r="D320" s="23"/>
       <c r="E320" s="23"/>
       <c r="F320" s="23"/>
     </row>
-    <row r="321" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="321" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C321" s="24"/>
       <c r="D321" s="22"/>
       <c r="E321" s="22"/>
       <c r="F321" s="22"/>
     </row>
-    <row r="322" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="322" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C322" s="25"/>
       <c r="D322" s="23"/>
       <c r="E322" s="23"/>
       <c r="F322" s="23"/>
     </row>
-    <row r="323" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="323" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C323" s="24"/>
       <c r="D323" s="22"/>
       <c r="E323" s="22"/>
       <c r="F323" s="22"/>
     </row>
-    <row r="324" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="324" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C324" s="25"/>
       <c r="D324" s="23"/>
       <c r="E324" s="23"/>
       <c r="F324" s="23"/>
     </row>
-    <row r="325" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="325" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C325" s="24"/>
       <c r="D325" s="22"/>
       <c r="E325" s="22"/>
       <c r="F325" s="22"/>
     </row>
-    <row r="326" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="326" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C326" s="25"/>
       <c r="D326" s="23"/>
       <c r="E326" s="23"/>
       <c r="F326" s="23"/>
     </row>
-    <row r="327" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="327" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C327" s="24"/>
       <c r="D327" s="22"/>
       <c r="E327" s="22"/>
       <c r="F327" s="22"/>
     </row>
-    <row r="328" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="328" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C328" s="25"/>
       <c r="D328" s="23"/>
       <c r="E328" s="23"/>
       <c r="F328" s="23"/>
     </row>
-    <row r="329" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="329" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C329" s="24"/>
       <c r="D329" s="22"/>
       <c r="E329" s="22"/>
       <c r="F329" s="22"/>
     </row>
-    <row r="330" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="330" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C330" s="25"/>
       <c r="D330" s="23"/>
       <c r="E330" s="23"/>
       <c r="F330" s="23"/>
     </row>
-    <row r="331" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="331" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C331" s="24"/>
       <c r="D331" s="22"/>
       <c r="E331" s="22"/>
       <c r="F331" s="22"/>
     </row>
-    <row r="332" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="332" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C332" s="25"/>
       <c r="D332" s="23"/>
       <c r="E332" s="23"/>
       <c r="F332" s="23"/>
     </row>
-    <row r="333" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="333" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C333" s="24"/>
       <c r="D333" s="22"/>
       <c r="E333" s="22"/>
       <c r="F333" s="22"/>
     </row>
-    <row r="334" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="334" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C334" s="25"/>
       <c r="D334" s="23"/>
       <c r="E334" s="23"/>
       <c r="F334" s="23"/>
     </row>
-    <row r="335" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="335" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C335" s="24"/>
       <c r="D335" s="22"/>
       <c r="E335" s="22"/>
       <c r="F335" s="22"/>
     </row>
-    <row r="336" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="336" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C336" s="25"/>
       <c r="D336" s="23"/>
       <c r="E336" s="23"/>
       <c r="F336" s="23"/>
     </row>
-    <row r="337" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="337" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C337" s="24"/>
       <c r="D337" s="22"/>
       <c r="E337" s="22"/>
       <c r="F337" s="22"/>
     </row>
-    <row r="338" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="338" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C338" s="25"/>
       <c r="D338" s="23"/>
       <c r="E338" s="23"/>
       <c r="F338" s="23"/>
     </row>
-    <row r="339" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="339" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C339" s="24"/>
       <c r="D339" s="22"/>
       <c r="E339" s="22"/>
       <c r="F339" s="22"/>
     </row>
-    <row r="340" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="340" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C340" s="25"/>
       <c r="D340" s="23"/>
       <c r="E340" s="23"/>
       <c r="F340" s="23"/>
     </row>
-    <row r="341" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="341" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C341" s="24"/>
       <c r="D341" s="22"/>
       <c r="E341" s="22"/>
       <c r="F341" s="22"/>
     </row>
-    <row r="342" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="342" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C342" s="25"/>
       <c r="D342" s="23"/>
       <c r="E342" s="23"/>
       <c r="F342" s="23"/>
     </row>
-    <row r="343" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="343" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C343" s="24"/>
       <c r="D343" s="22"/>
       <c r="E343" s="22"/>
       <c r="F343" s="22"/>
     </row>
-    <row r="344" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="344" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C344" s="25"/>
       <c r="D344" s="23"/>
       <c r="E344" s="23"/>
       <c r="F344" s="23"/>
     </row>
-    <row r="345" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="345" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C345" s="24"/>
       <c r="D345" s="22"/>
       <c r="E345" s="22"/>
       <c r="F345" s="22"/>
     </row>
-    <row r="346" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="346" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C346" s="25"/>
       <c r="D346" s="23"/>
       <c r="E346" s="23"/>
       <c r="F346" s="23"/>
     </row>
-    <row r="347" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="347" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C347" s="24"/>
       <c r="D347" s="22"/>
       <c r="E347" s="22"/>
       <c r="F347" s="22"/>
     </row>
-    <row r="348" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="348" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C348" s="25"/>
       <c r="D348" s="23"/>
       <c r="E348" s="23"/>
       <c r="F348" s="23"/>
     </row>
-    <row r="349" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="349" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C349" s="24"/>
       <c r="D349" s="22"/>
       <c r="E349" s="22"/>
       <c r="F349" s="22"/>
     </row>
-    <row r="350" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="350" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C350" s="25"/>
       <c r="D350" s="23"/>
       <c r="E350" s="23"/>
       <c r="F350" s="23"/>
     </row>
-    <row r="351" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="351" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C351" s="24"/>
       <c r="D351" s="22"/>
       <c r="E351" s="22"/>
       <c r="F351" s="22"/>
     </row>
-    <row r="352" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="352" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C352" s="25"/>
       <c r="D352" s="23"/>
       <c r="E352" s="23"/>
       <c r="F352" s="23"/>
     </row>
-    <row r="353" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="353" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C353" s="24"/>
       <c r="D353" s="22"/>
       <c r="E353" s="22"/>
       <c r="F353" s="22"/>
     </row>
-    <row r="354" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="354" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C354" s="25"/>
       <c r="D354" s="23"/>
       <c r="E354" s="23"/>
       <c r="F354" s="23"/>
     </row>
-    <row r="355" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="355" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C355" s="24"/>
       <c r="D355" s="22"/>
       <c r="E355" s="22"/>
       <c r="F355" s="22"/>
     </row>
-    <row r="356" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="356" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C356" s="25"/>
       <c r="D356" s="23"/>
       <c r="E356" s="23"/>
       <c r="F356" s="23"/>
     </row>
-    <row r="357" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="357" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C357" s="24"/>
       <c r="D357" s="22"/>
       <c r="E357" s="22"/>
       <c r="F357" s="22"/>
     </row>
-    <row r="358" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="358" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C358" s="25"/>
       <c r="D358" s="23"/>
       <c r="E358" s="23"/>
       <c r="F358" s="23"/>
     </row>
-    <row r="359" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="359" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C359" s="24"/>
       <c r="D359" s="22"/>
       <c r="E359" s="22"/>
       <c r="F359" s="22"/>
     </row>
-    <row r="360" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="360" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C360" s="25"/>
       <c r="D360" s="23"/>
       <c r="E360" s="23"/>
       <c r="F360" s="23"/>
     </row>
-    <row r="361" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="361" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C361" s="24"/>
       <c r="D361" s="22"/>
       <c r="E361" s="22"/>
       <c r="F361" s="22"/>
     </row>
-    <row r="362" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="362" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C362" s="25"/>
       <c r="D362" s="23"/>
       <c r="E362" s="23"/>
       <c r="F362" s="23"/>
     </row>
-    <row r="363" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="363" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C363" s="24"/>
       <c r="D363" s="22"/>
       <c r="E363" s="22"/>
       <c r="F363" s="22"/>
     </row>
-    <row r="364" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="364" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C364" s="25"/>
       <c r="D364" s="23"/>
       <c r="E364" s="23"/>
       <c r="F364" s="23"/>
     </row>
-    <row r="365" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="365" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C365" s="24"/>
       <c r="D365" s="22"/>
       <c r="E365" s="22"/>
       <c r="F365" s="22"/>
     </row>
-    <row r="366" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="366" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C366" s="25"/>
       <c r="D366" s="23"/>
       <c r="E366" s="23"/>
       <c r="F366" s="23"/>
     </row>
-    <row r="367" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="367" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C367" s="24"/>
       <c r="D367" s="22"/>
       <c r="E367" s="22"/>
       <c r="F367" s="22"/>
     </row>
-    <row r="368" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="368" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C368" s="25"/>
       <c r="D368" s="23"/>
       <c r="E368" s="23"/>
       <c r="F368" s="23"/>
     </row>
-    <row r="369" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="369" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C369" s="24"/>
       <c r="D369" s="22"/>
       <c r="E369" s="22"/>
       <c r="F369" s="22"/>
     </row>
-    <row r="370" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="370" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C370" s="25"/>
       <c r="D370" s="23"/>
       <c r="E370" s="23"/>
       <c r="F370" s="23"/>
     </row>
-    <row r="371" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="371" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C371" s="24"/>
       <c r="D371" s="22"/>
       <c r="E371" s="22"/>
       <c r="F371" s="22"/>
     </row>
-    <row r="372" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="372" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C372" s="25"/>
       <c r="D372" s="23"/>
       <c r="E372" s="23"/>
       <c r="F372" s="23"/>
     </row>
-    <row r="373" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="373" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C373" s="24"/>
       <c r="D373" s="22"/>
       <c r="E373" s="22"/>
       <c r="F373" s="22"/>
     </row>
-    <row r="374" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="374" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C374" s="25"/>
       <c r="D374" s="23"/>
       <c r="E374" s="23"/>
       <c r="F374" s="23"/>
     </row>
-    <row r="375" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="375" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C375" s="24"/>
       <c r="D375" s="22"/>
       <c r="E375" s="22"/>
       <c r="F375" s="22"/>
     </row>
-    <row r="376" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="376" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C376" s="25"/>
       <c r="D376" s="23"/>
       <c r="E376" s="23"/>
       <c r="F376" s="23"/>
     </row>
-    <row r="377" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="377" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C377" s="24"/>
       <c r="D377" s="22"/>
       <c r="E377" s="22"/>
       <c r="F377" s="22"/>
     </row>
-    <row r="378" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="378" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C378" s="25"/>
       <c r="D378" s="23"/>
       <c r="E378" s="23"/>
       <c r="F378" s="23"/>
     </row>
-    <row r="379" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="379" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C379" s="24"/>
       <c r="D379" s="22"/>
       <c r="E379" s="22"/>
       <c r="F379" s="22"/>
     </row>
-    <row r="380" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="380" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C380" s="25"/>
       <c r="D380" s="23"/>
       <c r="E380" s="23"/>
       <c r="F380" s="23"/>
     </row>
-    <row r="381" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="381" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C381" s="24"/>
       <c r="D381" s="22"/>
       <c r="E381" s="22"/>
       <c r="F381" s="22"/>
     </row>
-    <row r="382" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="382" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C382" s="25"/>
       <c r="D382" s="23"/>
       <c r="E382" s="23"/>
       <c r="F382" s="23"/>
     </row>
-    <row r="383" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="383" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C383" s="24"/>
       <c r="D383" s="22"/>
       <c r="E383" s="22"/>
       <c r="F383" s="22"/>
     </row>
-    <row r="384" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="384" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C384" s="25"/>
       <c r="D384" s="23"/>
       <c r="E384" s="23"/>
       <c r="F384" s="23"/>
     </row>
-    <row r="385" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="385" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C385" s="24"/>
       <c r="D385" s="22"/>
       <c r="E385" s="22"/>
       <c r="F385" s="22"/>
     </row>
-    <row r="386" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="386" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C386" s="25"/>
       <c r="D386" s="23"/>
       <c r="E386" s="23"/>
       <c r="F386" s="23"/>
     </row>
-    <row r="387" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="387" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C387" s="24"/>
       <c r="D387" s="22"/>
       <c r="E387" s="22"/>
       <c r="F387" s="22"/>
     </row>
-    <row r="388" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="388" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C388" s="25"/>
       <c r="D388" s="23"/>
       <c r="E388" s="23"/>
       <c r="F388" s="23"/>
     </row>
-    <row r="389" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="389" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C389" s="24"/>
       <c r="D389" s="22"/>
       <c r="E389" s="22"/>
       <c r="F389" s="22"/>
     </row>
-    <row r="390" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="390" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C390" s="25"/>
       <c r="D390" s="23"/>
       <c r="E390" s="23"/>
       <c r="F390" s="23"/>
     </row>
-    <row r="391" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="391" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C391" s="24"/>
       <c r="D391" s="22"/>
       <c r="E391" s="22"/>
       <c r="F391" s="22"/>
     </row>
-    <row r="392" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="392" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C392" s="25"/>
       <c r="D392" s="23"/>
       <c r="E392" s="23"/>
       <c r="F392" s="23"/>
     </row>
-    <row r="393" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="393" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C393" s="24"/>
       <c r="D393" s="22"/>
       <c r="E393" s="22"/>
       <c r="F393" s="22"/>
     </row>
-    <row r="394" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="394" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C394" s="25"/>
       <c r="D394" s="23"/>
       <c r="E394" s="23"/>
       <c r="F394" s="23"/>
     </row>
-    <row r="395" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="395" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C395" s="24"/>
       <c r="D395" s="22"/>
       <c r="E395" s="22"/>
       <c r="F395" s="22"/>
     </row>
-    <row r="396" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="396" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C396" s="25"/>
       <c r="D396" s="23"/>
       <c r="E396" s="23"/>
       <c r="F396" s="23"/>
     </row>
-    <row r="397" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="397" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C397" s="24"/>
       <c r="D397" s="22"/>
       <c r="E397" s="22"/>
       <c r="F397" s="22"/>
     </row>
-    <row r="398" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="398" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C398" s="25"/>
       <c r="D398" s="23"/>
       <c r="E398" s="23"/>
       <c r="F398" s="23"/>
     </row>
-    <row r="399" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="399" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C399" s="24"/>
       <c r="D399" s="22"/>
       <c r="E399" s="22"/>
       <c r="F399" s="22"/>
     </row>
-    <row r="400" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="400" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C400" s="25"/>
       <c r="D400" s="23"/>
       <c r="E400" s="23"/>
       <c r="F400" s="23"/>
     </row>
-    <row r="401" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="401" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C401" s="24"/>
       <c r="D401" s="22"/>
       <c r="E401" s="22"/>
       <c r="F401" s="22"/>
     </row>
-    <row r="402" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="402" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C402" s="25"/>
       <c r="D402" s="23"/>
       <c r="E402" s="23"/>
       <c r="F402" s="23"/>
     </row>
-    <row r="403" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="403" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C403" s="24"/>
       <c r="D403" s="22"/>
       <c r="E403" s="22"/>
       <c r="F403" s="22"/>
     </row>
-    <row r="404" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="404" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C404" s="25"/>
       <c r="D404" s="23"/>
       <c r="E404" s="23"/>
       <c r="F404" s="23"/>
     </row>
-    <row r="405" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="405" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C405" s="24"/>
       <c r="D405" s="22"/>
       <c r="E405" s="22"/>
       <c r="F405" s="22"/>
     </row>
-    <row r="406" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="406" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C406" s="25"/>
       <c r="D406" s="23"/>
       <c r="E406" s="23"/>
       <c r="F406" s="23"/>
     </row>
-    <row r="407" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="407" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C407" s="24"/>
       <c r="D407" s="22"/>
       <c r="E407" s="22"/>
       <c r="F407" s="22"/>
     </row>
-    <row r="408" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="408" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C408" s="25"/>
       <c r="D408" s="23"/>
       <c r="E408" s="23"/>
       <c r="F408" s="23"/>
     </row>
-    <row r="409" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="409" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C409" s="24"/>
       <c r="D409" s="22"/>
       <c r="E409" s="22"/>
       <c r="F409" s="22"/>
     </row>
-    <row r="410" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="410" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C410" s="25"/>
       <c r="D410" s="23"/>
       <c r="E410" s="23"/>
       <c r="F410" s="23"/>
     </row>
-    <row r="411" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="411" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C411" s="24"/>
       <c r="D411" s="22"/>
       <c r="E411" s="22"/>
       <c r="F411" s="22"/>
     </row>
-    <row r="412" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="412" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C412" s="25"/>
       <c r="D412" s="23"/>
       <c r="E412" s="23"/>
       <c r="F412" s="23"/>
     </row>
-    <row r="413" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="413" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C413" s="24"/>
       <c r="D413" s="22"/>
       <c r="E413" s="22"/>
       <c r="F413" s="22"/>
     </row>
-    <row r="414" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="414" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C414" s="25"/>
       <c r="D414" s="23"/>
       <c r="E414" s="23"/>
       <c r="F414" s="23"/>
     </row>
-    <row r="415" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="415" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C415" s="24"/>
       <c r="D415" s="22"/>
       <c r="E415" s="22"/>
       <c r="F415" s="22"/>
     </row>
-    <row r="416" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="416" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C416" s="25"/>
       <c r="D416" s="23"/>
       <c r="E416" s="23"/>
       <c r="F416" s="23"/>
     </row>
-    <row r="417" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="417" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C417" s="24"/>
       <c r="D417" s="22"/>
       <c r="E417" s="22"/>
       <c r="F417" s="22"/>
     </row>
-    <row r="418" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="418" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C418" s="25"/>
       <c r="D418" s="23"/>
       <c r="E418" s="23"/>
       <c r="F418" s="23"/>
     </row>
-    <row r="419" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="419" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C419" s="24"/>
       <c r="D419" s="22"/>
       <c r="E419" s="22"/>
       <c r="F419" s="22"/>
     </row>
-    <row r="420" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="420" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C420" s="25"/>
       <c r="D420" s="23"/>
       <c r="E420" s="23"/>
       <c r="F420" s="23"/>
     </row>
-    <row r="421" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="421" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C421" s="24"/>
       <c r="D421" s="22"/>
       <c r="E421" s="22"/>
       <c r="F421" s="22"/>
     </row>
-    <row r="422" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="422" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C422" s="25"/>
       <c r="D422" s="23"/>
       <c r="E422" s="23"/>
       <c r="F422" s="23"/>
     </row>
-    <row r="423" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="423" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C423" s="24"/>
       <c r="D423" s="22"/>
       <c r="E423" s="22"/>
       <c r="F423" s="22"/>
     </row>
-    <row r="424" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="424" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C424" s="25"/>
       <c r="D424" s="23"/>
       <c r="E424" s="23"/>
       <c r="F424" s="23"/>
     </row>
-    <row r="425" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="425" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C425" s="24"/>
       <c r="D425" s="22"/>
       <c r="E425" s="22"/>
       <c r="F425" s="22"/>
     </row>
-    <row r="426" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="426" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C426" s="25"/>
       <c r="D426" s="23"/>
       <c r="E426" s="23"/>
       <c r="F426" s="23"/>
     </row>
-    <row r="427" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="427" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C427" s="24"/>
       <c r="D427" s="22"/>
       <c r="E427" s="22"/>
       <c r="F427" s="22"/>
     </row>
-    <row r="428" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="428" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C428" s="25"/>
       <c r="D428" s="23"/>
       <c r="E428" s="23"/>
       <c r="F428" s="23"/>
     </row>
-    <row r="429" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="429" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C429" s="24"/>
       <c r="D429" s="22"/>
       <c r="E429" s="22"/>
       <c r="F429" s="22"/>
     </row>
-    <row r="430" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="430" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C430" s="25"/>
       <c r="D430" s="23"/>
       <c r="E430" s="23"/>
       <c r="F430" s="23"/>
     </row>
-    <row r="431" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="431" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C431" s="24"/>
       <c r="D431" s="22"/>
       <c r="E431" s="22"/>
       <c r="F431" s="22"/>
     </row>
-    <row r="432" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="432" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C432" s="25"/>
       <c r="D432" s="23"/>
       <c r="E432" s="23"/>
       <c r="F432" s="23"/>
     </row>
-    <row r="433" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="433" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C433" s="24"/>
       <c r="D433" s="22"/>
       <c r="E433" s="22"/>
       <c r="F433" s="22"/>
     </row>
-    <row r="434" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="434" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C434" s="25"/>
       <c r="D434" s="23"/>
       <c r="E434" s="23"/>
       <c r="F434" s="23"/>
     </row>
-    <row r="435" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="435" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C435" s="24"/>
       <c r="D435" s="22"/>
       <c r="E435" s="22"/>
       <c r="F435" s="22"/>
     </row>
-    <row r="436" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="436" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C436" s="25"/>
       <c r="D436" s="23"/>
       <c r="E436" s="23"/>
       <c r="F436" s="23"/>
     </row>
-    <row r="437" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="437" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C437" s="24"/>
       <c r="D437" s="22"/>
       <c r="E437" s="22"/>
       <c r="F437" s="22"/>
     </row>
-    <row r="438" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="438" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C438" s="25"/>
       <c r="D438" s="23"/>
       <c r="E438" s="23"/>
       <c r="F438" s="23"/>
     </row>
-    <row r="439" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="439" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C439" s="24"/>
       <c r="D439" s="22"/>
       <c r="E439" s="22"/>
       <c r="F439" s="22"/>
     </row>
-    <row r="440" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="440" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C440" s="25"/>
       <c r="D440" s="23"/>
       <c r="E440" s="23"/>
       <c r="F440" s="23"/>
     </row>
-    <row r="441" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="441" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C441" s="24"/>
       <c r="D441" s="22"/>
       <c r="E441" s="22"/>
       <c r="F441" s="22"/>
     </row>
-    <row r="442" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="442" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C442" s="25"/>
       <c r="D442" s="23"/>
       <c r="E442" s="23"/>
       <c r="F442" s="23"/>
     </row>
-    <row r="443" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="443" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C443" s="24"/>
       <c r="D443" s="22"/>
       <c r="E443" s="22"/>
       <c r="F443" s="22"/>
     </row>
-    <row r="444" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="444" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C444" s="25"/>
       <c r="D444" s="23"/>
       <c r="E444" s="23"/>
       <c r="F444" s="23"/>
     </row>
-    <row r="445" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="445" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C445" s="24"/>
       <c r="D445" s="22"/>
       <c r="E445" s="22"/>
       <c r="F445" s="22"/>
     </row>
-    <row r="446" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="446" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C446" s="25"/>
       <c r="D446" s="23"/>
       <c r="E446" s="23"/>
       <c r="F446" s="23"/>
     </row>
-    <row r="447" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="447" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C447" s="24"/>
       <c r="D447" s="22"/>
       <c r="E447" s="22"/>
       <c r="F447" s="22"/>
     </row>
-    <row r="448" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="448" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C448" s="25"/>
       <c r="D448" s="23"/>
       <c r="E448" s="23"/>
       <c r="F448" s="23"/>
     </row>
-    <row r="449" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="449" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C449" s="24"/>
       <c r="D449" s="22"/>
       <c r="E449" s="22"/>
       <c r="F449" s="22"/>
     </row>
-    <row r="450" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="450" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C450" s="25"/>
       <c r="D450" s="23"/>
       <c r="E450" s="23"/>
       <c r="F450" s="23"/>
     </row>
-    <row r="451" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="451" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C451" s="24"/>
       <c r="D451" s="22"/>
       <c r="E451" s="22"/>
       <c r="F451" s="22"/>
     </row>
-    <row r="452" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="452" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C452" s="25"/>
       <c r="D452" s="23"/>
       <c r="E452" s="23"/>
       <c r="F452" s="23"/>
     </row>
-    <row r="453" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="453" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C453" s="24"/>
       <c r="D453" s="22"/>
       <c r="E453" s="22"/>
       <c r="F453" s="22"/>
     </row>
-    <row r="454" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="454" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C454" s="25"/>
       <c r="D454" s="23"/>
       <c r="E454" s="23"/>
       <c r="F454" s="23"/>
     </row>
-    <row r="455" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="455" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C455" s="24"/>
       <c r="D455" s="22"/>
       <c r="E455" s="22"/>
       <c r="F455" s="22"/>
     </row>
-    <row r="456" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="456" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C456" s="25"/>
       <c r="D456" s="23"/>
       <c r="E456" s="23"/>
       <c r="F456" s="23"/>
     </row>
-    <row r="457" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="457" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C457" s="24"/>
       <c r="D457" s="22"/>
       <c r="E457" s="22"/>
       <c r="F457" s="22"/>
     </row>
-    <row r="458" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="458" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C458" s="25"/>
       <c r="D458" s="23"/>
       <c r="E458" s="23"/>
       <c r="F458" s="23"/>
     </row>
-    <row r="459" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="459" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C459" s="24"/>
       <c r="D459" s="22"/>
       <c r="E459" s="22"/>
       <c r="F459" s="22"/>
     </row>
-    <row r="460" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="460" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C460" s="25"/>
       <c r="D460" s="23"/>
       <c r="E460" s="23"/>
       <c r="F460" s="23"/>
     </row>
-    <row r="461" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="461" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C461" s="24"/>
       <c r="D461" s="22"/>
       <c r="E461" s="22"/>
       <c r="F461" s="22"/>
     </row>
-    <row r="462" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="462" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C462" s="25"/>
       <c r="D462" s="23"/>
       <c r="E462" s="23"/>
       <c r="F462" s="23"/>
     </row>
-    <row r="463" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="463" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C463" s="24"/>
       <c r="D463" s="22"/>
       <c r="E463" s="22"/>
       <c r="F463" s="22"/>
     </row>
-    <row r="464" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="464" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C464" s="25"/>
       <c r="D464" s="23"/>
       <c r="E464" s="23"/>
       <c r="F464" s="23"/>
     </row>
-    <row r="465" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="465" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C465" s="24"/>
       <c r="D465" s="22"/>
       <c r="E465" s="22"/>
       <c r="F465" s="22"/>
     </row>
-    <row r="466" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="466" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C466" s="25"/>
       <c r="D466" s="23"/>
       <c r="E466" s="23"/>
       <c r="F466" s="23"/>
     </row>
-    <row r="467" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="467" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C467" s="24"/>
       <c r="D467" s="22"/>
       <c r="E467" s="22"/>
       <c r="F467" s="22"/>
     </row>
-    <row r="468" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="468" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C468" s="25"/>
       <c r="D468" s="23"/>
       <c r="E468" s="23"/>
       <c r="F468" s="23"/>
     </row>
-    <row r="469" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="469" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C469" s="24"/>
       <c r="D469" s="22"/>
       <c r="E469" s="22"/>
       <c r="F469" s="22"/>
     </row>
-    <row r="470" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="470" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C470" s="25"/>
       <c r="D470" s="23"/>
       <c r="E470" s="23"/>
       <c r="F470" s="23"/>
     </row>
-    <row r="471" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="471" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C471" s="24"/>
       <c r="D471" s="22"/>
       <c r="E471" s="22"/>
       <c r="F471" s="22"/>
     </row>
-    <row r="472" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="472" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C472" s="25"/>
       <c r="D472" s="23"/>
       <c r="E472" s="23"/>
       <c r="F472" s="23"/>
     </row>
-    <row r="473" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="473" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C473" s="24"/>
       <c r="D473" s="22"/>
       <c r="E473" s="22"/>
       <c r="F473" s="22"/>
     </row>
-    <row r="474" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="474" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C474" s="25"/>
       <c r="D474" s="23"/>
       <c r="E474" s="23"/>
       <c r="F474" s="23"/>
     </row>
-    <row r="475" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="475" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C475" s="24"/>
       <c r="D475" s="22"/>
       <c r="E475" s="22"/>
       <c r="F475" s="22"/>
     </row>
-    <row r="476" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="476" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C476" s="25"/>
       <c r="D476" s="23"/>
       <c r="E476" s="23"/>
       <c r="F476" s="23"/>
     </row>
-    <row r="477" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="477" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C477" s="24"/>
       <c r="D477" s="22"/>
       <c r="E477" s="22"/>
       <c r="F477" s="22"/>
     </row>
-    <row r="478" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="478" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C478" s="25"/>
       <c r="D478" s="23"/>
       <c r="E478" s="23"/>
       <c r="F478" s="23"/>
     </row>
-    <row r="479" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="479" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C479" s="24"/>
       <c r="D479" s="22"/>
       <c r="E479" s="22"/>
       <c r="F479" s="22"/>
     </row>
-    <row r="480" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="480" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C480" s="25"/>
       <c r="D480" s="23"/>
       <c r="E480" s="23"/>
       <c r="F480" s="23"/>
     </row>
-    <row r="481" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="481" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C481" s="24"/>
       <c r="D481" s="22"/>
       <c r="E481" s="22"/>
       <c r="F481" s="22"/>
     </row>
-    <row r="482" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="482" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C482" s="25"/>
       <c r="D482" s="23"/>
       <c r="E482" s="23"/>
       <c r="F482" s="23"/>
     </row>
-    <row r="483" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="483" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C483" s="24"/>
       <c r="D483" s="22"/>
       <c r="E483" s="22"/>
       <c r="F483" s="22"/>
     </row>
-    <row r="484" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="484" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C484" s="25"/>
       <c r="D484" s="23"/>
       <c r="E484" s="23"/>
       <c r="F484" s="23"/>
     </row>
-    <row r="485" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="485" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C485" s="24"/>
       <c r="D485" s="22"/>
       <c r="E485" s="22"/>
       <c r="F485" s="22"/>
     </row>
-    <row r="486" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="486" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C486" s="25"/>
       <c r="D486" s="23"/>
       <c r="E486" s="23"/>
       <c r="F486" s="23"/>
     </row>
-    <row r="487" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="487" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C487" s="24"/>
       <c r="D487" s="22"/>
       <c r="E487" s="22"/>
       <c r="F487" s="22"/>
     </row>
-    <row r="488" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="488" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C488" s="25"/>
       <c r="D488" s="23"/>
       <c r="E488" s="23"/>
       <c r="F488" s="23"/>
     </row>
-    <row r="489" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="489" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C489" s="24"/>
       <c r="D489" s="22"/>
       <c r="E489" s="22"/>
       <c r="F489" s="22"/>
     </row>
-    <row r="490" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="490" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C490" s="25"/>
       <c r="D490" s="23"/>
       <c r="E490" s="23"/>
       <c r="F490" s="23"/>
     </row>
-    <row r="491" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="491" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C491" s="24"/>
       <c r="D491" s="22"/>
       <c r="E491" s="22"/>
       <c r="F491" s="22"/>
     </row>
-    <row r="492" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="492" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C492" s="25"/>
       <c r="D492" s="23"/>
       <c r="E492" s="23"/>
       <c r="F492" s="23"/>
     </row>
-    <row r="493" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="493" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C493" s="24"/>
       <c r="D493" s="22"/>
       <c r="E493" s="22"/>
       <c r="F493" s="22"/>
     </row>
-    <row r="494" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="494" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C494" s="25"/>
       <c r="D494" s="23"/>
       <c r="E494" s="23"/>
       <c r="F494" s="23"/>
     </row>
-    <row r="495" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="495" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C495" s="24"/>
       <c r="D495" s="22"/>
       <c r="E495" s="22"/>
       <c r="F495" s="22"/>
     </row>
-    <row r="496" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="496" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C496" s="25"/>
       <c r="D496" s="23"/>
       <c r="E496" s="23"/>
       <c r="F496" s="23"/>
     </row>
-    <row r="497" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="497" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C497" s="24"/>
       <c r="D497" s="22"/>
       <c r="E497" s="22"/>
       <c r="F497" s="22"/>
     </row>
-    <row r="498" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="498" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C498" s="25"/>
       <c r="D498" s="23"/>
       <c r="E498" s="23"/>
       <c r="F498" s="23"/>
     </row>
-    <row r="499" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="499" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C499" s="24"/>
       <c r="D499" s="22"/>
       <c r="E499" s="22"/>
       <c r="F499" s="22"/>
     </row>
-    <row r="500" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="500" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C500" s="25"/>
       <c r="D500" s="23"/>
       <c r="E500" s="23"/>
       <c r="F500" s="23"/>
     </row>
-    <row r="501" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="501" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C501" s="24"/>
       <c r="D501" s="22"/>
       <c r="E501" s="22"/>
       <c r="F501" s="22"/>
     </row>
-    <row r="502" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="502" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C502" s="25"/>
       <c r="D502" s="23"/>
       <c r="E502" s="23"/>
       <c r="F502" s="23"/>
     </row>
-    <row r="503" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="503" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C503" s="24"/>
       <c r="D503" s="22"/>
       <c r="E503" s="22"/>
       <c r="F503" s="22"/>
     </row>
-    <row r="504" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="504" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C504" s="25"/>
       <c r="D504" s="23"/>
       <c r="E504" s="23"/>
       <c r="F504" s="23"/>
     </row>
-    <row r="505" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="505" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C505" s="24"/>
       <c r="D505" s="22"/>
       <c r="E505" s="22"/>
       <c r="F505" s="22"/>
     </row>
-    <row r="506" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="506" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C506" s="25"/>
       <c r="D506" s="23"/>
       <c r="E506" s="23"/>
       <c r="F506" s="23"/>
     </row>
-    <row r="507" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="507" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C507" s="24"/>
       <c r="D507" s="22"/>
       <c r="E507" s="22"/>
       <c r="F507" s="22"/>
     </row>
-    <row r="508" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="508" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C508" s="25"/>
       <c r="D508" s="23"/>
       <c r="E508" s="23"/>
       <c r="F508" s="23"/>
     </row>
-    <row r="509" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="509" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C509" s="24"/>
       <c r="D509" s="22"/>
       <c r="E509" s="22"/>
       <c r="F509" s="22"/>
     </row>
-    <row r="510" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="510" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C510" s="25"/>
       <c r="D510" s="23"/>
       <c r="E510" s="23"/>
       <c r="F510" s="23"/>
     </row>
-    <row r="511" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="511" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C511" s="24"/>
       <c r="D511" s="22"/>
       <c r="E511" s="22"/>
       <c r="F511" s="22"/>
     </row>
-    <row r="512" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="512" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C512" s="25"/>
       <c r="D512" s="23"/>
       <c r="E512" s="23"/>
       <c r="F512" s="23"/>
     </row>
-    <row r="513" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="513" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C513" s="24"/>
       <c r="D513" s="22"/>
       <c r="E513" s="22"/>
       <c r="F513" s="22"/>
     </row>
-    <row r="514" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="514" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C514" s="25"/>
       <c r="D514" s="23"/>
       <c r="E514" s="23"/>
       <c r="F514" s="23"/>
     </row>
-    <row r="515" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="515" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C515" s="24"/>
       <c r="D515" s="22"/>
       <c r="E515" s="22"/>
       <c r="F515" s="22"/>
     </row>
-    <row r="516" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="516" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C516" s="25"/>
       <c r="D516" s="23"/>
       <c r="E516" s="23"/>
       <c r="F516" s="23"/>
     </row>
-    <row r="517" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="517" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C517" s="24"/>
       <c r="D517" s="22"/>
       <c r="E517" s="22"/>
       <c r="F517" s="22"/>
     </row>
-    <row r="518" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="518" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C518" s="25"/>
       <c r="D518" s="23"/>
       <c r="E518" s="23"/>
       <c r="F518" s="23"/>
     </row>
-    <row r="519" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="519" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C519" s="24"/>
       <c r="D519" s="22"/>
       <c r="E519" s="22"/>
       <c r="F519" s="22"/>
     </row>
-    <row r="520" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="520" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C520" s="25"/>
       <c r="D520" s="23"/>
       <c r="E520" s="23"/>
       <c r="F520" s="23"/>
     </row>
-    <row r="521" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="521" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C521" s="24"/>
       <c r="D521" s="22"/>
       <c r="E521" s="22"/>
       <c r="F521" s="22"/>
     </row>
-    <row r="522" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="522" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C522" s="25"/>
       <c r="D522" s="23"/>
       <c r="E522" s="23"/>
       <c r="F522" s="23"/>
     </row>
-    <row r="523" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="523" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C523" s="24"/>
       <c r="D523" s="22"/>
       <c r="E523" s="22"/>
       <c r="F523" s="22"/>
     </row>
-    <row r="524" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="524" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C524" s="25"/>
       <c r="D524" s="23"/>
       <c r="E524" s="23"/>
       <c r="F524" s="23"/>
     </row>
-    <row r="525" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="525" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C525" s="24"/>
       <c r="D525" s="22"/>
       <c r="E525" s="22"/>
       <c r="F525" s="22"/>
     </row>
-    <row r="526" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="526" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C526" s="25"/>
       <c r="D526" s="23"/>
       <c r="E526" s="23"/>
       <c r="F526" s="23"/>
     </row>
-    <row r="527" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="527" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C527" s="24"/>
       <c r="D527" s="22"/>
       <c r="E527" s="22"/>
       <c r="F527" s="22"/>
     </row>
-    <row r="528" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="528" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C528" s="25"/>
       <c r="D528" s="23"/>
       <c r="E528" s="23"/>
       <c r="F528" s="23"/>
     </row>
-    <row r="529" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="529" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C529" s="24"/>
       <c r="D529" s="22"/>
       <c r="E529" s="22"/>
       <c r="F529" s="22"/>
     </row>
-    <row r="530" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="530" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C530" s="25"/>
       <c r="D530" s="23"/>
       <c r="E530" s="23"/>
       <c r="F530" s="23"/>
     </row>
-    <row r="531" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="531" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C531" s="24"/>
       <c r="D531" s="22"/>
       <c r="E531" s="22"/>
       <c r="F531" s="22"/>
     </row>
-    <row r="532" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="532" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C532" s="25"/>
       <c r="D532" s="23"/>
       <c r="E532" s="23"/>
       <c r="F532" s="23"/>
     </row>
-    <row r="533" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="533" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C533" s="24"/>
       <c r="D533" s="22"/>
       <c r="E533" s="22"/>
       <c r="F533" s="22"/>
     </row>
-    <row r="534" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="534" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C534" s="25"/>
       <c r="D534" s="23"/>
       <c r="E534" s="23"/>
       <c r="F534" s="23"/>
     </row>
-    <row r="535" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="535" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C535" s="24"/>
       <c r="D535" s="22"/>
       <c r="E535" s="22"/>
       <c r="F535" s="22"/>
     </row>
-    <row r="536" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="536" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C536" s="25"/>
       <c r="D536" s="23"/>
       <c r="E536" s="23"/>
       <c r="F536" s="23"/>
     </row>
-    <row r="537" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="537" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C537" s="24"/>
       <c r="D537" s="22"/>
       <c r="E537" s="22"/>
       <c r="F537" s="22"/>
     </row>
-    <row r="538" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="538" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C538" s="25"/>
       <c r="D538" s="23"/>
       <c r="E538" s="23"/>
       <c r="F538" s="23"/>
     </row>
-    <row r="539" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="539" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C539" s="24"/>
       <c r="D539" s="22"/>
       <c r="E539" s="22"/>
       <c r="F539" s="22"/>
     </row>
-    <row r="540" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="540" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C540" s="25"/>
       <c r="D540" s="23"/>
       <c r="E540" s="23"/>
       <c r="F540" s="23"/>
     </row>
-    <row r="541" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="541" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C541" s="24"/>
       <c r="D541" s="22"/>
       <c r="E541" s="22"/>
       <c r="F541" s="22"/>
     </row>
-    <row r="542" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="542" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C542" s="25"/>
       <c r="D542" s="23"/>
       <c r="E542" s="23"/>
       <c r="F542" s="23"/>
     </row>
-    <row r="543" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="543" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C543" s="24"/>
       <c r="D543" s="22"/>
       <c r="E543" s="22"/>
       <c r="F543" s="22"/>
     </row>
-    <row r="544" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="544" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C544" s="25"/>
       <c r="D544" s="23"/>
       <c r="E544" s="23"/>
       <c r="F544" s="23"/>
     </row>
-    <row r="545" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="545" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C545" s="24"/>
       <c r="D545" s="22"/>
       <c r="E545" s="22"/>
       <c r="F545" s="22"/>
     </row>
-    <row r="546" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="546" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C546" s="25"/>
       <c r="D546" s="23"/>
       <c r="E546" s="23"/>
       <c r="F546" s="23"/>
     </row>
-    <row r="547" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="547" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C547" s="24"/>
       <c r="D547" s="22"/>
       <c r="E547" s="22"/>
       <c r="F547" s="22"/>
     </row>
-    <row r="548" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="548" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C548" s="25"/>
       <c r="D548" s="23"/>
       <c r="E548" s="23"/>
       <c r="F548" s="23"/>
     </row>
-    <row r="549" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="549" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C549" s="24"/>
       <c r="D549" s="22"/>
       <c r="E549" s="22"/>
       <c r="F549" s="22"/>
     </row>
-    <row r="550" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="550" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C550" s="25"/>
       <c r="D550" s="23"/>
       <c r="E550" s="23"/>
       <c r="F550" s="23"/>
     </row>
-    <row r="551" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="551" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C551" s="24"/>
       <c r="D551" s="22"/>
       <c r="E551" s="22"/>
       <c r="F551" s="22"/>
     </row>
-    <row r="552" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="552" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C552" s="25"/>
       <c r="D552" s="23"/>
       <c r="E552" s="23"/>
       <c r="F552" s="23"/>
     </row>
-    <row r="553" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="553" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C553" s="24"/>
       <c r="D553" s="22"/>
       <c r="E553" s="22"/>
       <c r="F553" s="22"/>
     </row>
-    <row r="554" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="554" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C554" s="25"/>
       <c r="D554" s="23"/>
       <c r="E554" s="23"/>
       <c r="F554" s="23"/>
     </row>
-    <row r="555" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="555" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C555" s="24"/>
       <c r="D555" s="22"/>
       <c r="E555" s="22"/>
       <c r="F555" s="22"/>
     </row>
-    <row r="556" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="556" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C556" s="25"/>
       <c r="D556" s="23"/>
       <c r="E556" s="23"/>
       <c r="F556" s="23"/>
     </row>
-    <row r="557" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="557" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C557" s="24"/>
       <c r="D557" s="22"/>
       <c r="E557" s="22"/>
       <c r="F557" s="22"/>
     </row>
-    <row r="558" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="558" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C558" s="25"/>
       <c r="D558" s="23"/>
       <c r="E558" s="23"/>
       <c r="F558" s="23"/>
     </row>
-    <row r="559" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="559" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C559" s="24"/>
       <c r="D559" s="22"/>
       <c r="E559" s="22"/>
       <c r="F559" s="22"/>
     </row>
-    <row r="560" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="560" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C560" s="25"/>
       <c r="D560" s="23"/>
       <c r="E560" s="23"/>
       <c r="F560" s="23"/>
     </row>
-    <row r="561" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="561" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C561" s="24"/>
       <c r="D561" s="22"/>
       <c r="E561" s="22"/>
       <c r="F561" s="22"/>
     </row>
-    <row r="562" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="562" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C562" s="25"/>
       <c r="D562" s="23"/>
       <c r="E562" s="23"/>
       <c r="F562" s="23"/>
     </row>
-    <row r="563" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="563" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C563" s="24"/>
       <c r="D563" s="22"/>
       <c r="E563" s="22"/>
       <c r="F563" s="22"/>
     </row>
-    <row r="564" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="564" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C564" s="25"/>
       <c r="D564" s="23"/>
       <c r="E564" s="23"/>
       <c r="F564" s="23"/>
     </row>
-    <row r="565" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="565" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C565" s="24"/>
       <c r="D565" s="22"/>
       <c r="E565" s="22"/>
       <c r="F565" s="22"/>
     </row>
-    <row r="566" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="566" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C566" s="25"/>
       <c r="D566" s="23"/>
       <c r="E566" s="23"/>
       <c r="F566" s="23"/>
     </row>
-    <row r="567" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="567" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C567" s="24"/>
       <c r="D567" s="22"/>
       <c r="E567" s="22"/>
       <c r="F567" s="22"/>
     </row>
-    <row r="568" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="568" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C568" s="25"/>
       <c r="D568" s="23"/>
       <c r="E568" s="23"/>
       <c r="F568" s="23"/>
     </row>
-    <row r="569" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="569" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C569" s="24"/>
       <c r="D569" s="22"/>
       <c r="E569" s="22"/>
       <c r="F569" s="22"/>
     </row>
-    <row r="570" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="570" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C570" s="25"/>
       <c r="D570" s="23"/>
       <c r="E570" s="23"/>
       <c r="F570" s="23"/>
     </row>
-    <row r="571" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="571" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C571" s="24"/>
       <c r="D571" s="22"/>
       <c r="E571" s="22"/>
       <c r="F571" s="22"/>
     </row>
-    <row r="572" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="572" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C572" s="25"/>
       <c r="D572" s="23"/>
       <c r="E572" s="23"/>
       <c r="F572" s="23"/>
     </row>
-    <row r="573" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="573" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C573" s="24"/>
       <c r="D573" s="22"/>
       <c r="E573" s="22"/>
       <c r="F573" s="22"/>
     </row>
-    <row r="574" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="574" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C574" s="25"/>
       <c r="D574" s="23"/>
       <c r="E574" s="23"/>
       <c r="F574" s="23"/>
     </row>
-    <row r="575" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="575" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C575" s="24"/>
       <c r="D575" s="22"/>
       <c r="E575" s="22"/>
       <c r="F575" s="22"/>
     </row>
-    <row r="576" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="576" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C576" s="25"/>
       <c r="D576" s="23"/>
       <c r="E576" s="23"/>
       <c r="F576" s="23"/>
     </row>
-    <row r="577" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="577" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C577" s="24"/>
       <c r="D577" s="22"/>
       <c r="E577" s="22"/>
       <c r="F577" s="22"/>
     </row>
-    <row r="578" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="578" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C578" s="25"/>
       <c r="D578" s="23"/>
       <c r="E578" s="23"/>
       <c r="F578" s="23"/>
     </row>
-    <row r="579" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="579" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C579" s="24"/>
       <c r="D579" s="22"/>
       <c r="E579" s="22"/>
       <c r="F579" s="22"/>
     </row>
-    <row r="580" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="580" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C580" s="25"/>
       <c r="D580" s="23"/>
       <c r="E580" s="23"/>
       <c r="F580" s="23"/>
     </row>
-    <row r="581" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="581" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C581" s="24"/>
       <c r="D581" s="22"/>
       <c r="E581" s="22"/>
       <c r="F581" s="22"/>
     </row>
-    <row r="582" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="582" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C582" s="25"/>
       <c r="D582" s="23"/>
       <c r="E582" s="23"/>
       <c r="F582" s="23"/>
     </row>
-    <row r="583" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="583" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C583" s="24"/>
       <c r="D583" s="22"/>
       <c r="E583" s="22"/>
       <c r="F583" s="22"/>
     </row>
-    <row r="584" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="584" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C584" s="25"/>
       <c r="D584" s="23"/>
       <c r="E584" s="23"/>
       <c r="F584" s="23"/>
     </row>
-    <row r="585" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="585" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C585" s="24"/>
       <c r="D585" s="22"/>
       <c r="E585" s="22"/>
       <c r="F585" s="22"/>
     </row>
-    <row r="586" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="586" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C586" s="25"/>
       <c r="D586" s="23"/>
       <c r="E586" s="23"/>
       <c r="F586" s="23"/>
     </row>
-    <row r="587" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="587" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C587" s="24"/>
       <c r="D587" s="22"/>
       <c r="E587" s="22"/>
       <c r="F587" s="22"/>
     </row>
-    <row r="588" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="588" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C588" s="25"/>
       <c r="D588" s="23"/>
       <c r="E588" s="23"/>
       <c r="F588" s="23"/>
     </row>
-    <row r="589" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="589" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C589" s="24"/>
       <c r="D589" s="22"/>
       <c r="E589" s="22"/>
       <c r="F589" s="22"/>
     </row>
-    <row r="590" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="590" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C590" s="25"/>
       <c r="D590" s="23"/>
       <c r="E590" s="23"/>
       <c r="F590" s="23"/>
     </row>
-    <row r="591" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="591" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C591" s="24"/>
       <c r="D591" s="22"/>
       <c r="E591" s="22"/>
       <c r="F591" s="22"/>
     </row>
-    <row r="592" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="592" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C592" s="25"/>
       <c r="D592" s="23"/>
       <c r="E592" s="23"/>
       <c r="F592" s="23"/>
     </row>
-    <row r="593" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="593" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C593" s="24"/>
       <c r="D593" s="22"/>
       <c r="E593" s="22"/>
       <c r="F593" s="22"/>
     </row>
-    <row r="594" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="594" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C594" s="25"/>
       <c r="D594" s="23"/>
       <c r="E594" s="23"/>
       <c r="F594" s="23"/>
     </row>
-    <row r="595" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="595" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C595" s="24"/>
       <c r="D595" s="22"/>
       <c r="E595" s="22"/>
       <c r="F595" s="22"/>
     </row>
-    <row r="596" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="596" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C596" s="25"/>
       <c r="D596" s="23"/>
       <c r="E596" s="23"/>
       <c r="F596" s="23"/>
     </row>
-    <row r="597" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="597" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C597" s="24"/>
       <c r="D597" s="22"/>
       <c r="E597" s="22"/>
       <c r="F597" s="22"/>
     </row>
-    <row r="598" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="598" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C598" s="25"/>
       <c r="D598" s="23"/>
       <c r="E598" s="23"/>
       <c r="F598" s="23"/>
     </row>
-    <row r="599" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="599" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C599" s="24"/>
       <c r="D599" s="22"/>
       <c r="E599" s="22"/>
       <c r="F599" s="22"/>
     </row>
-    <row r="600" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="600" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C600" s="25"/>
       <c r="D600" s="23"/>
       <c r="E600" s="23"/>
       <c r="F600" s="23"/>
     </row>
-    <row r="601" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="601" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C601" s="24"/>
       <c r="D601" s="22"/>
       <c r="E601" s="22"/>
       <c r="F601" s="22"/>
     </row>
-    <row r="602" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="602" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C602" s="25"/>
       <c r="D602" s="23"/>
       <c r="E602" s="23"/>
       <c r="F602" s="23"/>
     </row>
-    <row r="603" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="603" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C603" s="24"/>
       <c r="D603" s="22"/>
       <c r="E603" s="22"/>
       <c r="F603" s="22"/>
     </row>
-    <row r="604" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="604" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C604" s="25"/>
       <c r="D604" s="23"/>
       <c r="E604" s="23"/>
       <c r="F604" s="23"/>
     </row>
-    <row r="605" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="605" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C605" s="24"/>
       <c r="D605" s="22"/>
       <c r="E605" s="22"/>
       <c r="F605" s="22"/>
     </row>
-    <row r="606" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="606" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C606" s="25"/>
       <c r="D606" s="23"/>
       <c r="E606" s="23"/>
       <c r="F606" s="23"/>
     </row>
-    <row r="607" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="607" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C607" s="24"/>
       <c r="D607" s="22"/>
       <c r="E607" s="22"/>
       <c r="F607" s="22"/>
     </row>
-    <row r="608" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="608" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C608" s="25"/>
       <c r="D608" s="23"/>
       <c r="E608" s="23"/>
       <c r="F608" s="23"/>
     </row>
-    <row r="609" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="609" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C609" s="24"/>
       <c r="D609" s="22"/>
       <c r="E609" s="22"/>
       <c r="F609" s="22"/>
     </row>
-    <row r="610" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="610" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C610" s="25"/>
       <c r="D610" s="23"/>
       <c r="E610" s="23"/>
       <c r="F610" s="23"/>
     </row>
-    <row r="611" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="611" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C611" s="24"/>
       <c r="D611" s="22"/>
       <c r="E611" s="22"/>
       <c r="F611" s="22"/>
     </row>
-    <row r="612" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="612" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C612" s="25"/>
       <c r="D612" s="23"/>
       <c r="E612" s="23"/>
       <c r="F612" s="23"/>
     </row>
-    <row r="613" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="613" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C613" s="24"/>
       <c r="D613" s="22"/>
       <c r="E613" s="22"/>
       <c r="F613" s="22"/>
     </row>
-    <row r="614" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="614" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C614" s="25"/>
       <c r="D614" s="23"/>
       <c r="E614" s="23"/>
       <c r="F614" s="23"/>
     </row>
-    <row r="615" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="615" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C615" s="24"/>
       <c r="D615" s="22"/>
       <c r="E615" s="22"/>
       <c r="F615" s="22"/>
     </row>
-    <row r="616" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="616" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C616" s="25"/>
       <c r="D616" s="23"/>
       <c r="E616" s="23"/>
       <c r="F616" s="23"/>
     </row>
-    <row r="617" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="617" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C617" s="24"/>
       <c r="D617" s="22"/>
       <c r="E617" s="22"/>
       <c r="F617" s="22"/>
     </row>
-    <row r="618" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="618" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C618" s="25"/>
       <c r="D618" s="23"/>
       <c r="E618" s="23"/>
       <c r="F618" s="23"/>
     </row>
-    <row r="619" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="619" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C619" s="24"/>
       <c r="D619" s="22"/>
       <c r="E619" s="22"/>
       <c r="F619" s="22"/>
     </row>
-    <row r="620" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="620" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C620" s="25"/>
       <c r="D620" s="23"/>
       <c r="E620" s="23"/>
       <c r="F620" s="23"/>
     </row>
-    <row r="621" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="621" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C621" s="24"/>
       <c r="D621" s="22"/>
       <c r="E621" s="22"/>
       <c r="F621" s="22"/>
     </row>
-    <row r="622" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="622" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C622" s="25"/>
       <c r="D622" s="23"/>
       <c r="E622" s="23"/>
       <c r="F622" s="23"/>
     </row>
-    <row r="623" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="623" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C623" s="24"/>
       <c r="D623" s="22"/>
       <c r="E623" s="22"/>
       <c r="F623" s="22"/>
     </row>
-    <row r="624" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="624" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C624" s="25"/>
       <c r="D624" s="23"/>
       <c r="E624" s="23"/>
       <c r="F624" s="23"/>
     </row>
-    <row r="625" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="625" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C625" s="24"/>
       <c r="D625" s="22"/>
       <c r="E625" s="22"/>
       <c r="F625" s="22"/>
     </row>
-    <row r="626" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="626" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C626" s="25"/>
       <c r="D626" s="23"/>
       <c r="E626" s="23"/>
       <c r="F626" s="23"/>
     </row>
-    <row r="627" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="627" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C627" s="24"/>
       <c r="D627" s="22"/>
       <c r="E627" s="22"/>
       <c r="F627" s="22"/>
     </row>
-    <row r="628" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="628" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C628" s="25"/>
       <c r="D628" s="23"/>
       <c r="E628" s="23"/>
       <c r="F628" s="23"/>
     </row>
-    <row r="629" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="629" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C629" s="24"/>
       <c r="D629" s="22"/>
       <c r="E629" s="22"/>
       <c r="F629" s="22"/>
     </row>
-    <row r="630" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="630" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C630" s="25"/>
       <c r="D630" s="23"/>
       <c r="E630" s="23"/>
       <c r="F630" s="23"/>
     </row>
-    <row r="631" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="631" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C631" s="24"/>
       <c r="D631" s="22"/>
       <c r="E631" s="22"/>
       <c r="F631" s="22"/>
     </row>
-    <row r="632" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="632" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C632" s="25"/>
       <c r="D632" s="23"/>
       <c r="E632" s="23"/>
       <c r="F632" s="23"/>
     </row>
-    <row r="633" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="633" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C633" s="24"/>
       <c r="D633" s="22"/>
       <c r="E633" s="22"/>
       <c r="F633" s="22"/>
     </row>
-    <row r="634" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="634" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C634" s="25"/>
       <c r="D634" s="23"/>
       <c r="E634" s="23"/>
       <c r="F634" s="23"/>
     </row>
-    <row r="635" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="635" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C635" s="24"/>
       <c r="D635" s="22"/>
       <c r="E635" s="22"/>
       <c r="F635" s="22"/>
     </row>
-    <row r="636" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="636" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C636" s="25"/>
       <c r="D636" s="23"/>
       <c r="E636" s="23"/>
       <c r="F636" s="23"/>
     </row>
-    <row r="637" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="637" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C637" s="24"/>
       <c r="D637" s="22"/>
       <c r="E637" s="22"/>
       <c r="F637" s="22"/>
     </row>
-    <row r="638" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="638" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C638" s="25"/>
       <c r="D638" s="23"/>
       <c r="E638" s="23"/>
       <c r="F638" s="23"/>
     </row>
-    <row r="639" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="639" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C639" s="24"/>
       <c r="D639" s="22"/>
       <c r="E639" s="22"/>
       <c r="F639" s="22"/>
     </row>
-    <row r="640" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="640" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C640" s="25"/>
       <c r="D640" s="23"/>
       <c r="E640" s="23"/>
       <c r="F640" s="23"/>
     </row>
-    <row r="641" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="641" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C641" s="24"/>
       <c r="D641" s="22"/>
       <c r="E641" s="22"/>
       <c r="F641" s="22"/>
     </row>
-    <row r="642" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="642" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C642" s="25"/>
       <c r="D642" s="23"/>
       <c r="E642" s="23"/>
       <c r="F642" s="23"/>
     </row>
-    <row r="643" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="643" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C643" s="24"/>
       <c r="D643" s="22"/>
       <c r="E643" s="22"/>
       <c r="F643" s="22"/>
     </row>
-    <row r="644" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="644" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C644" s="25"/>
       <c r="D644" s="23"/>
       <c r="E644" s="23"/>
       <c r="F644" s="23"/>
     </row>
-    <row r="645" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="645" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C645" s="24"/>
       <c r="D645" s="22"/>
       <c r="E645" s="22"/>
       <c r="F645" s="22"/>
     </row>
-    <row r="646" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="646" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C646" s="25"/>
       <c r="D646" s="23"/>
       <c r="E646" s="23"/>
       <c r="F646" s="23"/>
     </row>
-    <row r="647" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="647" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C647" s="24"/>
       <c r="D647" s="22"/>
       <c r="E647" s="22"/>
       <c r="F647" s="22"/>
     </row>
-    <row r="648" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="648" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C648" s="25"/>
       <c r="D648" s="23"/>
       <c r="E648" s="23"/>
       <c r="F648" s="23"/>
     </row>
-    <row r="649" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="649" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C649" s="24"/>
       <c r="D649" s="22"/>
       <c r="E649" s="22"/>
       <c r="F649" s="22"/>
     </row>
-    <row r="650" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="650" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C650" s="25"/>
       <c r="D650" s="23"/>
       <c r="E650" s="23"/>
       <c r="F650" s="23"/>
     </row>
-    <row r="651" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="651" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C651" s="24"/>
       <c r="D651" s="22"/>
       <c r="E651" s="22"/>
       <c r="F651" s="22"/>
     </row>
-    <row r="652" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="652" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C652" s="25"/>
       <c r="D652" s="23"/>
       <c r="E652" s="23"/>
       <c r="F652" s="23"/>
     </row>
-    <row r="653" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="653" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C653" s="24"/>
       <c r="D653" s="22"/>
       <c r="E653" s="22"/>
       <c r="F653" s="22"/>
     </row>
-    <row r="654" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="654" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C654" s="25"/>
       <c r="D654" s="23"/>
       <c r="E654" s="23"/>
       <c r="F654" s="23"/>
     </row>
-    <row r="655" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="655" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C655" s="24"/>
       <c r="D655" s="22"/>
       <c r="E655" s="22"/>
       <c r="F655" s="22"/>
     </row>
-    <row r="656" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="656" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C656" s="25"/>
       <c r="D656" s="23"/>
       <c r="E656" s="23"/>
       <c r="F656" s="23"/>
     </row>
-    <row r="657" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="657" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C657" s="24"/>
       <c r="D657" s="22"/>
       <c r="E657" s="22"/>
       <c r="F657" s="22"/>
     </row>
-    <row r="658" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="658" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C658" s="25"/>
       <c r="D658" s="23"/>
       <c r="E658" s="23"/>
       <c r="F658" s="23"/>
     </row>
-    <row r="659" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="659" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C659" s="24"/>
       <c r="D659" s="22"/>
       <c r="E659" s="22"/>
       <c r="F659" s="22"/>
     </row>
-    <row r="660" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="660" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C660" s="25"/>
       <c r="D660" s="23"/>
       <c r="E660" s="23"/>
       <c r="F660" s="23"/>
     </row>
-    <row r="661" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="661" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C661" s="24"/>
       <c r="D661" s="22"/>
       <c r="E661" s="22"/>
       <c r="F661" s="22"/>
     </row>
-    <row r="662" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="662" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C662" s="25"/>
       <c r="D662" s="23"/>
       <c r="E662" s="23"/>
       <c r="F662" s="23"/>
     </row>
-    <row r="663" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="663" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C663" s="24"/>
       <c r="D663" s="22"/>
       <c r="E663" s="22"/>
       <c r="F663" s="22"/>
     </row>
-    <row r="664" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="664" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C664" s="25"/>
       <c r="D664" s="23"/>
       <c r="E664" s="23"/>
       <c r="F664" s="23"/>
     </row>
-    <row r="665" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="665" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C665" s="24"/>
       <c r="D665" s="22"/>
       <c r="E665" s="22"/>
       <c r="F665" s="22"/>
     </row>
-    <row r="666" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="666" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C666" s="25"/>
       <c r="D666" s="23"/>
       <c r="E666" s="23"/>
       <c r="F666" s="23"/>
     </row>
-    <row r="667" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="667" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C667" s="24"/>
       <c r="D667" s="22"/>
       <c r="E667" s="22"/>
       <c r="F667" s="22"/>
     </row>
-    <row r="668" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="668" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C668" s="25"/>
       <c r="D668" s="23"/>
       <c r="E668" s="23"/>
       <c r="F668" s="23"/>
     </row>
-    <row r="669" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="669" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C669" s="24"/>
       <c r="D669" s="22"/>
       <c r="E669" s="22"/>
       <c r="F669" s="22"/>
     </row>
-    <row r="670" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="670" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C670" s="25"/>
       <c r="D670" s="23"/>
       <c r="E670" s="23"/>
       <c r="F670" s="23"/>
     </row>
-    <row r="671" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="671" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C671" s="24"/>
       <c r="D671" s="22"/>
       <c r="E671" s="22"/>
       <c r="F671" s="22"/>
     </row>
-    <row r="672" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="672" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C672" s="25"/>
       <c r="D672" s="23"/>
       <c r="E672" s="23"/>
       <c r="F672" s="23"/>
     </row>
-    <row r="673" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="673" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C673" s="24"/>
       <c r="D673" s="22"/>
       <c r="E673" s="22"/>
       <c r="F673" s="22"/>
     </row>
-    <row r="674" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="674" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C674" s="25"/>
       <c r="D674" s="23"/>
       <c r="E674" s="23"/>
       <c r="F674" s="23"/>
     </row>
-    <row r="675" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="675" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C675" s="24"/>
       <c r="D675" s="22"/>
       <c r="E675" s="22"/>
       <c r="F675" s="22"/>
     </row>
-    <row r="676" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="676" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C676" s="25"/>
       <c r="D676" s="23"/>
       <c r="E676" s="23"/>
       <c r="F676" s="23"/>
     </row>
-    <row r="677" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="677" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C677" s="24"/>
       <c r="D677" s="22"/>
       <c r="E677" s="22"/>
       <c r="F677" s="22"/>
     </row>
-    <row r="678" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="678" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C678" s="25"/>
       <c r="D678" s="23"/>
       <c r="E678" s="23"/>
       <c r="F678" s="23"/>
     </row>
-    <row r="679" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="679" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C679" s="24"/>
       <c r="D679" s="22"/>
       <c r="E679" s="22"/>
       <c r="F679" s="22"/>
     </row>
-    <row r="680" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="680" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C680" s="25"/>
       <c r="D680" s="23"/>
       <c r="E680" s="23"/>
       <c r="F680" s="23"/>
     </row>
-    <row r="681" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="681" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C681" s="24"/>
       <c r="D681" s="22"/>
       <c r="E681" s="22"/>
       <c r="F681" s="22"/>
     </row>
-    <row r="682" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="682" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C682" s="25"/>
       <c r="D682" s="23"/>
       <c r="E682" s="23"/>
       <c r="F682" s="23"/>
     </row>
-    <row r="683" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="683" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C683" s="24"/>
       <c r="D683" s="22"/>
       <c r="E683" s="22"/>
       <c r="F683" s="22"/>
     </row>
-    <row r="684" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="684" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C684" s="25"/>
       <c r="D684" s="23"/>
       <c r="E684" s="23"/>
       <c r="F684" s="23"/>
     </row>
-    <row r="685" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="685" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C685" s="24"/>
       <c r="D685" s="22"/>
       <c r="E685" s="22"/>
       <c r="F685" s="22"/>
     </row>
-    <row r="686" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="686" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C686" s="25"/>
       <c r="D686" s="23"/>
       <c r="E686" s="23"/>
       <c r="F686" s="23"/>
     </row>
-    <row r="687" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="687" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C687" s="24"/>
       <c r="D687" s="22"/>
       <c r="E687" s="22"/>
       <c r="F687" s="22"/>
     </row>
-    <row r="688" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="688" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C688" s="25"/>
       <c r="D688" s="23"/>
       <c r="E688" s="23"/>
       <c r="F688" s="23"/>
     </row>
-    <row r="689" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="689" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C689" s="24"/>
       <c r="D689" s="22"/>
       <c r="E689" s="22"/>
       <c r="F689" s="22"/>
     </row>
-    <row r="690" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="690" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C690" s="25"/>
       <c r="D690" s="23"/>
       <c r="E690" s="23"/>
       <c r="F690" s="23"/>
     </row>
-    <row r="691" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="691" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C691" s="24"/>
       <c r="D691" s="22"/>
       <c r="E691" s="22"/>
       <c r="F691" s="22"/>
     </row>
-    <row r="692" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="692" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C692" s="25"/>
       <c r="D692" s="23"/>
       <c r="E692" s="23"/>
       <c r="F692" s="23"/>
     </row>
-    <row r="693" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="693" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C693" s="24"/>
       <c r="D693" s="22"/>
       <c r="E693" s="22"/>
       <c r="F693" s="22"/>
     </row>
-    <row r="694" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="694" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C694" s="25"/>
       <c r="D694" s="23"/>
       <c r="E694" s="23"/>
       <c r="F694" s="23"/>
     </row>
-    <row r="695" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="695" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C695" s="24"/>
       <c r="D695" s="22"/>
       <c r="E695" s="22"/>
       <c r="F695" s="22"/>
     </row>
-    <row r="696" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="696" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C696" s="25"/>
       <c r="D696" s="23"/>
       <c r="E696" s="23"/>
       <c r="F696" s="23"/>
     </row>
-    <row r="697" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="697" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C697" s="24"/>
       <c r="D697" s="22"/>
       <c r="E697" s="22"/>
       <c r="F697" s="22"/>
     </row>
-    <row r="698" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="698" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C698" s="25"/>
       <c r="D698" s="23"/>
       <c r="E698" s="23"/>
       <c r="F698" s="23"/>
     </row>
-    <row r="699" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="699" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C699" s="24"/>
       <c r="D699" s="22"/>
       <c r="E699" s="22"/>
       <c r="F699" s="22"/>
     </row>
-    <row r="700" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="700" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C700" s="25"/>
       <c r="D700" s="23"/>
       <c r="E700" s="23"/>
       <c r="F700" s="23"/>
     </row>
-    <row r="701" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="701" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C701" s="24"/>
       <c r="D701" s="22"/>
       <c r="E701" s="22"/>
       <c r="F701" s="22"/>
     </row>
-    <row r="702" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="702" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C702" s="25"/>
       <c r="D702" s="23"/>
       <c r="E702" s="23"/>
       <c r="F702" s="23"/>
     </row>
-    <row r="703" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="703" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C703" s="24"/>
       <c r="D703" s="22"/>
       <c r="E703" s="22"/>
       <c r="F703" s="22"/>
     </row>
-    <row r="704" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="704" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C704" s="25"/>
       <c r="D704" s="23"/>
       <c r="E704" s="23"/>
       <c r="F704" s="23"/>
     </row>
-    <row r="705" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="705" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C705" s="24"/>
       <c r="D705" s="22"/>
       <c r="E705" s="22"/>
       <c r="F705" s="22"/>
     </row>
-    <row r="706" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="706" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C706" s="25"/>
       <c r="D706" s="23"/>
       <c r="E706" s="23"/>
       <c r="F706" s="23"/>
     </row>
-    <row r="707" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="707" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C707" s="24"/>
       <c r="D707" s="22"/>
       <c r="E707" s="22"/>
       <c r="F707" s="22"/>
     </row>
-    <row r="708" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="708" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C708" s="25"/>
       <c r="D708" s="23"/>
       <c r="E708" s="23"/>
       <c r="F708" s="23"/>
     </row>
-    <row r="709" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="709" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C709" s="24"/>
       <c r="D709" s="22"/>
       <c r="E709" s="22"/>
       <c r="F709" s="22"/>
     </row>
-    <row r="710" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="710" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C710" s="25"/>
       <c r="D710" s="23"/>
       <c r="E710" s="23"/>
       <c r="F710" s="23"/>
     </row>
-    <row r="711" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="711" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C711" s="24"/>
       <c r="D711" s="22"/>
       <c r="E711" s="22"/>
       <c r="F711" s="22"/>
     </row>
-    <row r="712" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="712" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C712" s="25"/>
       <c r="D712" s="23"/>
       <c r="E712" s="23"/>
       <c r="F712" s="23"/>
     </row>
-    <row r="713" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="713" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C713" s="24"/>
       <c r="D713" s="22"/>
       <c r="E713" s="22"/>
       <c r="F713" s="22"/>
     </row>
-    <row r="714" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="714" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C714" s="25"/>
       <c r="D714" s="23"/>
       <c r="E714" s="23"/>
       <c r="F714" s="23"/>
     </row>
-    <row r="715" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="715" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C715" s="24"/>
       <c r="D715" s="22"/>
       <c r="E715" s="22"/>
       <c r="F715" s="22"/>
     </row>
-    <row r="716" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="716" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C716" s="25"/>
       <c r="D716" s="23"/>
       <c r="E716" s="23"/>
       <c r="F716" s="23"/>
     </row>
-    <row r="717" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="717" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C717" s="24"/>
       <c r="D717" s="22"/>
       <c r="E717" s="22"/>
       <c r="F717" s="22"/>
     </row>
-    <row r="718" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="718" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C718" s="25"/>
       <c r="D718" s="23"/>
       <c r="E718" s="23"/>
       <c r="F718" s="23"/>
     </row>
-    <row r="719" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="719" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C719" s="24"/>
       <c r="D719" s="22"/>
       <c r="E719" s="22"/>
       <c r="F719" s="22"/>
     </row>
-    <row r="720" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="720" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C720" s="25"/>
       <c r="D720" s="23"/>
       <c r="E720" s="23"/>
       <c r="F720" s="23"/>
     </row>
-    <row r="721" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="721" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C721" s="24"/>
       <c r="D721" s="22"/>
       <c r="E721" s="22"/>
       <c r="F721" s="22"/>
     </row>
-    <row r="722" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="722" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C722" s="25"/>
       <c r="D722" s="23"/>
       <c r="E722" s="23"/>
       <c r="F722" s="23"/>
     </row>
-    <row r="723" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="723" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C723" s="24"/>
       <c r="D723" s="22"/>
       <c r="E723" s="22"/>
       <c r="F723" s="22"/>
     </row>
-    <row r="724" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="724" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C724" s="25"/>
       <c r="D724" s="23"/>
       <c r="E724" s="23"/>
       <c r="F724" s="23"/>
     </row>
-    <row r="725" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="725" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C725" s="24"/>
       <c r="D725" s="22"/>
       <c r="E725" s="22"/>
       <c r="F725" s="22"/>
     </row>
-    <row r="726" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="726" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C726" s="25"/>
       <c r="D726" s="23"/>
       <c r="E726" s="23"/>
       <c r="F726" s="23"/>
     </row>
-    <row r="727" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="727" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C727" s="24"/>
       <c r="D727" s="22"/>
       <c r="E727" s="22"/>
       <c r="F727" s="22"/>
     </row>
-    <row r="728" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="728" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C728" s="25"/>
       <c r="D728" s="23"/>
       <c r="E728" s="23"/>
       <c r="F728" s="23"/>
     </row>
-    <row r="729" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="729" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C729" s="24"/>
       <c r="D729" s="22"/>
       <c r="E729" s="22"/>
       <c r="F729" s="22"/>
     </row>
-    <row r="730" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="730" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C730" s="25"/>
       <c r="D730" s="23"/>
       <c r="E730" s="23"/>
       <c r="F730" s="23"/>
     </row>
-    <row r="731" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="731" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C731" s="24"/>
       <c r="D731" s="22"/>
       <c r="E731" s="22"/>
       <c r="F731" s="22"/>
     </row>
-    <row r="732" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="732" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C732" s="25"/>
       <c r="D732" s="23"/>
       <c r="E732" s="23"/>
       <c r="F732" s="23"/>
     </row>
-    <row r="733" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="733" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C733" s="24"/>
       <c r="D733" s="22"/>
       <c r="E733" s="22"/>
       <c r="F733" s="22"/>
     </row>
-    <row r="734" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="734" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C734" s="25"/>
       <c r="D734" s="23"/>
       <c r="E734" s="23"/>
       <c r="F734" s="23"/>
     </row>
-    <row r="735" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="735" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C735" s="24"/>
       <c r="D735" s="22"/>
       <c r="E735" s="22"/>
       <c r="F735" s="22"/>
     </row>
-    <row r="736" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="736" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C736" s="25"/>
       <c r="D736" s="23"/>
       <c r="E736" s="23"/>
       <c r="F736" s="23"/>
     </row>
-    <row r="737" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="737" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C737" s="24"/>
       <c r="D737" s="22"/>
       <c r="E737" s="22"/>
       <c r="F737" s="22"/>
     </row>
-    <row r="738" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="738" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C738" s="25"/>
       <c r="D738" s="23"/>
       <c r="E738" s="23"/>
       <c r="F738" s="23"/>
     </row>
-    <row r="739" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="739" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C739" s="24"/>
       <c r="D739" s="22"/>
       <c r="E739" s="22"/>
       <c r="F739" s="22"/>
     </row>
-    <row r="740" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="740" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C740" s="25"/>
       <c r="D740" s="23"/>
       <c r="E740" s="23"/>
       <c r="F740" s="23"/>
     </row>
-    <row r="741" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="741" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C741" s="24"/>
       <c r="D741" s="22"/>
       <c r="E741" s="22"/>
       <c r="F741" s="22"/>
     </row>
-    <row r="742" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="742" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C742" s="25"/>
       <c r="D742" s="23"/>
       <c r="E742" s="23"/>
       <c r="F742" s="23"/>
     </row>
-    <row r="743" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="743" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C743" s="24"/>
       <c r="D743" s="22"/>
       <c r="E743" s="22"/>
       <c r="F743" s="22"/>
     </row>
-    <row r="744" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="744" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C744" s="25"/>
       <c r="D744" s="23"/>
       <c r="E744" s="23"/>
       <c r="F744" s="23"/>
     </row>
-    <row r="745" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="745" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C745" s="24"/>
       <c r="D745" s="22"/>
       <c r="E745" s="22"/>
       <c r="F745" s="22"/>
     </row>
-    <row r="746" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="746" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C746" s="25"/>
       <c r="D746" s="23"/>
       <c r="E746" s="23"/>
       <c r="F746" s="23"/>
     </row>
-    <row r="747" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="747" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C747" s="24"/>
       <c r="D747" s="22"/>
       <c r="E747" s="22"/>
       <c r="F747" s="22"/>
     </row>
-    <row r="748" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="748" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C748" s="25"/>
       <c r="D748" s="23"/>
       <c r="E748" s="23"/>
       <c r="F748" s="23"/>
     </row>
-    <row r="749" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="749" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C749" s="24"/>
       <c r="D749" s="22"/>
       <c r="E749" s="22"/>
       <c r="F749" s="22"/>
     </row>
-    <row r="750" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="750" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C750" s="25"/>
       <c r="D750" s="23"/>
       <c r="E750" s="23"/>
       <c r="F750" s="23"/>
     </row>
-    <row r="751" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="751" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C751" s="24"/>
       <c r="D751" s="22"/>
       <c r="E751" s="22"/>
       <c r="F751" s="22"/>
     </row>
-    <row r="752" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="752" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C752" s="25"/>
       <c r="D752" s="23"/>
       <c r="E752" s="23"/>
       <c r="F752" s="23"/>
     </row>
-    <row r="753" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="753" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C753" s="24"/>
       <c r="D753" s="22"/>
       <c r="E753" s="22"/>
       <c r="F753" s="22"/>
     </row>
-    <row r="754" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="754" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C754" s="25"/>
       <c r="D754" s="23"/>
       <c r="E754" s="23"/>
       <c r="F754" s="23"/>
     </row>
-    <row r="755" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="755" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C755" s="24"/>
       <c r="D755" s="22"/>
       <c r="E755" s="22"/>
       <c r="F755" s="22"/>
     </row>
-    <row r="756" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="756" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C756" s="25"/>
       <c r="D756" s="23"/>
       <c r="E756" s="23"/>
       <c r="F756" s="23"/>
     </row>
-    <row r="757" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="757" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C757" s="24"/>
       <c r="D757" s="22"/>
       <c r="E757" s="22"/>
       <c r="F757" s="22"/>
     </row>
-    <row r="758" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="758" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C758" s="25"/>
       <c r="D758" s="23"/>
       <c r="E758" s="23"/>
       <c r="F758" s="23"/>
     </row>
-    <row r="759" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="759" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C759" s="24"/>
       <c r="D759" s="22"/>
       <c r="E759" s="22"/>
       <c r="F759" s="22"/>
     </row>
-    <row r="760" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="760" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C760" s="25"/>
       <c r="D760" s="23"/>
       <c r="E760" s="23"/>
       <c r="F760" s="23"/>
     </row>
-    <row r="761" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="761" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C761" s="24"/>
       <c r="D761" s="22"/>
       <c r="E761" s="22"/>
       <c r="F761" s="22"/>
     </row>
-    <row r="762" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="762" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C762" s="25"/>
       <c r="D762" s="23"/>
       <c r="E762" s="23"/>
       <c r="F762" s="23"/>
     </row>
-    <row r="763" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="763" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C763" s="24"/>
       <c r="D763" s="22"/>
       <c r="E763" s="22"/>
       <c r="F763" s="22"/>
     </row>
-    <row r="764" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="764" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C764" s="25"/>
       <c r="D764" s="23"/>
       <c r="E764" s="23"/>
       <c r="F764" s="23"/>
     </row>
-    <row r="765" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="765" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C765" s="24"/>
       <c r="D765" s="22"/>
       <c r="E765" s="22"/>
       <c r="F765" s="22"/>
     </row>
-    <row r="766" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="766" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C766" s="25"/>
       <c r="D766" s="23"/>
       <c r="E766" s="23"/>
       <c r="F766" s="23"/>
     </row>
-    <row r="767" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="767" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C767" s="24"/>
       <c r="D767" s="22"/>
       <c r="E767" s="22"/>
       <c r="F767" s="22"/>
     </row>
-    <row r="768" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="768" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C768" s="25"/>
       <c r="D768" s="23"/>
       <c r="E768" s="23"/>
       <c r="F768" s="23"/>
     </row>
-    <row r="769" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="769" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C769" s="24"/>
       <c r="D769" s="22"/>
       <c r="E769" s="22"/>
       <c r="F769" s="22"/>
     </row>
-    <row r="770" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="770" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C770" s="25"/>
       <c r="D770" s="23"/>
       <c r="E770" s="23"/>
       <c r="F770" s="23"/>
     </row>
-    <row r="771" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="771" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C771" s="24"/>
       <c r="D771" s="22"/>
       <c r="E771" s="22"/>
       <c r="F771" s="22"/>
     </row>
-    <row r="772" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="772" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C772" s="25"/>
       <c r="D772" s="23"/>
       <c r="E772" s="23"/>
       <c r="F772" s="23"/>
     </row>
-    <row r="773" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="773" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C773" s="24"/>
       <c r="D773" s="22"/>
       <c r="E773" s="22"/>
       <c r="F773" s="22"/>
     </row>
-    <row r="774" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="774" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C774" s="25"/>
       <c r="D774" s="23"/>
       <c r="E774" s="23"/>
       <c r="F774" s="23"/>
     </row>
-    <row r="775" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="775" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C775" s="24"/>
       <c r="D775" s="22"/>
       <c r="E775" s="22"/>
       <c r="F775" s="22"/>
     </row>
-    <row r="776" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="776" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C776" s="25"/>
       <c r="D776" s="23"/>
       <c r="E776" s="23"/>
       <c r="F776" s="23"/>
     </row>
-    <row r="777" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="777" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C777" s="24"/>
       <c r="D777" s="22"/>
       <c r="E777" s="22"/>
       <c r="F777" s="22"/>
     </row>
-    <row r="778" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="778" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C778" s="25"/>
       <c r="D778" s="23"/>
       <c r="E778" s="23"/>
       <c r="F778" s="23"/>
     </row>
-    <row r="779" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="779" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C779" s="24"/>
       <c r="D779" s="22"/>
       <c r="E779" s="22"/>
       <c r="F779" s="22"/>
     </row>
-    <row r="780" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="780" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C780" s="25"/>
       <c r="D780" s="23"/>
       <c r="E780" s="23"/>
       <c r="F780" s="23"/>
     </row>
-    <row r="781" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="781" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C781" s="24"/>
       <c r="D781" s="22"/>
       <c r="E781" s="22"/>
       <c r="F781" s="22"/>
     </row>
-    <row r="782" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="782" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C782" s="25"/>
       <c r="D782" s="23"/>
       <c r="E782" s="23"/>
       <c r="F782" s="23"/>
     </row>
-    <row r="783" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="783" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C783" s="24"/>
       <c r="D783" s="22"/>
       <c r="E783" s="22"/>
       <c r="F783" s="22"/>
     </row>
-    <row r="784" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="784" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C784" s="25"/>
       <c r="D784" s="23"/>
       <c r="E784" s="23"/>
       <c r="F784" s="23"/>
     </row>
-    <row r="785" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="785" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C785" s="24"/>
       <c r="D785" s="22"/>
       <c r="E785" s="22"/>
       <c r="F785" s="22"/>
     </row>
-    <row r="786" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="786" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C786" s="25"/>
       <c r="D786" s="23"/>
       <c r="E786" s="23"/>
       <c r="F786" s="23"/>
     </row>
-    <row r="787" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="787" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C787" s="24"/>
       <c r="D787" s="22"/>
       <c r="E787" s="22"/>
       <c r="F787" s="22"/>
     </row>
-    <row r="788" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="788" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C788" s="25"/>
       <c r="D788" s="23"/>
       <c r="E788" s="23"/>
       <c r="F788" s="23"/>
     </row>
-    <row r="789" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="789" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C789" s="24"/>
       <c r="D789" s="22"/>
       <c r="E789" s="22"/>
       <c r="F789" s="22"/>
     </row>
-    <row r="790" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="790" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C790" s="25"/>
       <c r="D790" s="23"/>
       <c r="E790" s="23"/>
       <c r="F790" s="23"/>
     </row>
-    <row r="791" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="791" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C791" s="24"/>
       <c r="D791" s="22"/>
       <c r="E791" s="22"/>
       <c r="F791" s="22"/>
     </row>
-    <row r="792" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="792" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C792" s="25"/>
       <c r="D792" s="23"/>
       <c r="E792" s="23"/>
       <c r="F792" s="23"/>
     </row>
-    <row r="793" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="793" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C793" s="24"/>
       <c r="D793" s="22"/>
       <c r="E793" s="22"/>
       <c r="F793" s="22"/>
     </row>
-    <row r="794" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="794" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C794" s="25"/>
       <c r="D794" s="23"/>
       <c r="E794" s="23"/>
       <c r="F794" s="23"/>
     </row>
-    <row r="795" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="795" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C795" s="24"/>
       <c r="D795" s="22"/>
       <c r="E795" s="22"/>
       <c r="F795" s="22"/>
     </row>
-    <row r="796" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="796" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C796" s="25"/>
       <c r="D796" s="23"/>
       <c r="E796" s="23"/>
       <c r="F796" s="23"/>
     </row>
-    <row r="797" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="797" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C797" s="24"/>
       <c r="D797" s="22"/>
       <c r="E797" s="22"/>
       <c r="F797" s="22"/>
     </row>
-    <row r="798" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="798" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C798" s="25"/>
       <c r="D798" s="23"/>
       <c r="E798" s="23"/>
       <c r="F798" s="23"/>
     </row>
-    <row r="799" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="799" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C799" s="24"/>
       <c r="D799" s="22"/>
       <c r="E799" s="22"/>
       <c r="F799" s="22"/>
     </row>
-    <row r="800" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="800" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C800" s="25"/>
       <c r="D800" s="23"/>
       <c r="E800" s="23"/>
       <c r="F800" s="23"/>
     </row>
-    <row r="801" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="801" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C801" s="24"/>
       <c r="D801" s="22"/>
       <c r="E801" s="22"/>
       <c r="F801" s="22"/>
     </row>
-    <row r="802" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="802" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C802" s="25"/>
       <c r="D802" s="23"/>
       <c r="E802" s="23"/>
       <c r="F802" s="23"/>
     </row>
-    <row r="803" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="803" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C803" s="24"/>
       <c r="D803" s="22"/>
       <c r="E803" s="22"/>
       <c r="F803" s="22"/>
     </row>
-    <row r="804" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="804" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C804" s="25"/>
       <c r="D804" s="23"/>
       <c r="E804" s="23"/>
       <c r="F804" s="23"/>
     </row>
-    <row r="805" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="805" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C805" s="24"/>
       <c r="D805" s="22"/>
       <c r="E805" s="22"/>
       <c r="F805" s="22"/>
     </row>
-    <row r="806" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="806" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C806" s="25"/>
       <c r="D806" s="23"/>
       <c r="E806" s="23"/>
       <c r="F806" s="23"/>
     </row>
-    <row r="807" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="807" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C807" s="24"/>
       <c r="D807" s="22"/>
       <c r="E807" s="22"/>
       <c r="F807" s="22"/>
     </row>
-    <row r="808" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="808" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C808" s="25"/>
       <c r="D808" s="23"/>
       <c r="E808" s="23"/>
       <c r="F808" s="23"/>
     </row>
-    <row r="809" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="809" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C809" s="24"/>
       <c r="D809" s="22"/>
       <c r="E809" s="22"/>
       <c r="F809" s="22"/>
     </row>
-    <row r="810" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="810" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C810" s="25"/>
       <c r="D810" s="23"/>
       <c r="E810" s="23"/>
       <c r="F810" s="23"/>
     </row>
-    <row r="811" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="811" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C811" s="24"/>
       <c r="D811" s="22"/>
       <c r="E811" s="22"/>
       <c r="F811" s="22"/>
     </row>
-    <row r="812" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="812" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C812" s="25"/>
       <c r="D812" s="23"/>
       <c r="E812" s="23"/>
       <c r="F812" s="23"/>
     </row>
-    <row r="813" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="813" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C813" s="24"/>
       <c r="D813" s="22"/>
       <c r="E813" s="22"/>
       <c r="F813" s="22"/>
     </row>
-    <row r="814" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="814" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C814" s="25"/>
       <c r="D814" s="23"/>
       <c r="E814" s="23"/>
       <c r="F814" s="23"/>
     </row>
-    <row r="815" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="815" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C815" s="24"/>
       <c r="D815" s="22"/>
       <c r="E815" s="22"/>
       <c r="F815" s="22"/>
     </row>
-    <row r="816" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="816" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C816" s="25"/>
       <c r="D816" s="23"/>
       <c r="E816" s="23"/>
       <c r="F816" s="23"/>
     </row>
-    <row r="817" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="817" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C817" s="24"/>
       <c r="D817" s="22"/>
       <c r="E817" s="22"/>
       <c r="F817" s="22"/>
     </row>
-    <row r="818" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="818" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C818" s="25"/>
       <c r="D818" s="23"/>
       <c r="E818" s="23"/>
       <c r="F818" s="23"/>
     </row>
-    <row r="819" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="819" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C819" s="24"/>
       <c r="D819" s="22"/>
       <c r="E819" s="22"/>
       <c r="F819" s="22"/>
     </row>
-    <row r="820" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="820" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C820" s="25"/>
       <c r="D820" s="23"/>
       <c r="E820" s="23"/>
       <c r="F820" s="23"/>
     </row>
-    <row r="821" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="821" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C821" s="24"/>
       <c r="D821" s="22"/>
       <c r="E821" s="22"/>
       <c r="F821" s="22"/>
     </row>
-    <row r="822" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="822" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C822" s="25"/>
       <c r="D822" s="23"/>
       <c r="E822" s="23"/>
       <c r="F822" s="23"/>
     </row>
-    <row r="823" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="823" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C823" s="24"/>
       <c r="D823" s="22"/>
       <c r="E823" s="22"/>
       <c r="F823" s="22"/>
     </row>
-    <row r="824" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="824" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C824" s="25"/>
       <c r="D824" s="23"/>
       <c r="E824" s="23"/>
       <c r="F824" s="23"/>
     </row>
-    <row r="825" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="825" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C825" s="24"/>
       <c r="D825" s="22"/>
       <c r="E825" s="22"/>
       <c r="F825" s="22"/>
     </row>
-    <row r="826" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="826" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C826" s="25"/>
       <c r="D826" s="23"/>
       <c r="E826" s="23"/>
       <c r="F826" s="23"/>
     </row>
-    <row r="827" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="827" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C827" s="24"/>
       <c r="D827" s="22"/>
       <c r="E827" s="22"/>
       <c r="F827" s="22"/>
     </row>
-    <row r="828" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="828" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C828" s="25"/>
       <c r="D828" s="23"/>
       <c r="E828" s="23"/>
       <c r="F828" s="23"/>
     </row>
-    <row r="829" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="829" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C829" s="24"/>
       <c r="D829" s="22"/>
       <c r="E829" s="22"/>
       <c r="F829" s="22"/>
     </row>
-    <row r="830" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="830" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C830" s="25"/>
       <c r="D830" s="23"/>
       <c r="E830" s="23"/>
       <c r="F830" s="23"/>
     </row>
-    <row r="831" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="831" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C831" s="24"/>
       <c r="D831" s="22"/>
       <c r="E831" s="22"/>
       <c r="F831" s="22"/>
     </row>
-    <row r="832" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="832" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C832" s="25"/>
       <c r="D832" s="23"/>
       <c r="E832" s="23"/>
       <c r="F832" s="23"/>
     </row>
-    <row r="833" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="833" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C833" s="24"/>
       <c r="D833" s="22"/>
       <c r="E833" s="22"/>
       <c r="F833" s="22"/>
     </row>
-    <row r="834" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="834" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C834" s="25"/>
       <c r="D834" s="23"/>
       <c r="E834" s="23"/>
       <c r="F834" s="23"/>
     </row>
-    <row r="835" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="835" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C835" s="24"/>
       <c r="D835" s="22"/>
       <c r="E835" s="22"/>
       <c r="F835" s="22"/>
     </row>
-    <row r="836" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="836" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C836" s="25"/>
       <c r="D836" s="23"/>
       <c r="E836" s="23"/>
       <c r="F836" s="23"/>
     </row>
-    <row r="837" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="837" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C837" s="24"/>
       <c r="D837" s="22"/>
       <c r="E837" s="22"/>
       <c r="F837" s="22"/>
     </row>
-    <row r="838" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="838" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C838" s="25"/>
       <c r="D838" s="23"/>
       <c r="E838" s="23"/>
       <c r="F838" s="23"/>
     </row>
-    <row r="839" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="839" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C839" s="24"/>
       <c r="D839" s="22"/>
       <c r="E839" s="22"/>
       <c r="F839" s="22"/>
     </row>
-    <row r="840" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="840" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C840" s="25"/>
       <c r="D840" s="23"/>
       <c r="E840" s="23"/>
       <c r="F840" s="23"/>
     </row>
-    <row r="841" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="841" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C841" s="24"/>
       <c r="D841" s="22"/>
       <c r="E841" s="22"/>
       <c r="F841" s="22"/>
     </row>
-    <row r="842" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="842" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C842" s="25"/>
       <c r="D842" s="23"/>
       <c r="E842" s="23"/>
       <c r="F842" s="23"/>
     </row>
-    <row r="843" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="843" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C843" s="24"/>
       <c r="D843" s="22"/>
       <c r="E843" s="22"/>
       <c r="F843" s="22"/>
     </row>
-    <row r="844" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="844" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C844" s="25"/>
       <c r="D844" s="23"/>
       <c r="E844" s="23"/>
       <c r="F844" s="23"/>
     </row>
-    <row r="845" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="845" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C845" s="24"/>
       <c r="D845" s="22"/>
       <c r="E845" s="22"/>
       <c r="F845" s="22"/>
     </row>
-    <row r="846" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="846" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C846" s="25"/>
       <c r="D846" s="23"/>
       <c r="E846" s="23"/>
       <c r="F846" s="23"/>
     </row>
-    <row r="847" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="847" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C847" s="24"/>
       <c r="D847" s="22"/>
       <c r="E847" s="22"/>
       <c r="F847" s="22"/>
     </row>
-    <row r="848" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="848" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C848" s="25"/>
       <c r="D848" s="23"/>
       <c r="E848" s="23"/>
       <c r="F848" s="23"/>
     </row>
-    <row r="849" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="849" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C849" s="24"/>
       <c r="D849" s="22"/>
       <c r="E849" s="22"/>
       <c r="F849" s="22"/>
     </row>
-    <row r="850" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="850" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C850" s="25"/>
       <c r="D850" s="23"/>
       <c r="E850" s="23"/>
       <c r="F850" s="23"/>
     </row>
-    <row r="851" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="851" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C851" s="24"/>
       <c r="D851" s="22"/>
       <c r="E851" s="22"/>
       <c r="F851" s="22"/>
     </row>
-    <row r="852" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="852" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C852" s="25"/>
       <c r="D852" s="23"/>
       <c r="E852" s="23"/>
       <c r="F852" s="23"/>
     </row>
-    <row r="853" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="853" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C853" s="24"/>
       <c r="D853" s="22"/>
       <c r="E853" s="22"/>
       <c r="F853" s="22"/>
     </row>
-    <row r="854" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="854" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C854" s="25"/>
       <c r="D854" s="23"/>
       <c r="E854" s="23"/>
       <c r="F854" s="23"/>
     </row>
-    <row r="855" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="855" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C855" s="24"/>
       <c r="D855" s="22"/>
       <c r="E855" s="22"/>
       <c r="F855" s="22"/>
     </row>
-    <row r="856" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="856" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C856" s="25"/>
       <c r="D856" s="23"/>
       <c r="E856" s="23"/>
       <c r="F856" s="23"/>
     </row>
-    <row r="857" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="857" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C857" s="24"/>
       <c r="D857" s="22"/>
       <c r="E857" s="22"/>
       <c r="F857" s="22"/>
     </row>
-    <row r="858" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="858" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C858" s="25"/>
       <c r="D858" s="23"/>
       <c r="E858" s="23"/>
       <c r="F858" s="23"/>
     </row>
-    <row r="859" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="859" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C859" s="24"/>
       <c r="D859" s="22"/>
       <c r="E859" s="22"/>
       <c r="F859" s="22"/>
     </row>
-    <row r="860" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="860" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C860" s="25"/>
       <c r="D860" s="23"/>
       <c r="E860" s="23"/>
       <c r="F860" s="23"/>
     </row>
-    <row r="861" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="861" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C861" s="24"/>
       <c r="D861" s="22"/>
       <c r="E861" s="22"/>
       <c r="F861" s="22"/>
     </row>
-    <row r="862" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="862" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C862" s="25"/>
       <c r="D862" s="23"/>
       <c r="E862" s="23"/>
       <c r="F862" s="23"/>
     </row>
-    <row r="863" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="863" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C863" s="24"/>
       <c r="D863" s="22"/>
       <c r="E863" s="22"/>
       <c r="F863" s="22"/>
     </row>
-    <row r="864" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="864" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C864" s="25"/>
       <c r="D864" s="23"/>
       <c r="E864" s="23"/>
       <c r="F864" s="23"/>
     </row>
-    <row r="865" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="865" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C865" s="24"/>
       <c r="D865" s="22"/>
       <c r="E865" s="22"/>
       <c r="F865" s="22"/>
     </row>
-    <row r="866" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="866" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C866" s="25"/>
       <c r="D866" s="23"/>
       <c r="E866" s="23"/>
       <c r="F866" s="23"/>
     </row>
-    <row r="867" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="867" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C867" s="24"/>
       <c r="D867" s="22"/>
       <c r="E867" s="22"/>
       <c r="F867" s="22"/>
     </row>
-    <row r="868" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="868" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C868" s="25"/>
       <c r="D868" s="23"/>
       <c r="E868" s="23"/>
       <c r="F868" s="23"/>
     </row>
-    <row r="869" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="869" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C869" s="24"/>
       <c r="D869" s="22"/>
       <c r="E869" s="22"/>
       <c r="F869" s="22"/>
     </row>
-    <row r="870" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="870" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C870" s="25"/>
       <c r="D870" s="23"/>
       <c r="E870" s="23"/>
       <c r="F870" s="23"/>
     </row>
-    <row r="871" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="871" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C871" s="24"/>
       <c r="D871" s="22"/>
       <c r="E871" s="22"/>
       <c r="F871" s="22"/>
     </row>
-    <row r="872" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="872" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C872" s="25"/>
       <c r="D872" s="23"/>
       <c r="E872" s="23"/>
       <c r="F872" s="23"/>
     </row>
-    <row r="873" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="873" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C873" s="24"/>
       <c r="D873" s="22"/>
       <c r="E873" s="22"/>
       <c r="F873" s="22"/>
     </row>
-    <row r="874" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="874" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C874" s="25"/>
       <c r="D874" s="23"/>
       <c r="E874" s="23"/>
       <c r="F874" s="23"/>
     </row>
-    <row r="875" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="875" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C875" s="24"/>
       <c r="D875" s="22"/>
       <c r="E875" s="22"/>
       <c r="F875" s="22"/>
     </row>
-    <row r="876" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="876" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C876" s="25"/>
       <c r="D876" s="23"/>
       <c r="E876" s="23"/>
       <c r="F876" s="23"/>
     </row>
-    <row r="877" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="877" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C877" s="24"/>
       <c r="D877" s="22"/>
       <c r="E877" s="22"/>
       <c r="F877" s="22"/>
     </row>
-    <row r="878" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="878" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C878" s="25"/>
       <c r="D878" s="23"/>
       <c r="E878" s="23"/>
       <c r="F878" s="23"/>
     </row>
-    <row r="879" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="879" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C879" s="24"/>
       <c r="D879" s="22"/>
       <c r="E879" s="22"/>
       <c r="F879" s="22"/>
     </row>
-    <row r="880" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="880" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C880" s="25"/>
       <c r="D880" s="23"/>
       <c r="E880" s="23"/>
       <c r="F880" s="23"/>
     </row>
-    <row r="881" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="881" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C881" s="24"/>
       <c r="D881" s="22"/>
       <c r="E881" s="22"/>
       <c r="F881" s="22"/>
     </row>
-    <row r="882" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="882" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C882" s="25"/>
       <c r="D882" s="23"/>
       <c r="E882" s="23"/>
       <c r="F882" s="23"/>
     </row>
-    <row r="883" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="883" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C883" s="24"/>
       <c r="D883" s="22"/>
       <c r="E883" s="22"/>
       <c r="F883" s="22"/>
     </row>
-    <row r="884" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="884" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C884" s="25"/>
       <c r="D884" s="23"/>
       <c r="E884" s="23"/>
       <c r="F884" s="23"/>
     </row>
-    <row r="885" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="885" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C885" s="24"/>
       <c r="D885" s="22"/>
       <c r="E885" s="22"/>
       <c r="F885" s="22"/>
     </row>
-    <row r="886" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="886" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C886" s="25"/>
       <c r="D886" s="23"/>
       <c r="E886" s="23"/>
       <c r="F886" s="23"/>
     </row>
-    <row r="887" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="887" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C887" s="24"/>
       <c r="D887" s="22"/>
       <c r="E887" s="22"/>
       <c r="F887" s="22"/>
     </row>
-    <row r="888" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="888" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C888" s="25"/>
       <c r="D888" s="23"/>
       <c r="E888" s="23"/>
       <c r="F888" s="23"/>
     </row>
-    <row r="889" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="889" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C889" s="24"/>
       <c r="D889" s="22"/>
       <c r="E889" s="22"/>
       <c r="F889" s="22"/>
     </row>
-    <row r="890" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="890" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C890" s="25"/>
       <c r="D890" s="23"/>
       <c r="E890" s="23"/>
       <c r="F890" s="23"/>
     </row>
-    <row r="891" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="891" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C891" s="24"/>
       <c r="D891" s="22"/>
       <c r="E891" s="22"/>
       <c r="F891" s="22"/>
     </row>
-    <row r="892" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="892" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C892" s="25"/>
       <c r="D892" s="23"/>
       <c r="E892" s="23"/>
       <c r="F892" s="23"/>
     </row>
-    <row r="893" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="893" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C893" s="24"/>
       <c r="D893" s="22"/>
       <c r="E893" s="22"/>
       <c r="F893" s="22"/>
     </row>
-    <row r="894" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="894" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C894" s="25"/>
       <c r="D894" s="23"/>
       <c r="E894" s="23"/>
       <c r="F894" s="23"/>
     </row>
-    <row r="895" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="895" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C895" s="24"/>
       <c r="D895" s="22"/>
       <c r="E895" s="22"/>
       <c r="F895" s="22"/>
     </row>
-    <row r="896" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="896" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C896" s="25"/>
       <c r="D896" s="23"/>
       <c r="E896" s="23"/>
       <c r="F896" s="23"/>
     </row>
-    <row r="897" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="897" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C897" s="24"/>
       <c r="D897" s="22"/>
       <c r="E897" s="22"/>
       <c r="F897" s="22"/>
     </row>
-    <row r="898" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="898" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C898" s="25"/>
       <c r="D898" s="23"/>
       <c r="E898" s="23"/>
       <c r="F898" s="23"/>
     </row>
-    <row r="899" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="899" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C899" s="24"/>
       <c r="D899" s="22"/>
       <c r="E899" s="22"/>
       <c r="F899" s="22"/>
     </row>
-    <row r="900" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="900" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C900" s="25"/>
       <c r="D900" s="23"/>
       <c r="E900" s="23"/>
       <c r="F900" s="23"/>
     </row>
-    <row r="901" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="901" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C901" s="24"/>
       <c r="D901" s="22"/>
       <c r="E901" s="22"/>
       <c r="F901" s="22"/>
     </row>
-    <row r="902" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="902" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C902" s="25"/>
       <c r="D902" s="23"/>
       <c r="E902" s="23"/>
       <c r="F902" s="23"/>
     </row>
-    <row r="903" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="903" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C903" s="24"/>
       <c r="D903" s="22"/>
       <c r="E903" s="22"/>
       <c r="F903" s="22"/>
     </row>
-    <row r="904" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="904" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C904" s="25"/>
       <c r="D904" s="23"/>
       <c r="E904" s="23"/>
       <c r="F904" s="23"/>
     </row>
-    <row r="905" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="905" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C905" s="24"/>
       <c r="D905" s="22"/>
       <c r="E905" s="22"/>
       <c r="F905" s="22"/>
     </row>
-    <row r="906" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="906" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C906" s="25"/>
       <c r="D906" s="23"/>
       <c r="E906" s="23"/>
       <c r="F906" s="23"/>
     </row>
-    <row r="907" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="907" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C907" s="24"/>
       <c r="D907" s="22"/>
       <c r="E907" s="22"/>
       <c r="F907" s="22"/>
     </row>
-    <row r="908" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="908" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C908" s="25"/>
       <c r="D908" s="23"/>
       <c r="E908" s="23"/>
       <c r="F908" s="23"/>
     </row>
-    <row r="909" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="909" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C909" s="24"/>
       <c r="D909" s="22"/>
       <c r="E909" s="22"/>
       <c r="F909" s="22"/>
     </row>
-    <row r="910" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="910" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C910" s="25"/>
       <c r="D910" s="23"/>
       <c r="E910" s="23"/>
       <c r="F910" s="23"/>
     </row>
-    <row r="911" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="911" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C911" s="24"/>
       <c r="D911" s="22"/>
       <c r="E911" s="22"/>
       <c r="F911" s="22"/>
     </row>
-    <row r="912" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="912" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C912" s="25"/>
       <c r="D912" s="23"/>
       <c r="E912" s="23"/>
       <c r="F912" s="23"/>
     </row>
-    <row r="913" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="913" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C913" s="24"/>
       <c r="D913" s="22"/>
       <c r="E913" s="22"/>
       <c r="F913" s="22"/>
     </row>
-    <row r="914" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="914" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C914" s="25"/>
       <c r="D914" s="23"/>
       <c r="E914" s="23"/>
       <c r="F914" s="23"/>
     </row>
-    <row r="915" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="915" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C915" s="24"/>
       <c r="D915" s="22"/>
       <c r="E915" s="22"/>
       <c r="F915" s="22"/>
     </row>
-    <row r="916" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="916" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C916" s="25"/>
       <c r="D916" s="23"/>
       <c r="E916" s="23"/>
       <c r="F916" s="23"/>
     </row>
-    <row r="917" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="917" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C917" s="24"/>
       <c r="D917" s="22"/>
       <c r="E917" s="22"/>
       <c r="F917" s="22"/>
     </row>
-    <row r="918" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="918" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C918" s="25"/>
       <c r="D918" s="23"/>
       <c r="E918" s="23"/>
       <c r="F918" s="23"/>
     </row>
-    <row r="919" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="919" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C919" s="24"/>
       <c r="D919" s="22"/>
       <c r="E919" s="22"/>
       <c r="F919" s="22"/>
     </row>
-    <row r="920" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="920" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C920" s="25"/>
       <c r="D920" s="23"/>
       <c r="E920" s="23"/>
       <c r="F920" s="23"/>
     </row>
-    <row r="921" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="921" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C921" s="24"/>
       <c r="D921" s="22"/>
       <c r="E921" s="22"/>
       <c r="F921" s="22"/>
     </row>
-    <row r="922" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="922" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C922" s="25"/>
       <c r="D922" s="23"/>
       <c r="E922" s="23"/>
       <c r="F922" s="23"/>
     </row>
-    <row r="923" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="923" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C923" s="24"/>
       <c r="D923" s="22"/>
       <c r="E923" s="22"/>
       <c r="F923" s="22"/>
     </row>
-    <row r="924" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="924" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C924" s="25"/>
       <c r="D924" s="23"/>
       <c r="E924" s="23"/>
       <c r="F924" s="23"/>
     </row>
-    <row r="925" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="925" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C925" s="24"/>
       <c r="D925" s="22"/>
       <c r="E925" s="22"/>
       <c r="F925" s="22"/>
     </row>
-    <row r="926" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="926" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C926" s="25"/>
       <c r="D926" s="23"/>
       <c r="E926" s="23"/>
       <c r="F926" s="23"/>
     </row>
-    <row r="927" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="927" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C927" s="24"/>
       <c r="D927" s="22"/>
       <c r="E927" s="22"/>
       <c r="F927" s="22"/>
     </row>
-    <row r="928" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="928" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C928" s="25"/>
       <c r="D928" s="23"/>
       <c r="E928" s="23"/>
       <c r="F928" s="23"/>
     </row>
-    <row r="929" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="929" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C929" s="24"/>
       <c r="D929" s="22"/>
       <c r="E929" s="22"/>
       <c r="F929" s="22"/>
     </row>
-    <row r="930" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="930" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C930" s="25"/>
       <c r="D930" s="23"/>
       <c r="E930" s="23"/>
       <c r="F930" s="23"/>
     </row>
-    <row r="931" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="931" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C931" s="24"/>
       <c r="D931" s="22"/>
       <c r="E931" s="22"/>
       <c r="F931" s="22"/>
     </row>
-    <row r="932" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="932" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C932" s="25"/>
       <c r="D932" s="23"/>
       <c r="E932" s="23"/>
       <c r="F932" s="23"/>
     </row>
-    <row r="933" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="933" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C933" s="24"/>
       <c r="D933" s="22"/>
       <c r="E933" s="22"/>
       <c r="F933" s="22"/>
     </row>
-    <row r="934" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="934" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C934" s="25"/>
       <c r="D934" s="23"/>
       <c r="E934" s="23"/>
       <c r="F934" s="23"/>
     </row>
-    <row r="935" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="935" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C935" s="24"/>
       <c r="D935" s="22"/>
       <c r="E935" s="22"/>
       <c r="F935" s="22"/>
     </row>
-    <row r="936" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="936" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C936" s="25"/>
       <c r="D936" s="23"/>
       <c r="E936" s="23"/>
       <c r="F936" s="23"/>
     </row>
-    <row r="937" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="937" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C937" s="24"/>
       <c r="D937" s="22"/>
       <c r="E937" s="22"/>
       <c r="F937" s="22"/>
     </row>
-    <row r="938" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="938" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C938" s="25"/>
       <c r="D938" s="23"/>
       <c r="E938" s="23"/>
       <c r="F938" s="23"/>
     </row>
-    <row r="939" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="939" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C939" s="24"/>
       <c r="D939" s="22"/>
       <c r="E939" s="22"/>
       <c r="F939" s="22"/>
     </row>
-    <row r="940" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="940" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C940" s="25"/>
       <c r="D940" s="23"/>
       <c r="E940" s="23"/>
       <c r="F940" s="23"/>
     </row>
-    <row r="941" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="941" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C941" s="24"/>
       <c r="D941" s="22"/>
       <c r="E941" s="22"/>
       <c r="F941" s="22"/>
     </row>
-    <row r="942" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="942" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C942" s="25"/>
       <c r="D942" s="23"/>
       <c r="E942" s="23"/>
       <c r="F942" s="23"/>
     </row>
-    <row r="943" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="943" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C943" s="24"/>
       <c r="D943" s="22"/>
       <c r="E943" s="22"/>
       <c r="F943" s="22"/>
     </row>
-    <row r="944" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="944" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C944" s="25"/>
       <c r="D944" s="23"/>
       <c r="E944" s="23"/>
       <c r="F944" s="23"/>
     </row>
-    <row r="945" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="945" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C945" s="24"/>
       <c r="D945" s="22"/>
       <c r="E945" s="22"/>
       <c r="F945" s="22"/>
     </row>
-    <row r="946" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="946" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C946" s="25"/>
       <c r="D946" s="23"/>
       <c r="E946" s="23"/>
       <c r="F946" s="23"/>
     </row>
-    <row r="947" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="947" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C947" s="24"/>
       <c r="D947" s="22"/>
       <c r="E947" s="22"/>
       <c r="F947" s="22"/>
     </row>
-    <row r="948" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="948" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C948" s="25"/>
       <c r="D948" s="23"/>
       <c r="E948" s="23"/>
       <c r="F948" s="23"/>
     </row>
-    <row r="949" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="949" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C949" s="24"/>
       <c r="D949" s="22"/>
       <c r="E949" s="22"/>
       <c r="F949" s="22"/>
     </row>
-    <row r="950" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="950" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C950" s="25"/>
       <c r="D950" s="23"/>
       <c r="E950" s="23"/>
       <c r="F950" s="23"/>
     </row>
-    <row r="951" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="951" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C951" s="24"/>
       <c r="D951" s="22"/>
       <c r="E951" s="22"/>
       <c r="F951" s="22"/>
     </row>
-    <row r="952" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="952" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C952" s="25"/>
       <c r="D952" s="23"/>
       <c r="E952" s="23"/>
       <c r="F952" s="23"/>
     </row>
-    <row r="953" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="953" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C953" s="24"/>
       <c r="D953" s="22"/>
       <c r="E953" s="22"/>
       <c r="F953" s="22"/>
     </row>
-    <row r="954" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="954" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C954" s="25"/>
       <c r="D954" s="23"/>
       <c r="E954" s="23"/>
       <c r="F954" s="23"/>
     </row>
-    <row r="955" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="955" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C955" s="24"/>
       <c r="D955" s="22"/>
       <c r="E955" s="22"/>
       <c r="F955" s="22"/>
     </row>
-    <row r="956" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="956" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C956" s="25"/>
       <c r="D956" s="23"/>
       <c r="E956" s="23"/>
       <c r="F956" s="23"/>
     </row>
-    <row r="957" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="957" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C957" s="24"/>
       <c r="D957" s="22"/>
       <c r="E957" s="22"/>
       <c r="F957" s="22"/>
     </row>
-    <row r="958" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="958" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C958" s="25"/>
       <c r="D958" s="23"/>
       <c r="E958" s="23"/>
       <c r="F958" s="23"/>
     </row>
-    <row r="959" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="959" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C959" s="24"/>
       <c r="D959" s="22"/>
       <c r="E959" s="22"/>
       <c r="F959" s="22"/>
     </row>
-    <row r="960" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="960" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C960" s="25"/>
       <c r="D960" s="23"/>
       <c r="E960" s="23"/>
       <c r="F960" s="23"/>
     </row>
-    <row r="961" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="961" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C961" s="24"/>
       <c r="D961" s="22"/>
       <c r="E961" s="22"/>
       <c r="F961" s="22"/>
     </row>
-    <row r="962" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="962" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C962" s="25"/>
       <c r="D962" s="23"/>
       <c r="E962" s="23"/>
       <c r="F962" s="23"/>
     </row>
-    <row r="963" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="963" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C963" s="24"/>
       <c r="D963" s="22"/>
       <c r="E963" s="22"/>
       <c r="F963" s="22"/>
     </row>
-    <row r="964" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="964" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C964" s="25"/>
       <c r="D964" s="23"/>
       <c r="E964" s="23"/>
       <c r="F964" s="23"/>
     </row>
-    <row r="965" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="965" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C965" s="24"/>
       <c r="D965" s="22"/>
       <c r="E965" s="22"/>
       <c r="F965" s="22"/>
     </row>
-    <row r="966" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="966" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C966" s="25"/>
       <c r="D966" s="23"/>
       <c r="E966" s="23"/>
       <c r="F966" s="23"/>
     </row>
-    <row r="967" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="967" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C967" s="24"/>
       <c r="D967" s="22"/>
       <c r="E967" s="22"/>
       <c r="F967" s="22"/>
     </row>
-    <row r="968" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="968" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C968" s="25"/>
       <c r="D968" s="23"/>
       <c r="E968" s="23"/>
       <c r="F968" s="23"/>
     </row>
-    <row r="969" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="969" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C969" s="24"/>
       <c r="D969" s="22"/>
       <c r="E969" s="22"/>
       <c r="F969" s="22"/>
     </row>
-    <row r="970" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="970" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C970" s="25"/>
       <c r="D970" s="23"/>
       <c r="E970" s="23"/>
       <c r="F970" s="23"/>
     </row>
-    <row r="971" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="971" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C971" s="24"/>
       <c r="D971" s="22"/>
       <c r="E971" s="22"/>
       <c r="F971" s="22"/>
     </row>
-    <row r="972" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="972" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C972" s="25"/>
       <c r="D972" s="23"/>
       <c r="E972" s="23"/>
       <c r="F972" s="23"/>
     </row>
-    <row r="973" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="973" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C973" s="24"/>
       <c r="D973" s="22"/>
       <c r="E973" s="22"/>
       <c r="F973" s="22"/>
     </row>
-    <row r="974" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="974" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C974" s="25"/>
       <c r="D974" s="23"/>
       <c r="E974" s="23"/>
       <c r="F974" s="23"/>
     </row>
-    <row r="975" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="975" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C975" s="24"/>
       <c r="D975" s="22"/>
       <c r="E975" s="22"/>
       <c r="F975" s="22"/>
     </row>
-    <row r="976" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="976" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C976" s="25"/>
       <c r="D976" s="23"/>
       <c r="E976" s="23"/>
       <c r="F976" s="23"/>
     </row>
-    <row r="977" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="977" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C977" s="24"/>
       <c r="D977" s="22"/>
       <c r="E977" s="22"/>
       <c r="F977" s="22"/>
     </row>
-    <row r="978" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="978" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C978" s="25"/>
       <c r="D978" s="23"/>
       <c r="E978" s="23"/>
       <c r="F978" s="23"/>
     </row>
-    <row r="979" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="979" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C979" s="24"/>
       <c r="D979" s="22"/>
       <c r="E979" s="22"/>
       <c r="F979" s="22"/>
     </row>
-    <row r="980" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="980" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C980" s="25"/>
       <c r="D980" s="23"/>
       <c r="E980" s="23"/>
       <c r="F980" s="23"/>
     </row>
-    <row r="981" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="981" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C981" s="24"/>
       <c r="D981" s="22"/>
       <c r="E981" s="22"/>
       <c r="F981" s="22"/>
     </row>
-    <row r="982" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="982" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C982" s="25"/>
       <c r="D982" s="23"/>
       <c r="E982" s="23"/>
       <c r="F982" s="23"/>
     </row>
-    <row r="983" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="983" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C983" s="24"/>
       <c r="D983" s="22"/>
       <c r="E983" s="22"/>
       <c r="F983" s="22"/>
     </row>
-    <row r="984" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="984" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C984" s="25"/>
       <c r="D984" s="23"/>
       <c r="E984" s="23"/>
       <c r="F984" s="23"/>
     </row>
-    <row r="985" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="985" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C985" s="24"/>
       <c r="D985" s="22"/>
       <c r="E985" s="22"/>
       <c r="F985" s="22"/>
     </row>
-    <row r="986" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="986" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C986" s="25"/>
       <c r="D986" s="23"/>
       <c r="E986" s="23"/>
       <c r="F986" s="23"/>
     </row>
-    <row r="987" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="987" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C987" s="24"/>
       <c r="D987" s="22"/>
       <c r="E987" s="22"/>
       <c r="F987" s="22"/>
     </row>
-    <row r="988" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="988" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C988" s="25"/>
       <c r="D988" s="23"/>
       <c r="E988" s="23"/>
       <c r="F988" s="23"/>
     </row>
-    <row r="989" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="989" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C989" s="24"/>
       <c r="D989" s="22"/>
       <c r="E989" s="22"/>
       <c r="F989" s="22"/>
     </row>
-    <row r="990" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="990" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C990" s="25"/>
       <c r="D990" s="23"/>
       <c r="E990" s="23"/>
       <c r="F990" s="23"/>
     </row>
-    <row r="991" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="991" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C991" s="24"/>
       <c r="D991" s="22"/>
       <c r="E991" s="22"/>
       <c r="F991" s="22"/>
     </row>
-    <row r="992" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="992" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C992" s="25"/>
       <c r="D992" s="23"/>
       <c r="E992" s="23"/>
       <c r="F992" s="23"/>
     </row>
-    <row r="993" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="993" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C993" s="24"/>
       <c r="D993" s="22"/>
       <c r="E993" s="22"/>
       <c r="F993" s="22"/>
     </row>
-    <row r="994" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="994" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C994" s="25"/>
       <c r="D994" s="23"/>
       <c r="E994" s="23"/>
       <c r="F994" s="23"/>
     </row>
-    <row r="995" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="995" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C995" s="24"/>
       <c r="D995" s="22"/>
       <c r="E995" s="22"/>
       <c r="F995" s="22"/>
     </row>
-    <row r="996" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="996" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C996" s="25"/>
       <c r="D996" s="23"/>
       <c r="E996" s="23"/>
       <c r="F996" s="23"/>
     </row>
-    <row r="997" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="997" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C997" s="24"/>
       <c r="D997" s="22"/>
       <c r="E997" s="22"/>
       <c r="F997" s="22"/>
     </row>
-    <row r="998" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="998" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C998" s="25"/>
       <c r="D998" s="23"/>
       <c r="E998" s="23"/>
       <c r="F998" s="23"/>
     </row>
-    <row r="999" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="999" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C999" s="24"/>
       <c r="D999" s="22"/>
       <c r="E999" s="22"/>
       <c r="F999" s="22"/>
     </row>
-    <row r="1000" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="1000" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C1000" s="25"/>
       <c r="D1000" s="23"/>
       <c r="E1000" s="23"/>
@@ -17697,14 +17708,14 @@
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="B1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="41.6640625" customWidth="1"/>
+    <col min="2" max="2" width="41.7109375" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1" s="31" t="s">
         <v>26</v>
       </c>
@@ -17715,80 +17726,80 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>6675</v>
+        <v>6720</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>29</v>
       </c>

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45EB74C-FF32-48B6-9C04-C2DAA7149C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CACC6C7E-C3F3-454F-A02E-230AC2183C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
+    <workbookView xWindow="-6165" yWindow="-15435" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="101">
   <si>
     <t>Week:</t>
   </si>
@@ -338,6 +338,12 @@
   </si>
   <si>
     <t>Preparing for Final Deliverables</t>
+  </si>
+  <si>
+    <t>Fixing domain issues</t>
+  </si>
+  <si>
+    <t>Built CM, IA, IR</t>
   </si>
 </sst>
 </file>
@@ -1917,10 +1923,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6720</c:v>
+                  <c:v>6975</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1980</c:v>
+                  <c:v>1725</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12133,16 +12139,32 @@
       </c>
     </row>
     <row r="76" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C76" s="25"/>
-      <c r="D76" s="23"/>
-      <c r="E76" s="23"/>
-      <c r="F76" s="23"/>
+      <c r="C76" s="33">
+        <v>45989</v>
+      </c>
+      <c r="D76" s="23">
+        <v>30</v>
+      </c>
+      <c r="E76" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F76" s="23" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="77" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C77" s="24"/>
-      <c r="D77" s="22"/>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
+      <c r="C77" s="32">
+        <v>45989</v>
+      </c>
+      <c r="D77" s="22">
+        <v>225</v>
+      </c>
+      <c r="E77" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" s="22" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="78" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C78" s="25"/>
@@ -17732,11 +17754,11 @@
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>6720</v>
+        <v>6975</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>1980</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CACC6C7E-C3F3-454F-A02E-230AC2183C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CEBA2FD-8828-4B44-A613-D9B6285D94FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-6165" yWindow="-15435" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="102">
   <si>
     <t>Week:</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>Built CM, IA, IR</t>
+  </si>
+  <si>
+    <t>Built MA, MP</t>
   </si>
 </sst>
 </file>
@@ -1923,10 +1926,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6975</c:v>
+                  <c:v>7155</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1725</c:v>
+                  <c:v>1545</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12167,10 +12170,18 @@
       </c>
     </row>
     <row r="78" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C78" s="25"/>
-      <c r="D78" s="23"/>
-      <c r="E78" s="23"/>
-      <c r="F78" s="23"/>
+      <c r="C78" s="33">
+        <v>45990</v>
+      </c>
+      <c r="D78" s="23">
+        <v>180</v>
+      </c>
+      <c r="E78" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F78" s="23" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="79" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C79" s="24"/>
@@ -17754,11 +17765,11 @@
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>6975</v>
+        <v>7155</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>1725</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CEBA2FD-8828-4B44-A613-D9B6285D94FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0CF504-1C5C-41DE-8A42-C958E1D5D0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6165" yWindow="-15435" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="103">
   <si>
     <t>Week:</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>Built MA, MP</t>
+  </si>
+  <si>
+    <t>wrote system vision and stakeholder documents., built capstone board</t>
   </si>
 </sst>
 </file>
@@ -1926,10 +1929,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7155</c:v>
+                  <c:v>7455</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1545</c:v>
+                  <c:v>1245</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12184,10 +12187,18 @@
       </c>
     </row>
     <row r="79" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C79" s="24"/>
-      <c r="D79" s="22"/>
-      <c r="E79" s="22"/>
-      <c r="F79" s="22"/>
+      <c r="C79" s="32">
+        <v>45991</v>
+      </c>
+      <c r="D79" s="22">
+        <v>300</v>
+      </c>
+      <c r="E79" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F79" s="22" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="80" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C80" s="25"/>
@@ -17765,11 +17776,11 @@
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>7155</v>
+        <v>7455</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>1545</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0CF504-1C5C-41DE-8A42-C958E1D5D0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{120E6DDB-7BE2-43C7-A902-71B6FA73F2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="105">
   <si>
     <t>Week:</t>
   </si>
@@ -350,6 +350,12 @@
   </si>
   <si>
     <t>wrote system vision and stakeholder documents., built capstone board</t>
+  </si>
+  <si>
+    <t>Fixed documentation</t>
+  </si>
+  <si>
+    <t>Built PS,PE,RA,CA and fixed some minor errors</t>
   </si>
 </sst>
 </file>
@@ -1929,10 +1935,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7455</c:v>
+                  <c:v>7725</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1245</c:v>
+                  <c:v>975</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3156,16 +3162,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>937260</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>173355</xdr:rowOff>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>937260</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>1905</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3180,8 +3186,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10732770" y="354330"/>
-          <a:ext cx="0" cy="2543175"/>
+          <a:off x="12489180" y="363855"/>
+          <a:ext cx="0" cy="2571750"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -10642,20 +10648,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P30"/>
-  <sheetFormatPr defaultColWidth="16.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="16.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="16.28515625" customWidth="1"/>
-    <col min="12" max="13" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.28515625" customWidth="1"/>
+    <col min="3" max="4" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="16.33203125" customWidth="1"/>
+    <col min="12" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -10690,7 +10696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
@@ -10739,7 +10745,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="39" t="s">
         <v>4</v>
       </c>
@@ -10762,7 +10768,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="40"/>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -10777,7 +10783,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="36"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="40"/>
       <c r="B5" s="45" t="s">
         <v>4</v>
@@ -10792,7 +10798,7 @@
       <c r="J5" s="3"/>
       <c r="K5" s="36"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
         <v>13</v>
       </c>
@@ -10809,7 +10815,7 @@
       <c r="J6" s="3"/>
       <c r="K6" s="36"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="41"/>
       <c r="B7" s="3"/>
       <c r="C7" s="8"/>
@@ -10824,7 +10830,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="36"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="41"/>
       <c r="B8" s="3"/>
       <c r="C8" s="8"/>
@@ -10839,7 +10845,7 @@
       <c r="J8" s="3"/>
       <c r="K8" s="36"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="41"/>
       <c r="B9" s="3"/>
       <c r="C9" s="8"/>
@@ -10854,7 +10860,7 @@
       <c r="J9" s="3"/>
       <c r="K9" s="36"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="43" t="s">
         <v>14</v>
       </c>
@@ -10871,7 +10877,7 @@
       <c r="J10" s="3"/>
       <c r="K10" s="36"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="43"/>
       <c r="B11" s="3"/>
       <c r="C11" s="8"/>
@@ -10886,7 +10892,7 @@
       <c r="J11" s="3"/>
       <c r="K11" s="36"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="43"/>
       <c r="B12" s="3"/>
       <c r="C12" s="8"/>
@@ -10901,7 +10907,7 @@
       <c r="J12" s="3"/>
       <c r="K12" s="36"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="43"/>
       <c r="B13" s="3"/>
       <c r="C13" s="8"/>
@@ -10916,7 +10922,7 @@
       <c r="J13" s="3"/>
       <c r="K13" s="36"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="43"/>
       <c r="B14" s="3"/>
       <c r="C14" s="8"/>
@@ -10931,7 +10937,7 @@
       <c r="J14" s="3"/>
       <c r="K14" s="36"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="29"/>
       <c r="B15" s="3"/>
       <c r="C15" s="8"/>
@@ -10946,7 +10952,7 @@
       <c r="J15" s="38"/>
       <c r="K15" s="36"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="30" t="s">
         <v>15</v>
       </c>
@@ -10963,7 +10969,7 @@
       <c r="J16" s="42"/>
       <c r="K16" s="37"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="34" t="s">
         <v>36</v>
       </c>
@@ -10971,7 +10977,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="35" t="s">
         <v>29</v>
       </c>
@@ -10979,7 +10985,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="35" t="s">
         <v>4</v>
       </c>
@@ -10987,12 +10993,12 @@
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="35" t="s">
         <v>5</v>
       </c>
@@ -11000,7 +11006,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="35" t="s">
         <v>6</v>
       </c>
@@ -11008,7 +11014,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="35" t="s">
         <v>28</v>
       </c>
@@ -11016,7 +11022,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="35" t="s">
         <v>7</v>
       </c>
@@ -11024,7 +11030,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="35" t="s">
         <v>8</v>
       </c>
@@ -11032,7 +11038,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="35" t="s">
         <v>9</v>
       </c>
@@ -11040,7 +11046,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="35" t="s">
         <v>19</v>
       </c>
@@ -11048,7 +11054,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="35" t="s">
         <v>27</v>
       </c>
@@ -11056,7 +11062,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="35" t="s">
         <v>38</v>
       </c>
@@ -11090,15 +11096,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8154930E-2F36-41CB-8896-D63BC278B832}">
   <dimension ref="C1:F1000"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="21.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
-    <col min="5" max="5" width="38.5703125" customWidth="1"/>
-    <col min="6" max="6" width="114.7109375" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" customWidth="1"/>
+    <col min="5" max="5" width="38.5546875" customWidth="1"/>
+    <col min="6" max="6" width="114.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C1" s="26" t="s">
         <v>22</v>
       </c>
@@ -11112,7 +11118,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C2" s="28">
         <v>45927</v>
       </c>
@@ -11126,7 +11132,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C3" s="32">
         <v>45927</v>
       </c>
@@ -11140,7 +11146,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C4" s="33">
         <v>45928</v>
       </c>
@@ -11154,7 +11160,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C5" s="32">
         <v>45928</v>
       </c>
@@ -11168,7 +11174,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C6" s="33">
         <v>45929</v>
       </c>
@@ -11182,7 +11188,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C7" s="32">
         <v>45934</v>
       </c>
@@ -11196,7 +11202,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C8" s="33">
         <v>45934</v>
       </c>
@@ -11210,7 +11216,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C9" s="32">
         <v>45934</v>
       </c>
@@ -11224,7 +11230,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C10" s="33">
         <v>45935</v>
       </c>
@@ -11238,7 +11244,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C11" s="32">
         <v>45936</v>
       </c>
@@ -11252,7 +11258,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C12" s="33">
         <v>45940</v>
       </c>
@@ -11264,7 +11270,7 @@
       </c>
       <c r="F12" s="23"/>
     </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C13" s="32">
         <v>45941</v>
       </c>
@@ -11276,7 +11282,7 @@
       </c>
       <c r="F13" s="22"/>
     </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C14" s="33">
         <v>45942</v>
       </c>
@@ -11290,7 +11296,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C15" s="32">
         <v>45944</v>
       </c>
@@ -11304,7 +11310,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C16" s="33">
         <v>45944</v>
       </c>
@@ -11318,7 +11324,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C17" s="32">
         <v>45944</v>
       </c>
@@ -11332,7 +11338,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C18" s="33">
         <v>45944</v>
       </c>
@@ -11346,7 +11352,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C19" s="32">
         <v>45944</v>
       </c>
@@ -11360,7 +11366,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C20" s="33">
         <v>45945</v>
       </c>
@@ -11374,7 +11380,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C21" s="32">
         <v>45945</v>
       </c>
@@ -11388,7 +11394,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C22" s="33">
         <v>45945</v>
       </c>
@@ -11402,7 +11408,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C23" s="32">
         <v>45946</v>
       </c>
@@ -11416,7 +11422,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C24" s="33">
         <v>45946</v>
       </c>
@@ -11430,7 +11436,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C25" s="32">
         <v>45946</v>
       </c>
@@ -11444,7 +11450,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C26" s="33">
         <v>45946</v>
       </c>
@@ -11458,7 +11464,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C27" s="32">
         <v>45946</v>
       </c>
@@ -11472,7 +11478,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C28" s="33">
         <v>45946</v>
       </c>
@@ -11486,7 +11492,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C29" s="32">
         <v>45950</v>
       </c>
@@ -11500,7 +11506,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C30" s="33">
         <v>45950</v>
       </c>
@@ -11514,7 +11520,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C31" s="32">
         <v>45950</v>
       </c>
@@ -11528,7 +11534,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C32" s="33">
         <v>45951</v>
       </c>
@@ -11542,7 +11548,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C33" s="32">
         <v>45951</v>
       </c>
@@ -11556,7 +11562,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C34" s="33">
         <v>45955</v>
       </c>
@@ -11570,7 +11576,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C35" s="32">
         <v>45956</v>
       </c>
@@ -11584,7 +11590,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C36" s="33">
         <v>45956</v>
       </c>
@@ -11598,7 +11604,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C37" s="32">
         <v>45957</v>
       </c>
@@ -11612,7 +11618,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C38" s="33">
         <v>45958</v>
       </c>
@@ -11626,7 +11632,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C39" s="32">
         <v>45958</v>
       </c>
@@ -11640,7 +11646,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C40" s="33">
         <v>45960</v>
       </c>
@@ -11654,7 +11660,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C41" s="32">
         <v>45961</v>
       </c>
@@ -11668,7 +11674,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C42" s="33">
         <v>45962</v>
       </c>
@@ -11682,7 +11688,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C43" s="32">
         <v>45962</v>
       </c>
@@ -11696,7 +11702,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C44" s="33">
         <v>45963</v>
       </c>
@@ -11710,7 +11716,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="45" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C45" s="32">
         <v>45963</v>
       </c>
@@ -11724,7 +11730,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C46" s="33">
         <v>45964</v>
       </c>
@@ -11738,7 +11744,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C47" s="32">
         <v>45964</v>
       </c>
@@ -11752,7 +11758,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="48" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C48" s="33">
         <v>45965</v>
       </c>
@@ -11766,7 +11772,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C49" s="32">
         <v>45965</v>
       </c>
@@ -11780,7 +11786,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C50" s="33">
         <v>45969</v>
       </c>
@@ -11794,7 +11800,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="51" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C51" s="32">
         <v>45970</v>
       </c>
@@ -11808,7 +11814,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C52" s="33">
         <v>45971</v>
       </c>
@@ -11822,7 +11828,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C53" s="32">
         <v>45971</v>
       </c>
@@ -11836,7 +11842,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C54" s="33">
         <v>45972</v>
       </c>
@@ -11850,7 +11856,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C55" s="32">
         <v>45974</v>
       </c>
@@ -11864,7 +11870,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C56" s="33">
         <v>45974</v>
       </c>
@@ -11878,7 +11884,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="57" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C57" s="32">
         <v>45974</v>
       </c>
@@ -11892,7 +11898,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C58" s="33">
         <v>45975</v>
       </c>
@@ -11906,7 +11912,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C59" s="32">
         <v>45976</v>
       </c>
@@ -11920,7 +11926,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C60" s="33">
         <v>45976</v>
       </c>
@@ -11934,7 +11940,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C61" s="32">
         <v>45977</v>
       </c>
@@ -11948,7 +11954,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C62" s="33">
         <v>45977</v>
       </c>
@@ -11962,7 +11968,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="63" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C63" s="32">
         <v>45978</v>
       </c>
@@ -11976,7 +11982,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="64" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C64" s="33">
         <v>45980</v>
       </c>
@@ -11990,7 +11996,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="65" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C65" s="32">
         <v>45981</v>
       </c>
@@ -12004,7 +12010,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="66" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C66" s="33">
         <v>45981</v>
       </c>
@@ -12018,7 +12024,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="67" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C67" s="32">
         <v>45982</v>
       </c>
@@ -12032,7 +12038,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C68" s="33">
         <v>45983</v>
       </c>
@@ -12046,7 +12052,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="69" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C69" s="32">
         <v>45983</v>
       </c>
@@ -12060,7 +12066,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="70" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C70" s="33">
         <v>45984</v>
       </c>
@@ -12074,7 +12080,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="71" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C71" s="32">
         <v>45984</v>
       </c>
@@ -12088,7 +12094,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="72" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C72" s="33">
         <v>45984</v>
       </c>
@@ -12102,7 +12108,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="73" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C73" s="32">
         <v>45984</v>
       </c>
@@ -12116,7 +12122,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="74" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C74" s="33">
         <v>45984</v>
       </c>
@@ -12130,7 +12136,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="75" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C75" s="32">
         <v>45985</v>
       </c>
@@ -12144,7 +12150,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="76" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C76" s="33">
         <v>45989</v>
       </c>
@@ -12158,7 +12164,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="77" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C77" s="32">
         <v>45989</v>
       </c>
@@ -12172,7 +12178,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="78" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C78" s="33">
         <v>45990</v>
       </c>
@@ -12186,7 +12192,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="79" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C79" s="32">
         <v>45991</v>
       </c>
@@ -12200,5527 +12206,5543 @@
         <v>102</v>
       </c>
     </row>
-    <row r="80" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C80" s="25"/>
-      <c r="D80" s="23"/>
-      <c r="E80" s="23"/>
-      <c r="F80" s="23"/>
-    </row>
-    <row r="81" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C81" s="24"/>
-      <c r="D81" s="22"/>
-      <c r="E81" s="22"/>
-      <c r="F81" s="22"/>
-    </row>
-    <row r="82" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C80" s="33">
+        <v>45993</v>
+      </c>
+      <c r="D80" s="23">
+        <v>30</v>
+      </c>
+      <c r="E80" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F80" s="23" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="81" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C81" s="32">
+        <v>45993</v>
+      </c>
+      <c r="D81" s="22">
+        <v>240</v>
+      </c>
+      <c r="E81" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F81" s="22" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="82" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C82" s="25"/>
       <c r="D82" s="23"/>
       <c r="E82" s="23"/>
       <c r="F82" s="23"/>
     </row>
-    <row r="83" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C83" s="24"/>
       <c r="D83" s="22"/>
       <c r="E83" s="22"/>
       <c r="F83" s="22"/>
     </row>
-    <row r="84" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C84" s="25"/>
       <c r="D84" s="23"/>
       <c r="E84" s="23"/>
       <c r="F84" s="23"/>
     </row>
-    <row r="85" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C85" s="24"/>
       <c r="D85" s="22"/>
       <c r="E85" s="22"/>
       <c r="F85" s="22"/>
     </row>
-    <row r="86" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C86" s="25"/>
       <c r="D86" s="23"/>
       <c r="E86" s="23"/>
       <c r="F86" s="23"/>
     </row>
-    <row r="87" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C87" s="24"/>
       <c r="D87" s="22"/>
       <c r="E87" s="22"/>
       <c r="F87" s="22"/>
     </row>
-    <row r="88" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C88" s="25"/>
       <c r="D88" s="23"/>
       <c r="E88" s="23"/>
       <c r="F88" s="23"/>
     </row>
-    <row r="89" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C89" s="24"/>
       <c r="D89" s="22"/>
       <c r="E89" s="22"/>
       <c r="F89" s="22"/>
     </row>
-    <row r="90" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C90" s="25"/>
       <c r="D90" s="23"/>
       <c r="E90" s="23"/>
       <c r="F90" s="23"/>
     </row>
-    <row r="91" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C91" s="24"/>
       <c r="D91" s="22"/>
       <c r="E91" s="22"/>
       <c r="F91" s="22"/>
     </row>
-    <row r="92" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C92" s="25"/>
       <c r="D92" s="23"/>
       <c r="E92" s="23"/>
       <c r="F92" s="23"/>
     </row>
-    <row r="93" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C93" s="24"/>
       <c r="D93" s="22"/>
       <c r="E93" s="22"/>
       <c r="F93" s="22"/>
     </row>
-    <row r="94" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C94" s="25"/>
       <c r="D94" s="23"/>
       <c r="E94" s="23"/>
       <c r="F94" s="23"/>
     </row>
-    <row r="95" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C95" s="24"/>
       <c r="D95" s="22"/>
       <c r="E95" s="22"/>
       <c r="F95" s="22"/>
     </row>
-    <row r="96" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C96" s="25"/>
       <c r="D96" s="23"/>
       <c r="E96" s="23"/>
       <c r="F96" s="23"/>
     </row>
-    <row r="97" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C97" s="24"/>
       <c r="D97" s="22"/>
       <c r="E97" s="22"/>
       <c r="F97" s="22"/>
     </row>
-    <row r="98" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C98" s="25"/>
       <c r="D98" s="23"/>
       <c r="E98" s="23"/>
       <c r="F98" s="23"/>
     </row>
-    <row r="99" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C99" s="24"/>
       <c r="D99" s="22"/>
       <c r="E99" s="22"/>
       <c r="F99" s="22"/>
     </row>
-    <row r="100" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C100" s="25"/>
       <c r="D100" s="23"/>
       <c r="E100" s="23"/>
       <c r="F100" s="23"/>
     </row>
-    <row r="101" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C101" s="24"/>
       <c r="D101" s="22"/>
       <c r="E101" s="22"/>
       <c r="F101" s="22"/>
     </row>
-    <row r="102" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C102" s="25"/>
       <c r="D102" s="23"/>
       <c r="E102" s="23"/>
       <c r="F102" s="23"/>
     </row>
-    <row r="103" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C103" s="24"/>
       <c r="D103" s="22"/>
       <c r="E103" s="22"/>
       <c r="F103" s="22"/>
     </row>
-    <row r="104" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C104" s="25"/>
       <c r="D104" s="23"/>
       <c r="E104" s="23"/>
       <c r="F104" s="23"/>
     </row>
-    <row r="105" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C105" s="24"/>
       <c r="D105" s="22"/>
       <c r="E105" s="22"/>
       <c r="F105" s="22"/>
     </row>
-    <row r="106" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C106" s="25"/>
       <c r="D106" s="23"/>
       <c r="E106" s="23"/>
       <c r="F106" s="23"/>
     </row>
-    <row r="107" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C107" s="24"/>
       <c r="D107" s="22"/>
       <c r="E107" s="22"/>
       <c r="F107" s="22"/>
     </row>
-    <row r="108" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C108" s="25"/>
       <c r="D108" s="23"/>
       <c r="E108" s="23"/>
       <c r="F108" s="23"/>
     </row>
-    <row r="109" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C109" s="24"/>
       <c r="D109" s="22"/>
       <c r="E109" s="22"/>
       <c r="F109" s="22"/>
     </row>
-    <row r="110" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C110" s="25"/>
       <c r="D110" s="23"/>
       <c r="E110" s="23"/>
       <c r="F110" s="23"/>
     </row>
-    <row r="111" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C111" s="24"/>
       <c r="D111" s="22"/>
       <c r="E111" s="22"/>
       <c r="F111" s="22"/>
     </row>
-    <row r="112" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C112" s="25"/>
       <c r="D112" s="23"/>
       <c r="E112" s="23"/>
       <c r="F112" s="23"/>
     </row>
-    <row r="113" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C113" s="24"/>
       <c r="D113" s="22"/>
       <c r="E113" s="22"/>
       <c r="F113" s="22"/>
     </row>
-    <row r="114" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C114" s="25"/>
       <c r="D114" s="23"/>
       <c r="E114" s="23"/>
       <c r="F114" s="23"/>
     </row>
-    <row r="115" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C115" s="24"/>
       <c r="D115" s="22"/>
       <c r="E115" s="22"/>
       <c r="F115" s="22"/>
     </row>
-    <row r="116" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C116" s="25"/>
       <c r="D116" s="23"/>
       <c r="E116" s="23"/>
       <c r="F116" s="23"/>
     </row>
-    <row r="117" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C117" s="24"/>
       <c r="D117" s="22"/>
       <c r="E117" s="22"/>
       <c r="F117" s="22"/>
     </row>
-    <row r="118" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C118" s="25"/>
       <c r="D118" s="23"/>
       <c r="E118" s="23"/>
       <c r="F118" s="23"/>
     </row>
-    <row r="119" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C119" s="24"/>
       <c r="D119" s="22"/>
       <c r="E119" s="22"/>
       <c r="F119" s="22"/>
     </row>
-    <row r="120" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C120" s="25"/>
       <c r="D120" s="23"/>
       <c r="E120" s="23"/>
       <c r="F120" s="23"/>
     </row>
-    <row r="121" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C121" s="24"/>
       <c r="D121" s="22"/>
       <c r="E121" s="22"/>
       <c r="F121" s="22"/>
     </row>
-    <row r="122" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C122" s="25"/>
       <c r="D122" s="23"/>
       <c r="E122" s="23"/>
       <c r="F122" s="23"/>
     </row>
-    <row r="123" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C123" s="24"/>
       <c r="D123" s="22"/>
       <c r="E123" s="22"/>
       <c r="F123" s="22"/>
     </row>
-    <row r="124" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C124" s="25"/>
       <c r="D124" s="23"/>
       <c r="E124" s="23"/>
       <c r="F124" s="23"/>
     </row>
-    <row r="125" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C125" s="24"/>
       <c r="D125" s="22"/>
       <c r="E125" s="22"/>
       <c r="F125" s="22"/>
     </row>
-    <row r="126" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C126" s="25"/>
       <c r="D126" s="23"/>
       <c r="E126" s="23"/>
       <c r="F126" s="23"/>
     </row>
-    <row r="127" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C127" s="24"/>
       <c r="D127" s="22"/>
       <c r="E127" s="22"/>
       <c r="F127" s="22"/>
     </row>
-    <row r="128" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C128" s="25"/>
       <c r="D128" s="23"/>
       <c r="E128" s="23"/>
       <c r="F128" s="23"/>
     </row>
-    <row r="129" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C129" s="24"/>
       <c r="D129" s="22"/>
       <c r="E129" s="22"/>
       <c r="F129" s="22"/>
     </row>
-    <row r="130" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C130" s="25"/>
       <c r="D130" s="23"/>
       <c r="E130" s="23"/>
       <c r="F130" s="23"/>
     </row>
-    <row r="131" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C131" s="24"/>
       <c r="D131" s="22"/>
       <c r="E131" s="22"/>
       <c r="F131" s="22"/>
     </row>
-    <row r="132" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C132" s="25"/>
       <c r="D132" s="23"/>
       <c r="E132" s="23"/>
       <c r="F132" s="23"/>
     </row>
-    <row r="133" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C133" s="24"/>
       <c r="D133" s="22"/>
       <c r="E133" s="22"/>
       <c r="F133" s="22"/>
     </row>
-    <row r="134" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C134" s="25"/>
       <c r="D134" s="23"/>
       <c r="E134" s="23"/>
       <c r="F134" s="23"/>
     </row>
-    <row r="135" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C135" s="24"/>
       <c r="D135" s="22"/>
       <c r="E135" s="22"/>
       <c r="F135" s="22"/>
     </row>
-    <row r="136" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C136" s="25"/>
       <c r="D136" s="23"/>
       <c r="E136" s="23"/>
       <c r="F136" s="23"/>
     </row>
-    <row r="137" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C137" s="24"/>
       <c r="D137" s="22"/>
       <c r="E137" s="22"/>
       <c r="F137" s="22"/>
     </row>
-    <row r="138" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C138" s="25"/>
       <c r="D138" s="23"/>
       <c r="E138" s="23"/>
       <c r="F138" s="23"/>
     </row>
-    <row r="139" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C139" s="24"/>
       <c r="D139" s="22"/>
       <c r="E139" s="22"/>
       <c r="F139" s="22"/>
     </row>
-    <row r="140" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C140" s="25"/>
       <c r="D140" s="23"/>
       <c r="E140" s="23"/>
       <c r="F140" s="23"/>
     </row>
-    <row r="141" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C141" s="24"/>
       <c r="D141" s="22"/>
       <c r="E141" s="22"/>
       <c r="F141" s="22"/>
     </row>
-    <row r="142" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C142" s="25"/>
       <c r="D142" s="23"/>
       <c r="E142" s="23"/>
       <c r="F142" s="23"/>
     </row>
-    <row r="143" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C143" s="24"/>
       <c r="D143" s="22"/>
       <c r="E143" s="22"/>
       <c r="F143" s="22"/>
     </row>
-    <row r="144" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C144" s="25"/>
       <c r="D144" s="23"/>
       <c r="E144" s="23"/>
       <c r="F144" s="23"/>
     </row>
-    <row r="145" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C145" s="24"/>
       <c r="D145" s="22"/>
       <c r="E145" s="22"/>
       <c r="F145" s="22"/>
     </row>
-    <row r="146" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C146" s="25"/>
       <c r="D146" s="23"/>
       <c r="E146" s="23"/>
       <c r="F146" s="23"/>
     </row>
-    <row r="147" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C147" s="24"/>
       <c r="D147" s="22"/>
       <c r="E147" s="22"/>
       <c r="F147" s="22"/>
     </row>
-    <row r="148" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C148" s="25"/>
       <c r="D148" s="23"/>
       <c r="E148" s="23"/>
       <c r="F148" s="23"/>
     </row>
-    <row r="149" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C149" s="24"/>
       <c r="D149" s="22"/>
       <c r="E149" s="22"/>
       <c r="F149" s="22"/>
     </row>
-    <row r="150" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C150" s="25"/>
       <c r="D150" s="23"/>
       <c r="E150" s="23"/>
       <c r="F150" s="23"/>
     </row>
-    <row r="151" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C151" s="24"/>
       <c r="D151" s="22"/>
       <c r="E151" s="22"/>
       <c r="F151" s="22"/>
     </row>
-    <row r="152" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C152" s="25"/>
       <c r="D152" s="23"/>
       <c r="E152" s="23"/>
       <c r="F152" s="23"/>
     </row>
-    <row r="153" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C153" s="24"/>
       <c r="D153" s="22"/>
       <c r="E153" s="22"/>
       <c r="F153" s="22"/>
     </row>
-    <row r="154" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C154" s="25"/>
       <c r="D154" s="23"/>
       <c r="E154" s="23"/>
       <c r="F154" s="23"/>
     </row>
-    <row r="155" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C155" s="24"/>
       <c r="D155" s="22"/>
       <c r="E155" s="22"/>
       <c r="F155" s="22"/>
     </row>
-    <row r="156" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C156" s="25"/>
       <c r="D156" s="23"/>
       <c r="E156" s="23"/>
       <c r="F156" s="23"/>
     </row>
-    <row r="157" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C157" s="24"/>
       <c r="D157" s="22"/>
       <c r="E157" s="22"/>
       <c r="F157" s="22"/>
     </row>
-    <row r="158" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C158" s="25"/>
       <c r="D158" s="23"/>
       <c r="E158" s="23"/>
       <c r="F158" s="23"/>
     </row>
-    <row r="159" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C159" s="24"/>
       <c r="D159" s="22"/>
       <c r="E159" s="22"/>
       <c r="F159" s="22"/>
     </row>
-    <row r="160" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C160" s="25"/>
       <c r="D160" s="23"/>
       <c r="E160" s="23"/>
       <c r="F160" s="23"/>
     </row>
-    <row r="161" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C161" s="24"/>
       <c r="D161" s="22"/>
       <c r="E161" s="22"/>
       <c r="F161" s="22"/>
     </row>
-    <row r="162" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C162" s="25"/>
       <c r="D162" s="23"/>
       <c r="E162" s="23"/>
       <c r="F162" s="23"/>
     </row>
-    <row r="163" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C163" s="24"/>
       <c r="D163" s="22"/>
       <c r="E163" s="22"/>
       <c r="F163" s="22"/>
     </row>
-    <row r="164" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C164" s="25"/>
       <c r="D164" s="23"/>
       <c r="E164" s="23"/>
       <c r="F164" s="23"/>
     </row>
-    <row r="165" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C165" s="24"/>
       <c r="D165" s="22"/>
       <c r="E165" s="22"/>
       <c r="F165" s="22"/>
     </row>
-    <row r="166" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C166" s="25"/>
       <c r="D166" s="23"/>
       <c r="E166" s="23"/>
       <c r="F166" s="23"/>
     </row>
-    <row r="167" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C167" s="24"/>
       <c r="D167" s="22"/>
       <c r="E167" s="22"/>
       <c r="F167" s="22"/>
     </row>
-    <row r="168" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C168" s="25"/>
       <c r="D168" s="23"/>
       <c r="E168" s="23"/>
       <c r="F168" s="23"/>
     </row>
-    <row r="169" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C169" s="24"/>
       <c r="D169" s="22"/>
       <c r="E169" s="22"/>
       <c r="F169" s="22"/>
     </row>
-    <row r="170" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C170" s="25"/>
       <c r="D170" s="23"/>
       <c r="E170" s="23"/>
       <c r="F170" s="23"/>
     </row>
-    <row r="171" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C171" s="24"/>
       <c r="D171" s="22"/>
       <c r="E171" s="22"/>
       <c r="F171" s="22"/>
     </row>
-    <row r="172" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C172" s="25"/>
       <c r="D172" s="23"/>
       <c r="E172" s="23"/>
       <c r="F172" s="23"/>
     </row>
-    <row r="173" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C173" s="24"/>
       <c r="D173" s="22"/>
       <c r="E173" s="22"/>
       <c r="F173" s="22"/>
     </row>
-    <row r="174" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C174" s="25"/>
       <c r="D174" s="23"/>
       <c r="E174" s="23"/>
       <c r="F174" s="23"/>
     </row>
-    <row r="175" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C175" s="24"/>
       <c r="D175" s="22"/>
       <c r="E175" s="22"/>
       <c r="F175" s="22"/>
     </row>
-    <row r="176" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C176" s="25"/>
       <c r="D176" s="23"/>
       <c r="E176" s="23"/>
       <c r="F176" s="23"/>
     </row>
-    <row r="177" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C177" s="24"/>
       <c r="D177" s="22"/>
       <c r="E177" s="22"/>
       <c r="F177" s="22"/>
     </row>
-    <row r="178" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C178" s="25"/>
       <c r="D178" s="23"/>
       <c r="E178" s="23"/>
       <c r="F178" s="23"/>
     </row>
-    <row r="179" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C179" s="24"/>
       <c r="D179" s="22"/>
       <c r="E179" s="22"/>
       <c r="F179" s="22"/>
     </row>
-    <row r="180" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C180" s="25"/>
       <c r="D180" s="23"/>
       <c r="E180" s="23"/>
       <c r="F180" s="23"/>
     </row>
-    <row r="181" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C181" s="24"/>
       <c r="D181" s="22"/>
       <c r="E181" s="22"/>
       <c r="F181" s="22"/>
     </row>
-    <row r="182" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C182" s="25"/>
       <c r="D182" s="23"/>
       <c r="E182" s="23"/>
       <c r="F182" s="23"/>
     </row>
-    <row r="183" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C183" s="24"/>
       <c r="D183" s="22"/>
       <c r="E183" s="22"/>
       <c r="F183" s="22"/>
     </row>
-    <row r="184" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C184" s="25"/>
       <c r="D184" s="23"/>
       <c r="E184" s="23"/>
       <c r="F184" s="23"/>
     </row>
-    <row r="185" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C185" s="24"/>
       <c r="D185" s="22"/>
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
     </row>
-    <row r="186" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C186" s="25"/>
       <c r="D186" s="23"/>
       <c r="E186" s="23"/>
       <c r="F186" s="23"/>
     </row>
-    <row r="187" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C187" s="24"/>
       <c r="D187" s="22"/>
       <c r="E187" s="22"/>
       <c r="F187" s="22"/>
     </row>
-    <row r="188" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C188" s="25"/>
       <c r="D188" s="23"/>
       <c r="E188" s="23"/>
       <c r="F188" s="23"/>
     </row>
-    <row r="189" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C189" s="24"/>
       <c r="D189" s="22"/>
       <c r="E189" s="22"/>
       <c r="F189" s="22"/>
     </row>
-    <row r="190" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C190" s="25"/>
       <c r="D190" s="23"/>
       <c r="E190" s="23"/>
       <c r="F190" s="23"/>
     </row>
-    <row r="191" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C191" s="24"/>
       <c r="D191" s="22"/>
       <c r="E191" s="22"/>
       <c r="F191" s="22"/>
     </row>
-    <row r="192" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C192" s="25"/>
       <c r="D192" s="23"/>
       <c r="E192" s="23"/>
       <c r="F192" s="23"/>
     </row>
-    <row r="193" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C193" s="24"/>
       <c r="D193" s="22"/>
       <c r="E193" s="22"/>
       <c r="F193" s="22"/>
     </row>
-    <row r="194" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C194" s="25"/>
       <c r="D194" s="23"/>
       <c r="E194" s="23"/>
       <c r="F194" s="23"/>
     </row>
-    <row r="195" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C195" s="24"/>
       <c r="D195" s="22"/>
       <c r="E195" s="22"/>
       <c r="F195" s="22"/>
     </row>
-    <row r="196" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C196" s="25"/>
       <c r="D196" s="23"/>
       <c r="E196" s="23"/>
       <c r="F196" s="23"/>
     </row>
-    <row r="197" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C197" s="24"/>
       <c r="D197" s="22"/>
       <c r="E197" s="22"/>
       <c r="F197" s="22"/>
     </row>
-    <row r="198" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C198" s="25"/>
       <c r="D198" s="23"/>
       <c r="E198" s="23"/>
       <c r="F198" s="23"/>
     </row>
-    <row r="199" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C199" s="24"/>
       <c r="D199" s="22"/>
       <c r="E199" s="22"/>
       <c r="F199" s="22"/>
     </row>
-    <row r="200" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C200" s="25"/>
       <c r="D200" s="23"/>
       <c r="E200" s="23"/>
       <c r="F200" s="23"/>
     </row>
-    <row r="201" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C201" s="24"/>
       <c r="D201" s="22"/>
       <c r="E201" s="22"/>
       <c r="F201" s="22"/>
     </row>
-    <row r="202" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C202" s="25"/>
       <c r="D202" s="23"/>
       <c r="E202" s="23"/>
       <c r="F202" s="23"/>
     </row>
-    <row r="203" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C203" s="24"/>
       <c r="D203" s="22"/>
       <c r="E203" s="22"/>
       <c r="F203" s="22"/>
     </row>
-    <row r="204" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C204" s="25"/>
       <c r="D204" s="23"/>
       <c r="E204" s="23"/>
       <c r="F204" s="23"/>
     </row>
-    <row r="205" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C205" s="24"/>
       <c r="D205" s="22"/>
       <c r="E205" s="22"/>
       <c r="F205" s="22"/>
     </row>
-    <row r="206" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C206" s="25"/>
       <c r="D206" s="23"/>
       <c r="E206" s="23"/>
       <c r="F206" s="23"/>
     </row>
-    <row r="207" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C207" s="24"/>
       <c r="D207" s="22"/>
       <c r="E207" s="22"/>
       <c r="F207" s="22"/>
     </row>
-    <row r="208" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C208" s="25"/>
       <c r="D208" s="23"/>
       <c r="E208" s="23"/>
       <c r="F208" s="23"/>
     </row>
-    <row r="209" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C209" s="24"/>
       <c r="D209" s="22"/>
       <c r="E209" s="22"/>
       <c r="F209" s="22"/>
     </row>
-    <row r="210" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C210" s="25"/>
       <c r="D210" s="23"/>
       <c r="E210" s="23"/>
       <c r="F210" s="23"/>
     </row>
-    <row r="211" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C211" s="24"/>
       <c r="D211" s="22"/>
       <c r="E211" s="22"/>
       <c r="F211" s="22"/>
     </row>
-    <row r="212" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C212" s="25"/>
       <c r="D212" s="23"/>
       <c r="E212" s="23"/>
       <c r="F212" s="23"/>
     </row>
-    <row r="213" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C213" s="24"/>
       <c r="D213" s="22"/>
       <c r="E213" s="22"/>
       <c r="F213" s="22"/>
     </row>
-    <row r="214" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C214" s="25"/>
       <c r="D214" s="23"/>
       <c r="E214" s="23"/>
       <c r="F214" s="23"/>
     </row>
-    <row r="215" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C215" s="24"/>
       <c r="D215" s="22"/>
       <c r="E215" s="22"/>
       <c r="F215" s="22"/>
     </row>
-    <row r="216" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C216" s="25"/>
       <c r="D216" s="23"/>
       <c r="E216" s="23"/>
       <c r="F216" s="23"/>
     </row>
-    <row r="217" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C217" s="24"/>
       <c r="D217" s="22"/>
       <c r="E217" s="22"/>
       <c r="F217" s="22"/>
     </row>
-    <row r="218" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C218" s="25"/>
       <c r="D218" s="23"/>
       <c r="E218" s="23"/>
       <c r="F218" s="23"/>
     </row>
-    <row r="219" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C219" s="24"/>
       <c r="D219" s="22"/>
       <c r="E219" s="22"/>
       <c r="F219" s="22"/>
     </row>
-    <row r="220" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C220" s="25"/>
       <c r="D220" s="23"/>
       <c r="E220" s="23"/>
       <c r="F220" s="23"/>
     </row>
-    <row r="221" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C221" s="24"/>
       <c r="D221" s="22"/>
       <c r="E221" s="22"/>
       <c r="F221" s="22"/>
     </row>
-    <row r="222" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C222" s="25"/>
       <c r="D222" s="23"/>
       <c r="E222" s="23"/>
       <c r="F222" s="23"/>
     </row>
-    <row r="223" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C223" s="24"/>
       <c r="D223" s="22"/>
       <c r="E223" s="22"/>
       <c r="F223" s="22"/>
     </row>
-    <row r="224" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C224" s="25"/>
       <c r="D224" s="23"/>
       <c r="E224" s="23"/>
       <c r="F224" s="23"/>
     </row>
-    <row r="225" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C225" s="24"/>
       <c r="D225" s="22"/>
       <c r="E225" s="22"/>
       <c r="F225" s="22"/>
     </row>
-    <row r="226" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C226" s="25"/>
       <c r="D226" s="23"/>
       <c r="E226" s="23"/>
       <c r="F226" s="23"/>
     </row>
-    <row r="227" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C227" s="24"/>
       <c r="D227" s="22"/>
       <c r="E227" s="22"/>
       <c r="F227" s="22"/>
     </row>
-    <row r="228" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C228" s="25"/>
       <c r="D228" s="23"/>
       <c r="E228" s="23"/>
       <c r="F228" s="23"/>
     </row>
-    <row r="229" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C229" s="24"/>
       <c r="D229" s="22"/>
       <c r="E229" s="22"/>
       <c r="F229" s="22"/>
     </row>
-    <row r="230" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C230" s="25"/>
       <c r="D230" s="23"/>
       <c r="E230" s="23"/>
       <c r="F230" s="23"/>
     </row>
-    <row r="231" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C231" s="24"/>
       <c r="D231" s="22"/>
       <c r="E231" s="22"/>
       <c r="F231" s="22"/>
     </row>
-    <row r="232" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C232" s="25"/>
       <c r="D232" s="23"/>
       <c r="E232" s="23"/>
       <c r="F232" s="23"/>
     </row>
-    <row r="233" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C233" s="24"/>
       <c r="D233" s="22"/>
       <c r="E233" s="22"/>
       <c r="F233" s="22"/>
     </row>
-    <row r="234" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C234" s="25"/>
       <c r="D234" s="23"/>
       <c r="E234" s="23"/>
       <c r="F234" s="23"/>
     </row>
-    <row r="235" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C235" s="24"/>
       <c r="D235" s="22"/>
       <c r="E235" s="22"/>
       <c r="F235" s="22"/>
     </row>
-    <row r="236" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C236" s="25"/>
       <c r="D236" s="23"/>
       <c r="E236" s="23"/>
       <c r="F236" s="23"/>
     </row>
-    <row r="237" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C237" s="24"/>
       <c r="D237" s="22"/>
       <c r="E237" s="22"/>
       <c r="F237" s="22"/>
     </row>
-    <row r="238" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C238" s="25"/>
       <c r="D238" s="23"/>
       <c r="E238" s="23"/>
       <c r="F238" s="23"/>
     </row>
-    <row r="239" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C239" s="24"/>
       <c r="D239" s="22"/>
       <c r="E239" s="22"/>
       <c r="F239" s="22"/>
     </row>
-    <row r="240" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C240" s="25"/>
       <c r="D240" s="23"/>
       <c r="E240" s="23"/>
       <c r="F240" s="23"/>
     </row>
-    <row r="241" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C241" s="24"/>
       <c r="D241" s="22"/>
       <c r="E241" s="22"/>
       <c r="F241" s="22"/>
     </row>
-    <row r="242" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C242" s="25"/>
       <c r="D242" s="23"/>
       <c r="E242" s="23"/>
       <c r="F242" s="23"/>
     </row>
-    <row r="243" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C243" s="24"/>
       <c r="D243" s="22"/>
       <c r="E243" s="22"/>
       <c r="F243" s="22"/>
     </row>
-    <row r="244" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C244" s="25"/>
       <c r="D244" s="23"/>
       <c r="E244" s="23"/>
       <c r="F244" s="23"/>
     </row>
-    <row r="245" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C245" s="24"/>
       <c r="D245" s="22"/>
       <c r="E245" s="22"/>
       <c r="F245" s="22"/>
     </row>
-    <row r="246" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C246" s="25"/>
       <c r="D246" s="23"/>
       <c r="E246" s="23"/>
       <c r="F246" s="23"/>
     </row>
-    <row r="247" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C247" s="24"/>
       <c r="D247" s="22"/>
       <c r="E247" s="22"/>
       <c r="F247" s="22"/>
     </row>
-    <row r="248" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C248" s="25"/>
       <c r="D248" s="23"/>
       <c r="E248" s="23"/>
       <c r="F248" s="23"/>
     </row>
-    <row r="249" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C249" s="24"/>
       <c r="D249" s="22"/>
       <c r="E249" s="22"/>
       <c r="F249" s="22"/>
     </row>
-    <row r="250" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C250" s="25"/>
       <c r="D250" s="23"/>
       <c r="E250" s="23"/>
       <c r="F250" s="23"/>
     </row>
-    <row r="251" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C251" s="24"/>
       <c r="D251" s="22"/>
       <c r="E251" s="22"/>
       <c r="F251" s="22"/>
     </row>
-    <row r="252" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C252" s="25"/>
       <c r="D252" s="23"/>
       <c r="E252" s="23"/>
       <c r="F252" s="23"/>
     </row>
-    <row r="253" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C253" s="24"/>
       <c r="D253" s="22"/>
       <c r="E253" s="22"/>
       <c r="F253" s="22"/>
     </row>
-    <row r="254" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C254" s="25"/>
       <c r="D254" s="23"/>
       <c r="E254" s="23"/>
       <c r="F254" s="23"/>
     </row>
-    <row r="255" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C255" s="24"/>
       <c r="D255" s="22"/>
       <c r="E255" s="22"/>
       <c r="F255" s="22"/>
     </row>
-    <row r="256" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C256" s="25"/>
       <c r="D256" s="23"/>
       <c r="E256" s="23"/>
       <c r="F256" s="23"/>
     </row>
-    <row r="257" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C257" s="24"/>
       <c r="D257" s="22"/>
       <c r="E257" s="22"/>
       <c r="F257" s="22"/>
     </row>
-    <row r="258" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C258" s="25"/>
       <c r="D258" s="23"/>
       <c r="E258" s="23"/>
       <c r="F258" s="23"/>
     </row>
-    <row r="259" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C259" s="24"/>
       <c r="D259" s="22"/>
       <c r="E259" s="22"/>
       <c r="F259" s="22"/>
     </row>
-    <row r="260" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C260" s="25"/>
       <c r="D260" s="23"/>
       <c r="E260" s="23"/>
       <c r="F260" s="23"/>
     </row>
-    <row r="261" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C261" s="24"/>
       <c r="D261" s="22"/>
       <c r="E261" s="22"/>
       <c r="F261" s="22"/>
     </row>
-    <row r="262" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C262" s="25"/>
       <c r="D262" s="23"/>
       <c r="E262" s="23"/>
       <c r="F262" s="23"/>
     </row>
-    <row r="263" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C263" s="24"/>
       <c r="D263" s="22"/>
       <c r="E263" s="22"/>
       <c r="F263" s="22"/>
     </row>
-    <row r="264" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C264" s="25"/>
       <c r="D264" s="23"/>
       <c r="E264" s="23"/>
       <c r="F264" s="23"/>
     </row>
-    <row r="265" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C265" s="24"/>
       <c r="D265" s="22"/>
       <c r="E265" s="22"/>
       <c r="F265" s="22"/>
     </row>
-    <row r="266" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C266" s="25"/>
       <c r="D266" s="23"/>
       <c r="E266" s="23"/>
       <c r="F266" s="23"/>
     </row>
-    <row r="267" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C267" s="24"/>
       <c r="D267" s="22"/>
       <c r="E267" s="22"/>
       <c r="F267" s="22"/>
     </row>
-    <row r="268" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C268" s="25"/>
       <c r="D268" s="23"/>
       <c r="E268" s="23"/>
       <c r="F268" s="23"/>
     </row>
-    <row r="269" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C269" s="24"/>
       <c r="D269" s="22"/>
       <c r="E269" s="22"/>
       <c r="F269" s="22"/>
     </row>
-    <row r="270" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C270" s="25"/>
       <c r="D270" s="23"/>
       <c r="E270" s="23"/>
       <c r="F270" s="23"/>
     </row>
-    <row r="271" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C271" s="24"/>
       <c r="D271" s="22"/>
       <c r="E271" s="22"/>
       <c r="F271" s="22"/>
     </row>
-    <row r="272" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C272" s="25"/>
       <c r="D272" s="23"/>
       <c r="E272" s="23"/>
       <c r="F272" s="23"/>
     </row>
-    <row r="273" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C273" s="24"/>
       <c r="D273" s="22"/>
       <c r="E273" s="22"/>
       <c r="F273" s="22"/>
     </row>
-    <row r="274" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C274" s="25"/>
       <c r="D274" s="23"/>
       <c r="E274" s="23"/>
       <c r="F274" s="23"/>
     </row>
-    <row r="275" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C275" s="24"/>
       <c r="D275" s="22"/>
       <c r="E275" s="22"/>
       <c r="F275" s="22"/>
     </row>
-    <row r="276" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C276" s="25"/>
       <c r="D276" s="23"/>
       <c r="E276" s="23"/>
       <c r="F276" s="23"/>
     </row>
-    <row r="277" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C277" s="24"/>
       <c r="D277" s="22"/>
       <c r="E277" s="22"/>
       <c r="F277" s="22"/>
     </row>
-    <row r="278" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C278" s="25"/>
       <c r="D278" s="23"/>
       <c r="E278" s="23"/>
       <c r="F278" s="23"/>
     </row>
-    <row r="279" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C279" s="24"/>
       <c r="D279" s="22"/>
       <c r="E279" s="22"/>
       <c r="F279" s="22"/>
     </row>
-    <row r="280" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C280" s="25"/>
       <c r="D280" s="23"/>
       <c r="E280" s="23"/>
       <c r="F280" s="23"/>
     </row>
-    <row r="281" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C281" s="24"/>
       <c r="D281" s="22"/>
       <c r="E281" s="22"/>
       <c r="F281" s="22"/>
     </row>
-    <row r="282" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C282" s="25"/>
       <c r="D282" s="23"/>
       <c r="E282" s="23"/>
       <c r="F282" s="23"/>
     </row>
-    <row r="283" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C283" s="24"/>
       <c r="D283" s="22"/>
       <c r="E283" s="22"/>
       <c r="F283" s="22"/>
     </row>
-    <row r="284" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C284" s="25"/>
       <c r="D284" s="23"/>
       <c r="E284" s="23"/>
       <c r="F284" s="23"/>
     </row>
-    <row r="285" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C285" s="24"/>
       <c r="D285" s="22"/>
       <c r="E285" s="22"/>
       <c r="F285" s="22"/>
     </row>
-    <row r="286" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C286" s="25"/>
       <c r="D286" s="23"/>
       <c r="E286" s="23"/>
       <c r="F286" s="23"/>
     </row>
-    <row r="287" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C287" s="24"/>
       <c r="D287" s="22"/>
       <c r="E287" s="22"/>
       <c r="F287" s="22"/>
     </row>
-    <row r="288" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C288" s="25"/>
       <c r="D288" s="23"/>
       <c r="E288" s="23"/>
       <c r="F288" s="23"/>
     </row>
-    <row r="289" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C289" s="24"/>
       <c r="D289" s="22"/>
       <c r="E289" s="22"/>
       <c r="F289" s="22"/>
     </row>
-    <row r="290" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C290" s="25"/>
       <c r="D290" s="23"/>
       <c r="E290" s="23"/>
       <c r="F290" s="23"/>
     </row>
-    <row r="291" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C291" s="24"/>
       <c r="D291" s="22"/>
       <c r="E291" s="22"/>
       <c r="F291" s="22"/>
     </row>
-    <row r="292" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C292" s="25"/>
       <c r="D292" s="23"/>
       <c r="E292" s="23"/>
       <c r="F292" s="23"/>
     </row>
-    <row r="293" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C293" s="24"/>
       <c r="D293" s="22"/>
       <c r="E293" s="22"/>
       <c r="F293" s="22"/>
     </row>
-    <row r="294" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C294" s="25"/>
       <c r="D294" s="23"/>
       <c r="E294" s="23"/>
       <c r="F294" s="23"/>
     </row>
-    <row r="295" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C295" s="24"/>
       <c r="D295" s="22"/>
       <c r="E295" s="22"/>
       <c r="F295" s="22"/>
     </row>
-    <row r="296" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C296" s="25"/>
       <c r="D296" s="23"/>
       <c r="E296" s="23"/>
       <c r="F296" s="23"/>
     </row>
-    <row r="297" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C297" s="24"/>
       <c r="D297" s="22"/>
       <c r="E297" s="22"/>
       <c r="F297" s="22"/>
     </row>
-    <row r="298" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C298" s="25"/>
       <c r="D298" s="23"/>
       <c r="E298" s="23"/>
       <c r="F298" s="23"/>
     </row>
-    <row r="299" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C299" s="24"/>
       <c r="D299" s="22"/>
       <c r="E299" s="22"/>
       <c r="F299" s="22"/>
     </row>
-    <row r="300" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C300" s="25"/>
       <c r="D300" s="23"/>
       <c r="E300" s="23"/>
       <c r="F300" s="23"/>
     </row>
-    <row r="301" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C301" s="24"/>
       <c r="D301" s="22"/>
       <c r="E301" s="22"/>
       <c r="F301" s="22"/>
     </row>
-    <row r="302" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C302" s="25"/>
       <c r="D302" s="23"/>
       <c r="E302" s="23"/>
       <c r="F302" s="23"/>
     </row>
-    <row r="303" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C303" s="24"/>
       <c r="D303" s="22"/>
       <c r="E303" s="22"/>
       <c r="F303" s="22"/>
     </row>
-    <row r="304" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C304" s="25"/>
       <c r="D304" s="23"/>
       <c r="E304" s="23"/>
       <c r="F304" s="23"/>
     </row>
-    <row r="305" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C305" s="24"/>
       <c r="D305" s="22"/>
       <c r="E305" s="22"/>
       <c r="F305" s="22"/>
     </row>
-    <row r="306" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C306" s="25"/>
       <c r="D306" s="23"/>
       <c r="E306" s="23"/>
       <c r="F306" s="23"/>
     </row>
-    <row r="307" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C307" s="24"/>
       <c r="D307" s="22"/>
       <c r="E307" s="22"/>
       <c r="F307" s="22"/>
     </row>
-    <row r="308" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C308" s="25"/>
       <c r="D308" s="23"/>
       <c r="E308" s="23"/>
       <c r="F308" s="23"/>
     </row>
-    <row r="309" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C309" s="24"/>
       <c r="D309" s="22"/>
       <c r="E309" s="22"/>
       <c r="F309" s="22"/>
     </row>
-    <row r="310" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C310" s="25"/>
       <c r="D310" s="23"/>
       <c r="E310" s="23"/>
       <c r="F310" s="23"/>
     </row>
-    <row r="311" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C311" s="24"/>
       <c r="D311" s="22"/>
       <c r="E311" s="22"/>
       <c r="F311" s="22"/>
     </row>
-    <row r="312" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C312" s="25"/>
       <c r="D312" s="23"/>
       <c r="E312" s="23"/>
       <c r="F312" s="23"/>
     </row>
-    <row r="313" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C313" s="24"/>
       <c r="D313" s="22"/>
       <c r="E313" s="22"/>
       <c r="F313" s="22"/>
     </row>
-    <row r="314" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C314" s="25"/>
       <c r="D314" s="23"/>
       <c r="E314" s="23"/>
       <c r="F314" s="23"/>
     </row>
-    <row r="315" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C315" s="24"/>
       <c r="D315" s="22"/>
       <c r="E315" s="22"/>
       <c r="F315" s="22"/>
     </row>
-    <row r="316" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C316" s="25"/>
       <c r="D316" s="23"/>
       <c r="E316" s="23"/>
       <c r="F316" s="23"/>
     </row>
-    <row r="317" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C317" s="24"/>
       <c r="D317" s="22"/>
       <c r="E317" s="22"/>
       <c r="F317" s="22"/>
     </row>
-    <row r="318" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C318" s="25"/>
       <c r="D318" s="23"/>
       <c r="E318" s="23"/>
       <c r="F318" s="23"/>
     </row>
-    <row r="319" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C319" s="24"/>
       <c r="D319" s="22"/>
       <c r="E319" s="22"/>
       <c r="F319" s="22"/>
     </row>
-    <row r="320" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C320" s="25"/>
       <c r="D320" s="23"/>
       <c r="E320" s="23"/>
       <c r="F320" s="23"/>
     </row>
-    <row r="321" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C321" s="24"/>
       <c r="D321" s="22"/>
       <c r="E321" s="22"/>
       <c r="F321" s="22"/>
     </row>
-    <row r="322" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C322" s="25"/>
       <c r="D322" s="23"/>
       <c r="E322" s="23"/>
       <c r="F322" s="23"/>
     </row>
-    <row r="323" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C323" s="24"/>
       <c r="D323" s="22"/>
       <c r="E323" s="22"/>
       <c r="F323" s="22"/>
     </row>
-    <row r="324" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C324" s="25"/>
       <c r="D324" s="23"/>
       <c r="E324" s="23"/>
       <c r="F324" s="23"/>
     </row>
-    <row r="325" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C325" s="24"/>
       <c r="D325" s="22"/>
       <c r="E325" s="22"/>
       <c r="F325" s="22"/>
     </row>
-    <row r="326" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C326" s="25"/>
       <c r="D326" s="23"/>
       <c r="E326" s="23"/>
       <c r="F326" s="23"/>
     </row>
-    <row r="327" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C327" s="24"/>
       <c r="D327" s="22"/>
       <c r="E327" s="22"/>
       <c r="F327" s="22"/>
     </row>
-    <row r="328" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C328" s="25"/>
       <c r="D328" s="23"/>
       <c r="E328" s="23"/>
       <c r="F328" s="23"/>
     </row>
-    <row r="329" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C329" s="24"/>
       <c r="D329" s="22"/>
       <c r="E329" s="22"/>
       <c r="F329" s="22"/>
     </row>
-    <row r="330" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C330" s="25"/>
       <c r="D330" s="23"/>
       <c r="E330" s="23"/>
       <c r="F330" s="23"/>
     </row>
-    <row r="331" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C331" s="24"/>
       <c r="D331" s="22"/>
       <c r="E331" s="22"/>
       <c r="F331" s="22"/>
     </row>
-    <row r="332" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C332" s="25"/>
       <c r="D332" s="23"/>
       <c r="E332" s="23"/>
       <c r="F332" s="23"/>
     </row>
-    <row r="333" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C333" s="24"/>
       <c r="D333" s="22"/>
       <c r="E333" s="22"/>
       <c r="F333" s="22"/>
     </row>
-    <row r="334" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C334" s="25"/>
       <c r="D334" s="23"/>
       <c r="E334" s="23"/>
       <c r="F334" s="23"/>
     </row>
-    <row r="335" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C335" s="24"/>
       <c r="D335" s="22"/>
       <c r="E335" s="22"/>
       <c r="F335" s="22"/>
     </row>
-    <row r="336" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C336" s="25"/>
       <c r="D336" s="23"/>
       <c r="E336" s="23"/>
       <c r="F336" s="23"/>
     </row>
-    <row r="337" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C337" s="24"/>
       <c r="D337" s="22"/>
       <c r="E337" s="22"/>
       <c r="F337" s="22"/>
     </row>
-    <row r="338" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C338" s="25"/>
       <c r="D338" s="23"/>
       <c r="E338" s="23"/>
       <c r="F338" s="23"/>
     </row>
-    <row r="339" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C339" s="24"/>
       <c r="D339" s="22"/>
       <c r="E339" s="22"/>
       <c r="F339" s="22"/>
     </row>
-    <row r="340" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C340" s="25"/>
       <c r="D340" s="23"/>
       <c r="E340" s="23"/>
       <c r="F340" s="23"/>
     </row>
-    <row r="341" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C341" s="24"/>
       <c r="D341" s="22"/>
       <c r="E341" s="22"/>
       <c r="F341" s="22"/>
     </row>
-    <row r="342" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C342" s="25"/>
       <c r="D342" s="23"/>
       <c r="E342" s="23"/>
       <c r="F342" s="23"/>
     </row>
-    <row r="343" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C343" s="24"/>
       <c r="D343" s="22"/>
       <c r="E343" s="22"/>
       <c r="F343" s="22"/>
     </row>
-    <row r="344" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C344" s="25"/>
       <c r="D344" s="23"/>
       <c r="E344" s="23"/>
       <c r="F344" s="23"/>
     </row>
-    <row r="345" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C345" s="24"/>
       <c r="D345" s="22"/>
       <c r="E345" s="22"/>
       <c r="F345" s="22"/>
     </row>
-    <row r="346" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C346" s="25"/>
       <c r="D346" s="23"/>
       <c r="E346" s="23"/>
       <c r="F346" s="23"/>
     </row>
-    <row r="347" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C347" s="24"/>
       <c r="D347" s="22"/>
       <c r="E347" s="22"/>
       <c r="F347" s="22"/>
     </row>
-    <row r="348" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C348" s="25"/>
       <c r="D348" s="23"/>
       <c r="E348" s="23"/>
       <c r="F348" s="23"/>
     </row>
-    <row r="349" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C349" s="24"/>
       <c r="D349" s="22"/>
       <c r="E349" s="22"/>
       <c r="F349" s="22"/>
     </row>
-    <row r="350" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C350" s="25"/>
       <c r="D350" s="23"/>
       <c r="E350" s="23"/>
       <c r="F350" s="23"/>
     </row>
-    <row r="351" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C351" s="24"/>
       <c r="D351" s="22"/>
       <c r="E351" s="22"/>
       <c r="F351" s="22"/>
     </row>
-    <row r="352" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C352" s="25"/>
       <c r="D352" s="23"/>
       <c r="E352" s="23"/>
       <c r="F352" s="23"/>
     </row>
-    <row r="353" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C353" s="24"/>
       <c r="D353" s="22"/>
       <c r="E353" s="22"/>
       <c r="F353" s="22"/>
     </row>
-    <row r="354" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C354" s="25"/>
       <c r="D354" s="23"/>
       <c r="E354" s="23"/>
       <c r="F354" s="23"/>
     </row>
-    <row r="355" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C355" s="24"/>
       <c r="D355" s="22"/>
       <c r="E355" s="22"/>
       <c r="F355" s="22"/>
     </row>
-    <row r="356" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C356" s="25"/>
       <c r="D356" s="23"/>
       <c r="E356" s="23"/>
       <c r="F356" s="23"/>
     </row>
-    <row r="357" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C357" s="24"/>
       <c r="D357" s="22"/>
       <c r="E357" s="22"/>
       <c r="F357" s="22"/>
     </row>
-    <row r="358" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C358" s="25"/>
       <c r="D358" s="23"/>
       <c r="E358" s="23"/>
       <c r="F358" s="23"/>
     </row>
-    <row r="359" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C359" s="24"/>
       <c r="D359" s="22"/>
       <c r="E359" s="22"/>
       <c r="F359" s="22"/>
     </row>
-    <row r="360" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C360" s="25"/>
       <c r="D360" s="23"/>
       <c r="E360" s="23"/>
       <c r="F360" s="23"/>
     </row>
-    <row r="361" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C361" s="24"/>
       <c r="D361" s="22"/>
       <c r="E361" s="22"/>
       <c r="F361" s="22"/>
     </row>
-    <row r="362" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C362" s="25"/>
       <c r="D362" s="23"/>
       <c r="E362" s="23"/>
       <c r="F362" s="23"/>
     </row>
-    <row r="363" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C363" s="24"/>
       <c r="D363" s="22"/>
       <c r="E363" s="22"/>
       <c r="F363" s="22"/>
     </row>
-    <row r="364" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C364" s="25"/>
       <c r="D364" s="23"/>
       <c r="E364" s="23"/>
       <c r="F364" s="23"/>
     </row>
-    <row r="365" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C365" s="24"/>
       <c r="D365" s="22"/>
       <c r="E365" s="22"/>
       <c r="F365" s="22"/>
     </row>
-    <row r="366" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C366" s="25"/>
       <c r="D366" s="23"/>
       <c r="E366" s="23"/>
       <c r="F366" s="23"/>
     </row>
-    <row r="367" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C367" s="24"/>
       <c r="D367" s="22"/>
       <c r="E367" s="22"/>
       <c r="F367" s="22"/>
     </row>
-    <row r="368" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C368" s="25"/>
       <c r="D368" s="23"/>
       <c r="E368" s="23"/>
       <c r="F368" s="23"/>
     </row>
-    <row r="369" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C369" s="24"/>
       <c r="D369" s="22"/>
       <c r="E369" s="22"/>
       <c r="F369" s="22"/>
     </row>
-    <row r="370" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C370" s="25"/>
       <c r="D370" s="23"/>
       <c r="E370" s="23"/>
       <c r="F370" s="23"/>
     </row>
-    <row r="371" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C371" s="24"/>
       <c r="D371" s="22"/>
       <c r="E371" s="22"/>
       <c r="F371" s="22"/>
     </row>
-    <row r="372" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C372" s="25"/>
       <c r="D372" s="23"/>
       <c r="E372" s="23"/>
       <c r="F372" s="23"/>
     </row>
-    <row r="373" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C373" s="24"/>
       <c r="D373" s="22"/>
       <c r="E373" s="22"/>
       <c r="F373" s="22"/>
     </row>
-    <row r="374" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C374" s="25"/>
       <c r="D374" s="23"/>
       <c r="E374" s="23"/>
       <c r="F374" s="23"/>
     </row>
-    <row r="375" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C375" s="24"/>
       <c r="D375" s="22"/>
       <c r="E375" s="22"/>
       <c r="F375" s="22"/>
     </row>
-    <row r="376" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C376" s="25"/>
       <c r="D376" s="23"/>
       <c r="E376" s="23"/>
       <c r="F376" s="23"/>
     </row>
-    <row r="377" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C377" s="24"/>
       <c r="D377" s="22"/>
       <c r="E377" s="22"/>
       <c r="F377" s="22"/>
     </row>
-    <row r="378" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C378" s="25"/>
       <c r="D378" s="23"/>
       <c r="E378" s="23"/>
       <c r="F378" s="23"/>
     </row>
-    <row r="379" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C379" s="24"/>
       <c r="D379" s="22"/>
       <c r="E379" s="22"/>
       <c r="F379" s="22"/>
     </row>
-    <row r="380" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C380" s="25"/>
       <c r="D380" s="23"/>
       <c r="E380" s="23"/>
       <c r="F380" s="23"/>
     </row>
-    <row r="381" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C381" s="24"/>
       <c r="D381" s="22"/>
       <c r="E381" s="22"/>
       <c r="F381" s="22"/>
     </row>
-    <row r="382" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C382" s="25"/>
       <c r="D382" s="23"/>
       <c r="E382" s="23"/>
       <c r="F382" s="23"/>
     </row>
-    <row r="383" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C383" s="24"/>
       <c r="D383" s="22"/>
       <c r="E383" s="22"/>
       <c r="F383" s="22"/>
     </row>
-    <row r="384" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C384" s="25"/>
       <c r="D384" s="23"/>
       <c r="E384" s="23"/>
       <c r="F384" s="23"/>
     </row>
-    <row r="385" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C385" s="24"/>
       <c r="D385" s="22"/>
       <c r="E385" s="22"/>
       <c r="F385" s="22"/>
     </row>
-    <row r="386" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C386" s="25"/>
       <c r="D386" s="23"/>
       <c r="E386" s="23"/>
       <c r="F386" s="23"/>
     </row>
-    <row r="387" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C387" s="24"/>
       <c r="D387" s="22"/>
       <c r="E387" s="22"/>
       <c r="F387" s="22"/>
     </row>
-    <row r="388" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C388" s="25"/>
       <c r="D388" s="23"/>
       <c r="E388" s="23"/>
       <c r="F388" s="23"/>
     </row>
-    <row r="389" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C389" s="24"/>
       <c r="D389" s="22"/>
       <c r="E389" s="22"/>
       <c r="F389" s="22"/>
     </row>
-    <row r="390" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C390" s="25"/>
       <c r="D390" s="23"/>
       <c r="E390" s="23"/>
       <c r="F390" s="23"/>
     </row>
-    <row r="391" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C391" s="24"/>
       <c r="D391" s="22"/>
       <c r="E391" s="22"/>
       <c r="F391" s="22"/>
     </row>
-    <row r="392" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C392" s="25"/>
       <c r="D392" s="23"/>
       <c r="E392" s="23"/>
       <c r="F392" s="23"/>
     </row>
-    <row r="393" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C393" s="24"/>
       <c r="D393" s="22"/>
       <c r="E393" s="22"/>
       <c r="F393" s="22"/>
     </row>
-    <row r="394" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C394" s="25"/>
       <c r="D394" s="23"/>
       <c r="E394" s="23"/>
       <c r="F394" s="23"/>
     </row>
-    <row r="395" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C395" s="24"/>
       <c r="D395" s="22"/>
       <c r="E395" s="22"/>
       <c r="F395" s="22"/>
     </row>
-    <row r="396" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C396" s="25"/>
       <c r="D396" s="23"/>
       <c r="E396" s="23"/>
       <c r="F396" s="23"/>
     </row>
-    <row r="397" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C397" s="24"/>
       <c r="D397" s="22"/>
       <c r="E397" s="22"/>
       <c r="F397" s="22"/>
     </row>
-    <row r="398" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C398" s="25"/>
       <c r="D398" s="23"/>
       <c r="E398" s="23"/>
       <c r="F398" s="23"/>
     </row>
-    <row r="399" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C399" s="24"/>
       <c r="D399" s="22"/>
       <c r="E399" s="22"/>
       <c r="F399" s="22"/>
     </row>
-    <row r="400" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C400" s="25"/>
       <c r="D400" s="23"/>
       <c r="E400" s="23"/>
       <c r="F400" s="23"/>
     </row>
-    <row r="401" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C401" s="24"/>
       <c r="D401" s="22"/>
       <c r="E401" s="22"/>
       <c r="F401" s="22"/>
     </row>
-    <row r="402" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C402" s="25"/>
       <c r="D402" s="23"/>
       <c r="E402" s="23"/>
       <c r="F402" s="23"/>
     </row>
-    <row r="403" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C403" s="24"/>
       <c r="D403" s="22"/>
       <c r="E403" s="22"/>
       <c r="F403" s="22"/>
     </row>
-    <row r="404" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C404" s="25"/>
       <c r="D404" s="23"/>
       <c r="E404" s="23"/>
       <c r="F404" s="23"/>
     </row>
-    <row r="405" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C405" s="24"/>
       <c r="D405" s="22"/>
       <c r="E405" s="22"/>
       <c r="F405" s="22"/>
     </row>
-    <row r="406" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C406" s="25"/>
       <c r="D406" s="23"/>
       <c r="E406" s="23"/>
       <c r="F406" s="23"/>
     </row>
-    <row r="407" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C407" s="24"/>
       <c r="D407" s="22"/>
       <c r="E407" s="22"/>
       <c r="F407" s="22"/>
     </row>
-    <row r="408" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C408" s="25"/>
       <c r="D408" s="23"/>
       <c r="E408" s="23"/>
       <c r="F408" s="23"/>
     </row>
-    <row r="409" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C409" s="24"/>
       <c r="D409" s="22"/>
       <c r="E409" s="22"/>
       <c r="F409" s="22"/>
     </row>
-    <row r="410" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C410" s="25"/>
       <c r="D410" s="23"/>
       <c r="E410" s="23"/>
       <c r="F410" s="23"/>
     </row>
-    <row r="411" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C411" s="24"/>
       <c r="D411" s="22"/>
       <c r="E411" s="22"/>
       <c r="F411" s="22"/>
     </row>
-    <row r="412" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C412" s="25"/>
       <c r="D412" s="23"/>
       <c r="E412" s="23"/>
       <c r="F412" s="23"/>
     </row>
-    <row r="413" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C413" s="24"/>
       <c r="D413" s="22"/>
       <c r="E413" s="22"/>
       <c r="F413" s="22"/>
     </row>
-    <row r="414" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C414" s="25"/>
       <c r="D414" s="23"/>
       <c r="E414" s="23"/>
       <c r="F414" s="23"/>
     </row>
-    <row r="415" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C415" s="24"/>
       <c r="D415" s="22"/>
       <c r="E415" s="22"/>
       <c r="F415" s="22"/>
     </row>
-    <row r="416" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C416" s="25"/>
       <c r="D416" s="23"/>
       <c r="E416" s="23"/>
       <c r="F416" s="23"/>
     </row>
-    <row r="417" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C417" s="24"/>
       <c r="D417" s="22"/>
       <c r="E417" s="22"/>
       <c r="F417" s="22"/>
     </row>
-    <row r="418" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C418" s="25"/>
       <c r="D418" s="23"/>
       <c r="E418" s="23"/>
       <c r="F418" s="23"/>
     </row>
-    <row r="419" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C419" s="24"/>
       <c r="D419" s="22"/>
       <c r="E419" s="22"/>
       <c r="F419" s="22"/>
     </row>
-    <row r="420" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C420" s="25"/>
       <c r="D420" s="23"/>
       <c r="E420" s="23"/>
       <c r="F420" s="23"/>
     </row>
-    <row r="421" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C421" s="24"/>
       <c r="D421" s="22"/>
       <c r="E421" s="22"/>
       <c r="F421" s="22"/>
     </row>
-    <row r="422" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C422" s="25"/>
       <c r="D422" s="23"/>
       <c r="E422" s="23"/>
       <c r="F422" s="23"/>
     </row>
-    <row r="423" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C423" s="24"/>
       <c r="D423" s="22"/>
       <c r="E423" s="22"/>
       <c r="F423" s="22"/>
     </row>
-    <row r="424" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C424" s="25"/>
       <c r="D424" s="23"/>
       <c r="E424" s="23"/>
       <c r="F424" s="23"/>
     </row>
-    <row r="425" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C425" s="24"/>
       <c r="D425" s="22"/>
       <c r="E425" s="22"/>
       <c r="F425" s="22"/>
     </row>
-    <row r="426" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C426" s="25"/>
       <c r="D426" s="23"/>
       <c r="E426" s="23"/>
       <c r="F426" s="23"/>
     </row>
-    <row r="427" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C427" s="24"/>
       <c r="D427" s="22"/>
       <c r="E427" s="22"/>
       <c r="F427" s="22"/>
     </row>
-    <row r="428" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C428" s="25"/>
       <c r="D428" s="23"/>
       <c r="E428" s="23"/>
       <c r="F428" s="23"/>
     </row>
-    <row r="429" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C429" s="24"/>
       <c r="D429" s="22"/>
       <c r="E429" s="22"/>
       <c r="F429" s="22"/>
     </row>
-    <row r="430" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C430" s="25"/>
       <c r="D430" s="23"/>
       <c r="E430" s="23"/>
       <c r="F430" s="23"/>
     </row>
-    <row r="431" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C431" s="24"/>
       <c r="D431" s="22"/>
       <c r="E431" s="22"/>
       <c r="F431" s="22"/>
     </row>
-    <row r="432" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C432" s="25"/>
       <c r="D432" s="23"/>
       <c r="E432" s="23"/>
       <c r="F432" s="23"/>
     </row>
-    <row r="433" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C433" s="24"/>
       <c r="D433" s="22"/>
       <c r="E433" s="22"/>
       <c r="F433" s="22"/>
     </row>
-    <row r="434" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C434" s="25"/>
       <c r="D434" s="23"/>
       <c r="E434" s="23"/>
       <c r="F434" s="23"/>
     </row>
-    <row r="435" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C435" s="24"/>
       <c r="D435" s="22"/>
       <c r="E435" s="22"/>
       <c r="F435" s="22"/>
     </row>
-    <row r="436" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C436" s="25"/>
       <c r="D436" s="23"/>
       <c r="E436" s="23"/>
       <c r="F436" s="23"/>
     </row>
-    <row r="437" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C437" s="24"/>
       <c r="D437" s="22"/>
       <c r="E437" s="22"/>
       <c r="F437" s="22"/>
     </row>
-    <row r="438" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C438" s="25"/>
       <c r="D438" s="23"/>
       <c r="E438" s="23"/>
       <c r="F438" s="23"/>
     </row>
-    <row r="439" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C439" s="24"/>
       <c r="D439" s="22"/>
       <c r="E439" s="22"/>
       <c r="F439" s="22"/>
     </row>
-    <row r="440" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C440" s="25"/>
       <c r="D440" s="23"/>
       <c r="E440" s="23"/>
       <c r="F440" s="23"/>
     </row>
-    <row r="441" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C441" s="24"/>
       <c r="D441" s="22"/>
       <c r="E441" s="22"/>
       <c r="F441" s="22"/>
     </row>
-    <row r="442" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C442" s="25"/>
       <c r="D442" s="23"/>
       <c r="E442" s="23"/>
       <c r="F442" s="23"/>
     </row>
-    <row r="443" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C443" s="24"/>
       <c r="D443" s="22"/>
       <c r="E443" s="22"/>
       <c r="F443" s="22"/>
     </row>
-    <row r="444" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C444" s="25"/>
       <c r="D444" s="23"/>
       <c r="E444" s="23"/>
       <c r="F444" s="23"/>
     </row>
-    <row r="445" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C445" s="24"/>
       <c r="D445" s="22"/>
       <c r="E445" s="22"/>
       <c r="F445" s="22"/>
     </row>
-    <row r="446" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C446" s="25"/>
       <c r="D446" s="23"/>
       <c r="E446" s="23"/>
       <c r="F446" s="23"/>
     </row>
-    <row r="447" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C447" s="24"/>
       <c r="D447" s="22"/>
       <c r="E447" s="22"/>
       <c r="F447" s="22"/>
     </row>
-    <row r="448" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C448" s="25"/>
       <c r="D448" s="23"/>
       <c r="E448" s="23"/>
       <c r="F448" s="23"/>
     </row>
-    <row r="449" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C449" s="24"/>
       <c r="D449" s="22"/>
       <c r="E449" s="22"/>
       <c r="F449" s="22"/>
     </row>
-    <row r="450" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C450" s="25"/>
       <c r="D450" s="23"/>
       <c r="E450" s="23"/>
       <c r="F450" s="23"/>
     </row>
-    <row r="451" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C451" s="24"/>
       <c r="D451" s="22"/>
       <c r="E451" s="22"/>
       <c r="F451" s="22"/>
     </row>
-    <row r="452" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C452" s="25"/>
       <c r="D452" s="23"/>
       <c r="E452" s="23"/>
       <c r="F452" s="23"/>
     </row>
-    <row r="453" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C453" s="24"/>
       <c r="D453" s="22"/>
       <c r="E453" s="22"/>
       <c r="F453" s="22"/>
     </row>
-    <row r="454" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C454" s="25"/>
       <c r="D454" s="23"/>
       <c r="E454" s="23"/>
       <c r="F454" s="23"/>
     </row>
-    <row r="455" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C455" s="24"/>
       <c r="D455" s="22"/>
       <c r="E455" s="22"/>
       <c r="F455" s="22"/>
     </row>
-    <row r="456" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C456" s="25"/>
       <c r="D456" s="23"/>
       <c r="E456" s="23"/>
       <c r="F456" s="23"/>
     </row>
-    <row r="457" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C457" s="24"/>
       <c r="D457" s="22"/>
       <c r="E457" s="22"/>
       <c r="F457" s="22"/>
     </row>
-    <row r="458" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C458" s="25"/>
       <c r="D458" s="23"/>
       <c r="E458" s="23"/>
       <c r="F458" s="23"/>
     </row>
-    <row r="459" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C459" s="24"/>
       <c r="D459" s="22"/>
       <c r="E459" s="22"/>
       <c r="F459" s="22"/>
     </row>
-    <row r="460" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C460" s="25"/>
       <c r="D460" s="23"/>
       <c r="E460" s="23"/>
       <c r="F460" s="23"/>
     </row>
-    <row r="461" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C461" s="24"/>
       <c r="D461" s="22"/>
       <c r="E461" s="22"/>
       <c r="F461" s="22"/>
     </row>
-    <row r="462" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C462" s="25"/>
       <c r="D462" s="23"/>
       <c r="E462" s="23"/>
       <c r="F462" s="23"/>
     </row>
-    <row r="463" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C463" s="24"/>
       <c r="D463" s="22"/>
       <c r="E463" s="22"/>
       <c r="F463" s="22"/>
     </row>
-    <row r="464" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C464" s="25"/>
       <c r="D464" s="23"/>
       <c r="E464" s="23"/>
       <c r="F464" s="23"/>
     </row>
-    <row r="465" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C465" s="24"/>
       <c r="D465" s="22"/>
       <c r="E465" s="22"/>
       <c r="F465" s="22"/>
     </row>
-    <row r="466" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C466" s="25"/>
       <c r="D466" s="23"/>
       <c r="E466" s="23"/>
       <c r="F466" s="23"/>
     </row>
-    <row r="467" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C467" s="24"/>
       <c r="D467" s="22"/>
       <c r="E467" s="22"/>
       <c r="F467" s="22"/>
     </row>
-    <row r="468" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C468" s="25"/>
       <c r="D468" s="23"/>
       <c r="E468" s="23"/>
       <c r="F468" s="23"/>
     </row>
-    <row r="469" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C469" s="24"/>
       <c r="D469" s="22"/>
       <c r="E469" s="22"/>
       <c r="F469" s="22"/>
     </row>
-    <row r="470" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C470" s="25"/>
       <c r="D470" s="23"/>
       <c r="E470" s="23"/>
       <c r="F470" s="23"/>
     </row>
-    <row r="471" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C471" s="24"/>
       <c r="D471" s="22"/>
       <c r="E471" s="22"/>
       <c r="F471" s="22"/>
     </row>
-    <row r="472" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C472" s="25"/>
       <c r="D472" s="23"/>
       <c r="E472" s="23"/>
       <c r="F472" s="23"/>
     </row>
-    <row r="473" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C473" s="24"/>
       <c r="D473" s="22"/>
       <c r="E473" s="22"/>
       <c r="F473" s="22"/>
     </row>
-    <row r="474" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C474" s="25"/>
       <c r="D474" s="23"/>
       <c r="E474" s="23"/>
       <c r="F474" s="23"/>
     </row>
-    <row r="475" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C475" s="24"/>
       <c r="D475" s="22"/>
       <c r="E475" s="22"/>
       <c r="F475" s="22"/>
     </row>
-    <row r="476" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C476" s="25"/>
       <c r="D476" s="23"/>
       <c r="E476" s="23"/>
       <c r="F476" s="23"/>
     </row>
-    <row r="477" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C477" s="24"/>
       <c r="D477" s="22"/>
       <c r="E477" s="22"/>
       <c r="F477" s="22"/>
     </row>
-    <row r="478" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C478" s="25"/>
       <c r="D478" s="23"/>
       <c r="E478" s="23"/>
       <c r="F478" s="23"/>
     </row>
-    <row r="479" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C479" s="24"/>
       <c r="D479" s="22"/>
       <c r="E479" s="22"/>
       <c r="F479" s="22"/>
     </row>
-    <row r="480" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C480" s="25"/>
       <c r="D480" s="23"/>
       <c r="E480" s="23"/>
       <c r="F480" s="23"/>
     </row>
-    <row r="481" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C481" s="24"/>
       <c r="D481" s="22"/>
       <c r="E481" s="22"/>
       <c r="F481" s="22"/>
     </row>
-    <row r="482" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C482" s="25"/>
       <c r="D482" s="23"/>
       <c r="E482" s="23"/>
       <c r="F482" s="23"/>
     </row>
-    <row r="483" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C483" s="24"/>
       <c r="D483" s="22"/>
       <c r="E483" s="22"/>
       <c r="F483" s="22"/>
     </row>
-    <row r="484" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="484" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C484" s="25"/>
       <c r="D484" s="23"/>
       <c r="E484" s="23"/>
       <c r="F484" s="23"/>
     </row>
-    <row r="485" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C485" s="24"/>
       <c r="D485" s="22"/>
       <c r="E485" s="22"/>
       <c r="F485" s="22"/>
     </row>
-    <row r="486" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="486" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C486" s="25"/>
       <c r="D486" s="23"/>
       <c r="E486" s="23"/>
       <c r="F486" s="23"/>
     </row>
-    <row r="487" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="487" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C487" s="24"/>
       <c r="D487" s="22"/>
       <c r="E487" s="22"/>
       <c r="F487" s="22"/>
     </row>
-    <row r="488" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C488" s="25"/>
       <c r="D488" s="23"/>
       <c r="E488" s="23"/>
       <c r="F488" s="23"/>
     </row>
-    <row r="489" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C489" s="24"/>
       <c r="D489" s="22"/>
       <c r="E489" s="22"/>
       <c r="F489" s="22"/>
     </row>
-    <row r="490" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="490" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C490" s="25"/>
       <c r="D490" s="23"/>
       <c r="E490" s="23"/>
       <c r="F490" s="23"/>
     </row>
-    <row r="491" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C491" s="24"/>
       <c r="D491" s="22"/>
       <c r="E491" s="22"/>
       <c r="F491" s="22"/>
     </row>
-    <row r="492" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="492" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C492" s="25"/>
       <c r="D492" s="23"/>
       <c r="E492" s="23"/>
       <c r="F492" s="23"/>
     </row>
-    <row r="493" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="493" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C493" s="24"/>
       <c r="D493" s="22"/>
       <c r="E493" s="22"/>
       <c r="F493" s="22"/>
     </row>
-    <row r="494" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C494" s="25"/>
       <c r="D494" s="23"/>
       <c r="E494" s="23"/>
       <c r="F494" s="23"/>
     </row>
-    <row r="495" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="495" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C495" s="24"/>
       <c r="D495" s="22"/>
       <c r="E495" s="22"/>
       <c r="F495" s="22"/>
     </row>
-    <row r="496" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="496" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C496" s="25"/>
       <c r="D496" s="23"/>
       <c r="E496" s="23"/>
       <c r="F496" s="23"/>
     </row>
-    <row r="497" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="497" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C497" s="24"/>
       <c r="D497" s="22"/>
       <c r="E497" s="22"/>
       <c r="F497" s="22"/>
     </row>
-    <row r="498" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="498" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C498" s="25"/>
       <c r="D498" s="23"/>
       <c r="E498" s="23"/>
       <c r="F498" s="23"/>
     </row>
-    <row r="499" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="499" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C499" s="24"/>
       <c r="D499" s="22"/>
       <c r="E499" s="22"/>
       <c r="F499" s="22"/>
     </row>
-    <row r="500" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="500" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C500" s="25"/>
       <c r="D500" s="23"/>
       <c r="E500" s="23"/>
       <c r="F500" s="23"/>
     </row>
-    <row r="501" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="501" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C501" s="24"/>
       <c r="D501" s="22"/>
       <c r="E501" s="22"/>
       <c r="F501" s="22"/>
     </row>
-    <row r="502" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="502" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C502" s="25"/>
       <c r="D502" s="23"/>
       <c r="E502" s="23"/>
       <c r="F502" s="23"/>
     </row>
-    <row r="503" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="503" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C503" s="24"/>
       <c r="D503" s="22"/>
       <c r="E503" s="22"/>
       <c r="F503" s="22"/>
     </row>
-    <row r="504" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="504" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C504" s="25"/>
       <c r="D504" s="23"/>
       <c r="E504" s="23"/>
       <c r="F504" s="23"/>
     </row>
-    <row r="505" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="505" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C505" s="24"/>
       <c r="D505" s="22"/>
       <c r="E505" s="22"/>
       <c r="F505" s="22"/>
     </row>
-    <row r="506" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="506" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C506" s="25"/>
       <c r="D506" s="23"/>
       <c r="E506" s="23"/>
       <c r="F506" s="23"/>
     </row>
-    <row r="507" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="507" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C507" s="24"/>
       <c r="D507" s="22"/>
       <c r="E507" s="22"/>
       <c r="F507" s="22"/>
     </row>
-    <row r="508" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="508" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C508" s="25"/>
       <c r="D508" s="23"/>
       <c r="E508" s="23"/>
       <c r="F508" s="23"/>
     </row>
-    <row r="509" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C509" s="24"/>
       <c r="D509" s="22"/>
       <c r="E509" s="22"/>
       <c r="F509" s="22"/>
     </row>
-    <row r="510" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="510" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C510" s="25"/>
       <c r="D510" s="23"/>
       <c r="E510" s="23"/>
       <c r="F510" s="23"/>
     </row>
-    <row r="511" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="511" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C511" s="24"/>
       <c r="D511" s="22"/>
       <c r="E511" s="22"/>
       <c r="F511" s="22"/>
     </row>
-    <row r="512" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="512" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C512" s="25"/>
       <c r="D512" s="23"/>
       <c r="E512" s="23"/>
       <c r="F512" s="23"/>
     </row>
-    <row r="513" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="513" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C513" s="24"/>
       <c r="D513" s="22"/>
       <c r="E513" s="22"/>
       <c r="F513" s="22"/>
     </row>
-    <row r="514" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="514" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C514" s="25"/>
       <c r="D514" s="23"/>
       <c r="E514" s="23"/>
       <c r="F514" s="23"/>
     </row>
-    <row r="515" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C515" s="24"/>
       <c r="D515" s="22"/>
       <c r="E515" s="22"/>
       <c r="F515" s="22"/>
     </row>
-    <row r="516" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C516" s="25"/>
       <c r="D516" s="23"/>
       <c r="E516" s="23"/>
       <c r="F516" s="23"/>
     </row>
-    <row r="517" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C517" s="24"/>
       <c r="D517" s="22"/>
       <c r="E517" s="22"/>
       <c r="F517" s="22"/>
     </row>
-    <row r="518" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C518" s="25"/>
       <c r="D518" s="23"/>
       <c r="E518" s="23"/>
       <c r="F518" s="23"/>
     </row>
-    <row r="519" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C519" s="24"/>
       <c r="D519" s="22"/>
       <c r="E519" s="22"/>
       <c r="F519" s="22"/>
     </row>
-    <row r="520" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="520" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C520" s="25"/>
       <c r="D520" s="23"/>
       <c r="E520" s="23"/>
       <c r="F520" s="23"/>
     </row>
-    <row r="521" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C521" s="24"/>
       <c r="D521" s="22"/>
       <c r="E521" s="22"/>
       <c r="F521" s="22"/>
     </row>
-    <row r="522" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C522" s="25"/>
       <c r="D522" s="23"/>
       <c r="E522" s="23"/>
       <c r="F522" s="23"/>
     </row>
-    <row r="523" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="523" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C523" s="24"/>
       <c r="D523" s="22"/>
       <c r="E523" s="22"/>
       <c r="F523" s="22"/>
     </row>
-    <row r="524" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C524" s="25"/>
       <c r="D524" s="23"/>
       <c r="E524" s="23"/>
       <c r="F524" s="23"/>
     </row>
-    <row r="525" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C525" s="24"/>
       <c r="D525" s="22"/>
       <c r="E525" s="22"/>
       <c r="F525" s="22"/>
     </row>
-    <row r="526" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="526" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C526" s="25"/>
       <c r="D526" s="23"/>
       <c r="E526" s="23"/>
       <c r="F526" s="23"/>
     </row>
-    <row r="527" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="527" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C527" s="24"/>
       <c r="D527" s="22"/>
       <c r="E527" s="22"/>
       <c r="F527" s="22"/>
     </row>
-    <row r="528" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="528" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C528" s="25"/>
       <c r="D528" s="23"/>
       <c r="E528" s="23"/>
       <c r="F528" s="23"/>
     </row>
-    <row r="529" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="529" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C529" s="24"/>
       <c r="D529" s="22"/>
       <c r="E529" s="22"/>
       <c r="F529" s="22"/>
     </row>
-    <row r="530" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C530" s="25"/>
       <c r="D530" s="23"/>
       <c r="E530" s="23"/>
       <c r="F530" s="23"/>
     </row>
-    <row r="531" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C531" s="24"/>
       <c r="D531" s="22"/>
       <c r="E531" s="22"/>
       <c r="F531" s="22"/>
     </row>
-    <row r="532" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="532" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C532" s="25"/>
       <c r="D532" s="23"/>
       <c r="E532" s="23"/>
       <c r="F532" s="23"/>
     </row>
-    <row r="533" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C533" s="24"/>
       <c r="D533" s="22"/>
       <c r="E533" s="22"/>
       <c r="F533" s="22"/>
     </row>
-    <row r="534" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C534" s="25"/>
       <c r="D534" s="23"/>
       <c r="E534" s="23"/>
       <c r="F534" s="23"/>
     </row>
-    <row r="535" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C535" s="24"/>
       <c r="D535" s="22"/>
       <c r="E535" s="22"/>
       <c r="F535" s="22"/>
     </row>
-    <row r="536" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C536" s="25"/>
       <c r="D536" s="23"/>
       <c r="E536" s="23"/>
       <c r="F536" s="23"/>
     </row>
-    <row r="537" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C537" s="24"/>
       <c r="D537" s="22"/>
       <c r="E537" s="22"/>
       <c r="F537" s="22"/>
     </row>
-    <row r="538" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C538" s="25"/>
       <c r="D538" s="23"/>
       <c r="E538" s="23"/>
       <c r="F538" s="23"/>
     </row>
-    <row r="539" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C539" s="24"/>
       <c r="D539" s="22"/>
       <c r="E539" s="22"/>
       <c r="F539" s="22"/>
     </row>
-    <row r="540" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C540" s="25"/>
       <c r="D540" s="23"/>
       <c r="E540" s="23"/>
       <c r="F540" s="23"/>
     </row>
-    <row r="541" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C541" s="24"/>
       <c r="D541" s="22"/>
       <c r="E541" s="22"/>
       <c r="F541" s="22"/>
     </row>
-    <row r="542" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C542" s="25"/>
       <c r="D542" s="23"/>
       <c r="E542" s="23"/>
       <c r="F542" s="23"/>
     </row>
-    <row r="543" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C543" s="24"/>
       <c r="D543" s="22"/>
       <c r="E543" s="22"/>
       <c r="F543" s="22"/>
     </row>
-    <row r="544" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="544" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C544" s="25"/>
       <c r="D544" s="23"/>
       <c r="E544" s="23"/>
       <c r="F544" s="23"/>
     </row>
-    <row r="545" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C545" s="24"/>
       <c r="D545" s="22"/>
       <c r="E545" s="22"/>
       <c r="F545" s="22"/>
     </row>
-    <row r="546" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C546" s="25"/>
       <c r="D546" s="23"/>
       <c r="E546" s="23"/>
       <c r="F546" s="23"/>
     </row>
-    <row r="547" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="547" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C547" s="24"/>
       <c r="D547" s="22"/>
       <c r="E547" s="22"/>
       <c r="F547" s="22"/>
     </row>
-    <row r="548" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C548" s="25"/>
       <c r="D548" s="23"/>
       <c r="E548" s="23"/>
       <c r="F548" s="23"/>
     </row>
-    <row r="549" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C549" s="24"/>
       <c r="D549" s="22"/>
       <c r="E549" s="22"/>
       <c r="F549" s="22"/>
     </row>
-    <row r="550" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C550" s="25"/>
       <c r="D550" s="23"/>
       <c r="E550" s="23"/>
       <c r="F550" s="23"/>
     </row>
-    <row r="551" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C551" s="24"/>
       <c r="D551" s="22"/>
       <c r="E551" s="22"/>
       <c r="F551" s="22"/>
     </row>
-    <row r="552" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C552" s="25"/>
       <c r="D552" s="23"/>
       <c r="E552" s="23"/>
       <c r="F552" s="23"/>
     </row>
-    <row r="553" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="553" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C553" s="24"/>
       <c r="D553" s="22"/>
       <c r="E553" s="22"/>
       <c r="F553" s="22"/>
     </row>
-    <row r="554" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C554" s="25"/>
       <c r="D554" s="23"/>
       <c r="E554" s="23"/>
       <c r="F554" s="23"/>
     </row>
-    <row r="555" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C555" s="24"/>
       <c r="D555" s="22"/>
       <c r="E555" s="22"/>
       <c r="F555" s="22"/>
     </row>
-    <row r="556" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="556" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C556" s="25"/>
       <c r="D556" s="23"/>
       <c r="E556" s="23"/>
       <c r="F556" s="23"/>
     </row>
-    <row r="557" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C557" s="24"/>
       <c r="D557" s="22"/>
       <c r="E557" s="22"/>
       <c r="F557" s="22"/>
     </row>
-    <row r="558" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C558" s="25"/>
       <c r="D558" s="23"/>
       <c r="E558" s="23"/>
       <c r="F558" s="23"/>
     </row>
-    <row r="559" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="559" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C559" s="24"/>
       <c r="D559" s="22"/>
       <c r="E559" s="22"/>
       <c r="F559" s="22"/>
     </row>
-    <row r="560" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C560" s="25"/>
       <c r="D560" s="23"/>
       <c r="E560" s="23"/>
       <c r="F560" s="23"/>
     </row>
-    <row r="561" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C561" s="24"/>
       <c r="D561" s="22"/>
       <c r="E561" s="22"/>
       <c r="F561" s="22"/>
     </row>
-    <row r="562" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C562" s="25"/>
       <c r="D562" s="23"/>
       <c r="E562" s="23"/>
       <c r="F562" s="23"/>
     </row>
-    <row r="563" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C563" s="24"/>
       <c r="D563" s="22"/>
       <c r="E563" s="22"/>
       <c r="F563" s="22"/>
     </row>
-    <row r="564" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C564" s="25"/>
       <c r="D564" s="23"/>
       <c r="E564" s="23"/>
       <c r="F564" s="23"/>
     </row>
-    <row r="565" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C565" s="24"/>
       <c r="D565" s="22"/>
       <c r="E565" s="22"/>
       <c r="F565" s="22"/>
     </row>
-    <row r="566" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C566" s="25"/>
       <c r="D566" s="23"/>
       <c r="E566" s="23"/>
       <c r="F566" s="23"/>
     </row>
-    <row r="567" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C567" s="24"/>
       <c r="D567" s="22"/>
       <c r="E567" s="22"/>
       <c r="F567" s="22"/>
     </row>
-    <row r="568" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C568" s="25"/>
       <c r="D568" s="23"/>
       <c r="E568" s="23"/>
       <c r="F568" s="23"/>
     </row>
-    <row r="569" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C569" s="24"/>
       <c r="D569" s="22"/>
       <c r="E569" s="22"/>
       <c r="F569" s="22"/>
     </row>
-    <row r="570" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C570" s="25"/>
       <c r="D570" s="23"/>
       <c r="E570" s="23"/>
       <c r="F570" s="23"/>
     </row>
-    <row r="571" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="571" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C571" s="24"/>
       <c r="D571" s="22"/>
       <c r="E571" s="22"/>
       <c r="F571" s="22"/>
     </row>
-    <row r="572" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C572" s="25"/>
       <c r="D572" s="23"/>
       <c r="E572" s="23"/>
       <c r="F572" s="23"/>
     </row>
-    <row r="573" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C573" s="24"/>
       <c r="D573" s="22"/>
       <c r="E573" s="22"/>
       <c r="F573" s="22"/>
     </row>
-    <row r="574" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="574" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C574" s="25"/>
       <c r="D574" s="23"/>
       <c r="E574" s="23"/>
       <c r="F574" s="23"/>
     </row>
-    <row r="575" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C575" s="24"/>
       <c r="D575" s="22"/>
       <c r="E575" s="22"/>
       <c r="F575" s="22"/>
     </row>
-    <row r="576" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C576" s="25"/>
       <c r="D576" s="23"/>
       <c r="E576" s="23"/>
       <c r="F576" s="23"/>
     </row>
-    <row r="577" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="577" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C577" s="24"/>
       <c r="D577" s="22"/>
       <c r="E577" s="22"/>
       <c r="F577" s="22"/>
     </row>
-    <row r="578" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C578" s="25"/>
       <c r="D578" s="23"/>
       <c r="E578" s="23"/>
       <c r="F578" s="23"/>
     </row>
-    <row r="579" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C579" s="24"/>
       <c r="D579" s="22"/>
       <c r="E579" s="22"/>
       <c r="F579" s="22"/>
     </row>
-    <row r="580" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="580" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C580" s="25"/>
       <c r="D580" s="23"/>
       <c r="E580" s="23"/>
       <c r="F580" s="23"/>
     </row>
-    <row r="581" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C581" s="24"/>
       <c r="D581" s="22"/>
       <c r="E581" s="22"/>
       <c r="F581" s="22"/>
     </row>
-    <row r="582" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C582" s="25"/>
       <c r="D582" s="23"/>
       <c r="E582" s="23"/>
       <c r="F582" s="23"/>
     </row>
-    <row r="583" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C583" s="24"/>
       <c r="D583" s="22"/>
       <c r="E583" s="22"/>
       <c r="F583" s="22"/>
     </row>
-    <row r="584" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C584" s="25"/>
       <c r="D584" s="23"/>
       <c r="E584" s="23"/>
       <c r="F584" s="23"/>
     </row>
-    <row r="585" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C585" s="24"/>
       <c r="D585" s="22"/>
       <c r="E585" s="22"/>
       <c r="F585" s="22"/>
     </row>
-    <row r="586" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="586" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C586" s="25"/>
       <c r="D586" s="23"/>
       <c r="E586" s="23"/>
       <c r="F586" s="23"/>
     </row>
-    <row r="587" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C587" s="24"/>
       <c r="D587" s="22"/>
       <c r="E587" s="22"/>
       <c r="F587" s="22"/>
     </row>
-    <row r="588" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C588" s="25"/>
       <c r="D588" s="23"/>
       <c r="E588" s="23"/>
       <c r="F588" s="23"/>
     </row>
-    <row r="589" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C589" s="24"/>
       <c r="D589" s="22"/>
       <c r="E589" s="22"/>
       <c r="F589" s="22"/>
     </row>
-    <row r="590" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C590" s="25"/>
       <c r="D590" s="23"/>
       <c r="E590" s="23"/>
       <c r="F590" s="23"/>
     </row>
-    <row r="591" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C591" s="24"/>
       <c r="D591" s="22"/>
       <c r="E591" s="22"/>
       <c r="F591" s="22"/>
     </row>
-    <row r="592" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="592" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C592" s="25"/>
       <c r="D592" s="23"/>
       <c r="E592" s="23"/>
       <c r="F592" s="23"/>
     </row>
-    <row r="593" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C593" s="24"/>
       <c r="D593" s="22"/>
       <c r="E593" s="22"/>
       <c r="F593" s="22"/>
     </row>
-    <row r="594" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C594" s="25"/>
       <c r="D594" s="23"/>
       <c r="E594" s="23"/>
       <c r="F594" s="23"/>
     </row>
-    <row r="595" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="595" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C595" s="24"/>
       <c r="D595" s="22"/>
       <c r="E595" s="22"/>
       <c r="F595" s="22"/>
     </row>
-    <row r="596" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C596" s="25"/>
       <c r="D596" s="23"/>
       <c r="E596" s="23"/>
       <c r="F596" s="23"/>
     </row>
-    <row r="597" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C597" s="24"/>
       <c r="D597" s="22"/>
       <c r="E597" s="22"/>
       <c r="F597" s="22"/>
     </row>
-    <row r="598" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="598" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C598" s="25"/>
       <c r="D598" s="23"/>
       <c r="E598" s="23"/>
       <c r="F598" s="23"/>
     </row>
-    <row r="599" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C599" s="24"/>
       <c r="D599" s="22"/>
       <c r="E599" s="22"/>
       <c r="F599" s="22"/>
     </row>
-    <row r="600" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="600" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C600" s="25"/>
       <c r="D600" s="23"/>
       <c r="E600" s="23"/>
       <c r="F600" s="23"/>
     </row>
-    <row r="601" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="601" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C601" s="24"/>
       <c r="D601" s="22"/>
       <c r="E601" s="22"/>
       <c r="F601" s="22"/>
     </row>
-    <row r="602" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C602" s="25"/>
       <c r="D602" s="23"/>
       <c r="E602" s="23"/>
       <c r="F602" s="23"/>
     </row>
-    <row r="603" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C603" s="24"/>
       <c r="D603" s="22"/>
       <c r="E603" s="22"/>
       <c r="F603" s="22"/>
     </row>
-    <row r="604" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="604" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C604" s="25"/>
       <c r="D604" s="23"/>
       <c r="E604" s="23"/>
       <c r="F604" s="23"/>
     </row>
-    <row r="605" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C605" s="24"/>
       <c r="D605" s="22"/>
       <c r="E605" s="22"/>
       <c r="F605" s="22"/>
     </row>
-    <row r="606" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C606" s="25"/>
       <c r="D606" s="23"/>
       <c r="E606" s="23"/>
       <c r="F606" s="23"/>
     </row>
-    <row r="607" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="607" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C607" s="24"/>
       <c r="D607" s="22"/>
       <c r="E607" s="22"/>
       <c r="F607" s="22"/>
     </row>
-    <row r="608" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C608" s="25"/>
       <c r="D608" s="23"/>
       <c r="E608" s="23"/>
       <c r="F608" s="23"/>
     </row>
-    <row r="609" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C609" s="24"/>
       <c r="D609" s="22"/>
       <c r="E609" s="22"/>
       <c r="F609" s="22"/>
     </row>
-    <row r="610" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="610" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C610" s="25"/>
       <c r="D610" s="23"/>
       <c r="E610" s="23"/>
       <c r="F610" s="23"/>
     </row>
-    <row r="611" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C611" s="24"/>
       <c r="D611" s="22"/>
       <c r="E611" s="22"/>
       <c r="F611" s="22"/>
     </row>
-    <row r="612" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C612" s="25"/>
       <c r="D612" s="23"/>
       <c r="E612" s="23"/>
       <c r="F612" s="23"/>
     </row>
-    <row r="613" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="613" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C613" s="24"/>
       <c r="D613" s="22"/>
       <c r="E613" s="22"/>
       <c r="F613" s="22"/>
     </row>
-    <row r="614" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C614" s="25"/>
       <c r="D614" s="23"/>
       <c r="E614" s="23"/>
       <c r="F614" s="23"/>
     </row>
-    <row r="615" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C615" s="24"/>
       <c r="D615" s="22"/>
       <c r="E615" s="22"/>
       <c r="F615" s="22"/>
     </row>
-    <row r="616" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C616" s="25"/>
       <c r="D616" s="23"/>
       <c r="E616" s="23"/>
       <c r="F616" s="23"/>
     </row>
-    <row r="617" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C617" s="24"/>
       <c r="D617" s="22"/>
       <c r="E617" s="22"/>
       <c r="F617" s="22"/>
     </row>
-    <row r="618" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C618" s="25"/>
       <c r="D618" s="23"/>
       <c r="E618" s="23"/>
       <c r="F618" s="23"/>
     </row>
-    <row r="619" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C619" s="24"/>
       <c r="D619" s="22"/>
       <c r="E619" s="22"/>
       <c r="F619" s="22"/>
     </row>
-    <row r="620" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C620" s="25"/>
       <c r="D620" s="23"/>
       <c r="E620" s="23"/>
       <c r="F620" s="23"/>
     </row>
-    <row r="621" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C621" s="24"/>
       <c r="D621" s="22"/>
       <c r="E621" s="22"/>
       <c r="F621" s="22"/>
     </row>
-    <row r="622" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C622" s="25"/>
       <c r="D622" s="23"/>
       <c r="E622" s="23"/>
       <c r="F622" s="23"/>
     </row>
-    <row r="623" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C623" s="24"/>
       <c r="D623" s="22"/>
       <c r="E623" s="22"/>
       <c r="F623" s="22"/>
     </row>
-    <row r="624" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C624" s="25"/>
       <c r="D624" s="23"/>
       <c r="E624" s="23"/>
       <c r="F624" s="23"/>
     </row>
-    <row r="625" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C625" s="24"/>
       <c r="D625" s="22"/>
       <c r="E625" s="22"/>
       <c r="F625" s="22"/>
     </row>
-    <row r="626" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C626" s="25"/>
       <c r="D626" s="23"/>
       <c r="E626" s="23"/>
       <c r="F626" s="23"/>
     </row>
-    <row r="627" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C627" s="24"/>
       <c r="D627" s="22"/>
       <c r="E627" s="22"/>
       <c r="F627" s="22"/>
     </row>
-    <row r="628" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="628" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C628" s="25"/>
       <c r="D628" s="23"/>
       <c r="E628" s="23"/>
       <c r="F628" s="23"/>
     </row>
-    <row r="629" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="629" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C629" s="24"/>
       <c r="D629" s="22"/>
       <c r="E629" s="22"/>
       <c r="F629" s="22"/>
     </row>
-    <row r="630" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="630" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C630" s="25"/>
       <c r="D630" s="23"/>
       <c r="E630" s="23"/>
       <c r="F630" s="23"/>
     </row>
-    <row r="631" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="631" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C631" s="24"/>
       <c r="D631" s="22"/>
       <c r="E631" s="22"/>
       <c r="F631" s="22"/>
     </row>
-    <row r="632" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="632" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C632" s="25"/>
       <c r="D632" s="23"/>
       <c r="E632" s="23"/>
       <c r="F632" s="23"/>
     </row>
-    <row r="633" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="633" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C633" s="24"/>
       <c r="D633" s="22"/>
       <c r="E633" s="22"/>
       <c r="F633" s="22"/>
     </row>
-    <row r="634" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="634" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C634" s="25"/>
       <c r="D634" s="23"/>
       <c r="E634" s="23"/>
       <c r="F634" s="23"/>
     </row>
-    <row r="635" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C635" s="24"/>
       <c r="D635" s="22"/>
       <c r="E635" s="22"/>
       <c r="F635" s="22"/>
     </row>
-    <row r="636" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C636" s="25"/>
       <c r="D636" s="23"/>
       <c r="E636" s="23"/>
       <c r="F636" s="23"/>
     </row>
-    <row r="637" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="637" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C637" s="24"/>
       <c r="D637" s="22"/>
       <c r="E637" s="22"/>
       <c r="F637" s="22"/>
     </row>
-    <row r="638" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="638" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C638" s="25"/>
       <c r="D638" s="23"/>
       <c r="E638" s="23"/>
       <c r="F638" s="23"/>
     </row>
-    <row r="639" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="639" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C639" s="24"/>
       <c r="D639" s="22"/>
       <c r="E639" s="22"/>
       <c r="F639" s="22"/>
     </row>
-    <row r="640" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="640" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C640" s="25"/>
       <c r="D640" s="23"/>
       <c r="E640" s="23"/>
       <c r="F640" s="23"/>
     </row>
-    <row r="641" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C641" s="24"/>
       <c r="D641" s="22"/>
       <c r="E641" s="22"/>
       <c r="F641" s="22"/>
     </row>
-    <row r="642" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C642" s="25"/>
       <c r="D642" s="23"/>
       <c r="E642" s="23"/>
       <c r="F642" s="23"/>
     </row>
-    <row r="643" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C643" s="24"/>
       <c r="D643" s="22"/>
       <c r="E643" s="22"/>
       <c r="F643" s="22"/>
     </row>
-    <row r="644" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C644" s="25"/>
       <c r="D644" s="23"/>
       <c r="E644" s="23"/>
       <c r="F644" s="23"/>
     </row>
-    <row r="645" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C645" s="24"/>
       <c r="D645" s="22"/>
       <c r="E645" s="22"/>
       <c r="F645" s="22"/>
     </row>
-    <row r="646" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="646" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C646" s="25"/>
       <c r="D646" s="23"/>
       <c r="E646" s="23"/>
       <c r="F646" s="23"/>
     </row>
-    <row r="647" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="647" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C647" s="24"/>
       <c r="D647" s="22"/>
       <c r="E647" s="22"/>
       <c r="F647" s="22"/>
     </row>
-    <row r="648" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="648" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C648" s="25"/>
       <c r="D648" s="23"/>
       <c r="E648" s="23"/>
       <c r="F648" s="23"/>
     </row>
-    <row r="649" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="649" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C649" s="24"/>
       <c r="D649" s="22"/>
       <c r="E649" s="22"/>
       <c r="F649" s="22"/>
     </row>
-    <row r="650" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="650" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C650" s="25"/>
       <c r="D650" s="23"/>
       <c r="E650" s="23"/>
       <c r="F650" s="23"/>
     </row>
-    <row r="651" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="651" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C651" s="24"/>
       <c r="D651" s="22"/>
       <c r="E651" s="22"/>
       <c r="F651" s="22"/>
     </row>
-    <row r="652" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="652" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C652" s="25"/>
       <c r="D652" s="23"/>
       <c r="E652" s="23"/>
       <c r="F652" s="23"/>
     </row>
-    <row r="653" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="653" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C653" s="24"/>
       <c r="D653" s="22"/>
       <c r="E653" s="22"/>
       <c r="F653" s="22"/>
     </row>
-    <row r="654" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="654" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C654" s="25"/>
       <c r="D654" s="23"/>
       <c r="E654" s="23"/>
       <c r="F654" s="23"/>
     </row>
-    <row r="655" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="655" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C655" s="24"/>
       <c r="D655" s="22"/>
       <c r="E655" s="22"/>
       <c r="F655" s="22"/>
     </row>
-    <row r="656" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="656" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C656" s="25"/>
       <c r="D656" s="23"/>
       <c r="E656" s="23"/>
       <c r="F656" s="23"/>
     </row>
-    <row r="657" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C657" s="24"/>
       <c r="D657" s="22"/>
       <c r="E657" s="22"/>
       <c r="F657" s="22"/>
     </row>
-    <row r="658" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="658" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C658" s="25"/>
       <c r="D658" s="23"/>
       <c r="E658" s="23"/>
       <c r="F658" s="23"/>
     </row>
-    <row r="659" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="659" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C659" s="24"/>
       <c r="D659" s="22"/>
       <c r="E659" s="22"/>
       <c r="F659" s="22"/>
     </row>
-    <row r="660" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="660" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C660" s="25"/>
       <c r="D660" s="23"/>
       <c r="E660" s="23"/>
       <c r="F660" s="23"/>
     </row>
-    <row r="661" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="661" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C661" s="24"/>
       <c r="D661" s="22"/>
       <c r="E661" s="22"/>
       <c r="F661" s="22"/>
     </row>
-    <row r="662" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="662" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C662" s="25"/>
       <c r="D662" s="23"/>
       <c r="E662" s="23"/>
       <c r="F662" s="23"/>
     </row>
-    <row r="663" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="663" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C663" s="24"/>
       <c r="D663" s="22"/>
       <c r="E663" s="22"/>
       <c r="F663" s="22"/>
     </row>
-    <row r="664" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="664" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C664" s="25"/>
       <c r="D664" s="23"/>
       <c r="E664" s="23"/>
       <c r="F664" s="23"/>
     </row>
-    <row r="665" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="665" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C665" s="24"/>
       <c r="D665" s="22"/>
       <c r="E665" s="22"/>
       <c r="F665" s="22"/>
     </row>
-    <row r="666" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="666" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C666" s="25"/>
       <c r="D666" s="23"/>
       <c r="E666" s="23"/>
       <c r="F666" s="23"/>
     </row>
-    <row r="667" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="667" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C667" s="24"/>
       <c r="D667" s="22"/>
       <c r="E667" s="22"/>
       <c r="F667" s="22"/>
     </row>
-    <row r="668" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="668" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C668" s="25"/>
       <c r="D668" s="23"/>
       <c r="E668" s="23"/>
       <c r="F668" s="23"/>
     </row>
-    <row r="669" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="669" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C669" s="24"/>
       <c r="D669" s="22"/>
       <c r="E669" s="22"/>
       <c r="F669" s="22"/>
     </row>
-    <row r="670" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="670" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C670" s="25"/>
       <c r="D670" s="23"/>
       <c r="E670" s="23"/>
       <c r="F670" s="23"/>
     </row>
-    <row r="671" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="671" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C671" s="24"/>
       <c r="D671" s="22"/>
       <c r="E671" s="22"/>
       <c r="F671" s="22"/>
     </row>
-    <row r="672" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="672" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C672" s="25"/>
       <c r="D672" s="23"/>
       <c r="E672" s="23"/>
       <c r="F672" s="23"/>
     </row>
-    <row r="673" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="673" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C673" s="24"/>
       <c r="D673" s="22"/>
       <c r="E673" s="22"/>
       <c r="F673" s="22"/>
     </row>
-    <row r="674" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="674" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C674" s="25"/>
       <c r="D674" s="23"/>
       <c r="E674" s="23"/>
       <c r="F674" s="23"/>
     </row>
-    <row r="675" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="675" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C675" s="24"/>
       <c r="D675" s="22"/>
       <c r="E675" s="22"/>
       <c r="F675" s="22"/>
     </row>
-    <row r="676" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="676" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C676" s="25"/>
       <c r="D676" s="23"/>
       <c r="E676" s="23"/>
       <c r="F676" s="23"/>
     </row>
-    <row r="677" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="677" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C677" s="24"/>
       <c r="D677" s="22"/>
       <c r="E677" s="22"/>
       <c r="F677" s="22"/>
     </row>
-    <row r="678" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="678" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C678" s="25"/>
       <c r="D678" s="23"/>
       <c r="E678" s="23"/>
       <c r="F678" s="23"/>
     </row>
-    <row r="679" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="679" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C679" s="24"/>
       <c r="D679" s="22"/>
       <c r="E679" s="22"/>
       <c r="F679" s="22"/>
     </row>
-    <row r="680" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="680" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C680" s="25"/>
       <c r="D680" s="23"/>
       <c r="E680" s="23"/>
       <c r="F680" s="23"/>
     </row>
-    <row r="681" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="681" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C681" s="24"/>
       <c r="D681" s="22"/>
       <c r="E681" s="22"/>
       <c r="F681" s="22"/>
     </row>
-    <row r="682" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="682" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C682" s="25"/>
       <c r="D682" s="23"/>
       <c r="E682" s="23"/>
       <c r="F682" s="23"/>
     </row>
-    <row r="683" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="683" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C683" s="24"/>
       <c r="D683" s="22"/>
       <c r="E683" s="22"/>
       <c r="F683" s="22"/>
     </row>
-    <row r="684" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="684" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C684" s="25"/>
       <c r="D684" s="23"/>
       <c r="E684" s="23"/>
       <c r="F684" s="23"/>
     </row>
-    <row r="685" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="685" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C685" s="24"/>
       <c r="D685" s="22"/>
       <c r="E685" s="22"/>
       <c r="F685" s="22"/>
     </row>
-    <row r="686" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="686" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C686" s="25"/>
       <c r="D686" s="23"/>
       <c r="E686" s="23"/>
       <c r="F686" s="23"/>
     </row>
-    <row r="687" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="687" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C687" s="24"/>
       <c r="D687" s="22"/>
       <c r="E687" s="22"/>
       <c r="F687" s="22"/>
     </row>
-    <row r="688" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="688" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C688" s="25"/>
       <c r="D688" s="23"/>
       <c r="E688" s="23"/>
       <c r="F688" s="23"/>
     </row>
-    <row r="689" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="689" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C689" s="24"/>
       <c r="D689" s="22"/>
       <c r="E689" s="22"/>
       <c r="F689" s="22"/>
     </row>
-    <row r="690" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="690" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C690" s="25"/>
       <c r="D690" s="23"/>
       <c r="E690" s="23"/>
       <c r="F690" s="23"/>
     </row>
-    <row r="691" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="691" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C691" s="24"/>
       <c r="D691" s="22"/>
       <c r="E691" s="22"/>
       <c r="F691" s="22"/>
     </row>
-    <row r="692" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="692" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C692" s="25"/>
       <c r="D692" s="23"/>
       <c r="E692" s="23"/>
       <c r="F692" s="23"/>
     </row>
-    <row r="693" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="693" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C693" s="24"/>
       <c r="D693" s="22"/>
       <c r="E693" s="22"/>
       <c r="F693" s="22"/>
     </row>
-    <row r="694" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="694" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C694" s="25"/>
       <c r="D694" s="23"/>
       <c r="E694" s="23"/>
       <c r="F694" s="23"/>
     </row>
-    <row r="695" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="695" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C695" s="24"/>
       <c r="D695" s="22"/>
       <c r="E695" s="22"/>
       <c r="F695" s="22"/>
     </row>
-    <row r="696" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="696" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C696" s="25"/>
       <c r="D696" s="23"/>
       <c r="E696" s="23"/>
       <c r="F696" s="23"/>
     </row>
-    <row r="697" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="697" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C697" s="24"/>
       <c r="D697" s="22"/>
       <c r="E697" s="22"/>
       <c r="F697" s="22"/>
     </row>
-    <row r="698" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="698" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C698" s="25"/>
       <c r="D698" s="23"/>
       <c r="E698" s="23"/>
       <c r="F698" s="23"/>
     </row>
-    <row r="699" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="699" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C699" s="24"/>
       <c r="D699" s="22"/>
       <c r="E699" s="22"/>
       <c r="F699" s="22"/>
     </row>
-    <row r="700" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="700" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C700" s="25"/>
       <c r="D700" s="23"/>
       <c r="E700" s="23"/>
       <c r="F700" s="23"/>
     </row>
-    <row r="701" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="701" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C701" s="24"/>
       <c r="D701" s="22"/>
       <c r="E701" s="22"/>
       <c r="F701" s="22"/>
     </row>
-    <row r="702" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="702" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C702" s="25"/>
       <c r="D702" s="23"/>
       <c r="E702" s="23"/>
       <c r="F702" s="23"/>
     </row>
-    <row r="703" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="703" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C703" s="24"/>
       <c r="D703" s="22"/>
       <c r="E703" s="22"/>
       <c r="F703" s="22"/>
     </row>
-    <row r="704" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="704" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C704" s="25"/>
       <c r="D704" s="23"/>
       <c r="E704" s="23"/>
       <c r="F704" s="23"/>
     </row>
-    <row r="705" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="705" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C705" s="24"/>
       <c r="D705" s="22"/>
       <c r="E705" s="22"/>
       <c r="F705" s="22"/>
     </row>
-    <row r="706" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="706" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C706" s="25"/>
       <c r="D706" s="23"/>
       <c r="E706" s="23"/>
       <c r="F706" s="23"/>
     </row>
-    <row r="707" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="707" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C707" s="24"/>
       <c r="D707" s="22"/>
       <c r="E707" s="22"/>
       <c r="F707" s="22"/>
     </row>
-    <row r="708" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="708" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C708" s="25"/>
       <c r="D708" s="23"/>
       <c r="E708" s="23"/>
       <c r="F708" s="23"/>
     </row>
-    <row r="709" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="709" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C709" s="24"/>
       <c r="D709" s="22"/>
       <c r="E709" s="22"/>
       <c r="F709" s="22"/>
     </row>
-    <row r="710" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="710" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C710" s="25"/>
       <c r="D710" s="23"/>
       <c r="E710" s="23"/>
       <c r="F710" s="23"/>
     </row>
-    <row r="711" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="711" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C711" s="24"/>
       <c r="D711" s="22"/>
       <c r="E711" s="22"/>
       <c r="F711" s="22"/>
     </row>
-    <row r="712" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="712" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C712" s="25"/>
       <c r="D712" s="23"/>
       <c r="E712" s="23"/>
       <c r="F712" s="23"/>
     </row>
-    <row r="713" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="713" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C713" s="24"/>
       <c r="D713" s="22"/>
       <c r="E713" s="22"/>
       <c r="F713" s="22"/>
     </row>
-    <row r="714" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="714" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C714" s="25"/>
       <c r="D714" s="23"/>
       <c r="E714" s="23"/>
       <c r="F714" s="23"/>
     </row>
-    <row r="715" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="715" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C715" s="24"/>
       <c r="D715" s="22"/>
       <c r="E715" s="22"/>
       <c r="F715" s="22"/>
     </row>
-    <row r="716" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="716" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C716" s="25"/>
       <c r="D716" s="23"/>
       <c r="E716" s="23"/>
       <c r="F716" s="23"/>
     </row>
-    <row r="717" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="717" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C717" s="24"/>
       <c r="D717" s="22"/>
       <c r="E717" s="22"/>
       <c r="F717" s="22"/>
     </row>
-    <row r="718" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="718" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C718" s="25"/>
       <c r="D718" s="23"/>
       <c r="E718" s="23"/>
       <c r="F718" s="23"/>
     </row>
-    <row r="719" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="719" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C719" s="24"/>
       <c r="D719" s="22"/>
       <c r="E719" s="22"/>
       <c r="F719" s="22"/>
     </row>
-    <row r="720" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="720" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C720" s="25"/>
       <c r="D720" s="23"/>
       <c r="E720" s="23"/>
       <c r="F720" s="23"/>
     </row>
-    <row r="721" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="721" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C721" s="24"/>
       <c r="D721" s="22"/>
       <c r="E721" s="22"/>
       <c r="F721" s="22"/>
     </row>
-    <row r="722" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="722" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C722" s="25"/>
       <c r="D722" s="23"/>
       <c r="E722" s="23"/>
       <c r="F722" s="23"/>
     </row>
-    <row r="723" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="723" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C723" s="24"/>
       <c r="D723" s="22"/>
       <c r="E723" s="22"/>
       <c r="F723" s="22"/>
     </row>
-    <row r="724" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="724" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C724" s="25"/>
       <c r="D724" s="23"/>
       <c r="E724" s="23"/>
       <c r="F724" s="23"/>
     </row>
-    <row r="725" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="725" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C725" s="24"/>
       <c r="D725" s="22"/>
       <c r="E725" s="22"/>
       <c r="F725" s="22"/>
     </row>
-    <row r="726" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="726" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C726" s="25"/>
       <c r="D726" s="23"/>
       <c r="E726" s="23"/>
       <c r="F726" s="23"/>
     </row>
-    <row r="727" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="727" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C727" s="24"/>
       <c r="D727" s="22"/>
       <c r="E727" s="22"/>
       <c r="F727" s="22"/>
     </row>
-    <row r="728" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="728" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C728" s="25"/>
       <c r="D728" s="23"/>
       <c r="E728" s="23"/>
       <c r="F728" s="23"/>
     </row>
-    <row r="729" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="729" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C729" s="24"/>
       <c r="D729" s="22"/>
       <c r="E729" s="22"/>
       <c r="F729" s="22"/>
     </row>
-    <row r="730" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="730" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C730" s="25"/>
       <c r="D730" s="23"/>
       <c r="E730" s="23"/>
       <c r="F730" s="23"/>
     </row>
-    <row r="731" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="731" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C731" s="24"/>
       <c r="D731" s="22"/>
       <c r="E731" s="22"/>
       <c r="F731" s="22"/>
     </row>
-    <row r="732" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="732" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C732" s="25"/>
       <c r="D732" s="23"/>
       <c r="E732" s="23"/>
       <c r="F732" s="23"/>
     </row>
-    <row r="733" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="733" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C733" s="24"/>
       <c r="D733" s="22"/>
       <c r="E733" s="22"/>
       <c r="F733" s="22"/>
     </row>
-    <row r="734" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="734" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C734" s="25"/>
       <c r="D734" s="23"/>
       <c r="E734" s="23"/>
       <c r="F734" s="23"/>
     </row>
-    <row r="735" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="735" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C735" s="24"/>
       <c r="D735" s="22"/>
       <c r="E735" s="22"/>
       <c r="F735" s="22"/>
     </row>
-    <row r="736" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="736" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C736" s="25"/>
       <c r="D736" s="23"/>
       <c r="E736" s="23"/>
       <c r="F736" s="23"/>
     </row>
-    <row r="737" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="737" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C737" s="24"/>
       <c r="D737" s="22"/>
       <c r="E737" s="22"/>
       <c r="F737" s="22"/>
     </row>
-    <row r="738" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="738" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C738" s="25"/>
       <c r="D738" s="23"/>
       <c r="E738" s="23"/>
       <c r="F738" s="23"/>
     </row>
-    <row r="739" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="739" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C739" s="24"/>
       <c r="D739" s="22"/>
       <c r="E739" s="22"/>
       <c r="F739" s="22"/>
     </row>
-    <row r="740" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="740" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C740" s="25"/>
       <c r="D740" s="23"/>
       <c r="E740" s="23"/>
       <c r="F740" s="23"/>
     </row>
-    <row r="741" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="741" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C741" s="24"/>
       <c r="D741" s="22"/>
       <c r="E741" s="22"/>
       <c r="F741" s="22"/>
     </row>
-    <row r="742" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="742" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C742" s="25"/>
       <c r="D742" s="23"/>
       <c r="E742" s="23"/>
       <c r="F742" s="23"/>
     </row>
-    <row r="743" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="743" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C743" s="24"/>
       <c r="D743" s="22"/>
       <c r="E743" s="22"/>
       <c r="F743" s="22"/>
     </row>
-    <row r="744" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="744" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C744" s="25"/>
       <c r="D744" s="23"/>
       <c r="E744" s="23"/>
       <c r="F744" s="23"/>
     </row>
-    <row r="745" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="745" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C745" s="24"/>
       <c r="D745" s="22"/>
       <c r="E745" s="22"/>
       <c r="F745" s="22"/>
     </row>
-    <row r="746" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="746" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C746" s="25"/>
       <c r="D746" s="23"/>
       <c r="E746" s="23"/>
       <c r="F746" s="23"/>
     </row>
-    <row r="747" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="747" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C747" s="24"/>
       <c r="D747" s="22"/>
       <c r="E747" s="22"/>
       <c r="F747" s="22"/>
     </row>
-    <row r="748" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="748" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C748" s="25"/>
       <c r="D748" s="23"/>
       <c r="E748" s="23"/>
       <c r="F748" s="23"/>
     </row>
-    <row r="749" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="749" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C749" s="24"/>
       <c r="D749" s="22"/>
       <c r="E749" s="22"/>
       <c r="F749" s="22"/>
     </row>
-    <row r="750" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="750" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C750" s="25"/>
       <c r="D750" s="23"/>
       <c r="E750" s="23"/>
       <c r="F750" s="23"/>
     </row>
-    <row r="751" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="751" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C751" s="24"/>
       <c r="D751" s="22"/>
       <c r="E751" s="22"/>
       <c r="F751" s="22"/>
     </row>
-    <row r="752" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="752" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C752" s="25"/>
       <c r="D752" s="23"/>
       <c r="E752" s="23"/>
       <c r="F752" s="23"/>
     </row>
-    <row r="753" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="753" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C753" s="24"/>
       <c r="D753" s="22"/>
       <c r="E753" s="22"/>
       <c r="F753" s="22"/>
     </row>
-    <row r="754" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="754" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C754" s="25"/>
       <c r="D754" s="23"/>
       <c r="E754" s="23"/>
       <c r="F754" s="23"/>
     </row>
-    <row r="755" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="755" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C755" s="24"/>
       <c r="D755" s="22"/>
       <c r="E755" s="22"/>
       <c r="F755" s="22"/>
     </row>
-    <row r="756" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="756" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C756" s="25"/>
       <c r="D756" s="23"/>
       <c r="E756" s="23"/>
       <c r="F756" s="23"/>
     </row>
-    <row r="757" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="757" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C757" s="24"/>
       <c r="D757" s="22"/>
       <c r="E757" s="22"/>
       <c r="F757" s="22"/>
     </row>
-    <row r="758" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="758" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C758" s="25"/>
       <c r="D758" s="23"/>
       <c r="E758" s="23"/>
       <c r="F758" s="23"/>
     </row>
-    <row r="759" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="759" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C759" s="24"/>
       <c r="D759" s="22"/>
       <c r="E759" s="22"/>
       <c r="F759" s="22"/>
     </row>
-    <row r="760" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="760" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C760" s="25"/>
       <c r="D760" s="23"/>
       <c r="E760" s="23"/>
       <c r="F760" s="23"/>
     </row>
-    <row r="761" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="761" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C761" s="24"/>
       <c r="D761" s="22"/>
       <c r="E761" s="22"/>
       <c r="F761" s="22"/>
     </row>
-    <row r="762" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="762" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C762" s="25"/>
       <c r="D762" s="23"/>
       <c r="E762" s="23"/>
       <c r="F762" s="23"/>
     </row>
-    <row r="763" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="763" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C763" s="24"/>
       <c r="D763" s="22"/>
       <c r="E763" s="22"/>
       <c r="F763" s="22"/>
     </row>
-    <row r="764" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="764" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C764" s="25"/>
       <c r="D764" s="23"/>
       <c r="E764" s="23"/>
       <c r="F764" s="23"/>
     </row>
-    <row r="765" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="765" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C765" s="24"/>
       <c r="D765" s="22"/>
       <c r="E765" s="22"/>
       <c r="F765" s="22"/>
     </row>
-    <row r="766" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="766" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C766" s="25"/>
       <c r="D766" s="23"/>
       <c r="E766" s="23"/>
       <c r="F766" s="23"/>
     </row>
-    <row r="767" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="767" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C767" s="24"/>
       <c r="D767" s="22"/>
       <c r="E767" s="22"/>
       <c r="F767" s="22"/>
     </row>
-    <row r="768" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="768" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C768" s="25"/>
       <c r="D768" s="23"/>
       <c r="E768" s="23"/>
       <c r="F768" s="23"/>
     </row>
-    <row r="769" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="769" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C769" s="24"/>
       <c r="D769" s="22"/>
       <c r="E769" s="22"/>
       <c r="F769" s="22"/>
     </row>
-    <row r="770" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="770" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C770" s="25"/>
       <c r="D770" s="23"/>
       <c r="E770" s="23"/>
       <c r="F770" s="23"/>
     </row>
-    <row r="771" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="771" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C771" s="24"/>
       <c r="D771" s="22"/>
       <c r="E771" s="22"/>
       <c r="F771" s="22"/>
     </row>
-    <row r="772" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="772" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C772" s="25"/>
       <c r="D772" s="23"/>
       <c r="E772" s="23"/>
       <c r="F772" s="23"/>
     </row>
-    <row r="773" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="773" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C773" s="24"/>
       <c r="D773" s="22"/>
       <c r="E773" s="22"/>
       <c r="F773" s="22"/>
     </row>
-    <row r="774" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="774" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C774" s="25"/>
       <c r="D774" s="23"/>
       <c r="E774" s="23"/>
       <c r="F774" s="23"/>
     </row>
-    <row r="775" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="775" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C775" s="24"/>
       <c r="D775" s="22"/>
       <c r="E775" s="22"/>
       <c r="F775" s="22"/>
     </row>
-    <row r="776" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="776" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C776" s="25"/>
       <c r="D776" s="23"/>
       <c r="E776" s="23"/>
       <c r="F776" s="23"/>
     </row>
-    <row r="777" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="777" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C777" s="24"/>
       <c r="D777" s="22"/>
       <c r="E777" s="22"/>
       <c r="F777" s="22"/>
     </row>
-    <row r="778" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="778" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C778" s="25"/>
       <c r="D778" s="23"/>
       <c r="E778" s="23"/>
       <c r="F778" s="23"/>
     </row>
-    <row r="779" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="779" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C779" s="24"/>
       <c r="D779" s="22"/>
       <c r="E779" s="22"/>
       <c r="F779" s="22"/>
     </row>
-    <row r="780" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="780" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C780" s="25"/>
       <c r="D780" s="23"/>
       <c r="E780" s="23"/>
       <c r="F780" s="23"/>
     </row>
-    <row r="781" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="781" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C781" s="24"/>
       <c r="D781" s="22"/>
       <c r="E781" s="22"/>
       <c r="F781" s="22"/>
     </row>
-    <row r="782" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="782" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C782" s="25"/>
       <c r="D782" s="23"/>
       <c r="E782" s="23"/>
       <c r="F782" s="23"/>
     </row>
-    <row r="783" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="783" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C783" s="24"/>
       <c r="D783" s="22"/>
       <c r="E783" s="22"/>
       <c r="F783" s="22"/>
     </row>
-    <row r="784" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="784" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C784" s="25"/>
       <c r="D784" s="23"/>
       <c r="E784" s="23"/>
       <c r="F784" s="23"/>
     </row>
-    <row r="785" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="785" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C785" s="24"/>
       <c r="D785" s="22"/>
       <c r="E785" s="22"/>
       <c r="F785" s="22"/>
     </row>
-    <row r="786" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="786" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C786" s="25"/>
       <c r="D786" s="23"/>
       <c r="E786" s="23"/>
       <c r="F786" s="23"/>
     </row>
-    <row r="787" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="787" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C787" s="24"/>
       <c r="D787" s="22"/>
       <c r="E787" s="22"/>
       <c r="F787" s="22"/>
     </row>
-    <row r="788" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="788" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C788" s="25"/>
       <c r="D788" s="23"/>
       <c r="E788" s="23"/>
       <c r="F788" s="23"/>
     </row>
-    <row r="789" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="789" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C789" s="24"/>
       <c r="D789" s="22"/>
       <c r="E789" s="22"/>
       <c r="F789" s="22"/>
     </row>
-    <row r="790" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="790" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C790" s="25"/>
       <c r="D790" s="23"/>
       <c r="E790" s="23"/>
       <c r="F790" s="23"/>
     </row>
-    <row r="791" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="791" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C791" s="24"/>
       <c r="D791" s="22"/>
       <c r="E791" s="22"/>
       <c r="F791" s="22"/>
     </row>
-    <row r="792" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="792" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C792" s="25"/>
       <c r="D792" s="23"/>
       <c r="E792" s="23"/>
       <c r="F792" s="23"/>
     </row>
-    <row r="793" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="793" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C793" s="24"/>
       <c r="D793" s="22"/>
       <c r="E793" s="22"/>
       <c r="F793" s="22"/>
     </row>
-    <row r="794" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="794" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C794" s="25"/>
       <c r="D794" s="23"/>
       <c r="E794" s="23"/>
       <c r="F794" s="23"/>
     </row>
-    <row r="795" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="795" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C795" s="24"/>
       <c r="D795" s="22"/>
       <c r="E795" s="22"/>
       <c r="F795" s="22"/>
     </row>
-    <row r="796" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="796" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C796" s="25"/>
       <c r="D796" s="23"/>
       <c r="E796" s="23"/>
       <c r="F796" s="23"/>
     </row>
-    <row r="797" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="797" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C797" s="24"/>
       <c r="D797" s="22"/>
       <c r="E797" s="22"/>
       <c r="F797" s="22"/>
     </row>
-    <row r="798" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="798" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C798" s="25"/>
       <c r="D798" s="23"/>
       <c r="E798" s="23"/>
       <c r="F798" s="23"/>
     </row>
-    <row r="799" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="799" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C799" s="24"/>
       <c r="D799" s="22"/>
       <c r="E799" s="22"/>
       <c r="F799" s="22"/>
     </row>
-    <row r="800" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="800" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C800" s="25"/>
       <c r="D800" s="23"/>
       <c r="E800" s="23"/>
       <c r="F800" s="23"/>
     </row>
-    <row r="801" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="801" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C801" s="24"/>
       <c r="D801" s="22"/>
       <c r="E801" s="22"/>
       <c r="F801" s="22"/>
     </row>
-    <row r="802" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="802" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C802" s="25"/>
       <c r="D802" s="23"/>
       <c r="E802" s="23"/>
       <c r="F802" s="23"/>
     </row>
-    <row r="803" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="803" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C803" s="24"/>
       <c r="D803" s="22"/>
       <c r="E803" s="22"/>
       <c r="F803" s="22"/>
     </row>
-    <row r="804" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="804" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C804" s="25"/>
       <c r="D804" s="23"/>
       <c r="E804" s="23"/>
       <c r="F804" s="23"/>
     </row>
-    <row r="805" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="805" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C805" s="24"/>
       <c r="D805" s="22"/>
       <c r="E805" s="22"/>
       <c r="F805" s="22"/>
     </row>
-    <row r="806" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="806" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C806" s="25"/>
       <c r="D806" s="23"/>
       <c r="E806" s="23"/>
       <c r="F806" s="23"/>
     </row>
-    <row r="807" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="807" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C807" s="24"/>
       <c r="D807" s="22"/>
       <c r="E807" s="22"/>
       <c r="F807" s="22"/>
     </row>
-    <row r="808" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="808" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C808" s="25"/>
       <c r="D808" s="23"/>
       <c r="E808" s="23"/>
       <c r="F808" s="23"/>
     </row>
-    <row r="809" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="809" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C809" s="24"/>
       <c r="D809" s="22"/>
       <c r="E809" s="22"/>
       <c r="F809" s="22"/>
     </row>
-    <row r="810" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="810" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C810" s="25"/>
       <c r="D810" s="23"/>
       <c r="E810" s="23"/>
       <c r="F810" s="23"/>
     </row>
-    <row r="811" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="811" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C811" s="24"/>
       <c r="D811" s="22"/>
       <c r="E811" s="22"/>
       <c r="F811" s="22"/>
     </row>
-    <row r="812" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="812" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C812" s="25"/>
       <c r="D812" s="23"/>
       <c r="E812" s="23"/>
       <c r="F812" s="23"/>
     </row>
-    <row r="813" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="813" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C813" s="24"/>
       <c r="D813" s="22"/>
       <c r="E813" s="22"/>
       <c r="F813" s="22"/>
     </row>
-    <row r="814" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="814" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C814" s="25"/>
       <c r="D814" s="23"/>
       <c r="E814" s="23"/>
       <c r="F814" s="23"/>
     </row>
-    <row r="815" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="815" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C815" s="24"/>
       <c r="D815" s="22"/>
       <c r="E815" s="22"/>
       <c r="F815" s="22"/>
     </row>
-    <row r="816" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="816" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C816" s="25"/>
       <c r="D816" s="23"/>
       <c r="E816" s="23"/>
       <c r="F816" s="23"/>
     </row>
-    <row r="817" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="817" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C817" s="24"/>
       <c r="D817" s="22"/>
       <c r="E817" s="22"/>
       <c r="F817" s="22"/>
     </row>
-    <row r="818" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="818" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C818" s="25"/>
       <c r="D818" s="23"/>
       <c r="E818" s="23"/>
       <c r="F818" s="23"/>
     </row>
-    <row r="819" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="819" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C819" s="24"/>
       <c r="D819" s="22"/>
       <c r="E819" s="22"/>
       <c r="F819" s="22"/>
     </row>
-    <row r="820" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="820" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C820" s="25"/>
       <c r="D820" s="23"/>
       <c r="E820" s="23"/>
       <c r="F820" s="23"/>
     </row>
-    <row r="821" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="821" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C821" s="24"/>
       <c r="D821" s="22"/>
       <c r="E821" s="22"/>
       <c r="F821" s="22"/>
     </row>
-    <row r="822" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="822" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C822" s="25"/>
       <c r="D822" s="23"/>
       <c r="E822" s="23"/>
       <c r="F822" s="23"/>
     </row>
-    <row r="823" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="823" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C823" s="24"/>
       <c r="D823" s="22"/>
       <c r="E823" s="22"/>
       <c r="F823" s="22"/>
     </row>
-    <row r="824" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="824" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C824" s="25"/>
       <c r="D824" s="23"/>
       <c r="E824" s="23"/>
       <c r="F824" s="23"/>
     </row>
-    <row r="825" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="825" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C825" s="24"/>
       <c r="D825" s="22"/>
       <c r="E825" s="22"/>
       <c r="F825" s="22"/>
     </row>
-    <row r="826" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="826" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C826" s="25"/>
       <c r="D826" s="23"/>
       <c r="E826" s="23"/>
       <c r="F826" s="23"/>
     </row>
-    <row r="827" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="827" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C827" s="24"/>
       <c r="D827" s="22"/>
       <c r="E827" s="22"/>
       <c r="F827" s="22"/>
     </row>
-    <row r="828" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="828" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C828" s="25"/>
       <c r="D828" s="23"/>
       <c r="E828" s="23"/>
       <c r="F828" s="23"/>
     </row>
-    <row r="829" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="829" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C829" s="24"/>
       <c r="D829" s="22"/>
       <c r="E829" s="22"/>
       <c r="F829" s="22"/>
     </row>
-    <row r="830" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="830" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C830" s="25"/>
       <c r="D830" s="23"/>
       <c r="E830" s="23"/>
       <c r="F830" s="23"/>
     </row>
-    <row r="831" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="831" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C831" s="24"/>
       <c r="D831" s="22"/>
       <c r="E831" s="22"/>
       <c r="F831" s="22"/>
     </row>
-    <row r="832" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="832" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C832" s="25"/>
       <c r="D832" s="23"/>
       <c r="E832" s="23"/>
       <c r="F832" s="23"/>
     </row>
-    <row r="833" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="833" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C833" s="24"/>
       <c r="D833" s="22"/>
       <c r="E833" s="22"/>
       <c r="F833" s="22"/>
     </row>
-    <row r="834" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="834" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C834" s="25"/>
       <c r="D834" s="23"/>
       <c r="E834" s="23"/>
       <c r="F834" s="23"/>
     </row>
-    <row r="835" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="835" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C835" s="24"/>
       <c r="D835" s="22"/>
       <c r="E835" s="22"/>
       <c r="F835" s="22"/>
     </row>
-    <row r="836" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="836" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C836" s="25"/>
       <c r="D836" s="23"/>
       <c r="E836" s="23"/>
       <c r="F836" s="23"/>
     </row>
-    <row r="837" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="837" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C837" s="24"/>
       <c r="D837" s="22"/>
       <c r="E837" s="22"/>
       <c r="F837" s="22"/>
     </row>
-    <row r="838" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="838" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C838" s="25"/>
       <c r="D838" s="23"/>
       <c r="E838" s="23"/>
       <c r="F838" s="23"/>
     </row>
-    <row r="839" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="839" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C839" s="24"/>
       <c r="D839" s="22"/>
       <c r="E839" s="22"/>
       <c r="F839" s="22"/>
     </row>
-    <row r="840" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="840" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C840" s="25"/>
       <c r="D840" s="23"/>
       <c r="E840" s="23"/>
       <c r="F840" s="23"/>
     </row>
-    <row r="841" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="841" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C841" s="24"/>
       <c r="D841" s="22"/>
       <c r="E841" s="22"/>
       <c r="F841" s="22"/>
     </row>
-    <row r="842" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="842" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C842" s="25"/>
       <c r="D842" s="23"/>
       <c r="E842" s="23"/>
       <c r="F842" s="23"/>
     </row>
-    <row r="843" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="843" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C843" s="24"/>
       <c r="D843" s="22"/>
       <c r="E843" s="22"/>
       <c r="F843" s="22"/>
     </row>
-    <row r="844" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="844" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C844" s="25"/>
       <c r="D844" s="23"/>
       <c r="E844" s="23"/>
       <c r="F844" s="23"/>
     </row>
-    <row r="845" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="845" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C845" s="24"/>
       <c r="D845" s="22"/>
       <c r="E845" s="22"/>
       <c r="F845" s="22"/>
     </row>
-    <row r="846" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="846" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C846" s="25"/>
       <c r="D846" s="23"/>
       <c r="E846" s="23"/>
       <c r="F846" s="23"/>
     </row>
-    <row r="847" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="847" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C847" s="24"/>
       <c r="D847" s="22"/>
       <c r="E847" s="22"/>
       <c r="F847" s="22"/>
     </row>
-    <row r="848" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="848" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C848" s="25"/>
       <c r="D848" s="23"/>
       <c r="E848" s="23"/>
       <c r="F848" s="23"/>
     </row>
-    <row r="849" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="849" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C849" s="24"/>
       <c r="D849" s="22"/>
       <c r="E849" s="22"/>
       <c r="F849" s="22"/>
     </row>
-    <row r="850" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="850" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C850" s="25"/>
       <c r="D850" s="23"/>
       <c r="E850" s="23"/>
       <c r="F850" s="23"/>
     </row>
-    <row r="851" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="851" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C851" s="24"/>
       <c r="D851" s="22"/>
       <c r="E851" s="22"/>
       <c r="F851" s="22"/>
     </row>
-    <row r="852" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="852" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C852" s="25"/>
       <c r="D852" s="23"/>
       <c r="E852" s="23"/>
       <c r="F852" s="23"/>
     </row>
-    <row r="853" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="853" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C853" s="24"/>
       <c r="D853" s="22"/>
       <c r="E853" s="22"/>
       <c r="F853" s="22"/>
     </row>
-    <row r="854" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="854" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C854" s="25"/>
       <c r="D854" s="23"/>
       <c r="E854" s="23"/>
       <c r="F854" s="23"/>
     </row>
-    <row r="855" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="855" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C855" s="24"/>
       <c r="D855" s="22"/>
       <c r="E855" s="22"/>
       <c r="F855" s="22"/>
     </row>
-    <row r="856" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="856" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C856" s="25"/>
       <c r="D856" s="23"/>
       <c r="E856" s="23"/>
       <c r="F856" s="23"/>
     </row>
-    <row r="857" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="857" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C857" s="24"/>
       <c r="D857" s="22"/>
       <c r="E857" s="22"/>
       <c r="F857" s="22"/>
     </row>
-    <row r="858" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="858" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C858" s="25"/>
       <c r="D858" s="23"/>
       <c r="E858" s="23"/>
       <c r="F858" s="23"/>
     </row>
-    <row r="859" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="859" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C859" s="24"/>
       <c r="D859" s="22"/>
       <c r="E859" s="22"/>
       <c r="F859" s="22"/>
     </row>
-    <row r="860" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="860" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C860" s="25"/>
       <c r="D860" s="23"/>
       <c r="E860" s="23"/>
       <c r="F860" s="23"/>
     </row>
-    <row r="861" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="861" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C861" s="24"/>
       <c r="D861" s="22"/>
       <c r="E861" s="22"/>
       <c r="F861" s="22"/>
     </row>
-    <row r="862" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="862" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C862" s="25"/>
       <c r="D862" s="23"/>
       <c r="E862" s="23"/>
       <c r="F862" s="23"/>
     </row>
-    <row r="863" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="863" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C863" s="24"/>
       <c r="D863" s="22"/>
       <c r="E863" s="22"/>
       <c r="F863" s="22"/>
     </row>
-    <row r="864" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="864" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C864" s="25"/>
       <c r="D864" s="23"/>
       <c r="E864" s="23"/>
       <c r="F864" s="23"/>
     </row>
-    <row r="865" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="865" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C865" s="24"/>
       <c r="D865" s="22"/>
       <c r="E865" s="22"/>
       <c r="F865" s="22"/>
     </row>
-    <row r="866" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="866" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C866" s="25"/>
       <c r="D866" s="23"/>
       <c r="E866" s="23"/>
       <c r="F866" s="23"/>
     </row>
-    <row r="867" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="867" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C867" s="24"/>
       <c r="D867" s="22"/>
       <c r="E867" s="22"/>
       <c r="F867" s="22"/>
     </row>
-    <row r="868" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="868" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C868" s="25"/>
       <c r="D868" s="23"/>
       <c r="E868" s="23"/>
       <c r="F868" s="23"/>
     </row>
-    <row r="869" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="869" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C869" s="24"/>
       <c r="D869" s="22"/>
       <c r="E869" s="22"/>
       <c r="F869" s="22"/>
     </row>
-    <row r="870" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="870" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C870" s="25"/>
       <c r="D870" s="23"/>
       <c r="E870" s="23"/>
       <c r="F870" s="23"/>
     </row>
-    <row r="871" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="871" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C871" s="24"/>
       <c r="D871" s="22"/>
       <c r="E871" s="22"/>
       <c r="F871" s="22"/>
     </row>
-    <row r="872" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="872" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C872" s="25"/>
       <c r="D872" s="23"/>
       <c r="E872" s="23"/>
       <c r="F872" s="23"/>
     </row>
-    <row r="873" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="873" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C873" s="24"/>
       <c r="D873" s="22"/>
       <c r="E873" s="22"/>
       <c r="F873" s="22"/>
     </row>
-    <row r="874" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="874" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C874" s="25"/>
       <c r="D874" s="23"/>
       <c r="E874" s="23"/>
       <c r="F874" s="23"/>
     </row>
-    <row r="875" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="875" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C875" s="24"/>
       <c r="D875" s="22"/>
       <c r="E875" s="22"/>
       <c r="F875" s="22"/>
     </row>
-    <row r="876" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="876" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C876" s="25"/>
       <c r="D876" s="23"/>
       <c r="E876" s="23"/>
       <c r="F876" s="23"/>
     </row>
-    <row r="877" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="877" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C877" s="24"/>
       <c r="D877" s="22"/>
       <c r="E877" s="22"/>
       <c r="F877" s="22"/>
     </row>
-    <row r="878" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="878" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C878" s="25"/>
       <c r="D878" s="23"/>
       <c r="E878" s="23"/>
       <c r="F878" s="23"/>
     </row>
-    <row r="879" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="879" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C879" s="24"/>
       <c r="D879" s="22"/>
       <c r="E879" s="22"/>
       <c r="F879" s="22"/>
     </row>
-    <row r="880" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="880" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C880" s="25"/>
       <c r="D880" s="23"/>
       <c r="E880" s="23"/>
       <c r="F880" s="23"/>
     </row>
-    <row r="881" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="881" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C881" s="24"/>
       <c r="D881" s="22"/>
       <c r="E881" s="22"/>
       <c r="F881" s="22"/>
     </row>
-    <row r="882" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="882" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C882" s="25"/>
       <c r="D882" s="23"/>
       <c r="E882" s="23"/>
       <c r="F882" s="23"/>
     </row>
-    <row r="883" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="883" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C883" s="24"/>
       <c r="D883" s="22"/>
       <c r="E883" s="22"/>
       <c r="F883" s="22"/>
     </row>
-    <row r="884" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="884" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C884" s="25"/>
       <c r="D884" s="23"/>
       <c r="E884" s="23"/>
       <c r="F884" s="23"/>
     </row>
-    <row r="885" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="885" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C885" s="24"/>
       <c r="D885" s="22"/>
       <c r="E885" s="22"/>
       <c r="F885" s="22"/>
     </row>
-    <row r="886" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="886" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C886" s="25"/>
       <c r="D886" s="23"/>
       <c r="E886" s="23"/>
       <c r="F886" s="23"/>
     </row>
-    <row r="887" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="887" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C887" s="24"/>
       <c r="D887" s="22"/>
       <c r="E887" s="22"/>
       <c r="F887" s="22"/>
     </row>
-    <row r="888" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="888" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C888" s="25"/>
       <c r="D888" s="23"/>
       <c r="E888" s="23"/>
       <c r="F888" s="23"/>
     </row>
-    <row r="889" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="889" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C889" s="24"/>
       <c r="D889" s="22"/>
       <c r="E889" s="22"/>
       <c r="F889" s="22"/>
     </row>
-    <row r="890" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="890" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C890" s="25"/>
       <c r="D890" s="23"/>
       <c r="E890" s="23"/>
       <c r="F890" s="23"/>
     </row>
-    <row r="891" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="891" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C891" s="24"/>
       <c r="D891" s="22"/>
       <c r="E891" s="22"/>
       <c r="F891" s="22"/>
     </row>
-    <row r="892" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="892" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C892" s="25"/>
       <c r="D892" s="23"/>
       <c r="E892" s="23"/>
       <c r="F892" s="23"/>
     </row>
-    <row r="893" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="893" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C893" s="24"/>
       <c r="D893" s="22"/>
       <c r="E893" s="22"/>
       <c r="F893" s="22"/>
     </row>
-    <row r="894" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="894" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C894" s="25"/>
       <c r="D894" s="23"/>
       <c r="E894" s="23"/>
       <c r="F894" s="23"/>
     </row>
-    <row r="895" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="895" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C895" s="24"/>
       <c r="D895" s="22"/>
       <c r="E895" s="22"/>
       <c r="F895" s="22"/>
     </row>
-    <row r="896" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="896" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C896" s="25"/>
       <c r="D896" s="23"/>
       <c r="E896" s="23"/>
       <c r="F896" s="23"/>
     </row>
-    <row r="897" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="897" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C897" s="24"/>
       <c r="D897" s="22"/>
       <c r="E897" s="22"/>
       <c r="F897" s="22"/>
     </row>
-    <row r="898" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="898" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C898" s="25"/>
       <c r="D898" s="23"/>
       <c r="E898" s="23"/>
       <c r="F898" s="23"/>
     </row>
-    <row r="899" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="899" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C899" s="24"/>
       <c r="D899" s="22"/>
       <c r="E899" s="22"/>
       <c r="F899" s="22"/>
     </row>
-    <row r="900" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="900" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C900" s="25"/>
       <c r="D900" s="23"/>
       <c r="E900" s="23"/>
       <c r="F900" s="23"/>
     </row>
-    <row r="901" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="901" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C901" s="24"/>
       <c r="D901" s="22"/>
       <c r="E901" s="22"/>
       <c r="F901" s="22"/>
     </row>
-    <row r="902" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="902" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C902" s="25"/>
       <c r="D902" s="23"/>
       <c r="E902" s="23"/>
       <c r="F902" s="23"/>
     </row>
-    <row r="903" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="903" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C903" s="24"/>
       <c r="D903" s="22"/>
       <c r="E903" s="22"/>
       <c r="F903" s="22"/>
     </row>
-    <row r="904" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="904" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C904" s="25"/>
       <c r="D904" s="23"/>
       <c r="E904" s="23"/>
       <c r="F904" s="23"/>
     </row>
-    <row r="905" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="905" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C905" s="24"/>
       <c r="D905" s="22"/>
       <c r="E905" s="22"/>
       <c r="F905" s="22"/>
     </row>
-    <row r="906" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="906" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C906" s="25"/>
       <c r="D906" s="23"/>
       <c r="E906" s="23"/>
       <c r="F906" s="23"/>
     </row>
-    <row r="907" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="907" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C907" s="24"/>
       <c r="D907" s="22"/>
       <c r="E907" s="22"/>
       <c r="F907" s="22"/>
     </row>
-    <row r="908" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="908" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C908" s="25"/>
       <c r="D908" s="23"/>
       <c r="E908" s="23"/>
       <c r="F908" s="23"/>
     </row>
-    <row r="909" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="909" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C909" s="24"/>
       <c r="D909" s="22"/>
       <c r="E909" s="22"/>
       <c r="F909" s="22"/>
     </row>
-    <row r="910" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="910" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C910" s="25"/>
       <c r="D910" s="23"/>
       <c r="E910" s="23"/>
       <c r="F910" s="23"/>
     </row>
-    <row r="911" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="911" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C911" s="24"/>
       <c r="D911" s="22"/>
       <c r="E911" s="22"/>
       <c r="F911" s="22"/>
     </row>
-    <row r="912" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="912" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C912" s="25"/>
       <c r="D912" s="23"/>
       <c r="E912" s="23"/>
       <c r="F912" s="23"/>
     </row>
-    <row r="913" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="913" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C913" s="24"/>
       <c r="D913" s="22"/>
       <c r="E913" s="22"/>
       <c r="F913" s="22"/>
     </row>
-    <row r="914" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="914" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C914" s="25"/>
       <c r="D914" s="23"/>
       <c r="E914" s="23"/>
       <c r="F914" s="23"/>
     </row>
-    <row r="915" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="915" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C915" s="24"/>
       <c r="D915" s="22"/>
       <c r="E915" s="22"/>
       <c r="F915" s="22"/>
     </row>
-    <row r="916" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="916" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C916" s="25"/>
       <c r="D916" s="23"/>
       <c r="E916" s="23"/>
       <c r="F916" s="23"/>
     </row>
-    <row r="917" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="917" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C917" s="24"/>
       <c r="D917" s="22"/>
       <c r="E917" s="22"/>
       <c r="F917" s="22"/>
     </row>
-    <row r="918" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="918" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C918" s="25"/>
       <c r="D918" s="23"/>
       <c r="E918" s="23"/>
       <c r="F918" s="23"/>
     </row>
-    <row r="919" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="919" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C919" s="24"/>
       <c r="D919" s="22"/>
       <c r="E919" s="22"/>
       <c r="F919" s="22"/>
     </row>
-    <row r="920" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="920" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C920" s="25"/>
       <c r="D920" s="23"/>
       <c r="E920" s="23"/>
       <c r="F920" s="23"/>
     </row>
-    <row r="921" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="921" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C921" s="24"/>
       <c r="D921" s="22"/>
       <c r="E921" s="22"/>
       <c r="F921" s="22"/>
     </row>
-    <row r="922" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="922" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C922" s="25"/>
       <c r="D922" s="23"/>
       <c r="E922" s="23"/>
       <c r="F922" s="23"/>
     </row>
-    <row r="923" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="923" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C923" s="24"/>
       <c r="D923" s="22"/>
       <c r="E923" s="22"/>
       <c r="F923" s="22"/>
     </row>
-    <row r="924" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="924" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C924" s="25"/>
       <c r="D924" s="23"/>
       <c r="E924" s="23"/>
       <c r="F924" s="23"/>
     </row>
-    <row r="925" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="925" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C925" s="24"/>
       <c r="D925" s="22"/>
       <c r="E925" s="22"/>
       <c r="F925" s="22"/>
     </row>
-    <row r="926" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="926" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C926" s="25"/>
       <c r="D926" s="23"/>
       <c r="E926" s="23"/>
       <c r="F926" s="23"/>
     </row>
-    <row r="927" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="927" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C927" s="24"/>
       <c r="D927" s="22"/>
       <c r="E927" s="22"/>
       <c r="F927" s="22"/>
     </row>
-    <row r="928" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="928" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C928" s="25"/>
       <c r="D928" s="23"/>
       <c r="E928" s="23"/>
       <c r="F928" s="23"/>
     </row>
-    <row r="929" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="929" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C929" s="24"/>
       <c r="D929" s="22"/>
       <c r="E929" s="22"/>
       <c r="F929" s="22"/>
     </row>
-    <row r="930" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="930" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C930" s="25"/>
       <c r="D930" s="23"/>
       <c r="E930" s="23"/>
       <c r="F930" s="23"/>
     </row>
-    <row r="931" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="931" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C931" s="24"/>
       <c r="D931" s="22"/>
       <c r="E931" s="22"/>
       <c r="F931" s="22"/>
     </row>
-    <row r="932" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="932" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C932" s="25"/>
       <c r="D932" s="23"/>
       <c r="E932" s="23"/>
       <c r="F932" s="23"/>
     </row>
-    <row r="933" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="933" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C933" s="24"/>
       <c r="D933" s="22"/>
       <c r="E933" s="22"/>
       <c r="F933" s="22"/>
     </row>
-    <row r="934" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="934" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C934" s="25"/>
       <c r="D934" s="23"/>
       <c r="E934" s="23"/>
       <c r="F934" s="23"/>
     </row>
-    <row r="935" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="935" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C935" s="24"/>
       <c r="D935" s="22"/>
       <c r="E935" s="22"/>
       <c r="F935" s="22"/>
     </row>
-    <row r="936" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="936" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C936" s="25"/>
       <c r="D936" s="23"/>
       <c r="E936" s="23"/>
       <c r="F936" s="23"/>
     </row>
-    <row r="937" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="937" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C937" s="24"/>
       <c r="D937" s="22"/>
       <c r="E937" s="22"/>
       <c r="F937" s="22"/>
     </row>
-    <row r="938" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="938" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C938" s="25"/>
       <c r="D938" s="23"/>
       <c r="E938" s="23"/>
       <c r="F938" s="23"/>
     </row>
-    <row r="939" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="939" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C939" s="24"/>
       <c r="D939" s="22"/>
       <c r="E939" s="22"/>
       <c r="F939" s="22"/>
     </row>
-    <row r="940" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="940" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C940" s="25"/>
       <c r="D940" s="23"/>
       <c r="E940" s="23"/>
       <c r="F940" s="23"/>
     </row>
-    <row r="941" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="941" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C941" s="24"/>
       <c r="D941" s="22"/>
       <c r="E941" s="22"/>
       <c r="F941" s="22"/>
     </row>
-    <row r="942" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="942" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C942" s="25"/>
       <c r="D942" s="23"/>
       <c r="E942" s="23"/>
       <c r="F942" s="23"/>
     </row>
-    <row r="943" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="943" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C943" s="24"/>
       <c r="D943" s="22"/>
       <c r="E943" s="22"/>
       <c r="F943" s="22"/>
     </row>
-    <row r="944" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="944" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C944" s="25"/>
       <c r="D944" s="23"/>
       <c r="E944" s="23"/>
       <c r="F944" s="23"/>
     </row>
-    <row r="945" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="945" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C945" s="24"/>
       <c r="D945" s="22"/>
       <c r="E945" s="22"/>
       <c r="F945" s="22"/>
     </row>
-    <row r="946" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="946" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C946" s="25"/>
       <c r="D946" s="23"/>
       <c r="E946" s="23"/>
       <c r="F946" s="23"/>
     </row>
-    <row r="947" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="947" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C947" s="24"/>
       <c r="D947" s="22"/>
       <c r="E947" s="22"/>
       <c r="F947" s="22"/>
     </row>
-    <row r="948" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="948" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C948" s="25"/>
       <c r="D948" s="23"/>
       <c r="E948" s="23"/>
       <c r="F948" s="23"/>
     </row>
-    <row r="949" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="949" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C949" s="24"/>
       <c r="D949" s="22"/>
       <c r="E949" s="22"/>
       <c r="F949" s="22"/>
     </row>
-    <row r="950" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="950" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C950" s="25"/>
       <c r="D950" s="23"/>
       <c r="E950" s="23"/>
       <c r="F950" s="23"/>
     </row>
-    <row r="951" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="951" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C951" s="24"/>
       <c r="D951" s="22"/>
       <c r="E951" s="22"/>
       <c r="F951" s="22"/>
     </row>
-    <row r="952" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="952" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C952" s="25"/>
       <c r="D952" s="23"/>
       <c r="E952" s="23"/>
       <c r="F952" s="23"/>
     </row>
-    <row r="953" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="953" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C953" s="24"/>
       <c r="D953" s="22"/>
       <c r="E953" s="22"/>
       <c r="F953" s="22"/>
     </row>
-    <row r="954" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="954" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C954" s="25"/>
       <c r="D954" s="23"/>
       <c r="E954" s="23"/>
       <c r="F954" s="23"/>
     </row>
-    <row r="955" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="955" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C955" s="24"/>
       <c r="D955" s="22"/>
       <c r="E955" s="22"/>
       <c r="F955" s="22"/>
     </row>
-    <row r="956" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="956" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C956" s="25"/>
       <c r="D956" s="23"/>
       <c r="E956" s="23"/>
       <c r="F956" s="23"/>
     </row>
-    <row r="957" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="957" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C957" s="24"/>
       <c r="D957" s="22"/>
       <c r="E957" s="22"/>
       <c r="F957" s="22"/>
     </row>
-    <row r="958" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="958" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C958" s="25"/>
       <c r="D958" s="23"/>
       <c r="E958" s="23"/>
       <c r="F958" s="23"/>
     </row>
-    <row r="959" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="959" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C959" s="24"/>
       <c r="D959" s="22"/>
       <c r="E959" s="22"/>
       <c r="F959" s="22"/>
     </row>
-    <row r="960" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="960" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C960" s="25"/>
       <c r="D960" s="23"/>
       <c r="E960" s="23"/>
       <c r="F960" s="23"/>
     </row>
-    <row r="961" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="961" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C961" s="24"/>
       <c r="D961" s="22"/>
       <c r="E961" s="22"/>
       <c r="F961" s="22"/>
     </row>
-    <row r="962" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="962" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C962" s="25"/>
       <c r="D962" s="23"/>
       <c r="E962" s="23"/>
       <c r="F962" s="23"/>
     </row>
-    <row r="963" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="963" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C963" s="24"/>
       <c r="D963" s="22"/>
       <c r="E963" s="22"/>
       <c r="F963" s="22"/>
     </row>
-    <row r="964" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="964" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C964" s="25"/>
       <c r="D964" s="23"/>
       <c r="E964" s="23"/>
       <c r="F964" s="23"/>
     </row>
-    <row r="965" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="965" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C965" s="24"/>
       <c r="D965" s="22"/>
       <c r="E965" s="22"/>
       <c r="F965" s="22"/>
     </row>
-    <row r="966" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="966" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C966" s="25"/>
       <c r="D966" s="23"/>
       <c r="E966" s="23"/>
       <c r="F966" s="23"/>
     </row>
-    <row r="967" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="967" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C967" s="24"/>
       <c r="D967" s="22"/>
       <c r="E967" s="22"/>
       <c r="F967" s="22"/>
     </row>
-    <row r="968" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="968" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C968" s="25"/>
       <c r="D968" s="23"/>
       <c r="E968" s="23"/>
       <c r="F968" s="23"/>
     </row>
-    <row r="969" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="969" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C969" s="24"/>
       <c r="D969" s="22"/>
       <c r="E969" s="22"/>
       <c r="F969" s="22"/>
     </row>
-    <row r="970" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="970" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C970" s="25"/>
       <c r="D970" s="23"/>
       <c r="E970" s="23"/>
       <c r="F970" s="23"/>
     </row>
-    <row r="971" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="971" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C971" s="24"/>
       <c r="D971" s="22"/>
       <c r="E971" s="22"/>
       <c r="F971" s="22"/>
     </row>
-    <row r="972" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="972" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C972" s="25"/>
       <c r="D972" s="23"/>
       <c r="E972" s="23"/>
       <c r="F972" s="23"/>
     </row>
-    <row r="973" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="973" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C973" s="24"/>
       <c r="D973" s="22"/>
       <c r="E973" s="22"/>
       <c r="F973" s="22"/>
     </row>
-    <row r="974" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="974" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C974" s="25"/>
       <c r="D974" s="23"/>
       <c r="E974" s="23"/>
       <c r="F974" s="23"/>
     </row>
-    <row r="975" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="975" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C975" s="24"/>
       <c r="D975" s="22"/>
       <c r="E975" s="22"/>
       <c r="F975" s="22"/>
     </row>
-    <row r="976" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="976" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C976" s="25"/>
       <c r="D976" s="23"/>
       <c r="E976" s="23"/>
       <c r="F976" s="23"/>
     </row>
-    <row r="977" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="977" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C977" s="24"/>
       <c r="D977" s="22"/>
       <c r="E977" s="22"/>
       <c r="F977" s="22"/>
     </row>
-    <row r="978" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="978" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C978" s="25"/>
       <c r="D978" s="23"/>
       <c r="E978" s="23"/>
       <c r="F978" s="23"/>
     </row>
-    <row r="979" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="979" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C979" s="24"/>
       <c r="D979" s="22"/>
       <c r="E979" s="22"/>
       <c r="F979" s="22"/>
     </row>
-    <row r="980" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="980" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C980" s="25"/>
       <c r="D980" s="23"/>
       <c r="E980" s="23"/>
       <c r="F980" s="23"/>
     </row>
-    <row r="981" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="981" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C981" s="24"/>
       <c r="D981" s="22"/>
       <c r="E981" s="22"/>
       <c r="F981" s="22"/>
     </row>
-    <row r="982" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="982" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C982" s="25"/>
       <c r="D982" s="23"/>
       <c r="E982" s="23"/>
       <c r="F982" s="23"/>
     </row>
-    <row r="983" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="983" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C983" s="24"/>
       <c r="D983" s="22"/>
       <c r="E983" s="22"/>
       <c r="F983" s="22"/>
     </row>
-    <row r="984" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="984" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C984" s="25"/>
       <c r="D984" s="23"/>
       <c r="E984" s="23"/>
       <c r="F984" s="23"/>
     </row>
-    <row r="985" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="985" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C985" s="24"/>
       <c r="D985" s="22"/>
       <c r="E985" s="22"/>
       <c r="F985" s="22"/>
     </row>
-    <row r="986" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="986" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C986" s="25"/>
       <c r="D986" s="23"/>
       <c r="E986" s="23"/>
       <c r="F986" s="23"/>
     </row>
-    <row r="987" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="987" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C987" s="24"/>
       <c r="D987" s="22"/>
       <c r="E987" s="22"/>
       <c r="F987" s="22"/>
     </row>
-    <row r="988" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="988" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C988" s="25"/>
       <c r="D988" s="23"/>
       <c r="E988" s="23"/>
       <c r="F988" s="23"/>
     </row>
-    <row r="989" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="989" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C989" s="24"/>
       <c r="D989" s="22"/>
       <c r="E989" s="22"/>
       <c r="F989" s="22"/>
     </row>
-    <row r="990" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="990" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C990" s="25"/>
       <c r="D990" s="23"/>
       <c r="E990" s="23"/>
       <c r="F990" s="23"/>
     </row>
-    <row r="991" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="991" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C991" s="24"/>
       <c r="D991" s="22"/>
       <c r="E991" s="22"/>
       <c r="F991" s="22"/>
     </row>
-    <row r="992" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="992" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C992" s="25"/>
       <c r="D992" s="23"/>
       <c r="E992" s="23"/>
       <c r="F992" s="23"/>
     </row>
-    <row r="993" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="993" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C993" s="24"/>
       <c r="D993" s="22"/>
       <c r="E993" s="22"/>
       <c r="F993" s="22"/>
     </row>
-    <row r="994" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="994" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C994" s="25"/>
       <c r="D994" s="23"/>
       <c r="E994" s="23"/>
       <c r="F994" s="23"/>
     </row>
-    <row r="995" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="995" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C995" s="24"/>
       <c r="D995" s="22"/>
       <c r="E995" s="22"/>
       <c r="F995" s="22"/>
     </row>
-    <row r="996" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="996" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C996" s="25"/>
       <c r="D996" s="23"/>
       <c r="E996" s="23"/>
       <c r="F996" s="23"/>
     </row>
-    <row r="997" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="997" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C997" s="24"/>
       <c r="D997" s="22"/>
       <c r="E997" s="22"/>
       <c r="F997" s="22"/>
     </row>
-    <row r="998" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="998" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C998" s="25"/>
       <c r="D998" s="23"/>
       <c r="E998" s="23"/>
       <c r="F998" s="23"/>
     </row>
-    <row r="999" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="999" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C999" s="24"/>
       <c r="D999" s="22"/>
       <c r="E999" s="22"/>
       <c r="F999" s="22"/>
     </row>
-    <row r="1000" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="1000" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C1000" s="25"/>
       <c r="D1000" s="23"/>
       <c r="E1000" s="23"/>
@@ -17752,14 +17774,14 @@
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="B1:E15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="41.7109375" customWidth="1"/>
+    <col min="2" max="2" width="41.6640625" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B1" s="31" t="s">
         <v>26</v>
       </c>
@@ -17770,80 +17792,80 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>7455</v>
+        <v>7725</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>29</v>
       </c>

--- a/02_WorkingDocs/CMMCFledge_Workbook.xlsx
+++ b/02_WorkingDocs/CMMCFledge_Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckm32\OneDrive\Desktop\CMMCFledge\02_WorkingDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA50FEA5-D65E-4C08-B4BB-1ADEFA0DF5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6EC5F3-A8DD-46C0-9AAC-0C6CB1E4D22B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
+    <workbookView xWindow="41130" yWindow="3915" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{208106DA-3D21-4604-99AA-9AD5A5B6DE72}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="107">
   <si>
     <t>Week:</t>
   </si>
@@ -360,6 +360,9 @@
   <si>
     <t>added progress bar, fixed assessment navigation</t>
   </si>
+  <si>
+    <t>Discussion with outside testers and fixed bugs</t>
+  </si>
 </sst>
 </file>
 
@@ -659,7 +662,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -755,7 +758,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1228,7 +1230,9 @@
         <c:idx val="6"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent5"/>
+            <a:schemeClr val="accent5">
+              <a:tint val="80000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -1308,6 +1312,54 @@
           <a:solidFill>
             <a:schemeClr val="accent5">
               <a:shade val="41000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent5">
+              <a:shade val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent5">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent5">
+              <a:shade val="40000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:ln w="19050">
@@ -1595,6 +1647,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-7EDF-4341-B959-53B1A6BDC324}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="12"/>
@@ -1612,6 +1669,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-7EDF-4341-B959-53B1A6BDC324}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -1990,10 +2052,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7995</c:v>
+                  <c:v>8055</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>705</c:v>
+                  <c:v>645</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9758,7 +9820,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{542969FB-8A7D-470E-946B-17B5961CB080}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{542969FB-8A7D-470E-946B-17B5961CB080}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="A18:B32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0">
@@ -10278,7 +10340,7 @@
   <dataFields count="1">
     <dataField name="Sum of Time (Mins)" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="12">
+  <chartFormats count="15">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -10416,6 +10478,42 @@
           </reference>
           <reference field="2" count="1" selected="0">
             <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="13">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="14">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="13"/>
           </reference>
         </references>
       </pivotArea>
@@ -11100,7 +11198,7 @@
       <c r="A19" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="47">
+      <c r="B19">
         <v>495</v>
       </c>
     </row>
@@ -11108,7 +11206,7 @@
       <c r="A20" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="47">
+      <c r="B20">
         <v>600</v>
       </c>
     </row>
@@ -11116,7 +11214,7 @@
       <c r="A21" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="47">
+      <c r="B21">
         <v>360</v>
       </c>
     </row>
@@ -11124,7 +11222,7 @@
       <c r="A22" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="47">
+      <c r="B22">
         <v>285</v>
       </c>
     </row>
@@ -11132,7 +11230,7 @@
       <c r="A23" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="47">
+      <c r="B23">
         <v>645</v>
       </c>
     </row>
@@ -11140,7 +11238,7 @@
       <c r="A24" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="47">
+      <c r="B24">
         <v>60</v>
       </c>
     </row>
@@ -11148,7 +11246,7 @@
       <c r="A25" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="47">
+      <c r="B25">
         <v>60</v>
       </c>
     </row>
@@ -11156,7 +11254,7 @@
       <c r="A26" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="47">
+      <c r="B26">
         <v>315</v>
       </c>
     </row>
@@ -11164,7 +11262,7 @@
       <c r="A27" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="47">
+      <c r="B27">
         <v>195</v>
       </c>
     </row>
@@ -11172,7 +11270,7 @@
       <c r="A28" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="47">
+      <c r="B28">
         <v>4230</v>
       </c>
     </row>
@@ -11180,7 +11278,7 @@
       <c r="A29" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="47">
+      <c r="B29">
         <v>270</v>
       </c>
     </row>
@@ -11188,7 +11286,7 @@
       <c r="A30" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="47">
+      <c r="B30">
         <v>240</v>
       </c>
     </row>
@@ -11196,7 +11294,7 @@
       <c r="A31" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="47">
+      <c r="B31">
         <v>240</v>
       </c>
     </row>
@@ -11204,7 +11302,7 @@
       <c r="A32" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="47">
+      <c r="B32">
         <v>7995</v>
       </c>
     </row>
@@ -12401,10 +12499,18 @@
       </c>
     </row>
     <row r="84" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C84" s="25"/>
-      <c r="D84" s="23"/>
-      <c r="E84" s="23"/>
-      <c r="F84" s="23"/>
+      <c r="C84" s="33">
+        <v>45994</v>
+      </c>
+      <c r="D84" s="23">
+        <v>60</v>
+      </c>
+      <c r="E84" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F84" s="23" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="85" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C85" s="24"/>
@@ -17952,11 +18058,11 @@
       </c>
       <c r="D2">
         <f>SUM(Table2[Time (Mins)])</f>
-        <v>7995</v>
+        <v>8055</v>
       </c>
       <c r="E2">
         <f>8700-D2</f>
-        <v>705</v>
+        <v>645</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
